--- a/gstdatabase/GSTR-3B-2021-2022.xlsx
+++ b/gstdatabase/GSTR-3B-2021-2022.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Feb-26\GST Statistics Downloads 28th Feb 26\Downloads\GSTR 3B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\May-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 3B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F09B07E-F1F8-4ECF-88F2-8A6DFF8DA422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93066253-5E0A-4C4E-B2D9-9F55659F7E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -185,10 +185,10 @@
     <t>STATE WISE RETURN PERIOD WISE GSTR-3B FILING SUMMARY</t>
   </si>
   <si>
-    <t>Data Considered upto 28th Feb 2026</t>
+    <t>Data Considered upto 31st May 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 28th Feb 2026</t>
+    <t>Filing %age as on 31st May 2026</t>
   </si>
 </sst>
 </file>
@@ -435,7 +435,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="17" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -447,12 +447,6 @@
     <xf numFmtId="17" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="17" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -460,13 +454,19 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -768,13 +768,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:64" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -848,10 +848,10 @@
       <c r="AK2" s="1"/>
     </row>
     <row r="3" spans="1:64" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="34"/>
+      <c r="B3" s="35"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -928,11 +928,11 @@
       <c r="AK4" s="1"/>
     </row>
     <row r="5" spans="1:64" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -1072,10 +1072,10 @@
       <c r="BJ7" s="4"/>
     </row>
     <row r="8" spans="1:64" s="24" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="35" t="s">
+      <c r="A8" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="33" t="s">
+      <c r="B8" s="31" t="s">
         <v>2</v>
       </c>
       <c r="C8" s="27">
@@ -1085,69 +1085,69 @@
       <c r="E8" s="28"/>
       <c r="F8" s="28"/>
       <c r="G8" s="29"/>
-      <c r="H8" s="32">
+      <c r="H8" s="30">
         <v>44317</v>
       </c>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
-      <c r="K8" s="33"/>
-      <c r="L8" s="33"/>
-      <c r="M8" s="30">
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="31"/>
+      <c r="M8" s="33">
         <v>44348</v>
       </c>
-      <c r="N8" s="31"/>
-      <c r="O8" s="31"/>
-      <c r="P8" s="31"/>
-      <c r="Q8" s="31"/>
-      <c r="R8" s="32">
+      <c r="N8" s="34"/>
+      <c r="O8" s="34"/>
+      <c r="P8" s="34"/>
+      <c r="Q8" s="34"/>
+      <c r="R8" s="30">
         <v>44378</v>
       </c>
-      <c r="S8" s="33"/>
-      <c r="T8" s="33"/>
-      <c r="U8" s="33"/>
-      <c r="V8" s="33"/>
-      <c r="W8" s="32">
+      <c r="S8" s="31"/>
+      <c r="T8" s="31"/>
+      <c r="U8" s="31"/>
+      <c r="V8" s="31"/>
+      <c r="W8" s="30">
         <v>44409</v>
       </c>
-      <c r="X8" s="33"/>
-      <c r="Y8" s="33"/>
-      <c r="Z8" s="33"/>
-      <c r="AA8" s="33"/>
-      <c r="AB8" s="30">
+      <c r="X8" s="31"/>
+      <c r="Y8" s="31"/>
+      <c r="Z8" s="31"/>
+      <c r="AA8" s="31"/>
+      <c r="AB8" s="33">
         <v>44440</v>
       </c>
-      <c r="AC8" s="31"/>
-      <c r="AD8" s="31"/>
-      <c r="AE8" s="31"/>
-      <c r="AF8" s="31"/>
-      <c r="AG8" s="32">
+      <c r="AC8" s="34"/>
+      <c r="AD8" s="34"/>
+      <c r="AE8" s="34"/>
+      <c r="AF8" s="34"/>
+      <c r="AG8" s="30">
         <v>44470</v>
       </c>
-      <c r="AH8" s="33"/>
-      <c r="AI8" s="33"/>
-      <c r="AJ8" s="33"/>
-      <c r="AK8" s="33"/>
-      <c r="AL8" s="32">
+      <c r="AH8" s="31"/>
+      <c r="AI8" s="31"/>
+      <c r="AJ8" s="31"/>
+      <c r="AK8" s="31"/>
+      <c r="AL8" s="30">
         <v>44501</v>
       </c>
-      <c r="AM8" s="33"/>
-      <c r="AN8" s="33"/>
-      <c r="AO8" s="33"/>
-      <c r="AP8" s="33"/>
-      <c r="AQ8" s="32">
+      <c r="AM8" s="31"/>
+      <c r="AN8" s="31"/>
+      <c r="AO8" s="31"/>
+      <c r="AP8" s="31"/>
+      <c r="AQ8" s="30">
         <v>44531</v>
       </c>
-      <c r="AR8" s="33"/>
-      <c r="AS8" s="33"/>
-      <c r="AT8" s="33"/>
-      <c r="AU8" s="33"/>
-      <c r="AV8" s="32">
+      <c r="AR8" s="31"/>
+      <c r="AS8" s="31"/>
+      <c r="AT8" s="31"/>
+      <c r="AU8" s="31"/>
+      <c r="AV8" s="30">
         <v>44562</v>
       </c>
-      <c r="AW8" s="33"/>
-      <c r="AX8" s="33"/>
-      <c r="AY8" s="33"/>
-      <c r="AZ8" s="33"/>
+      <c r="AW8" s="31"/>
+      <c r="AX8" s="31"/>
+      <c r="AY8" s="31"/>
+      <c r="AZ8" s="31"/>
       <c r="BA8" s="27">
         <v>44593</v>
       </c>
@@ -1164,8 +1164,8 @@
       <c r="BJ8" s="29"/>
     </row>
     <row r="9" spans="1:64" s="24" customFormat="1" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="35"/>
-      <c r="B9" s="33"/>
+      <c r="A9" s="36"/>
+      <c r="B9" s="31"/>
       <c r="C9" s="23" t="s">
         <v>3</v>
       </c>
@@ -1483,7 +1483,7 @@
         <f>AO10-AM10</f>
         <v>14264</v>
       </c>
-      <c r="AO10" s="20">
+      <c r="AO10" s="11">
         <v>63483</v>
       </c>
       <c r="AP10" s="12">
@@ -1549,14 +1549,14 @@
       </c>
       <c r="BH10" s="10">
         <f>BI10-BG10</f>
-        <v>26267</v>
+        <v>26268</v>
       </c>
       <c r="BI10" s="11">
-        <v>104906</v>
+        <v>104907</v>
       </c>
       <c r="BJ10" s="12">
         <f>BI10/BF10</f>
-        <v>1.0060609547921822</v>
+        <v>1.0060705449105243</v>
       </c>
       <c r="BK10" s="24"/>
       <c r="BL10" s="24"/>
@@ -1576,14 +1576,14 @@
       </c>
       <c r="E11" s="10">
         <f t="shared" ref="E11:E48" si="0">F11-D11</f>
-        <v>35070</v>
+        <v>35071</v>
       </c>
       <c r="F11" s="20">
-        <v>42903</v>
+        <v>42904</v>
       </c>
       <c r="G11" s="12">
         <f t="shared" ref="G11:G48" si="1">F11/C11</f>
-        <v>0.96584871679423678</v>
+        <v>0.96587122917604684</v>
       </c>
       <c r="H11" s="15">
         <v>44517</v>
@@ -1593,14 +1593,14 @@
       </c>
       <c r="J11" s="10">
         <f t="shared" ref="J11:J48" si="2">K11-I11</f>
-        <v>33345</v>
+        <v>33346</v>
       </c>
       <c r="K11" s="20">
-        <v>43019</v>
+        <v>43020</v>
       </c>
       <c r="L11" s="12">
         <f t="shared" ref="L11:L48" si="3">K11/H11</f>
-        <v>0.96634993373318057</v>
+        <v>0.96637239706179656</v>
       </c>
       <c r="M11" s="16">
         <v>92010</v>
@@ -1610,14 +1610,14 @@
       </c>
       <c r="O11" s="10">
         <f t="shared" ref="O11:O48" si="4">P11-N11</f>
-        <v>26878</v>
+        <v>26879</v>
       </c>
       <c r="P11" s="13">
-        <v>89827</v>
+        <v>89828</v>
       </c>
       <c r="Q11" s="12">
         <f t="shared" ref="Q11:Q48" si="5">P11/M11</f>
-        <v>0.97627431800891207</v>
+        <v>0.97628518639278339</v>
       </c>
       <c r="R11" s="16">
         <v>44191</v>
@@ -1627,14 +1627,14 @@
       </c>
       <c r="T11" s="10">
         <f t="shared" ref="T11:T48" si="6">U11-S11</f>
-        <v>10831</v>
+        <v>10832</v>
       </c>
       <c r="U11" s="20">
-        <v>42227</v>
+        <v>42228</v>
       </c>
       <c r="V11" s="12">
         <f t="shared" ref="V11:V48" si="7">U11/R11</f>
-        <v>0.95555656129076061</v>
+        <v>0.9555791903328732</v>
       </c>
       <c r="W11" s="16">
         <v>44492</v>
@@ -1644,14 +1644,14 @@
       </c>
       <c r="Y11" s="10">
         <f t="shared" ref="Y11:Y48" si="8">Z11-X11</f>
-        <v>11096</v>
+        <v>11097</v>
       </c>
       <c r="Z11" s="20">
-        <v>43258</v>
+        <v>43259</v>
       </c>
       <c r="AA11" s="12">
         <f t="shared" ref="AA11:AA48" si="9">Z11/W11</f>
-        <v>0.97226467679582851</v>
+        <v>0.97228715274656119</v>
       </c>
       <c r="AB11" s="17">
         <v>93894</v>
@@ -1661,14 +1661,14 @@
       </c>
       <c r="AD11" s="10">
         <f t="shared" ref="AD11:AD48" si="10">AE11-AC11</f>
-        <v>17965</v>
+        <v>17966</v>
       </c>
       <c r="AE11" s="11">
-        <v>92224</v>
+        <v>92225</v>
       </c>
       <c r="AF11" s="12">
         <f t="shared" ref="AF11:AF48" si="11">AE11/AB11</f>
-        <v>0.98221398598419496</v>
+        <v>0.98222463629198886</v>
       </c>
       <c r="AG11" s="16">
         <v>43295</v>
@@ -1678,14 +1678,14 @@
       </c>
       <c r="AI11" s="10">
         <f t="shared" ref="AI11:AI48" si="12">AJ11-AH11</f>
-        <v>9214</v>
+        <v>9215</v>
       </c>
       <c r="AJ11" s="20">
-        <v>42199</v>
+        <v>42200</v>
       </c>
       <c r="AK11" s="12">
         <f t="shared" ref="AK11:AK48" si="13">AJ11/AG11</f>
-        <v>0.97468529853331798</v>
+        <v>0.97470839588867075</v>
       </c>
       <c r="AL11" s="18">
         <v>43932</v>
@@ -1695,14 +1695,14 @@
       </c>
       <c r="AN11" s="10">
         <f t="shared" ref="AN11:AN48" si="14">AO11-AM11</f>
-        <v>9614</v>
-      </c>
-      <c r="AO11" s="20">
-        <v>42907</v>
+        <v>9615</v>
+      </c>
+      <c r="AO11" s="11">
+        <v>42908</v>
       </c>
       <c r="AP11" s="12">
         <f t="shared" ref="AP11:AP48" si="15">AO11/AL11</f>
-        <v>0.97666848766275149</v>
+        <v>0.9766912501138123</v>
       </c>
       <c r="AQ11" s="11">
         <v>95802</v>
@@ -1712,14 +1712,14 @@
       </c>
       <c r="AS11" s="10">
         <f t="shared" ref="AS11:AS48" si="16">AT11-AR11</f>
-        <v>16884</v>
+        <v>16885</v>
       </c>
       <c r="AT11" s="13">
-        <v>93932</v>
+        <v>93933</v>
       </c>
       <c r="AU11" s="12">
         <f t="shared" ref="AU11:AU48" si="17">AT11/AQ11</f>
-        <v>0.9804805745182773</v>
+        <v>0.98049101271372208</v>
       </c>
       <c r="AV11" s="18">
         <v>43808</v>
@@ -1729,14 +1729,14 @@
       </c>
       <c r="AX11" s="10">
         <f t="shared" ref="AX11:AX48" si="18">AY11-AW11</f>
-        <v>9227</v>
+        <v>9228</v>
       </c>
       <c r="AY11" s="20">
-        <v>42502</v>
+        <v>42503</v>
       </c>
       <c r="AZ11" s="12">
         <f t="shared" ref="AZ11:AZ48" si="19">AY11/AV11</f>
-        <v>0.97018809349890434</v>
+        <v>0.97021092037983925</v>
       </c>
       <c r="BA11" s="18">
         <v>44164</v>
@@ -1746,14 +1746,14 @@
       </c>
       <c r="BC11" s="10">
         <f t="shared" ref="BC11:BC48" si="20">BD11-BB11</f>
-        <v>9292</v>
+        <v>9293</v>
       </c>
       <c r="BD11" s="20">
-        <v>43126</v>
+        <v>43127</v>
       </c>
       <c r="BE11" s="12">
         <f t="shared" ref="BE11:BE48" si="21">BD11/BA11</f>
-        <v>0.9764966941400236</v>
+        <v>0.97651933701657456</v>
       </c>
       <c r="BF11" s="18">
         <v>97423</v>
@@ -1763,14 +1763,14 @@
       </c>
       <c r="BH11" s="10">
         <f t="shared" ref="BH11:BH33" si="22">BI11-BG11</f>
-        <v>21908</v>
+        <v>21909</v>
       </c>
       <c r="BI11" s="11">
-        <v>95308</v>
+        <v>95309</v>
       </c>
       <c r="BJ11" s="12">
         <f t="shared" ref="BJ11:BJ33" si="23">BI11/BF11</f>
-        <v>0.97829054740666987</v>
+        <v>0.97830081192326246</v>
       </c>
       <c r="BK11" s="24"/>
       <c r="BL11" s="24"/>
@@ -1790,14 +1790,14 @@
       </c>
       <c r="E12" s="10">
         <f t="shared" si="0"/>
-        <v>115332</v>
+        <v>115333</v>
       </c>
       <c r="F12" s="20">
-        <v>150923</v>
+        <v>150924</v>
       </c>
       <c r="G12" s="12">
         <f t="shared" si="1"/>
-        <v>0.94055876505817615</v>
+        <v>0.94056499710209962</v>
       </c>
       <c r="H12" s="15">
         <v>161190</v>
@@ -1807,14 +1807,14 @@
       </c>
       <c r="J12" s="10">
         <f t="shared" si="2"/>
-        <v>115784</v>
+        <v>115785</v>
       </c>
       <c r="K12" s="20">
-        <v>152280</v>
+        <v>152281</v>
       </c>
       <c r="L12" s="12">
         <f t="shared" si="3"/>
-        <v>0.94472361809045224</v>
+        <v>0.94472982194925248</v>
       </c>
       <c r="M12" s="16">
         <v>320319</v>
@@ -1824,14 +1824,14 @@
       </c>
       <c r="O12" s="10">
         <f t="shared" si="4"/>
-        <v>71876</v>
+        <v>71877</v>
       </c>
       <c r="P12" s="13">
-        <v>310312</v>
+        <v>310313</v>
       </c>
       <c r="Q12" s="12">
         <f t="shared" si="5"/>
-        <v>0.96875926810460822</v>
+        <v>0.96876238999247621</v>
       </c>
       <c r="R12" s="16">
         <v>159828</v>
@@ -1841,14 +1841,14 @@
       </c>
       <c r="T12" s="10">
         <f t="shared" si="6"/>
-        <v>27544</v>
+        <v>27545</v>
       </c>
       <c r="U12" s="20">
-        <v>150742</v>
+        <v>150743</v>
       </c>
       <c r="V12" s="12">
         <f t="shared" si="7"/>
-        <v>0.9431513877418225</v>
+        <v>0.94315764446780292</v>
       </c>
       <c r="W12" s="16">
         <v>162180</v>
@@ -1858,14 +1858,14 @@
       </c>
       <c r="Y12" s="10">
         <f t="shared" si="8"/>
-        <v>30530</v>
+        <v>30531</v>
       </c>
       <c r="Z12" s="20">
-        <v>153695</v>
+        <v>153696</v>
       </c>
       <c r="AA12" s="12">
         <f t="shared" si="9"/>
-        <v>0.94768158835861394</v>
+        <v>0.94768775434702179</v>
       </c>
       <c r="AB12" s="17">
         <v>327297</v>
@@ -1875,14 +1875,14 @@
       </c>
       <c r="AD12" s="10">
         <f t="shared" si="10"/>
-        <v>52036</v>
+        <v>52037</v>
       </c>
       <c r="AE12" s="11">
-        <v>315590</v>
+        <v>315591</v>
       </c>
       <c r="AF12" s="12">
         <f t="shared" si="11"/>
-        <v>0.96423126395903413</v>
+        <v>0.96423431928798609</v>
       </c>
       <c r="AG12" s="16">
         <v>160729</v>
@@ -1892,14 +1892,14 @@
       </c>
       <c r="AI12" s="10">
         <f t="shared" si="12"/>
-        <v>25208</v>
+        <v>25209</v>
       </c>
       <c r="AJ12" s="20">
-        <v>151379</v>
+        <v>151380</v>
       </c>
       <c r="AK12" s="12">
         <f t="shared" si="13"/>
-        <v>0.94182754823336179</v>
+        <v>0.94183376988595713</v>
       </c>
       <c r="AL12" s="18">
         <v>162572</v>
@@ -1909,14 +1909,14 @@
       </c>
       <c r="AN12" s="10">
         <f t="shared" si="14"/>
-        <v>26347</v>
-      </c>
-      <c r="AO12" s="20">
-        <v>153366</v>
+        <v>26348</v>
+      </c>
+      <c r="AO12" s="11">
+        <v>153367</v>
       </c>
       <c r="AP12" s="12">
         <f t="shared" si="15"/>
-        <v>0.94337278252097534</v>
+        <v>0.94337893364170955</v>
       </c>
       <c r="AQ12" s="11">
         <v>333129</v>
@@ -1926,14 +1926,14 @@
       </c>
       <c r="AS12" s="10">
         <f t="shared" si="16"/>
-        <v>49577</v>
+        <v>49579</v>
       </c>
       <c r="AT12" s="13">
-        <v>319717</v>
+        <v>319719</v>
       </c>
       <c r="AU12" s="12">
         <f t="shared" si="17"/>
-        <v>0.95973932020328456</v>
+        <v>0.95974532388354061</v>
       </c>
       <c r="AV12" s="18">
         <v>161987</v>
@@ -1943,14 +1943,14 @@
       </c>
       <c r="AX12" s="10">
         <f t="shared" si="18"/>
-        <v>27155</v>
+        <v>27156</v>
       </c>
       <c r="AY12" s="20">
-        <v>152460</v>
+        <v>152461</v>
       </c>
       <c r="AZ12" s="12">
         <f t="shared" si="19"/>
-        <v>0.94118663843394845</v>
+        <v>0.94119281176884562</v>
       </c>
       <c r="BA12" s="18">
         <v>163270</v>
@@ -1960,14 +1960,14 @@
       </c>
       <c r="BC12" s="10">
         <f t="shared" si="20"/>
-        <v>27497</v>
+        <v>27498</v>
       </c>
       <c r="BD12" s="20">
-        <v>154518</v>
+        <v>154519</v>
       </c>
       <c r="BE12" s="12">
         <f t="shared" si="21"/>
-        <v>0.94639554112819257</v>
+        <v>0.94640166595210384</v>
       </c>
       <c r="BF12" s="18">
         <v>336608</v>
@@ -1977,14 +1977,14 @@
       </c>
       <c r="BH12" s="10">
         <f t="shared" si="22"/>
-        <v>63223</v>
+        <v>63225</v>
       </c>
       <c r="BI12" s="11">
-        <v>323424</v>
+        <v>323426</v>
       </c>
       <c r="BJ12" s="12">
         <f t="shared" si="23"/>
-        <v>0.96083277878125295</v>
+        <v>0.96083872041068541</v>
       </c>
       <c r="BK12" s="24"/>
       <c r="BL12" s="24"/>
@@ -2125,7 +2125,7 @@
         <f t="shared" si="14"/>
         <v>2664</v>
       </c>
-      <c r="AO13" s="20">
+      <c r="AO13" s="11">
         <v>15459</v>
       </c>
       <c r="AP13" s="12">
@@ -2269,14 +2269,14 @@
       </c>
       <c r="T14" s="10">
         <f t="shared" si="6"/>
-        <v>22053</v>
+        <v>22055</v>
       </c>
       <c r="U14" s="20">
-        <v>74602</v>
+        <v>74604</v>
       </c>
       <c r="V14" s="12">
         <f t="shared" si="7"/>
-        <v>0.94626956543798679</v>
+        <v>0.9462949339151171</v>
       </c>
       <c r="W14" s="16">
         <v>80553</v>
@@ -2286,14 +2286,14 @@
       </c>
       <c r="Y14" s="10">
         <f t="shared" si="8"/>
-        <v>22357</v>
+        <v>22358</v>
       </c>
       <c r="Z14" s="20">
-        <v>76598</v>
+        <v>76599</v>
       </c>
       <c r="AA14" s="12">
         <f t="shared" si="9"/>
-        <v>0.95090189068066988</v>
+        <v>0.95091430486760264</v>
       </c>
       <c r="AB14" s="17">
         <v>144082</v>
@@ -2339,7 +2339,7 @@
         <f t="shared" si="14"/>
         <v>19067</v>
       </c>
-      <c r="AO14" s="20">
+      <c r="AO14" s="11">
         <v>76992</v>
       </c>
       <c r="AP14" s="12">
@@ -2354,14 +2354,14 @@
       </c>
       <c r="AS14" s="10">
         <f t="shared" si="16"/>
-        <v>30163</v>
+        <v>30168</v>
       </c>
       <c r="AT14" s="13">
-        <v>142658</v>
+        <v>142663</v>
       </c>
       <c r="AU14" s="12">
         <f t="shared" si="17"/>
-        <v>0.96217608892126316</v>
+        <v>0.96220981209447887</v>
       </c>
       <c r="AV14" s="18">
         <v>81291</v>
@@ -2371,14 +2371,14 @@
       </c>
       <c r="AX14" s="10">
         <f t="shared" si="18"/>
-        <v>18861</v>
+        <v>18862</v>
       </c>
       <c r="AY14" s="20">
-        <v>77153</v>
+        <v>77154</v>
       </c>
       <c r="AZ14" s="12">
         <f t="shared" si="19"/>
-        <v>0.94909645594223224</v>
+        <v>0.94910875742702139</v>
       </c>
       <c r="BA14" s="18">
         <v>82359</v>
@@ -2388,14 +2388,14 @@
       </c>
       <c r="BC14" s="10">
         <f t="shared" si="20"/>
-        <v>20687</v>
+        <v>20688</v>
       </c>
       <c r="BD14" s="20">
-        <v>78376</v>
+        <v>78377</v>
       </c>
       <c r="BE14" s="12">
         <f t="shared" si="21"/>
-        <v>0.95163855802037423</v>
+        <v>0.95165069998421548</v>
       </c>
       <c r="BF14" s="18">
         <v>151377</v>
@@ -2405,14 +2405,14 @@
       </c>
       <c r="BH14" s="10">
         <f t="shared" si="22"/>
-        <v>36681</v>
+        <v>36685</v>
       </c>
       <c r="BI14" s="11">
-        <v>145231</v>
+        <v>145235</v>
       </c>
       <c r="BJ14" s="12">
         <f t="shared" si="23"/>
-        <v>0.95939938035500771</v>
+        <v>0.95942580444849612</v>
       </c>
       <c r="BK14" s="24"/>
       <c r="BL14" s="24"/>
@@ -2553,7 +2553,7 @@
         <f t="shared" si="14"/>
         <v>53421</v>
       </c>
-      <c r="AO15" s="20">
+      <c r="AO15" s="11">
         <v>248573</v>
       </c>
       <c r="AP15" s="12">
@@ -2646,14 +2646,14 @@
       </c>
       <c r="E16" s="10">
         <f t="shared" si="0"/>
-        <v>313662</v>
+        <v>313665</v>
       </c>
       <c r="F16" s="20">
-        <v>373027</v>
+        <v>373030</v>
       </c>
       <c r="G16" s="12">
         <f t="shared" si="1"/>
-        <v>0.91757433536021415</v>
+        <v>0.91758171478048689</v>
       </c>
       <c r="H16" s="15">
         <v>404491</v>
@@ -2663,14 +2663,14 @@
       </c>
       <c r="J16" s="10">
         <f t="shared" si="2"/>
-        <v>285983</v>
+        <v>285986</v>
       </c>
       <c r="K16" s="20">
-        <v>369984</v>
+        <v>369987</v>
       </c>
       <c r="L16" s="12">
         <f t="shared" si="3"/>
-        <v>0.91469031449401839</v>
+        <v>0.91469773122269715</v>
       </c>
       <c r="M16" s="16">
         <v>718779</v>
@@ -2680,14 +2680,14 @@
       </c>
       <c r="O16" s="10">
         <f t="shared" si="4"/>
-        <v>196833</v>
+        <v>196838</v>
       </c>
       <c r="P16" s="13">
-        <v>676512</v>
+        <v>676517</v>
       </c>
       <c r="Q16" s="12">
         <f t="shared" si="5"/>
-        <v>0.94119611173949158</v>
+        <v>0.94120306798056153</v>
       </c>
       <c r="R16" s="16">
         <v>403668</v>
@@ -2697,14 +2697,14 @@
       </c>
       <c r="T16" s="10">
         <f t="shared" si="6"/>
-        <v>91175</v>
+        <v>91177</v>
       </c>
       <c r="U16" s="20">
-        <v>373772</v>
+        <v>373774</v>
       </c>
       <c r="V16" s="12">
         <f t="shared" si="7"/>
-        <v>0.92593913810359008</v>
+        <v>0.92594409267021416</v>
       </c>
       <c r="W16" s="16">
         <v>406853</v>
@@ -2714,14 +2714,14 @@
       </c>
       <c r="Y16" s="10">
         <f t="shared" si="8"/>
-        <v>87579</v>
+        <v>87581</v>
       </c>
       <c r="Z16" s="20">
-        <v>381191</v>
+        <v>381193</v>
       </c>
       <c r="AA16" s="12">
         <f t="shared" si="9"/>
-        <v>0.93692562178477234</v>
+        <v>0.93693053756516487</v>
       </c>
       <c r="AB16" s="17">
         <v>722282</v>
@@ -2731,14 +2731,14 @@
       </c>
       <c r="AD16" s="10">
         <f t="shared" si="10"/>
-        <v>123984</v>
+        <v>123988</v>
       </c>
       <c r="AE16" s="11">
-        <v>693613</v>
+        <v>693617</v>
       </c>
       <c r="AF16" s="12">
         <f t="shared" si="11"/>
-        <v>0.9603077468357234</v>
+        <v>0.96031328483888567</v>
       </c>
       <c r="AG16" s="16">
         <v>397671</v>
@@ -2748,14 +2748,14 @@
       </c>
       <c r="AI16" s="10">
         <f t="shared" si="12"/>
-        <v>76326</v>
+        <v>76330</v>
       </c>
       <c r="AJ16" s="20">
-        <v>378728</v>
+        <v>378732</v>
       </c>
       <c r="AK16" s="12">
         <f t="shared" si="13"/>
-        <v>0.95236514606295153</v>
+        <v>0.95237520462895209</v>
       </c>
       <c r="AL16" s="18">
         <v>400740</v>
@@ -2765,14 +2765,14 @@
       </c>
       <c r="AN16" s="10">
         <f t="shared" si="14"/>
-        <v>77325</v>
-      </c>
-      <c r="AO16" s="20">
-        <v>383650</v>
+        <v>77329</v>
+      </c>
+      <c r="AO16" s="11">
+        <v>383654</v>
       </c>
       <c r="AP16" s="12">
         <f t="shared" si="15"/>
-        <v>0.95735389529370662</v>
+        <v>0.9573638768278685</v>
       </c>
       <c r="AQ16" s="11">
         <v>730568</v>
@@ -2782,14 +2782,14 @@
       </c>
       <c r="AS16" s="10">
         <f t="shared" si="16"/>
-        <v>116460</v>
+        <v>116467</v>
       </c>
       <c r="AT16" s="13">
-        <v>703036</v>
+        <v>703043</v>
       </c>
       <c r="AU16" s="12">
         <f t="shared" si="17"/>
-        <v>0.96231425411460669</v>
+        <v>0.96232383570044133</v>
       </c>
       <c r="AV16" s="18">
         <v>402711</v>
@@ -2799,14 +2799,14 @@
       </c>
       <c r="AX16" s="10">
         <f t="shared" si="18"/>
-        <v>74830</v>
+        <v>74836</v>
       </c>
       <c r="AY16" s="20">
-        <v>382473</v>
+        <v>382479</v>
       </c>
       <c r="AZ16" s="12">
         <f t="shared" si="19"/>
-        <v>0.94974559920141244</v>
+        <v>0.94976049822329167</v>
       </c>
       <c r="BA16" s="18">
         <v>402569</v>
@@ -2816,14 +2816,14 @@
       </c>
       <c r="BC16" s="10">
         <f t="shared" si="20"/>
-        <v>80930</v>
+        <v>80936</v>
       </c>
       <c r="BD16" s="20">
-        <v>387378</v>
+        <v>387384</v>
       </c>
       <c r="BE16" s="12">
         <f t="shared" si="21"/>
-        <v>0.96226485397534334</v>
+        <v>0.96227975825262257</v>
       </c>
       <c r="BF16" s="18">
         <v>736680</v>
@@ -2833,14 +2833,14 @@
       </c>
       <c r="BH16" s="10">
         <f t="shared" si="22"/>
-        <v>137176</v>
+        <v>137187</v>
       </c>
       <c r="BI16" s="11">
-        <v>709522</v>
+        <v>709533</v>
       </c>
       <c r="BJ16" s="12">
         <f t="shared" si="23"/>
-        <v>0.96313460389857197</v>
+        <v>0.96314953575500895</v>
       </c>
       <c r="BK16" s="24"/>
       <c r="BL16" s="24"/>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="E17" s="10">
         <f t="shared" si="0"/>
-        <v>221389</v>
+        <v>221392</v>
       </c>
       <c r="F17" s="20">
-        <v>259927</v>
+        <v>259930</v>
       </c>
       <c r="G17" s="12">
         <f t="shared" si="1"/>
-        <v>0.98485922030289141</v>
+        <v>0.98487058725461596</v>
       </c>
       <c r="H17" s="15">
         <v>264168</v>
@@ -2877,14 +2877,14 @@
       </c>
       <c r="J17" s="10">
         <f t="shared" si="2"/>
-        <v>201001</v>
+        <v>201003</v>
       </c>
       <c r="K17" s="20">
-        <v>260762</v>
+        <v>260764</v>
       </c>
       <c r="L17" s="12">
         <f t="shared" si="3"/>
-        <v>0.9871066896823234</v>
+        <v>0.98711426062202845</v>
       </c>
       <c r="M17" s="16">
         <v>591219</v>
@@ -2894,14 +2894,14 @@
       </c>
       <c r="O17" s="10">
         <f t="shared" si="4"/>
-        <v>171684</v>
+        <v>171689</v>
       </c>
       <c r="P17" s="13">
-        <v>584072</v>
+        <v>584077</v>
       </c>
       <c r="Q17" s="12">
         <f t="shared" si="5"/>
-        <v>0.98791141691995688</v>
+        <v>0.98791987402299319</v>
       </c>
       <c r="R17" s="16">
         <v>261213</v>
@@ -2911,14 +2911,14 @@
       </c>
       <c r="T17" s="10">
         <f t="shared" si="6"/>
-        <v>69616</v>
+        <v>69620</v>
       </c>
       <c r="U17" s="20">
-        <v>257374</v>
+        <v>257378</v>
       </c>
       <c r="V17" s="12">
         <f t="shared" si="7"/>
-        <v>0.98530318169463238</v>
+        <v>0.98531849486817269</v>
       </c>
       <c r="W17" s="16">
         <v>269820</v>
@@ -2928,14 +2928,14 @@
       </c>
       <c r="Y17" s="10">
         <f t="shared" si="8"/>
-        <v>72458</v>
+        <v>72461</v>
       </c>
       <c r="Z17" s="20">
-        <v>267023</v>
+        <v>267026</v>
       </c>
       <c r="AA17" s="12">
         <f t="shared" si="9"/>
-        <v>0.98963382996071458</v>
+        <v>0.98964494848417461</v>
       </c>
       <c r="AB17" s="17">
         <v>613565</v>
@@ -2945,14 +2945,14 @@
       </c>
       <c r="AD17" s="10">
         <f t="shared" si="10"/>
-        <v>123882</v>
+        <v>123888</v>
       </c>
       <c r="AE17" s="11">
-        <v>604342</v>
+        <v>604348</v>
       </c>
       <c r="AF17" s="12">
         <f t="shared" si="11"/>
-        <v>0.98496817778067525</v>
+        <v>0.98497795669570465</v>
       </c>
       <c r="AG17" s="16">
         <v>263808</v>
@@ -2962,14 +2962,14 @@
       </c>
       <c r="AI17" s="10">
         <f t="shared" si="12"/>
-        <v>62435</v>
+        <v>62437</v>
       </c>
       <c r="AJ17" s="20">
-        <v>259621</v>
+        <v>259623</v>
       </c>
       <c r="AK17" s="12">
         <f t="shared" si="13"/>
-        <v>0.98412860868510432</v>
+        <v>0.9841361899563319</v>
       </c>
       <c r="AL17" s="18">
         <v>270212</v>
@@ -2979,14 +2979,14 @@
       </c>
       <c r="AN17" s="10">
         <f t="shared" si="14"/>
-        <v>62606</v>
-      </c>
-      <c r="AO17" s="20">
-        <v>266618</v>
+        <v>62610</v>
+      </c>
+      <c r="AO17" s="11">
+        <v>266622</v>
       </c>
       <c r="AP17" s="12">
         <f t="shared" si="15"/>
-        <v>0.98669933237606033</v>
+        <v>0.98671413556762833</v>
       </c>
       <c r="AQ17" s="11">
         <v>633137</v>
@@ -2996,14 +2996,14 @@
       </c>
       <c r="AS17" s="10">
         <f t="shared" si="16"/>
-        <v>124213</v>
+        <v>124221</v>
       </c>
       <c r="AT17" s="13">
-        <v>619702</v>
+        <v>619710</v>
       </c>
       <c r="AU17" s="12">
         <f t="shared" si="17"/>
-        <v>0.97878026398709916</v>
+        <v>0.97879289948305026</v>
       </c>
       <c r="AV17" s="18">
         <v>270996</v>
@@ -3013,14 +3013,14 @@
       </c>
       <c r="AX17" s="10">
         <f t="shared" si="18"/>
-        <v>61980</v>
+        <v>61985</v>
       </c>
       <c r="AY17" s="20">
-        <v>265730</v>
+        <v>265735</v>
       </c>
       <c r="AZ17" s="12">
         <f t="shared" si="19"/>
-        <v>0.98056797886315661</v>
+        <v>0.98058642931998996</v>
       </c>
       <c r="BA17" s="18">
         <v>277009</v>
@@ -3030,14 +3030,14 @@
       </c>
       <c r="BC17" s="10">
         <f t="shared" si="20"/>
-        <v>65551</v>
+        <v>65556</v>
       </c>
       <c r="BD17" s="20">
-        <v>274581</v>
+        <v>274586</v>
       </c>
       <c r="BE17" s="12">
         <f t="shared" si="21"/>
-        <v>0.99123494182499483</v>
+        <v>0.99125299178005044</v>
       </c>
       <c r="BF17" s="18">
         <v>651560</v>
@@ -3047,14 +3047,14 @@
       </c>
       <c r="BH17" s="10">
         <f t="shared" si="22"/>
-        <v>160468</v>
+        <v>160478</v>
       </c>
       <c r="BI17" s="11">
-        <v>635873</v>
+        <v>635883</v>
       </c>
       <c r="BJ17" s="12">
         <f t="shared" si="23"/>
-        <v>0.97592393639879671</v>
+        <v>0.97593928417950759</v>
       </c>
       <c r="BK17" s="24"/>
       <c r="BL17" s="24"/>
@@ -3074,14 +3074,14 @@
       </c>
       <c r="E18" s="10">
         <f t="shared" si="0"/>
-        <v>625822</v>
+        <v>625829</v>
       </c>
       <c r="F18" s="20">
-        <v>740847</v>
+        <v>740854</v>
       </c>
       <c r="G18" s="12">
         <f t="shared" si="1"/>
-        <v>0.96402444261113296</v>
+        <v>0.96403355133546909</v>
       </c>
       <c r="H18" s="15">
         <v>766983</v>
@@ -3091,14 +3091,14 @@
       </c>
       <c r="J18" s="10">
         <f t="shared" si="2"/>
-        <v>564989</v>
+        <v>564996</v>
       </c>
       <c r="K18" s="20">
-        <v>740251</v>
+        <v>740258</v>
       </c>
       <c r="L18" s="12">
         <f t="shared" si="3"/>
-        <v>0.965146554747628</v>
+        <v>0.96515568141666763</v>
       </c>
       <c r="M18" s="16">
         <v>1193073</v>
@@ -3108,14 +3108,14 @@
       </c>
       <c r="O18" s="10">
         <f t="shared" si="4"/>
-        <v>410723</v>
+        <v>410732</v>
       </c>
       <c r="P18" s="13">
-        <v>1175473</v>
+        <v>1175482</v>
       </c>
       <c r="Q18" s="12">
         <f t="shared" si="5"/>
-        <v>0.98524817844339785</v>
+        <v>0.98525572198851197</v>
       </c>
       <c r="R18" s="16">
         <v>775495</v>
@@ -3125,14 +3125,14 @@
       </c>
       <c r="T18" s="10">
         <f t="shared" si="6"/>
-        <v>184163</v>
+        <v>184172</v>
       </c>
       <c r="U18" s="20">
-        <v>756192</v>
+        <v>756201</v>
       </c>
       <c r="V18" s="12">
         <f t="shared" si="7"/>
-        <v>0.97510880147518686</v>
+        <v>0.97512040696587343</v>
       </c>
       <c r="W18" s="16">
         <v>789854</v>
@@ -3142,14 +3142,14 @@
       </c>
       <c r="Y18" s="10">
         <f t="shared" si="8"/>
-        <v>178814</v>
+        <v>178821</v>
       </c>
       <c r="Z18" s="20">
-        <v>773175</v>
+        <v>773182</v>
       </c>
       <c r="AA18" s="12">
         <f t="shared" si="9"/>
-        <v>0.97888343921788079</v>
+        <v>0.97889230161523522</v>
       </c>
       <c r="AB18" s="17">
         <v>1245422</v>
@@ -3159,14 +3159,14 @@
       </c>
       <c r="AD18" s="10">
         <f t="shared" si="10"/>
-        <v>240969</v>
+        <v>240979</v>
       </c>
       <c r="AE18" s="11">
-        <v>1213759</v>
+        <v>1213769</v>
       </c>
       <c r="AF18" s="12">
         <f t="shared" si="11"/>
-        <v>0.97457648893306847</v>
+        <v>0.97458451833996829</v>
       </c>
       <c r="AG18" s="16">
         <v>794310</v>
@@ -3176,14 +3176,14 @@
       </c>
       <c r="AI18" s="10">
         <f t="shared" si="12"/>
-        <v>158870</v>
+        <v>158878</v>
       </c>
       <c r="AJ18" s="20">
-        <v>773908</v>
+        <v>773916</v>
       </c>
       <c r="AK18" s="12">
         <f t="shared" si="13"/>
-        <v>0.97431481411539578</v>
+        <v>0.97432488574989617</v>
       </c>
       <c r="AL18" s="18">
         <v>807429</v>
@@ -3193,14 +3193,14 @@
       </c>
       <c r="AN18" s="10">
         <f t="shared" si="14"/>
-        <v>156219</v>
-      </c>
-      <c r="AO18" s="20">
-        <v>787030</v>
+        <v>156227</v>
+      </c>
+      <c r="AO18" s="11">
+        <v>787038</v>
       </c>
       <c r="AP18" s="12">
         <f t="shared" si="15"/>
-        <v>0.97473585912817107</v>
+        <v>0.9747457671200811</v>
       </c>
       <c r="AQ18" s="11">
         <v>1285494</v>
@@ -3210,14 +3210,14 @@
       </c>
       <c r="AS18" s="10">
         <f t="shared" si="16"/>
-        <v>230858</v>
+        <v>230870</v>
       </c>
       <c r="AT18" s="13">
-        <v>1245478</v>
+        <v>1245490</v>
       </c>
       <c r="AU18" s="12">
         <f t="shared" si="17"/>
-        <v>0.96887111102813395</v>
+        <v>0.96888044596085243</v>
       </c>
       <c r="AV18" s="18">
         <v>820095</v>
@@ -3227,14 +3227,14 @@
       </c>
       <c r="AX18" s="10">
         <f t="shared" si="18"/>
-        <v>161725</v>
+        <v>161734</v>
       </c>
       <c r="AY18" s="20">
-        <v>793752</v>
+        <v>793761</v>
       </c>
       <c r="AZ18" s="12">
         <f t="shared" si="19"/>
-        <v>0.96787811168218318</v>
+        <v>0.96788908602052204</v>
       </c>
       <c r="BA18" s="18">
         <v>829968</v>
@@ -3244,14 +3244,14 @@
       </c>
       <c r="BC18" s="10">
         <f t="shared" si="20"/>
-        <v>198176</v>
+        <v>198186</v>
       </c>
       <c r="BD18" s="20">
-        <v>806477</v>
+        <v>806487</v>
       </c>
       <c r="BE18" s="12">
         <f t="shared" si="21"/>
-        <v>0.97169649914213563</v>
+        <v>0.97170854779943328</v>
       </c>
       <c r="BF18" s="18">
         <v>1319511</v>
@@ -3261,14 +3261,14 @@
       </c>
       <c r="BH18" s="10">
         <f t="shared" si="22"/>
-        <v>292020</v>
+        <v>292035</v>
       </c>
       <c r="BI18" s="11">
-        <v>1272798</v>
+        <v>1272813</v>
       </c>
       <c r="BJ18" s="12">
         <f t="shared" si="23"/>
-        <v>0.96459824889675039</v>
+        <v>0.96460961674438483</v>
       </c>
       <c r="BK18" s="24"/>
       <c r="BL18" s="24"/>
@@ -3288,14 +3288,14 @@
       </c>
       <c r="E19" s="10">
         <f t="shared" si="0"/>
-        <v>181875</v>
+        <v>181878</v>
       </c>
       <c r="F19" s="20">
-        <v>215769</v>
+        <v>215772</v>
       </c>
       <c r="G19" s="12">
         <f t="shared" si="1"/>
-        <v>0.87906084235742743</v>
+        <v>0.87907306460681023</v>
       </c>
       <c r="H19" s="15">
         <v>247965</v>
@@ -3305,14 +3305,14 @@
       </c>
       <c r="J19" s="10">
         <f t="shared" si="2"/>
-        <v>170656</v>
+        <v>170659</v>
       </c>
       <c r="K19" s="20">
-        <v>216746</v>
+        <v>216749</v>
       </c>
       <c r="L19" s="12">
         <f t="shared" si="3"/>
-        <v>0.87409916722118042</v>
+        <v>0.87411126570282094</v>
       </c>
       <c r="M19" s="16">
         <v>387570</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="O19" s="10">
         <f t="shared" si="4"/>
-        <v>139735</v>
+        <v>139738</v>
       </c>
       <c r="P19" s="13">
-        <v>357133</v>
+        <v>357136</v>
       </c>
       <c r="Q19" s="12">
         <f t="shared" si="5"/>
-        <v>0.9214670898160332</v>
+        <v>0.92147483035322653</v>
       </c>
       <c r="R19" s="16">
         <v>254467</v>
@@ -3339,14 +3339,14 @@
       </c>
       <c r="T19" s="10">
         <f t="shared" si="6"/>
-        <v>69076</v>
+        <v>69079</v>
       </c>
       <c r="U19" s="20">
-        <v>229787</v>
+        <v>229790</v>
       </c>
       <c r="V19" s="12">
         <f t="shared" si="7"/>
-        <v>0.90301296435294165</v>
+        <v>0.90302475370087276</v>
       </c>
       <c r="W19" s="16">
         <v>263449</v>
@@ -3356,14 +3356,14 @@
       </c>
       <c r="Y19" s="10">
         <f t="shared" si="8"/>
-        <v>66514</v>
+        <v>66517</v>
       </c>
       <c r="Z19" s="20">
-        <v>244523</v>
+        <v>244526</v>
       </c>
       <c r="AA19" s="12">
         <f t="shared" si="9"/>
-        <v>0.92816066866831914</v>
+        <v>0.9281720560715736</v>
       </c>
       <c r="AB19" s="17">
         <v>418128</v>
@@ -3373,14 +3373,14 @@
       </c>
       <c r="AD19" s="10">
         <f t="shared" si="10"/>
-        <v>85779</v>
+        <v>85782</v>
       </c>
       <c r="AE19" s="11">
-        <v>394353</v>
+        <v>394356</v>
       </c>
       <c r="AF19" s="12">
         <f t="shared" si="11"/>
-        <v>0.94313942142119156</v>
+        <v>0.94314659625760533</v>
       </c>
       <c r="AG19" s="16">
         <v>259213</v>
@@ -3390,14 +3390,14 @@
       </c>
       <c r="AI19" s="10">
         <f t="shared" si="12"/>
-        <v>59053</v>
+        <v>59056</v>
       </c>
       <c r="AJ19" s="20">
-        <v>234177</v>
+        <v>234180</v>
       </c>
       <c r="AK19" s="12">
         <f t="shared" si="13"/>
-        <v>0.90341533796530271</v>
+        <v>0.90342691145891607</v>
       </c>
       <c r="AL19" s="18">
         <v>262802</v>
@@ -3407,14 +3407,14 @@
       </c>
       <c r="AN19" s="10">
         <f t="shared" si="14"/>
-        <v>55768</v>
-      </c>
-      <c r="AO19" s="20">
-        <v>237103</v>
+        <v>55771</v>
+      </c>
+      <c r="AO19" s="11">
+        <v>237106</v>
       </c>
       <c r="AP19" s="12">
         <f t="shared" si="15"/>
-        <v>0.90221155090143912</v>
+        <v>0.9022229663396778</v>
       </c>
       <c r="AQ19" s="11">
         <v>437396</v>
@@ -3424,14 +3424,14 @@
       </c>
       <c r="AS19" s="10">
         <f t="shared" si="16"/>
-        <v>82221</v>
+        <v>82223</v>
       </c>
       <c r="AT19" s="13">
-        <v>401084</v>
+        <v>401086</v>
       </c>
       <c r="AU19" s="12">
         <f t="shared" si="17"/>
-        <v>0.91698140815188067</v>
+        <v>0.91698598066740433</v>
       </c>
       <c r="AV19" s="18">
         <v>265429</v>
@@ -3441,14 +3441,14 @@
       </c>
       <c r="AX19" s="10">
         <f t="shared" si="18"/>
-        <v>56293</v>
+        <v>56295</v>
       </c>
       <c r="AY19" s="20">
-        <v>237900</v>
+        <v>237902</v>
       </c>
       <c r="AZ19" s="12">
         <f t="shared" si="19"/>
-        <v>0.89628488220955504</v>
+        <v>0.89629241718124242</v>
       </c>
       <c r="BA19" s="18">
         <v>272122</v>
@@ -3458,14 +3458,14 @@
       </c>
       <c r="BC19" s="10">
         <f t="shared" si="20"/>
-        <v>65953</v>
+        <v>65955</v>
       </c>
       <c r="BD19" s="20">
-        <v>244811</v>
+        <v>244813</v>
       </c>
       <c r="BE19" s="12">
         <f t="shared" si="21"/>
-        <v>0.89963692755455271</v>
+        <v>0.89964427719919737</v>
       </c>
       <c r="BF19" s="18">
         <v>456786</v>
@@ -3475,14 +3475,14 @@
       </c>
       <c r="BH19" s="10">
         <f t="shared" si="22"/>
-        <v>115385</v>
+        <v>115387</v>
       </c>
       <c r="BI19" s="11">
-        <v>415707</v>
+        <v>415709</v>
       </c>
       <c r="BJ19" s="12">
         <f t="shared" si="23"/>
-        <v>0.91006948549211231</v>
+        <v>0.91007386391001477</v>
       </c>
       <c r="BK19" s="24"/>
       <c r="BL19" s="24"/>
@@ -3536,14 +3536,14 @@
       </c>
       <c r="O20" s="10">
         <f t="shared" si="4"/>
-        <v>3096</v>
+        <v>3097</v>
       </c>
       <c r="P20" s="13">
-        <v>7271</v>
+        <v>7272</v>
       </c>
       <c r="Q20" s="12">
         <f t="shared" si="5"/>
-        <v>0.90356654653908286</v>
+        <v>0.9036908164533366</v>
       </c>
       <c r="R20" s="16">
         <v>5619</v>
@@ -3587,14 +3587,14 @@
       </c>
       <c r="AD20" s="10">
         <f t="shared" si="10"/>
-        <v>2184</v>
+        <v>2186</v>
       </c>
       <c r="AE20" s="11">
-        <v>7489</v>
+        <v>7491</v>
       </c>
       <c r="AF20" s="12">
         <f t="shared" si="11"/>
-        <v>0.90076978590329559</v>
+        <v>0.90101034399807556</v>
       </c>
       <c r="AG20" s="16">
         <v>5709</v>
@@ -3604,14 +3604,14 @@
       </c>
       <c r="AI20" s="10">
         <f t="shared" si="12"/>
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="AJ20" s="20">
-        <v>4902</v>
+        <v>4903</v>
       </c>
       <c r="AK20" s="12">
         <f t="shared" si="13"/>
-        <v>0.8586442459274829</v>
+        <v>0.8588194079523559</v>
       </c>
       <c r="AL20" s="18">
         <v>5805</v>
@@ -3621,14 +3621,14 @@
       </c>
       <c r="AN20" s="10">
         <f t="shared" si="14"/>
-        <v>1488</v>
-      </c>
-      <c r="AO20" s="20">
-        <v>5000</v>
+        <v>1490</v>
+      </c>
+      <c r="AO20" s="11">
+        <v>5002</v>
       </c>
       <c r="AP20" s="12">
         <f t="shared" si="15"/>
-        <v>0.8613264427217916</v>
+        <v>0.86167097329888032</v>
       </c>
       <c r="AQ20" s="11">
         <v>8632</v>
@@ -3638,14 +3638,14 @@
       </c>
       <c r="AS20" s="10">
         <f t="shared" si="16"/>
-        <v>1919</v>
+        <v>1922</v>
       </c>
       <c r="AT20" s="13">
-        <v>7770</v>
+        <v>7773</v>
       </c>
       <c r="AU20" s="12">
         <f t="shared" si="17"/>
-        <v>0.90013901760889714</v>
+        <v>0.90048656163113994</v>
       </c>
       <c r="AV20" s="18">
         <v>5837</v>
@@ -3655,14 +3655,14 @@
       </c>
       <c r="AX20" s="10">
         <f t="shared" si="18"/>
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="AY20" s="20">
-        <v>4955</v>
+        <v>4957</v>
       </c>
       <c r="AZ20" s="12">
         <f t="shared" si="19"/>
-        <v>0.84889498029809829</v>
+        <v>0.84923762206612985</v>
       </c>
       <c r="BA20" s="18">
         <v>5912</v>
@@ -3672,14 +3672,14 @@
       </c>
       <c r="BC20" s="10">
         <f t="shared" si="20"/>
-        <v>1552</v>
+        <v>1554</v>
       </c>
       <c r="BD20" s="20">
-        <v>5060</v>
+        <v>5062</v>
       </c>
       <c r="BE20" s="12">
         <f t="shared" si="21"/>
-        <v>0.85588633288227334</v>
+        <v>0.85622462787550746</v>
       </c>
       <c r="BF20" s="18">
         <v>8941</v>
@@ -3689,14 +3689,14 @@
       </c>
       <c r="BH20" s="10">
         <f t="shared" si="22"/>
-        <v>2246</v>
+        <v>2249</v>
       </c>
       <c r="BI20" s="11">
-        <v>8002</v>
+        <v>8005</v>
       </c>
       <c r="BJ20" s="12">
         <f t="shared" si="23"/>
-        <v>0.89497819035902026</v>
+        <v>0.89531372329717029</v>
       </c>
       <c r="BK20" s="24"/>
       <c r="BL20" s="24"/>
@@ -3767,14 +3767,14 @@
       </c>
       <c r="T21" s="10">
         <f t="shared" si="6"/>
-        <v>3581</v>
+        <v>3582</v>
       </c>
       <c r="U21" s="20">
-        <v>7867</v>
+        <v>7868</v>
       </c>
       <c r="V21" s="12">
         <f t="shared" si="7"/>
-        <v>0.76848686138517142</v>
+        <v>0.76858454625378525</v>
       </c>
       <c r="W21" s="16">
         <v>10162</v>
@@ -3784,14 +3784,14 @@
       </c>
       <c r="Y21" s="10">
         <f t="shared" si="8"/>
-        <v>3549</v>
+        <v>3550</v>
       </c>
       <c r="Z21" s="20">
-        <v>7969</v>
+        <v>7970</v>
       </c>
       <c r="AA21" s="12">
         <f t="shared" si="9"/>
-        <v>0.78419602440464475</v>
+        <v>0.78429443023026968</v>
       </c>
       <c r="AB21" s="17">
         <v>13196</v>
@@ -3801,14 +3801,14 @@
       </c>
       <c r="AD21" s="10">
         <f t="shared" si="10"/>
-        <v>4242</v>
+        <v>4244</v>
       </c>
       <c r="AE21" s="11">
-        <v>10794</v>
+        <v>10796</v>
       </c>
       <c r="AF21" s="12">
         <f t="shared" si="11"/>
-        <v>0.81797514398302518</v>
+        <v>0.81812670506214002</v>
       </c>
       <c r="AG21" s="16">
         <v>10295</v>
@@ -3818,14 +3818,14 @@
       </c>
       <c r="AI21" s="10">
         <f t="shared" si="12"/>
-        <v>3023</v>
+        <v>3025</v>
       </c>
       <c r="AJ21" s="20">
-        <v>8029</v>
+        <v>8031</v>
       </c>
       <c r="AK21" s="12">
         <f t="shared" si="13"/>
-        <v>0.77989315201554155</v>
+        <v>0.78008742107819329</v>
       </c>
       <c r="AL21" s="18">
         <v>10459</v>
@@ -3835,14 +3835,14 @@
       </c>
       <c r="AN21" s="10">
         <f t="shared" si="14"/>
-        <v>2974</v>
-      </c>
-      <c r="AO21" s="20">
-        <v>8137</v>
+        <v>2976</v>
+      </c>
+      <c r="AO21" s="11">
+        <v>8139</v>
       </c>
       <c r="AP21" s="12">
         <f t="shared" si="15"/>
-        <v>0.77799024763361702</v>
+        <v>0.77818147050387221</v>
       </c>
       <c r="AQ21" s="11">
         <v>13595</v>
@@ -3852,14 +3852,14 @@
       </c>
       <c r="AS21" s="10">
         <f t="shared" si="16"/>
-        <v>3825</v>
+        <v>3827</v>
       </c>
       <c r="AT21" s="13">
-        <v>11058</v>
+        <v>11060</v>
       </c>
       <c r="AU21" s="12">
         <f t="shared" si="17"/>
-        <v>0.81338727473335781</v>
+        <v>0.81353438764251562</v>
       </c>
       <c r="AV21" s="18">
         <v>10391</v>
@@ -3869,14 +3869,14 @@
       </c>
       <c r="AX21" s="10">
         <f t="shared" si="18"/>
-        <v>3010</v>
+        <v>3012</v>
       </c>
       <c r="AY21" s="20">
-        <v>8236</v>
+        <v>8238</v>
       </c>
       <c r="AZ21" s="12">
         <f t="shared" si="19"/>
-        <v>0.79260898854778172</v>
+        <v>0.79280146280434993</v>
       </c>
       <c r="BA21" s="18">
         <v>10525</v>
@@ -3886,14 +3886,14 @@
       </c>
       <c r="BC21" s="10">
         <f t="shared" si="20"/>
-        <v>3116</v>
+        <v>3118</v>
       </c>
       <c r="BD21" s="20">
-        <v>8385</v>
+        <v>8387</v>
       </c>
       <c r="BE21" s="12">
         <f t="shared" si="21"/>
-        <v>0.79667458432304039</v>
+        <v>0.79686460807600945</v>
       </c>
       <c r="BF21" s="18">
         <v>13618</v>
@@ -3903,14 +3903,14 @@
       </c>
       <c r="BH21" s="10">
         <f t="shared" si="22"/>
-        <v>5145</v>
+        <v>5147</v>
       </c>
       <c r="BI21" s="11">
-        <v>11445</v>
+        <v>11447</v>
       </c>
       <c r="BJ21" s="12">
         <f t="shared" si="23"/>
-        <v>0.84043178146570718</v>
+        <v>0.84057864590982523</v>
       </c>
       <c r="BK21" s="24"/>
       <c r="BL21" s="24"/>
@@ -3930,14 +3930,14 @@
       </c>
       <c r="E22" s="10">
         <f t="shared" si="0"/>
-        <v>3844</v>
+        <v>3846</v>
       </c>
       <c r="F22" s="20">
-        <v>5157</v>
+        <v>5159</v>
       </c>
       <c r="G22" s="12">
         <f t="shared" si="1"/>
-        <v>0.87096774193548387</v>
+        <v>0.87130552271575745</v>
       </c>
       <c r="H22" s="15">
         <v>5940</v>
@@ -3947,14 +3947,14 @@
       </c>
       <c r="J22" s="10">
         <f t="shared" si="2"/>
-        <v>4124</v>
+        <v>4125</v>
       </c>
       <c r="K22" s="20">
-        <v>5173</v>
+        <v>5174</v>
       </c>
       <c r="L22" s="12">
         <f t="shared" si="3"/>
-        <v>0.87087542087542091</v>
+        <v>0.87104377104377106</v>
       </c>
       <c r="M22" s="16">
         <v>7004</v>
@@ -3964,14 +3964,14 @@
       </c>
       <c r="O22" s="10">
         <f t="shared" si="4"/>
-        <v>3145</v>
+        <v>3146</v>
       </c>
       <c r="P22" s="13">
-        <v>6187</v>
+        <v>6188</v>
       </c>
       <c r="Q22" s="12">
         <f t="shared" si="5"/>
-        <v>0.88335237007424328</v>
+        <v>0.88349514563106801</v>
       </c>
       <c r="R22" s="16">
         <v>5966</v>
@@ -3981,14 +3981,14 @@
       </c>
       <c r="T22" s="10">
         <f t="shared" si="6"/>
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="U22" s="20">
-        <v>5135</v>
+        <v>5136</v>
       </c>
       <c r="V22" s="12">
         <f t="shared" si="7"/>
-        <v>0.86071069393228294</v>
+        <v>0.86087831042574592</v>
       </c>
       <c r="W22" s="16">
         <v>5920</v>
@@ -3998,14 +3998,14 @@
       </c>
       <c r="Y22" s="10">
         <f t="shared" si="8"/>
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="Z22" s="20">
-        <v>5199</v>
+        <v>5200</v>
       </c>
       <c r="AA22" s="12">
         <f t="shared" si="9"/>
-        <v>0.8782094594594595</v>
+        <v>0.8783783783783784</v>
       </c>
       <c r="AB22" s="17">
         <v>7073</v>
@@ -4015,14 +4015,14 @@
       </c>
       <c r="AD22" s="10">
         <f t="shared" si="10"/>
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="AE22" s="11">
-        <v>6357</v>
+        <v>6358</v>
       </c>
       <c r="AF22" s="12">
         <f t="shared" si="11"/>
-        <v>0.89876997030962813</v>
+        <v>0.89891135303265945</v>
       </c>
       <c r="AG22" s="16">
         <v>5998</v>
@@ -4032,14 +4032,14 @@
       </c>
       <c r="AI22" s="10">
         <f t="shared" si="12"/>
-        <v>1587</v>
+        <v>1589</v>
       </c>
       <c r="AJ22" s="20">
-        <v>5297</v>
+        <v>5299</v>
       </c>
       <c r="AK22" s="12">
         <f t="shared" si="13"/>
-        <v>0.88312770923641215</v>
+        <v>0.88346115371790601</v>
       </c>
       <c r="AL22" s="18">
         <v>5988</v>
@@ -4049,14 +4049,14 @@
       </c>
       <c r="AN22" s="10">
         <f t="shared" si="14"/>
-        <v>1588</v>
-      </c>
-      <c r="AO22" s="20">
-        <v>5384</v>
+        <v>1590</v>
+      </c>
+      <c r="AO22" s="11">
+        <v>5386</v>
       </c>
       <c r="AP22" s="12">
         <f t="shared" si="15"/>
-        <v>0.89913159652638608</v>
+        <v>0.89946559786239144</v>
       </c>
       <c r="AQ22" s="11">
         <v>7036</v>
@@ -4066,14 +4066,14 @@
       </c>
       <c r="AS22" s="10">
         <f t="shared" si="16"/>
-        <v>1943</v>
+        <v>1945</v>
       </c>
       <c r="AT22" s="13">
-        <v>6497</v>
+        <v>6499</v>
       </c>
       <c r="AU22" s="12">
         <f t="shared" si="17"/>
-        <v>0.92339397384877775</v>
+        <v>0.92367822626492324</v>
       </c>
       <c r="AV22" s="18">
         <v>5943</v>
@@ -4083,14 +4083,14 @@
       </c>
       <c r="AX22" s="10">
         <f t="shared" si="18"/>
-        <v>1651</v>
+        <v>1653</v>
       </c>
       <c r="AY22" s="20">
-        <v>5409</v>
+        <v>5411</v>
       </c>
       <c r="AZ22" s="12">
         <f t="shared" si="19"/>
-        <v>0.91014639071176173</v>
+        <v>0.91048292108362783</v>
       </c>
       <c r="BA22" s="18">
         <v>5997</v>
@@ -4100,14 +4100,14 @@
       </c>
       <c r="BC22" s="10">
         <f t="shared" si="20"/>
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="BD22" s="20">
-        <v>5473</v>
+        <v>5475</v>
       </c>
       <c r="BE22" s="12">
         <f t="shared" si="21"/>
-        <v>0.91262297815574456</v>
+        <v>0.91295647823911952</v>
       </c>
       <c r="BF22" s="18">
         <v>7214</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="BH22" s="10">
         <f t="shared" si="22"/>
-        <v>2396</v>
+        <v>2399</v>
       </c>
       <c r="BI22" s="11">
-        <v>6679</v>
+        <v>6682</v>
       </c>
       <c r="BJ22" s="12">
         <f t="shared" si="23"/>
-        <v>0.92583864707513164</v>
+        <v>0.92625450512891605</v>
       </c>
       <c r="BK22" s="24"/>
       <c r="BL22" s="24"/>
@@ -4265,7 +4265,7 @@
         <f t="shared" si="14"/>
         <v>2895</v>
       </c>
-      <c r="AO23" s="20">
+      <c r="AO23" s="11">
         <v>7537</v>
       </c>
       <c r="AP23" s="12">
@@ -4479,7 +4479,7 @@
         <f t="shared" si="14"/>
         <v>1214</v>
       </c>
-      <c r="AO24" s="20">
+      <c r="AO24" s="11">
         <v>4882</v>
       </c>
       <c r="AP24" s="12">
@@ -4693,7 +4693,7 @@
         <f t="shared" si="14"/>
         <v>3304</v>
       </c>
-      <c r="AO25" s="20">
+      <c r="AO25" s="11">
         <v>16817</v>
       </c>
       <c r="AP25" s="12">
@@ -4708,14 +4708,14 @@
       </c>
       <c r="AS25" s="10">
         <f t="shared" si="16"/>
-        <v>4296</v>
+        <v>4297</v>
       </c>
       <c r="AT25" s="13">
-        <v>23885</v>
+        <v>23886</v>
       </c>
       <c r="AU25" s="12">
         <f t="shared" si="17"/>
-        <v>0.92692486805339958</v>
+        <v>0.92696367587705686</v>
       </c>
       <c r="AV25" s="18">
         <v>18472</v>
@@ -4759,14 +4759,14 @@
       </c>
       <c r="BH25" s="10">
         <f t="shared" si="22"/>
-        <v>6376</v>
+        <v>6379</v>
       </c>
       <c r="BI25" s="11">
-        <v>24497</v>
+        <v>24500</v>
       </c>
       <c r="BJ25" s="12">
         <f t="shared" si="23"/>
-        <v>0.93746890666258464</v>
+        <v>0.93758371283150277</v>
       </c>
       <c r="BK25" s="24"/>
       <c r="BL25" s="24"/>
@@ -4907,7 +4907,7 @@
         <f t="shared" si="14"/>
         <v>3491</v>
       </c>
-      <c r="AO26" s="20">
+      <c r="AO26" s="11">
         <v>12977</v>
       </c>
       <c r="AP26" s="12">
@@ -4973,14 +4973,14 @@
       </c>
       <c r="BH26" s="10">
         <f t="shared" si="22"/>
-        <v>6316</v>
+        <v>6317</v>
       </c>
       <c r="BI26" s="11">
-        <v>23222</v>
+        <v>23223</v>
       </c>
       <c r="BJ26" s="12">
         <f t="shared" si="23"/>
-        <v>0.87163125891449589</v>
+        <v>0.87166879363411154</v>
       </c>
       <c r="BK26" s="24"/>
       <c r="BL26" s="24"/>
@@ -5000,14 +5000,14 @@
       </c>
       <c r="E27" s="10">
         <f t="shared" si="0"/>
-        <v>84761</v>
+        <v>84769</v>
       </c>
       <c r="F27" s="20">
-        <v>102165</v>
+        <v>102173</v>
       </c>
       <c r="G27" s="12">
         <f t="shared" si="1"/>
-        <v>0.90542109414465111</v>
+        <v>0.90549199287467763</v>
       </c>
       <c r="H27" s="15">
         <v>111842</v>
@@ -5017,14 +5017,14 @@
       </c>
       <c r="J27" s="10">
         <f t="shared" si="2"/>
-        <v>84467</v>
+        <v>84475</v>
       </c>
       <c r="K27" s="20">
-        <v>102019</v>
+        <v>102027</v>
       </c>
       <c r="L27" s="12">
         <f t="shared" si="3"/>
-        <v>0.91217074086657968</v>
+        <v>0.91224227034566618</v>
       </c>
       <c r="M27" s="16">
         <v>156288</v>
@@ -5034,14 +5034,14 @@
       </c>
       <c r="O27" s="10">
         <f t="shared" si="4"/>
-        <v>74486</v>
+        <v>74497</v>
       </c>
       <c r="P27" s="13">
-        <v>145739</v>
+        <v>145750</v>
       </c>
       <c r="Q27" s="12">
         <f t="shared" si="5"/>
-        <v>0.93250281531531531</v>
+        <v>0.93257319819819817</v>
       </c>
       <c r="R27" s="16">
         <v>113087</v>
@@ -5051,14 +5051,14 @@
       </c>
       <c r="T27" s="10">
         <f t="shared" si="6"/>
-        <v>39361</v>
+        <v>39370</v>
       </c>
       <c r="U27" s="20">
-        <v>104489</v>
+        <v>104498</v>
       </c>
       <c r="V27" s="12">
         <f t="shared" si="7"/>
-        <v>0.92397004076507472</v>
+        <v>0.92404962550956349</v>
       </c>
       <c r="W27" s="16">
         <v>116164</v>
@@ -5068,14 +5068,14 @@
       </c>
       <c r="Y27" s="10">
         <f t="shared" si="8"/>
-        <v>38407</v>
+        <v>38417</v>
       </c>
       <c r="Z27" s="20">
-        <v>108017</v>
+        <v>108027</v>
       </c>
       <c r="AA27" s="12">
         <f t="shared" si="9"/>
-        <v>0.92986639578526908</v>
+        <v>0.92995248097517302</v>
       </c>
       <c r="AB27" s="17">
         <v>165468</v>
@@ -5085,14 +5085,14 @@
       </c>
       <c r="AD27" s="10">
         <f t="shared" si="10"/>
-        <v>48086</v>
+        <v>48098</v>
       </c>
       <c r="AE27" s="11">
-        <v>155625</v>
+        <v>155637</v>
       </c>
       <c r="AF27" s="12">
         <f t="shared" si="11"/>
-        <v>0.94051417796794545</v>
+        <v>0.94058669954311402</v>
       </c>
       <c r="AG27" s="16">
         <v>116084</v>
@@ -5102,14 +5102,14 @@
       </c>
       <c r="AI27" s="10">
         <f t="shared" si="12"/>
-        <v>32752</v>
+        <v>32763</v>
       </c>
       <c r="AJ27" s="20">
-        <v>107129</v>
+        <v>107140</v>
       </c>
       <c r="AK27" s="12">
         <f t="shared" si="13"/>
-        <v>0.92285758588608247</v>
+        <v>0.92295234485372657</v>
       </c>
       <c r="AL27" s="18">
         <v>117992</v>
@@ -5119,14 +5119,14 @@
       </c>
       <c r="AN27" s="10">
         <f t="shared" si="14"/>
-        <v>33335</v>
-      </c>
-      <c r="AO27" s="20">
-        <v>109159</v>
+        <v>33347</v>
+      </c>
+      <c r="AO27" s="11">
+        <v>109171</v>
       </c>
       <c r="AP27" s="12">
         <f t="shared" si="15"/>
-        <v>0.92513899247406606</v>
+        <v>0.92524069428435829</v>
       </c>
       <c r="AQ27" s="11">
         <v>170879</v>
@@ -5136,14 +5136,14 @@
       </c>
       <c r="AS27" s="10">
         <f t="shared" si="16"/>
-        <v>45145</v>
+        <v>45159</v>
       </c>
       <c r="AT27" s="13">
-        <v>160495</v>
+        <v>160509</v>
       </c>
       <c r="AU27" s="12">
         <f t="shared" si="17"/>
-        <v>0.93923185411899646</v>
+        <v>0.93931378343740313</v>
       </c>
       <c r="AV27" s="18">
         <v>116485</v>
@@ -5153,14 +5153,14 @@
       </c>
       <c r="AX27" s="10">
         <f t="shared" si="18"/>
-        <v>34146</v>
+        <v>34158</v>
       </c>
       <c r="AY27" s="20">
-        <v>109503</v>
+        <v>109515</v>
       </c>
       <c r="AZ27" s="12">
         <f t="shared" si="19"/>
-        <v>0.94006095205391249</v>
+        <v>0.94016396960982096</v>
       </c>
       <c r="BA27" s="18">
         <v>117017</v>
@@ -5170,14 +5170,14 @@
       </c>
       <c r="BC27" s="10">
         <f t="shared" si="20"/>
-        <v>38094</v>
+        <v>38106</v>
       </c>
       <c r="BD27" s="20">
-        <v>111396</v>
+        <v>111408</v>
       </c>
       <c r="BE27" s="12">
         <f t="shared" si="21"/>
-        <v>0.95196424451148121</v>
+        <v>0.95206679371373393</v>
       </c>
       <c r="BF27" s="18">
         <v>172738</v>
@@ -5187,14 +5187,14 @@
       </c>
       <c r="BH27" s="10">
         <f t="shared" si="22"/>
-        <v>63087</v>
+        <v>63104</v>
       </c>
       <c r="BI27" s="11">
-        <v>164632</v>
+        <v>164649</v>
       </c>
       <c r="BJ27" s="12">
         <f t="shared" si="23"/>
-        <v>0.95307344070210376</v>
+        <v>0.95317185564264961</v>
       </c>
       <c r="BK27" s="24"/>
       <c r="BL27" s="24"/>
@@ -5214,14 +5214,14 @@
       </c>
       <c r="E28" s="10">
         <f t="shared" si="0"/>
-        <v>248060</v>
+        <v>248064</v>
       </c>
       <c r="F28" s="20">
-        <v>327095</v>
+        <v>327099</v>
       </c>
       <c r="G28" s="12">
         <f t="shared" si="1"/>
-        <v>0.868217856735228</v>
+        <v>0.8682284740526035</v>
       </c>
       <c r="H28" s="15">
         <v>377506</v>
@@ -5231,14 +5231,14 @@
       </c>
       <c r="J28" s="10">
         <f t="shared" si="2"/>
-        <v>256656</v>
+        <v>256660</v>
       </c>
       <c r="K28" s="20">
-        <v>327714</v>
+        <v>327718</v>
       </c>
       <c r="L28" s="12">
         <f t="shared" si="3"/>
-        <v>0.86810275863165087</v>
+        <v>0.86811335448972993</v>
       </c>
       <c r="M28" s="16">
         <v>622937</v>
@@ -5248,14 +5248,14 @@
       </c>
       <c r="O28" s="10">
         <f t="shared" si="4"/>
-        <v>184089</v>
+        <v>184095</v>
       </c>
       <c r="P28" s="13">
-        <v>569139</v>
+        <v>569145</v>
       </c>
       <c r="Q28" s="12">
         <f t="shared" si="5"/>
-        <v>0.91363813676182337</v>
+        <v>0.91364776855444452</v>
       </c>
       <c r="R28" s="16">
         <v>379798</v>
@@ -5265,14 +5265,14 @@
       </c>
       <c r="T28" s="10">
         <f t="shared" si="6"/>
-        <v>82837</v>
+        <v>82841</v>
       </c>
       <c r="U28" s="20">
-        <v>329376</v>
+        <v>329380</v>
       </c>
       <c r="V28" s="12">
         <f t="shared" si="7"/>
-        <v>0.86723995387021524</v>
+        <v>0.86725048578454866</v>
       </c>
       <c r="W28" s="16">
         <v>378910</v>
@@ -5282,14 +5282,14 @@
       </c>
       <c r="Y28" s="10">
         <f t="shared" si="8"/>
-        <v>83063</v>
+        <v>83067</v>
       </c>
       <c r="Z28" s="20">
-        <v>334162</v>
+        <v>334166</v>
       </c>
       <c r="AA28" s="12">
         <f t="shared" si="9"/>
-        <v>0.88190335435855483</v>
+        <v>0.88191391095510807</v>
       </c>
       <c r="AB28" s="17">
         <v>628364</v>
@@ -5299,14 +5299,14 @@
       </c>
       <c r="AD28" s="10">
         <f t="shared" si="10"/>
-        <v>120941</v>
+        <v>120946</v>
       </c>
       <c r="AE28" s="11">
-        <v>580304</v>
+        <v>580309</v>
       </c>
       <c r="AF28" s="12">
         <f t="shared" si="11"/>
-        <v>0.92351566926176543</v>
+        <v>0.92352362643308661</v>
       </c>
       <c r="AG28" s="16">
         <v>375124</v>
@@ -5316,14 +5316,14 @@
       </c>
       <c r="AI28" s="10">
         <f t="shared" si="12"/>
-        <v>67353</v>
+        <v>67357</v>
       </c>
       <c r="AJ28" s="20">
-        <v>333737</v>
+        <v>333741</v>
       </c>
       <c r="AK28" s="12">
         <f t="shared" si="13"/>
-        <v>0.88967114874014996</v>
+        <v>0.88968181188087136</v>
       </c>
       <c r="AL28" s="18">
         <v>368781</v>
@@ -5333,14 +5333,14 @@
       </c>
       <c r="AN28" s="10">
         <f t="shared" si="14"/>
-        <v>68516</v>
-      </c>
-      <c r="AO28" s="20">
-        <v>338472</v>
+        <v>68520</v>
+      </c>
+      <c r="AO28" s="11">
+        <v>338476</v>
       </c>
       <c r="AP28" s="12">
         <f t="shared" si="15"/>
-        <v>0.9178130109739927</v>
+        <v>0.91782385751977458</v>
       </c>
       <c r="AQ28" s="11">
         <v>617418</v>
@@ -5350,14 +5350,14 @@
       </c>
       <c r="AS28" s="10">
         <f t="shared" si="16"/>
-        <v>98504</v>
+        <v>98509</v>
       </c>
       <c r="AT28" s="13">
-        <v>590266</v>
+        <v>590271</v>
       </c>
       <c r="AU28" s="12">
         <f t="shared" si="17"/>
-        <v>0.95602330997800522</v>
+        <v>0.95603140821939103</v>
       </c>
       <c r="AV28" s="18">
         <v>357852</v>
@@ -5367,14 +5367,14 @@
       </c>
       <c r="AX28" s="10">
         <f t="shared" si="18"/>
-        <v>67572</v>
+        <v>67576</v>
       </c>
       <c r="AY28" s="20">
-        <v>340244</v>
+        <v>340248</v>
       </c>
       <c r="AZ28" s="12">
         <f t="shared" si="19"/>
-        <v>0.95079530085063102</v>
+        <v>0.95080647865598067</v>
       </c>
       <c r="BA28" s="18">
         <v>359943</v>
@@ -5384,14 +5384,14 @@
       </c>
       <c r="BC28" s="10">
         <f t="shared" si="20"/>
-        <v>73124</v>
+        <v>73128</v>
       </c>
       <c r="BD28" s="20">
-        <v>344952</v>
+        <v>344956</v>
       </c>
       <c r="BE28" s="12">
         <f t="shared" si="21"/>
-        <v>0.95835173902534565</v>
+        <v>0.95836285189599468</v>
       </c>
       <c r="BF28" s="18">
         <v>622234</v>
@@ -5401,14 +5401,14 @@
       </c>
       <c r="BH28" s="10">
         <f t="shared" si="22"/>
-        <v>124727</v>
+        <v>124732</v>
       </c>
       <c r="BI28" s="11">
-        <v>600519</v>
+        <v>600524</v>
       </c>
       <c r="BJ28" s="12">
         <f t="shared" si="23"/>
-        <v>0.96510155343488147</v>
+        <v>0.96510958899706545</v>
       </c>
       <c r="BK28" s="24"/>
       <c r="BL28" s="24"/>
@@ -5549,7 +5549,7 @@
         <f t="shared" si="14"/>
         <v>23998</v>
       </c>
-      <c r="AO29" s="20">
+      <c r="AO29" s="11">
         <v>110929</v>
       </c>
       <c r="AP29" s="12">
@@ -5642,14 +5642,14 @@
       </c>
       <c r="E30" s="10">
         <f t="shared" si="0"/>
-        <v>116744</v>
+        <v>116751</v>
       </c>
       <c r="F30" s="20">
-        <v>143228</v>
+        <v>143235</v>
       </c>
       <c r="G30" s="12">
         <f t="shared" si="1"/>
-        <v>0.9592209862239397</v>
+        <v>0.95926786635145367</v>
       </c>
       <c r="H30" s="15">
         <v>149659</v>
@@ -5659,14 +5659,14 @@
       </c>
       <c r="J30" s="10">
         <f t="shared" si="2"/>
-        <v>116055</v>
+        <v>116062</v>
       </c>
       <c r="K30" s="20">
-        <v>143984</v>
+        <v>143991</v>
       </c>
       <c r="L30" s="12">
         <f t="shared" si="3"/>
-        <v>0.96208046291903593</v>
+        <v>0.96212723591631644</v>
       </c>
       <c r="M30" s="16">
         <v>249952</v>
@@ -5676,14 +5676,14 @@
       </c>
       <c r="O30" s="10">
         <f t="shared" si="4"/>
-        <v>99031</v>
+        <v>99038</v>
       </c>
       <c r="P30" s="13">
-        <v>241538</v>
+        <v>241545</v>
       </c>
       <c r="Q30" s="12">
         <f t="shared" si="5"/>
-        <v>0.96633753680706691</v>
+        <v>0.96636554218409931</v>
       </c>
       <c r="R30" s="16">
         <v>151431</v>
@@ -5693,14 +5693,14 @@
       </c>
       <c r="T30" s="10">
         <f t="shared" si="6"/>
-        <v>43780</v>
+        <v>43787</v>
       </c>
       <c r="U30" s="20">
-        <v>143275</v>
+        <v>143282</v>
       </c>
       <c r="V30" s="12">
         <f t="shared" si="7"/>
-        <v>0.94614048642616111</v>
+        <v>0.94618671209990024</v>
       </c>
       <c r="W30" s="16">
         <v>154416</v>
@@ -5710,14 +5710,14 @@
       </c>
       <c r="Y30" s="10">
         <f t="shared" si="8"/>
-        <v>43100</v>
+        <v>43107</v>
       </c>
       <c r="Z30" s="20">
-        <v>146800</v>
+        <v>146807</v>
       </c>
       <c r="AA30" s="12">
         <f t="shared" si="9"/>
-        <v>0.9506786861465133</v>
+        <v>0.95072401823645214</v>
       </c>
       <c r="AB30" s="17">
         <v>259264</v>
@@ -5727,14 +5727,14 @@
       </c>
       <c r="AD30" s="10">
         <f t="shared" si="10"/>
-        <v>60267</v>
+        <v>60274</v>
       </c>
       <c r="AE30" s="11">
-        <v>248434</v>
+        <v>248441</v>
       </c>
       <c r="AF30" s="12">
         <f t="shared" si="11"/>
-        <v>0.95822790668970625</v>
+        <v>0.95825490619600096</v>
       </c>
       <c r="AG30" s="16">
         <v>153178</v>
@@ -5744,14 +5744,14 @@
       </c>
       <c r="AI30" s="10">
         <f t="shared" si="12"/>
-        <v>35787</v>
+        <v>35794</v>
       </c>
       <c r="AJ30" s="20">
-        <v>144591</v>
+        <v>144598</v>
       </c>
       <c r="AK30" s="12">
         <f t="shared" si="13"/>
-        <v>0.94394103591899625</v>
+        <v>0.94398673438744463</v>
       </c>
       <c r="AL30" s="18">
         <v>156106</v>
@@ -5761,14 +5761,14 @@
       </c>
       <c r="AN30" s="10">
         <f t="shared" si="14"/>
-        <v>37167</v>
-      </c>
-      <c r="AO30" s="20">
-        <v>147863</v>
+        <v>37174</v>
+      </c>
+      <c r="AO30" s="11">
+        <v>147870</v>
       </c>
       <c r="AP30" s="12">
         <f t="shared" si="15"/>
-        <v>0.94719613595889973</v>
+        <v>0.9472409772846655</v>
       </c>
       <c r="AQ30" s="11">
         <v>266513</v>
@@ -5778,14 +5778,14 @@
       </c>
       <c r="AS30" s="10">
         <f t="shared" si="16"/>
-        <v>56613</v>
+        <v>56621</v>
       </c>
       <c r="AT30" s="13">
-        <v>254733</v>
+        <v>254741</v>
       </c>
       <c r="AU30" s="12">
         <f t="shared" si="17"/>
-        <v>0.95579952947886215</v>
+        <v>0.95582954677632981</v>
       </c>
       <c r="AV30" s="18">
         <v>155103</v>
@@ -5795,14 +5795,14 @@
       </c>
       <c r="AX30" s="10">
         <f t="shared" si="18"/>
-        <v>39197</v>
+        <v>39203</v>
       </c>
       <c r="AY30" s="20">
-        <v>148214</v>
+        <v>148220</v>
       </c>
       <c r="AZ30" s="12">
         <f t="shared" si="19"/>
-        <v>0.95558435362307625</v>
+        <v>0.95562303759437273</v>
       </c>
       <c r="BA30" s="18">
         <v>156855</v>
@@ -5812,14 +5812,14 @@
       </c>
       <c r="BC30" s="10">
         <f t="shared" si="20"/>
-        <v>41858</v>
+        <v>41864</v>
       </c>
       <c r="BD30" s="20">
-        <v>150788</v>
+        <v>150794</v>
       </c>
       <c r="BE30" s="12">
         <f t="shared" si="21"/>
-        <v>0.96132096522265786</v>
+        <v>0.96135921711134487</v>
       </c>
       <c r="BF30" s="18">
         <v>270589</v>
@@ -5829,14 +5829,14 @@
       </c>
       <c r="BH30" s="10">
         <f t="shared" si="22"/>
-        <v>73582</v>
+        <v>73590</v>
       </c>
       <c r="BI30" s="11">
-        <v>259797</v>
+        <v>259805</v>
       </c>
       <c r="BJ30" s="12">
         <f t="shared" si="23"/>
-        <v>0.96011663445298956</v>
+        <v>0.96014619958682723</v>
       </c>
       <c r="BK30" s="24"/>
       <c r="BL30" s="24"/>
@@ -5856,14 +5856,14 @@
       </c>
       <c r="E31" s="10">
         <f t="shared" si="0"/>
-        <v>57271</v>
+        <v>57273</v>
       </c>
       <c r="F31" s="20">
-        <v>69164</v>
+        <v>69166</v>
       </c>
       <c r="G31" s="12">
         <f t="shared" si="1"/>
-        <v>0.96279076242047967</v>
+        <v>0.96281860322674939</v>
       </c>
       <c r="H31" s="15">
         <v>72505</v>
@@ -5873,14 +5873,14 @@
       </c>
       <c r="J31" s="10">
         <f t="shared" si="2"/>
-        <v>52859</v>
+        <v>52860</v>
       </c>
       <c r="K31" s="20">
-        <v>69228</v>
+        <v>69229</v>
       </c>
       <c r="L31" s="12">
         <f t="shared" si="3"/>
-        <v>0.95480311702641196</v>
+        <v>0.95481690917867734</v>
       </c>
       <c r="M31" s="16">
         <v>118891</v>
@@ -5890,14 +5890,14 @@
       </c>
       <c r="O31" s="10">
         <f t="shared" si="4"/>
-        <v>51370</v>
+        <v>51371</v>
       </c>
       <c r="P31" s="13">
-        <v>115369</v>
+        <v>115370</v>
       </c>
       <c r="Q31" s="12">
         <f t="shared" si="5"/>
-        <v>0.97037622696419412</v>
+        <v>0.97038463802979202</v>
       </c>
       <c r="R31" s="16">
         <v>72813</v>
@@ -5907,14 +5907,14 @@
       </c>
       <c r="T31" s="10">
         <f t="shared" si="6"/>
-        <v>26572</v>
+        <v>26573</v>
       </c>
       <c r="U31" s="20">
-        <v>69425</v>
+        <v>69426</v>
       </c>
       <c r="V31" s="12">
         <f t="shared" si="7"/>
-        <v>0.95346984741735674</v>
+        <v>0.95348358122862675</v>
       </c>
       <c r="W31" s="16">
         <v>74776</v>
@@ -5924,14 +5924,14 @@
       </c>
       <c r="Y31" s="10">
         <f t="shared" si="8"/>
-        <v>26360</v>
+        <v>26361</v>
       </c>
       <c r="Z31" s="20">
-        <v>71217</v>
+        <v>71218</v>
       </c>
       <c r="AA31" s="12">
         <f t="shared" si="9"/>
-        <v>0.95240451481758848</v>
+        <v>0.9524178880924361</v>
       </c>
       <c r="AB31" s="17">
         <v>124489</v>
@@ -5941,14 +5941,14 @@
       </c>
       <c r="AD31" s="10">
         <f t="shared" si="10"/>
-        <v>35713</v>
+        <v>35714</v>
       </c>
       <c r="AE31" s="11">
-        <v>119898</v>
+        <v>119899</v>
       </c>
       <c r="AF31" s="12">
         <f t="shared" si="11"/>
-        <v>0.96312123962759766</v>
+        <v>0.96312927246584035</v>
       </c>
       <c r="AG31" s="16">
         <v>73552</v>
@@ -5958,14 +5958,14 @@
       </c>
       <c r="AI31" s="10">
         <f t="shared" si="12"/>
-        <v>22347</v>
+        <v>22348</v>
       </c>
       <c r="AJ31" s="20">
-        <v>69289</v>
+        <v>69290</v>
       </c>
       <c r="AK31" s="12">
         <f t="shared" si="13"/>
-        <v>0.94204100500326304</v>
+        <v>0.94205460082662607</v>
       </c>
       <c r="AL31" s="18">
         <v>74464</v>
@@ -5975,14 +5975,14 @@
       </c>
       <c r="AN31" s="10">
         <f t="shared" si="14"/>
-        <v>23177</v>
-      </c>
-      <c r="AO31" s="20">
-        <v>70274</v>
+        <v>23178</v>
+      </c>
+      <c r="AO31" s="11">
+        <v>70275</v>
       </c>
       <c r="AP31" s="12">
         <f t="shared" si="15"/>
-        <v>0.94373119896862911</v>
+        <v>0.94374462827675121</v>
       </c>
       <c r="AQ31" s="11">
         <v>126646</v>
@@ -5992,14 +5992,14 @@
       </c>
       <c r="AS31" s="10">
         <f t="shared" si="16"/>
-        <v>34478</v>
+        <v>34479</v>
       </c>
       <c r="AT31" s="13">
-        <v>122367</v>
+        <v>122368</v>
       </c>
       <c r="AU31" s="12">
         <f t="shared" si="17"/>
-        <v>0.96621290842190044</v>
+        <v>0.96622080444704139</v>
       </c>
       <c r="AV31" s="18">
         <v>72827</v>
@@ -6009,14 +6009,14 @@
       </c>
       <c r="AX31" s="10">
         <f t="shared" si="18"/>
-        <v>22805</v>
+        <v>22807</v>
       </c>
       <c r="AY31" s="20">
-        <v>69839</v>
+        <v>69841</v>
       </c>
       <c r="AZ31" s="12">
         <f t="shared" si="19"/>
-        <v>0.95897126065882154</v>
+        <v>0.9589987230010848</v>
       </c>
       <c r="BA31" s="18">
         <v>73978</v>
@@ -6026,14 +6026,14 @@
       </c>
       <c r="BC31" s="10">
         <f t="shared" si="20"/>
-        <v>25488</v>
+        <v>25490</v>
       </c>
       <c r="BD31" s="20">
-        <v>71781</v>
+        <v>71783</v>
       </c>
       <c r="BE31" s="12">
         <f t="shared" si="21"/>
-        <v>0.9703019816702263</v>
+        <v>0.97032901673470495</v>
       </c>
       <c r="BF31" s="18">
         <v>129555</v>
@@ -6043,14 +6043,14 @@
       </c>
       <c r="BH31" s="10">
         <f t="shared" si="22"/>
-        <v>48854</v>
+        <v>48856</v>
       </c>
       <c r="BI31" s="11">
-        <v>125615</v>
+        <v>125617</v>
       </c>
       <c r="BJ31" s="12">
         <f t="shared" si="23"/>
-        <v>0.96958820578132843</v>
+        <v>0.96960364324032267</v>
       </c>
       <c r="BK31" s="24"/>
       <c r="BL31" s="24"/>
@@ -6087,14 +6087,14 @@
       </c>
       <c r="J32" s="10">
         <f t="shared" si="2"/>
-        <v>138217</v>
+        <v>138218</v>
       </c>
       <c r="K32" s="20">
-        <v>183854</v>
+        <v>183855</v>
       </c>
       <c r="L32" s="12">
         <f t="shared" si="3"/>
-        <v>0.98639941198246672</v>
+        <v>0.9864047771059451</v>
       </c>
       <c r="M32" s="16">
         <v>382231</v>
@@ -6172,14 +6172,14 @@
       </c>
       <c r="AI32" s="10">
         <f t="shared" si="12"/>
-        <v>45244</v>
+        <v>45246</v>
       </c>
       <c r="AJ32" s="20">
-        <v>180782</v>
+        <v>180784</v>
       </c>
       <c r="AK32" s="12">
         <f t="shared" si="13"/>
-        <v>0.98708687556989738</v>
+        <v>0.98709779575969026</v>
       </c>
       <c r="AL32" s="18">
         <v>187303</v>
@@ -6189,14 +6189,14 @@
       </c>
       <c r="AN32" s="10">
         <f t="shared" si="14"/>
-        <v>45270</v>
-      </c>
-      <c r="AO32" s="20">
-        <v>184496</v>
+        <v>45271</v>
+      </c>
+      <c r="AO32" s="11">
+        <v>184497</v>
       </c>
       <c r="AP32" s="12">
         <f t="shared" si="15"/>
-        <v>0.98501358760938162</v>
+        <v>0.98501892655216416</v>
       </c>
       <c r="AQ32" s="11">
         <v>402574</v>
@@ -6206,14 +6206,14 @@
       </c>
       <c r="AS32" s="10">
         <f t="shared" si="16"/>
-        <v>82533</v>
+        <v>82535</v>
       </c>
       <c r="AT32" s="13">
-        <v>396001</v>
+        <v>396003</v>
       </c>
       <c r="AU32" s="12">
         <f t="shared" si="17"/>
-        <v>0.98367256703115447</v>
+        <v>0.98367753506187683</v>
       </c>
       <c r="AV32" s="18">
         <v>187080</v>
@@ -6223,14 +6223,14 @@
       </c>
       <c r="AX32" s="10">
         <f t="shared" si="18"/>
-        <v>44446</v>
+        <v>44447</v>
       </c>
       <c r="AY32" s="20">
-        <v>183818</v>
+        <v>183819</v>
       </c>
       <c r="AZ32" s="12">
         <f t="shared" si="19"/>
-        <v>0.98256360915116525</v>
+        <v>0.98256895445798587</v>
       </c>
       <c r="BA32" s="18">
         <v>189893</v>
@@ -6240,14 +6240,14 @@
       </c>
       <c r="BC32" s="10">
         <f t="shared" si="20"/>
-        <v>49710</v>
+        <v>49711</v>
       </c>
       <c r="BD32" s="20">
-        <v>188434</v>
+        <v>188435</v>
       </c>
       <c r="BE32" s="12">
         <f t="shared" si="21"/>
-        <v>0.99231672573501917</v>
+        <v>0.99232199185857295</v>
       </c>
       <c r="BF32" s="18">
         <v>410654</v>
@@ -6257,14 +6257,14 @@
       </c>
       <c r="BH32" s="10">
         <f t="shared" si="22"/>
-        <v>124577</v>
+        <v>124579</v>
       </c>
       <c r="BI32" s="11">
-        <v>404234</v>
+        <v>404236</v>
       </c>
       <c r="BJ32" s="12">
         <f t="shared" si="23"/>
-        <v>0.98436640091171645</v>
+        <v>0.98437127119180623</v>
       </c>
       <c r="BK32" s="24"/>
       <c r="BL32" s="24"/>
@@ -6284,14 +6284,14 @@
       </c>
       <c r="E33" s="10">
         <f t="shared" si="0"/>
-        <v>412434</v>
+        <v>412435</v>
       </c>
       <c r="F33" s="20">
-        <v>538749</v>
+        <v>538750</v>
       </c>
       <c r="G33" s="12">
         <f t="shared" si="1"/>
-        <v>0.97155918632330662</v>
+        <v>0.97156098968477245</v>
       </c>
       <c r="H33" s="15">
         <v>558618</v>
@@ -6301,14 +6301,14 @@
       </c>
       <c r="J33" s="10">
         <f t="shared" si="2"/>
-        <v>390447</v>
+        <v>390448</v>
       </c>
       <c r="K33" s="20">
-        <v>543647</v>
+        <v>543648</v>
       </c>
       <c r="L33" s="12">
         <f t="shared" si="3"/>
-        <v>0.973199932691034</v>
+        <v>0.9732017228231099</v>
       </c>
       <c r="M33" s="16">
         <v>943614</v>
@@ -6318,14 +6318,14 @@
       </c>
       <c r="O33" s="10">
         <f t="shared" si="4"/>
-        <v>222018</v>
+        <v>222023</v>
       </c>
       <c r="P33" s="13">
-        <v>930037</v>
+        <v>930042</v>
       </c>
       <c r="Q33" s="12">
         <f t="shared" si="5"/>
-        <v>0.98561170139484999</v>
+        <v>0.98561700017168041</v>
       </c>
       <c r="R33" s="16">
         <v>563773</v>
@@ -6335,14 +6335,14 @@
       </c>
       <c r="T33" s="10">
         <f t="shared" si="6"/>
-        <v>103842</v>
+        <v>103843</v>
       </c>
       <c r="U33" s="20">
-        <v>552422</v>
+        <v>552423</v>
       </c>
       <c r="V33" s="12">
         <f t="shared" si="7"/>
-        <v>0.97986600990114814</v>
+        <v>0.97986778366470195</v>
       </c>
       <c r="W33" s="16">
         <v>571583</v>
@@ -6352,14 +6352,14 @@
       </c>
       <c r="Y33" s="10">
         <f t="shared" si="8"/>
-        <v>110952</v>
+        <v>110954</v>
       </c>
       <c r="Z33" s="20">
-        <v>558696</v>
+        <v>558698</v>
       </c>
       <c r="AA33" s="12">
         <f t="shared" si="9"/>
-        <v>0.97745384309890249</v>
+        <v>0.97745734215328306</v>
       </c>
       <c r="AB33" s="17">
         <v>961057</v>
@@ -6369,14 +6369,14 @@
       </c>
       <c r="AD33" s="10">
         <f t="shared" si="10"/>
-        <v>149475</v>
+        <v>149479</v>
       </c>
       <c r="AE33" s="11">
-        <v>945164</v>
+        <v>945168</v>
       </c>
       <c r="AF33" s="12">
         <f t="shared" si="11"/>
-        <v>0.98346299959315631</v>
+        <v>0.98346716167719506</v>
       </c>
       <c r="AG33" s="16">
         <v>565645</v>
@@ -6386,14 +6386,14 @@
       </c>
       <c r="AI33" s="10">
         <f t="shared" si="12"/>
-        <v>97879</v>
+        <v>97880</v>
       </c>
       <c r="AJ33" s="20">
-        <v>554659</v>
+        <v>554660</v>
       </c>
       <c r="AK33" s="12">
         <f t="shared" si="13"/>
-        <v>0.98057792431648827</v>
+        <v>0.98057969220977825</v>
       </c>
       <c r="AL33" s="18">
         <v>569536</v>
@@ -6403,14 +6403,14 @@
       </c>
       <c r="AN33" s="10">
         <f t="shared" si="14"/>
-        <v>93728</v>
-      </c>
-      <c r="AO33" s="20">
-        <v>559623</v>
+        <v>93729</v>
+      </c>
+      <c r="AO33" s="11">
+        <v>559624</v>
       </c>
       <c r="AP33" s="12">
         <f t="shared" si="15"/>
-        <v>0.9825946033262164</v>
+        <v>0.98259635914147658</v>
       </c>
       <c r="AQ33" s="11">
         <v>971221</v>
@@ -6420,14 +6420,14 @@
       </c>
       <c r="AS33" s="10">
         <f t="shared" si="16"/>
-        <v>154791</v>
+        <v>154795</v>
       </c>
       <c r="AT33" s="13">
-        <v>956291</v>
+        <v>956295</v>
       </c>
       <c r="AU33" s="12">
         <f t="shared" si="17"/>
-        <v>0.98462759763225882</v>
+        <v>0.98463171615934997</v>
       </c>
       <c r="AV33" s="18">
         <v>571074</v>
@@ -6437,14 +6437,14 @@
       </c>
       <c r="AX33" s="10">
         <f t="shared" si="18"/>
-        <v>92995</v>
+        <v>92999</v>
       </c>
       <c r="AY33" s="20">
-        <v>564188</v>
+        <v>564192</v>
       </c>
       <c r="AZ33" s="12">
         <f t="shared" si="19"/>
-        <v>0.98794201802218273</v>
+        <v>0.98794902236837956</v>
       </c>
       <c r="BA33" s="18">
         <v>575700</v>
@@ -6454,14 +6454,14 @@
       </c>
       <c r="BC33" s="10">
         <f t="shared" si="20"/>
-        <v>96946</v>
+        <v>96947</v>
       </c>
       <c r="BD33" s="20">
-        <v>573852</v>
+        <v>573853</v>
       </c>
       <c r="BE33" s="12">
         <f t="shared" si="21"/>
-        <v>0.99678999478895258</v>
+        <v>0.99679173180475944</v>
       </c>
       <c r="BF33" s="18">
         <v>986775</v>
@@ -6471,14 +6471,14 @@
       </c>
       <c r="BH33" s="10">
         <f t="shared" si="22"/>
-        <v>171028</v>
+        <v>171034</v>
       </c>
       <c r="BI33" s="11">
-        <v>975792</v>
+        <v>975798</v>
       </c>
       <c r="BJ33" s="12">
         <f t="shared" si="23"/>
-        <v>0.98886980314661399</v>
+        <v>0.98887588356008205</v>
       </c>
       <c r="BK33" s="24"/>
       <c r="BL33" s="24"/>
@@ -6604,7 +6604,7 @@
       <c r="AN34" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="AO34" s="15">
+      <c r="AO34" s="11">
         <v>0</v>
       </c>
       <c r="AP34" s="15" t="s">
@@ -6809,7 +6809,7 @@
         <f t="shared" si="14"/>
         <v>2669</v>
       </c>
-      <c r="AO35" s="20">
+      <c r="AO35" s="11">
         <v>10851</v>
       </c>
       <c r="AP35" s="12">
@@ -6902,14 +6902,14 @@
       </c>
       <c r="E36" s="10">
         <f t="shared" si="0"/>
-        <v>551038</v>
+        <v>551050</v>
       </c>
       <c r="F36" s="20">
-        <v>726045</v>
+        <v>726057</v>
       </c>
       <c r="G36" s="12">
         <f t="shared" si="1"/>
-        <v>0.97113396270327679</v>
+        <v>0.97115001350942853</v>
       </c>
       <c r="H36" s="15">
         <v>754952</v>
@@ -6919,14 +6919,14 @@
       </c>
       <c r="J36" s="10">
         <f t="shared" si="2"/>
-        <v>545523</v>
+        <v>545534</v>
       </c>
       <c r="K36" s="20">
-        <v>731873</v>
+        <v>731884</v>
       </c>
       <c r="L36" s="12">
         <f t="shared" si="3"/>
-        <v>0.96942984454640824</v>
+        <v>0.96944441500916612</v>
       </c>
       <c r="M36" s="16">
         <v>1378095</v>
@@ -6936,14 +6936,14 @@
       </c>
       <c r="O36" s="10">
         <f t="shared" si="4"/>
-        <v>493424</v>
+        <v>493436</v>
       </c>
       <c r="P36" s="13">
-        <v>1346535</v>
+        <v>1346547</v>
       </c>
       <c r="Q36" s="12">
         <f t="shared" si="5"/>
-        <v>0.97709882119882885</v>
+        <v>0.97710752887137675</v>
       </c>
       <c r="R36" s="16">
         <v>758000</v>
@@ -6953,14 +6953,14 @@
       </c>
       <c r="T36" s="10">
         <f t="shared" si="6"/>
-        <v>231285</v>
+        <v>231296</v>
       </c>
       <c r="U36" s="20">
-        <v>732457</v>
+        <v>732468</v>
       </c>
       <c r="V36" s="12">
         <f t="shared" si="7"/>
-        <v>0.96630211081794193</v>
+        <v>0.96631662269129293</v>
       </c>
       <c r="W36" s="16">
         <v>766789</v>
@@ -6970,14 +6970,14 @@
       </c>
       <c r="Y36" s="10">
         <f t="shared" si="8"/>
-        <v>245525</v>
+        <v>245536</v>
       </c>
       <c r="Z36" s="20">
-        <v>748523</v>
+        <v>748534</v>
       </c>
       <c r="AA36" s="12">
         <f t="shared" si="9"/>
-        <v>0.97617858367816956</v>
+        <v>0.97619292921520784</v>
       </c>
       <c r="AB36" s="17">
         <v>1410553</v>
@@ -6987,14 +6987,14 @@
       </c>
       <c r="AD36" s="10">
         <f t="shared" si="10"/>
-        <v>344773</v>
+        <v>344786</v>
       </c>
       <c r="AE36" s="11">
-        <v>1378450</v>
+        <v>1378463</v>
       </c>
       <c r="AF36" s="12">
         <f t="shared" si="11"/>
-        <v>0.97724084100349295</v>
+        <v>0.97725005724705138</v>
       </c>
       <c r="AG36" s="16">
         <v>767229</v>
@@ -7004,14 +7004,14 @@
       </c>
       <c r="AI36" s="10">
         <f t="shared" si="12"/>
-        <v>202686</v>
+        <v>202696</v>
       </c>
       <c r="AJ36" s="20">
-        <v>744504</v>
+        <v>744514</v>
       </c>
       <c r="AK36" s="12">
         <f t="shared" si="13"/>
-        <v>0.97038042096948895</v>
+        <v>0.97039345488765416</v>
       </c>
       <c r="AL36" s="18">
         <v>779513</v>
@@ -7021,14 +7021,14 @@
       </c>
       <c r="AN36" s="10">
         <f t="shared" si="14"/>
-        <v>205093</v>
-      </c>
-      <c r="AO36" s="20">
-        <v>755691</v>
+        <v>205103</v>
+      </c>
+      <c r="AO36" s="11">
+        <v>755701</v>
       </c>
       <c r="AP36" s="12">
         <f t="shared" si="15"/>
-        <v>0.96943989388246254</v>
+        <v>0.96945272240488611</v>
       </c>
       <c r="AQ36" s="11">
         <v>1443943</v>
@@ -7038,14 +7038,14 @@
       </c>
       <c r="AS36" s="10">
         <f t="shared" si="16"/>
-        <v>324121</v>
+        <v>324132</v>
       </c>
       <c r="AT36" s="13">
-        <v>1402867</v>
+        <v>1402878</v>
       </c>
       <c r="AU36" s="12">
         <f t="shared" si="17"/>
-        <v>0.97155289370840814</v>
+        <v>0.97156051173765168</v>
       </c>
       <c r="AV36" s="18">
         <v>783108</v>
@@ -7055,14 +7055,14 @@
       </c>
       <c r="AX36" s="10">
         <f t="shared" si="18"/>
-        <v>207930</v>
+        <v>207941</v>
       </c>
       <c r="AY36" s="20">
-        <v>758527</v>
+        <v>758538</v>
       </c>
       <c r="AZ36" s="12">
         <f t="shared" si="19"/>
-        <v>0.96861097064517288</v>
+        <v>0.96862501723900152</v>
       </c>
       <c r="BA36" s="18">
         <v>793830</v>
@@ -7072,14 +7072,14 @@
       </c>
       <c r="BC36" s="10">
         <f t="shared" si="20"/>
-        <v>206306</v>
+        <v>206317</v>
       </c>
       <c r="BD36" s="20">
-        <v>772169</v>
+        <v>772180</v>
       </c>
       <c r="BE36" s="12">
         <f t="shared" si="21"/>
-        <v>0.9727133013365582</v>
+        <v>0.97272715820767675</v>
       </c>
       <c r="BF36" s="18">
         <v>1468416</v>
@@ -7089,14 +7089,14 @@
       </c>
       <c r="BH36" s="10">
         <f t="shared" si="24"/>
-        <v>383719</v>
+        <v>383735</v>
       </c>
       <c r="BI36" s="11">
-        <v>1426385</v>
+        <v>1426401</v>
       </c>
       <c r="BJ36" s="12">
         <f t="shared" si="25"/>
-        <v>0.97137663986227341</v>
+        <v>0.97138753595711302</v>
       </c>
       <c r="BK36" s="24"/>
       <c r="BL36" s="24"/>
@@ -7116,14 +7116,14 @@
       </c>
       <c r="E37" s="10">
         <f t="shared" si="0"/>
-        <v>478350</v>
+        <v>478356</v>
       </c>
       <c r="F37" s="20">
-        <v>566433</v>
+        <v>566439</v>
       </c>
       <c r="G37" s="12">
         <f t="shared" si="1"/>
-        <v>0.95613900343845637</v>
+        <v>0.95614913143950964</v>
       </c>
       <c r="H37" s="15">
         <v>593173</v>
@@ -7133,14 +7133,14 @@
       </c>
       <c r="J37" s="10">
         <f t="shared" si="2"/>
-        <v>459855</v>
+        <v>459860</v>
       </c>
       <c r="K37" s="20">
-        <v>566656</v>
+        <v>566661</v>
       </c>
       <c r="L37" s="12">
         <f t="shared" si="3"/>
-        <v>0.95529634693419962</v>
+        <v>0.95530477617828191</v>
       </c>
       <c r="M37" s="16">
         <v>768378</v>
@@ -7150,14 +7150,14 @@
       </c>
       <c r="O37" s="10">
         <f t="shared" si="4"/>
-        <v>267453</v>
+        <v>267458</v>
       </c>
       <c r="P37" s="13">
-        <v>738196</v>
+        <v>738201</v>
       </c>
       <c r="Q37" s="12">
         <f t="shared" si="5"/>
-        <v>0.9607198540301779</v>
+        <v>0.96072636124407518</v>
       </c>
       <c r="R37" s="16">
         <v>601605</v>
@@ -7167,14 +7167,14 @@
       </c>
       <c r="T37" s="10">
         <f t="shared" si="6"/>
-        <v>144747</v>
+        <v>144752</v>
       </c>
       <c r="U37" s="20">
-        <v>573933</v>
+        <v>573938</v>
       </c>
       <c r="V37" s="12">
         <f t="shared" si="7"/>
-        <v>0.95400304186301643</v>
+        <v>0.95401135296415418</v>
       </c>
       <c r="W37" s="16">
         <v>609453</v>
@@ -7184,14 +7184,14 @@
       </c>
       <c r="Y37" s="10">
         <f t="shared" si="8"/>
-        <v>142430</v>
+        <v>142435</v>
       </c>
       <c r="Z37" s="20">
-        <v>583166</v>
+        <v>583171</v>
       </c>
       <c r="AA37" s="12">
         <f t="shared" si="9"/>
-        <v>0.95686787988573363</v>
+        <v>0.95687608396381674</v>
       </c>
       <c r="AB37" s="17">
         <v>790568</v>
@@ -7201,14 +7201,14 @@
       </c>
       <c r="AD37" s="10">
         <f t="shared" si="10"/>
-        <v>172680</v>
+        <v>172687</v>
       </c>
       <c r="AE37" s="11">
-        <v>759612</v>
+        <v>759619</v>
       </c>
       <c r="AF37" s="12">
         <f t="shared" si="11"/>
-        <v>0.96084334301413665</v>
+        <v>0.96085219740743366</v>
       </c>
       <c r="AG37" s="16">
         <v>617773</v>
@@ -7218,14 +7218,14 @@
       </c>
       <c r="AI37" s="10">
         <f t="shared" si="12"/>
-        <v>117959</v>
+        <v>117963</v>
       </c>
       <c r="AJ37" s="20">
-        <v>589761</v>
+        <v>589765</v>
       </c>
       <c r="AK37" s="12">
         <f t="shared" si="13"/>
-        <v>0.95465648385410173</v>
+        <v>0.95466295872432105</v>
       </c>
       <c r="AL37" s="18">
         <v>624724</v>
@@ -7235,14 +7235,14 @@
       </c>
       <c r="AN37" s="10">
         <f t="shared" si="14"/>
-        <v>122514</v>
-      </c>
-      <c r="AO37" s="20">
-        <v>596603</v>
+        <v>122518</v>
+      </c>
+      <c r="AO37" s="11">
+        <v>596607</v>
       </c>
       <c r="AP37" s="12">
         <f t="shared" si="15"/>
-        <v>0.9549865220481365</v>
+        <v>0.95499292487562504</v>
       </c>
       <c r="AQ37" s="11">
         <v>810789</v>
@@ -7252,14 +7252,14 @@
       </c>
       <c r="AS37" s="10">
         <f t="shared" si="16"/>
-        <v>156896</v>
+        <v>156902</v>
       </c>
       <c r="AT37" s="13">
-        <v>777504</v>
+        <v>777510</v>
       </c>
       <c r="AU37" s="12">
         <f t="shared" si="17"/>
-        <v>0.95894739568494392</v>
+        <v>0.95895479588400923</v>
       </c>
       <c r="AV37" s="18">
         <v>633338</v>
@@ -7269,14 +7269,14 @@
       </c>
       <c r="AX37" s="10">
         <f t="shared" si="18"/>
-        <v>130832</v>
+        <v>130837</v>
       </c>
       <c r="AY37" s="20">
-        <v>605818</v>
+        <v>605823</v>
       </c>
       <c r="AZ37" s="12">
         <f t="shared" si="19"/>
-        <v>0.95654768859597872</v>
+        <v>0.95655558327464951</v>
       </c>
       <c r="BA37" s="18">
         <v>640933</v>
@@ -7286,14 +7286,14 @@
       </c>
       <c r="BC37" s="10">
         <f t="shared" si="20"/>
-        <v>131355</v>
+        <v>131362</v>
       </c>
       <c r="BD37" s="20">
-        <v>615032</v>
+        <v>615039</v>
       </c>
       <c r="BE37" s="12">
         <f t="shared" si="21"/>
-        <v>0.95958859974443511</v>
+        <v>0.95959952132282156</v>
       </c>
       <c r="BF37" s="18">
         <v>830528</v>
@@ -7303,14 +7303,14 @@
       </c>
       <c r="BH37" s="10">
         <f t="shared" si="24"/>
-        <v>185589</v>
+        <v>185600</v>
       </c>
       <c r="BI37" s="11">
-        <v>797097</v>
+        <v>797108</v>
       </c>
       <c r="BJ37" s="12">
         <f t="shared" si="25"/>
-        <v>0.95974729328812514</v>
+        <v>0.95976053787470139</v>
       </c>
       <c r="BK37" s="24"/>
       <c r="BL37" s="24"/>
@@ -7330,14 +7330,14 @@
       </c>
       <c r="E38" s="10">
         <f t="shared" si="0"/>
-        <v>16656</v>
+        <v>16657</v>
       </c>
       <c r="F38" s="20">
-        <v>20400</v>
+        <v>20401</v>
       </c>
       <c r="G38" s="12">
         <f t="shared" si="1"/>
-        <v>0.84047462096242587</v>
+        <v>0.84051582069874753</v>
       </c>
       <c r="H38" s="15">
         <v>24257</v>
@@ -7415,14 +7415,14 @@
       </c>
       <c r="AD38" s="10">
         <f t="shared" si="10"/>
-        <v>9145</v>
+        <v>9146</v>
       </c>
       <c r="AE38" s="11">
-        <v>32050</v>
+        <v>32051</v>
       </c>
       <c r="AF38" s="12">
         <f t="shared" si="11"/>
-        <v>0.88983286134710426</v>
+        <v>0.88986062524293408</v>
       </c>
       <c r="AG38" s="16">
         <v>24216</v>
@@ -7432,14 +7432,14 @@
       </c>
       <c r="AI38" s="10">
         <f t="shared" si="12"/>
-        <v>6186</v>
+        <v>6187</v>
       </c>
       <c r="AJ38" s="20">
-        <v>20368</v>
+        <v>20369</v>
       </c>
       <c r="AK38" s="12">
         <f t="shared" si="13"/>
-        <v>0.8410967955071027</v>
+        <v>0.84113809051866539</v>
       </c>
       <c r="AL38" s="18">
         <v>24425</v>
@@ -7449,14 +7449,14 @@
       </c>
       <c r="AN38" s="10">
         <f t="shared" si="14"/>
-        <v>6443</v>
-      </c>
-      <c r="AO38" s="20">
-        <v>20655</v>
+        <v>6444</v>
+      </c>
+      <c r="AO38" s="11">
+        <v>20656</v>
       </c>
       <c r="AP38" s="12">
         <f t="shared" si="15"/>
-        <v>0.84564994882292732</v>
+        <v>0.84569089048106449</v>
       </c>
       <c r="AQ38" s="11">
         <v>36434</v>
@@ -7466,14 +7466,14 @@
       </c>
       <c r="AS38" s="10">
         <f t="shared" si="16"/>
-        <v>9138</v>
+        <v>9139</v>
       </c>
       <c r="AT38" s="13">
-        <v>32581</v>
+        <v>32582</v>
       </c>
       <c r="AU38" s="12">
         <f t="shared" si="17"/>
-        <v>0.89424713179996707</v>
+        <v>0.89427457869023441</v>
       </c>
       <c r="AV38" s="18">
         <v>24471</v>
@@ -7483,14 +7483,14 @@
       </c>
       <c r="AX38" s="10">
         <f t="shared" si="18"/>
-        <v>6585</v>
+        <v>6586</v>
       </c>
       <c r="AY38" s="20">
-        <v>20734</v>
+        <v>20735</v>
       </c>
       <c r="AZ38" s="12">
         <f t="shared" si="19"/>
-        <v>0.84728862735482813</v>
+        <v>0.8473294920518164</v>
       </c>
       <c r="BA38" s="18">
         <v>24769</v>
@@ -7500,14 +7500,14 @@
       </c>
       <c r="BC38" s="10">
         <f t="shared" si="20"/>
-        <v>6724</v>
+        <v>6725</v>
       </c>
       <c r="BD38" s="20">
-        <v>21003</v>
+        <v>21004</v>
       </c>
       <c r="BE38" s="12">
         <f t="shared" si="21"/>
-        <v>0.84795510517178729</v>
+        <v>0.84799547821874122</v>
       </c>
       <c r="BF38" s="18">
         <v>37269</v>
@@ -7517,14 +7517,14 @@
       </c>
       <c r="BH38" s="10">
         <f t="shared" si="24"/>
-        <v>10390</v>
+        <v>10391</v>
       </c>
       <c r="BI38" s="11">
-        <v>33147</v>
+        <v>33148</v>
       </c>
       <c r="BJ38" s="12">
         <f t="shared" si="25"/>
-        <v>0.8893986959671577</v>
+        <v>0.88942552791864549</v>
       </c>
       <c r="BK38" s="24"/>
       <c r="BL38" s="24"/>
@@ -7665,7 +7665,7 @@
         <f t="shared" si="14"/>
         <v>57</v>
       </c>
-      <c r="AO39" s="20">
+      <c r="AO39" s="11">
         <v>169</v>
       </c>
       <c r="AP39" s="12">
@@ -7758,14 +7758,14 @@
       </c>
       <c r="E40" s="10">
         <f t="shared" si="0"/>
-        <v>228454</v>
+        <v>228456</v>
       </c>
       <c r="F40" s="20">
-        <v>243739</v>
+        <v>243741</v>
       </c>
       <c r="G40" s="12">
         <f t="shared" si="1"/>
-        <v>0.95564059234747289</v>
+        <v>0.95564843385492426</v>
       </c>
       <c r="H40" s="15">
         <v>254802</v>
@@ -7775,14 +7775,14 @@
       </c>
       <c r="J40" s="10">
         <f t="shared" si="2"/>
-        <v>221633</v>
+        <v>221637</v>
       </c>
       <c r="K40" s="20">
-        <v>243971</v>
+        <v>243975</v>
       </c>
       <c r="L40" s="12">
         <f t="shared" si="3"/>
-        <v>0.95749248436040535</v>
+        <v>0.95750818282431061</v>
       </c>
       <c r="M40" s="16">
         <v>315837</v>
@@ -7792,14 +7792,14 @@
       </c>
       <c r="O40" s="10">
         <f t="shared" si="4"/>
-        <v>162865</v>
+        <v>162868</v>
       </c>
       <c r="P40" s="13">
-        <v>303390</v>
+        <v>303393</v>
       </c>
       <c r="Q40" s="12">
         <f t="shared" si="5"/>
-        <v>0.96059043114011344</v>
+        <v>0.9605999297105785</v>
       </c>
       <c r="R40" s="16">
         <v>257348</v>
@@ -7809,14 +7809,14 @@
       </c>
       <c r="T40" s="10">
         <f t="shared" si="6"/>
-        <v>76820</v>
+        <v>76823</v>
       </c>
       <c r="U40" s="20">
-        <v>245519</v>
+        <v>245522</v>
       </c>
       <c r="V40" s="12">
         <f t="shared" si="7"/>
-        <v>0.95403500318634693</v>
+        <v>0.95404666055302545</v>
       </c>
       <c r="W40" s="16">
         <v>259512</v>
@@ -7826,14 +7826,14 @@
       </c>
       <c r="Y40" s="10">
         <f t="shared" si="8"/>
-        <v>69278</v>
+        <v>69281</v>
       </c>
       <c r="Z40" s="20">
-        <v>247800</v>
+        <v>247803</v>
       </c>
       <c r="AA40" s="12">
         <f t="shared" si="9"/>
-        <v>0.95486913899935266</v>
+        <v>0.95488069915842044</v>
       </c>
       <c r="AB40" s="17">
         <v>322067</v>
@@ -7843,14 +7843,14 @@
       </c>
       <c r="AD40" s="10">
         <f t="shared" si="10"/>
-        <v>74962</v>
+        <v>74965</v>
       </c>
       <c r="AE40" s="11">
-        <v>309028</v>
+        <v>309031</v>
       </c>
       <c r="AF40" s="12">
         <f t="shared" si="11"/>
-        <v>0.95951463515355495</v>
+        <v>0.95952394998556201</v>
       </c>
       <c r="AG40" s="16">
         <v>262041</v>
@@ -7860,14 +7860,14 @@
       </c>
       <c r="AI40" s="10">
         <f t="shared" si="12"/>
-        <v>51910</v>
+        <v>51915</v>
       </c>
       <c r="AJ40" s="20">
-        <v>250263</v>
+        <v>250268</v>
       </c>
       <c r="AK40" s="12">
         <f t="shared" si="13"/>
-        <v>0.95505283524333984</v>
+        <v>0.95507191622684995</v>
       </c>
       <c r="AL40" s="18">
         <v>264607</v>
@@ -7877,14 +7877,14 @@
       </c>
       <c r="AN40" s="10">
         <f t="shared" si="14"/>
-        <v>57102</v>
-      </c>
-      <c r="AO40" s="20">
-        <v>252871</v>
+        <v>57106</v>
+      </c>
+      <c r="AO40" s="11">
+        <v>252875</v>
       </c>
       <c r="AP40" s="12">
         <f t="shared" si="15"/>
-        <v>0.95564743185176504</v>
+        <v>0.95566254860982514</v>
       </c>
       <c r="AQ40" s="11">
         <v>328683</v>
@@ -7894,14 +7894,14 @@
       </c>
       <c r="AS40" s="10">
         <f t="shared" si="16"/>
-        <v>67743</v>
+        <v>67746</v>
       </c>
       <c r="AT40" s="13">
-        <v>316035</v>
+        <v>316038</v>
       </c>
       <c r="AU40" s="12">
         <f t="shared" si="17"/>
-        <v>0.96151915371345642</v>
+        <v>0.96152828104891341</v>
       </c>
       <c r="AV40" s="18">
         <v>267796</v>
@@ -7911,14 +7911,14 @@
       </c>
       <c r="AX40" s="10">
         <f t="shared" si="18"/>
-        <v>56483</v>
+        <v>56487</v>
       </c>
       <c r="AY40" s="20">
-        <v>256120</v>
+        <v>256124</v>
       </c>
       <c r="AZ40" s="12">
         <f t="shared" si="19"/>
-        <v>0.95639964749286765</v>
+        <v>0.95641458423576153</v>
       </c>
       <c r="BA40" s="18">
         <v>270158</v>
@@ -7928,14 +7928,14 @@
       </c>
       <c r="BC40" s="10">
         <f t="shared" si="20"/>
-        <v>57695</v>
+        <v>57698</v>
       </c>
       <c r="BD40" s="20">
-        <v>258878</v>
+        <v>258881</v>
       </c>
       <c r="BE40" s="12">
         <f t="shared" si="21"/>
-        <v>0.9582466556607615</v>
+        <v>0.95825776027361764</v>
       </c>
       <c r="BF40" s="18">
         <v>335514</v>
@@ -7945,14 +7945,14 @@
       </c>
       <c r="BH40" s="10">
         <f t="shared" si="24"/>
-        <v>84602</v>
+        <v>84607</v>
       </c>
       <c r="BI40" s="11">
-        <v>321790</v>
+        <v>321795</v>
       </c>
       <c r="BJ40" s="12">
         <f t="shared" si="25"/>
-        <v>0.95909559660699706</v>
+        <v>0.95911049911479107</v>
       </c>
       <c r="BK40" s="24"/>
       <c r="BL40" s="24"/>
@@ -7972,14 +7972,14 @@
       </c>
       <c r="E41" s="10">
         <f t="shared" si="0"/>
-        <v>641232</v>
+        <v>641249</v>
       </c>
       <c r="F41" s="20">
-        <v>777351</v>
+        <v>777368</v>
       </c>
       <c r="G41" s="12">
         <f t="shared" si="1"/>
-        <v>0.96790906510078145</v>
+        <v>0.9679302324423128</v>
       </c>
       <c r="H41" s="15">
         <v>805681</v>
@@ -7989,14 +7989,14 @@
       </c>
       <c r="J41" s="10">
         <f t="shared" si="2"/>
-        <v>648961</v>
+        <v>648972</v>
       </c>
       <c r="K41" s="20">
-        <v>778189</v>
+        <v>778200</v>
       </c>
       <c r="L41" s="12">
         <f t="shared" si="3"/>
-        <v>0.96587731372590391</v>
+        <v>0.96589096677220887</v>
       </c>
       <c r="M41" s="16">
         <v>924274</v>
@@ -8006,14 +8006,14 @@
       </c>
       <c r="O41" s="10">
         <f t="shared" si="4"/>
-        <v>314055</v>
+        <v>314069</v>
       </c>
       <c r="P41" s="13">
-        <v>890817</v>
+        <v>890831</v>
       </c>
       <c r="Q41" s="12">
         <f t="shared" si="5"/>
-        <v>0.96380185962171394</v>
+        <v>0.96381700664521563</v>
       </c>
       <c r="R41" s="16">
         <v>822173</v>
@@ -8023,14 +8023,14 @@
       </c>
       <c r="T41" s="10">
         <f t="shared" si="6"/>
-        <v>171583</v>
+        <v>171599</v>
       </c>
       <c r="U41" s="20">
-        <v>791142</v>
+        <v>791158</v>
       </c>
       <c r="V41" s="12">
         <f t="shared" si="7"/>
-        <v>0.96225733513506284</v>
+        <v>0.96227679575952996</v>
       </c>
       <c r="W41" s="16">
         <v>833879</v>
@@ -8040,14 +8040,14 @@
       </c>
       <c r="Y41" s="10">
         <f t="shared" si="8"/>
-        <v>179552</v>
+        <v>179570</v>
       </c>
       <c r="Z41" s="20">
-        <v>799891</v>
+        <v>799909</v>
       </c>
       <c r="AA41" s="12">
         <f t="shared" si="9"/>
-        <v>0.9592410889349654</v>
+        <v>0.95926267480054062</v>
       </c>
       <c r="AB41" s="17">
         <v>956956</v>
@@ -8057,14 +8057,14 @@
       </c>
       <c r="AD41" s="10">
         <f t="shared" si="10"/>
-        <v>182716</v>
+        <v>182738</v>
       </c>
       <c r="AE41" s="11">
-        <v>915443</v>
+        <v>915465</v>
       </c>
       <c r="AF41" s="12">
         <f t="shared" si="11"/>
-        <v>0.95661974009254347</v>
+        <v>0.95664272965528196</v>
       </c>
       <c r="AG41" s="16">
         <v>851169</v>
@@ -8074,14 +8074,14 @@
       </c>
       <c r="AI41" s="10">
         <f t="shared" si="12"/>
-        <v>150920</v>
+        <v>150940</v>
       </c>
       <c r="AJ41" s="20">
-        <v>811529</v>
+        <v>811549</v>
       </c>
       <c r="AK41" s="12">
         <f t="shared" si="13"/>
-        <v>0.95342875504159574</v>
+        <v>0.95345225213794205</v>
       </c>
       <c r="AL41" s="18">
         <v>859964</v>
@@ -8091,14 +8091,14 @@
       </c>
       <c r="AN41" s="10">
         <f t="shared" si="14"/>
-        <v>152814</v>
-      </c>
-      <c r="AO41" s="20">
-        <v>818530</v>
+        <v>152839</v>
+      </c>
+      <c r="AO41" s="11">
+        <v>818555</v>
       </c>
       <c r="AP41" s="12">
         <f t="shared" si="15"/>
-        <v>0.95181891334986113</v>
+        <v>0.9518479843342279</v>
       </c>
       <c r="AQ41" s="11">
         <v>982238</v>
@@ -8108,14 +8108,14 @@
       </c>
       <c r="AS41" s="10">
         <f t="shared" si="16"/>
-        <v>184909</v>
+        <v>184940</v>
       </c>
       <c r="AT41" s="13">
-        <v>934334</v>
+        <v>934365</v>
       </c>
       <c r="AU41" s="12">
         <f t="shared" si="17"/>
-        <v>0.95122974268965366</v>
+        <v>0.95126130326865788</v>
       </c>
       <c r="AV41" s="18">
         <v>867973</v>
@@ -8125,14 +8125,14 @@
       </c>
       <c r="AX41" s="10">
         <f t="shared" si="18"/>
-        <v>169770</v>
+        <v>169799</v>
       </c>
       <c r="AY41" s="20">
-        <v>827334</v>
+        <v>827363</v>
       </c>
       <c r="AZ41" s="12">
         <f t="shared" si="19"/>
-        <v>0.95317941917548121</v>
+        <v>0.95321283035301785</v>
       </c>
       <c r="BA41" s="18">
         <v>869274</v>
@@ -8142,14 +8142,14 @@
       </c>
       <c r="BC41" s="10">
         <f t="shared" si="20"/>
-        <v>154168</v>
+        <v>154198</v>
       </c>
       <c r="BD41" s="20">
-        <v>833502</v>
+        <v>833532</v>
       </c>
       <c r="BE41" s="12">
         <f t="shared" si="21"/>
-        <v>0.95884841833530055</v>
+        <v>0.95888292989322121</v>
       </c>
       <c r="BF41" s="18">
         <v>986817</v>
@@ -8159,14 +8159,14 @@
       </c>
       <c r="BH41" s="10">
         <f t="shared" si="24"/>
-        <v>196665</v>
+        <v>196709</v>
       </c>
       <c r="BI41" s="11">
-        <v>950271</v>
+        <v>950315</v>
       </c>
       <c r="BJ41" s="12">
         <f t="shared" si="25"/>
-        <v>0.96296577784938853</v>
+        <v>0.96301036565036879</v>
       </c>
       <c r="BK41" s="24"/>
       <c r="BL41" s="24"/>
@@ -8307,7 +8307,7 @@
         <f t="shared" si="14"/>
         <v>3775</v>
       </c>
-      <c r="AO42" s="20">
+      <c r="AO42" s="11">
         <v>16900</v>
       </c>
       <c r="AP42" s="12">
@@ -8339,14 +8339,14 @@
       </c>
       <c r="AX42" s="10">
         <f t="shared" si="18"/>
-        <v>3847</v>
+        <v>3848</v>
       </c>
       <c r="AY42" s="20">
-        <v>16993</v>
+        <v>16994</v>
       </c>
       <c r="AZ42" s="12">
         <f t="shared" si="19"/>
-        <v>0.954180470548599</v>
+        <v>0.95423662193273062</v>
       </c>
       <c r="BA42" s="18">
         <v>17859</v>
@@ -8356,14 +8356,14 @@
       </c>
       <c r="BC42" s="10">
         <f t="shared" si="20"/>
-        <v>3738</v>
+        <v>3739</v>
       </c>
       <c r="BD42" s="20">
-        <v>17086</v>
+        <v>17087</v>
       </c>
       <c r="BE42" s="12">
         <f t="shared" si="21"/>
-        <v>0.95671650148384568</v>
+        <v>0.95677249566045131</v>
       </c>
       <c r="BF42" s="18">
         <v>20264</v>
@@ -8521,7 +8521,7 @@
         <f t="shared" si="14"/>
         <v>1121</v>
       </c>
-      <c r="AO43" s="20">
+      <c r="AO43" s="11">
         <v>3069</v>
       </c>
       <c r="AP43" s="12">
@@ -8614,14 +8614,14 @@
       </c>
       <c r="E44" s="10">
         <f t="shared" si="0"/>
-        <v>211698</v>
+        <v>211700</v>
       </c>
       <c r="F44" s="20">
-        <v>276065</v>
+        <v>276067</v>
       </c>
       <c r="G44" s="12">
         <f t="shared" si="1"/>
-        <v>0.880401955562926</v>
+        <v>0.88040833378512406</v>
       </c>
       <c r="H44" s="15">
         <v>315037</v>
@@ -8631,14 +8631,14 @@
       </c>
       <c r="J44" s="10">
         <f t="shared" si="2"/>
-        <v>208637</v>
+        <v>208639</v>
       </c>
       <c r="K44" s="20">
-        <v>276729</v>
+        <v>276731</v>
       </c>
       <c r="L44" s="12">
         <f t="shared" si="3"/>
-        <v>0.87840158457577999</v>
+        <v>0.87840793303643694</v>
       </c>
       <c r="M44" s="16">
         <v>378050</v>
@@ -8648,14 +8648,14 @@
       </c>
       <c r="O44" s="10">
         <f t="shared" si="4"/>
-        <v>137099</v>
+        <v>137101</v>
       </c>
       <c r="P44" s="13">
-        <v>338586</v>
+        <v>338588</v>
       </c>
       <c r="Q44" s="12">
         <f t="shared" si="5"/>
-        <v>0.8956116915751885</v>
+        <v>0.8956169818807036</v>
       </c>
       <c r="R44" s="16">
         <v>322476</v>
@@ -8665,14 +8665,14 @@
       </c>
       <c r="T44" s="10">
         <f t="shared" si="6"/>
-        <v>85417</v>
+        <v>85420</v>
       </c>
       <c r="U44" s="20">
-        <v>282967</v>
+        <v>282970</v>
       </c>
       <c r="V44" s="12">
         <f t="shared" si="7"/>
-        <v>0.87748235527605156</v>
+        <v>0.87749165829395059</v>
       </c>
       <c r="W44" s="16">
         <v>327345</v>
@@ -8682,14 +8682,14 @@
       </c>
       <c r="Y44" s="10">
         <f t="shared" si="8"/>
-        <v>86936</v>
+        <v>86940</v>
       </c>
       <c r="Z44" s="20">
-        <v>286828</v>
+        <v>286832</v>
       </c>
       <c r="AA44" s="12">
         <f t="shared" si="9"/>
-        <v>0.87622538911545922</v>
+        <v>0.8762376086392033</v>
       </c>
       <c r="AB44" s="17">
         <v>393681</v>
@@ -8699,14 +8699,14 @@
       </c>
       <c r="AD44" s="10">
         <f t="shared" si="10"/>
-        <v>94080</v>
+        <v>94084</v>
       </c>
       <c r="AE44" s="11">
-        <v>349804</v>
+        <v>349808</v>
       </c>
       <c r="AF44" s="12">
         <f t="shared" si="11"/>
-        <v>0.88854681836309091</v>
+        <v>0.88855697887375817</v>
       </c>
       <c r="AG44" s="16">
         <v>333199</v>
@@ -8716,14 +8716,14 @@
       </c>
       <c r="AI44" s="10">
         <f t="shared" si="12"/>
-        <v>74153</v>
+        <v>74157</v>
       </c>
       <c r="AJ44" s="20">
-        <v>290342</v>
+        <v>290346</v>
       </c>
       <c r="AK44" s="12">
         <f t="shared" si="13"/>
-        <v>0.87137716499749396</v>
+        <v>0.87138916983544368</v>
       </c>
       <c r="AL44" s="18">
         <v>336893</v>
@@ -8733,14 +8733,14 @@
       </c>
       <c r="AN44" s="10">
         <f t="shared" si="14"/>
-        <v>77989</v>
-      </c>
-      <c r="AO44" s="20">
-        <v>294824</v>
+        <v>77993</v>
+      </c>
+      <c r="AO44" s="11">
+        <v>294828</v>
       </c>
       <c r="AP44" s="12">
         <f t="shared" si="15"/>
-        <v>0.8751265238517868</v>
+        <v>0.87513839705781959</v>
       </c>
       <c r="AQ44" s="11">
         <v>406157</v>
@@ -8750,14 +8750,14 @@
       </c>
       <c r="AS44" s="10">
         <f t="shared" si="16"/>
-        <v>90439</v>
+        <v>90443</v>
       </c>
       <c r="AT44" s="13">
-        <v>359858</v>
+        <v>359862</v>
       </c>
       <c r="AU44" s="12">
         <f t="shared" si="17"/>
-        <v>0.88600713517186702</v>
+        <v>0.88601698358024117</v>
       </c>
       <c r="AV44" s="18">
         <v>341214</v>
@@ -8767,14 +8767,14 @@
       </c>
       <c r="AX44" s="10">
         <f t="shared" si="18"/>
-        <v>79988</v>
+        <v>79992</v>
       </c>
       <c r="AY44" s="20">
-        <v>298433</v>
+        <v>298437</v>
       </c>
       <c r="AZ44" s="12">
         <f t="shared" si="19"/>
-        <v>0.87462120546050282</v>
+        <v>0.87463292830892048</v>
       </c>
       <c r="BA44" s="18">
         <v>343859</v>
@@ -8784,14 +8784,14 @@
       </c>
       <c r="BC44" s="10">
         <f t="shared" si="20"/>
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="BD44" s="20">
-        <v>302328</v>
+        <v>302332</v>
       </c>
       <c r="BE44" s="12">
         <f t="shared" si="21"/>
-        <v>0.87922084342710238</v>
+        <v>0.87923247610212329</v>
       </c>
       <c r="BF44" s="18">
         <v>410714</v>
@@ -8801,14 +8801,14 @@
       </c>
       <c r="BH44" s="10">
         <f t="shared" si="24"/>
-        <v>103147</v>
+        <v>103153</v>
       </c>
       <c r="BI44" s="11">
-        <v>367425</v>
+        <v>367431</v>
       </c>
       <c r="BJ44" s="12">
         <f t="shared" si="25"/>
-        <v>0.89460062233086768</v>
+        <v>0.8946152310366825</v>
       </c>
       <c r="BK44" s="24"/>
       <c r="BL44" s="24"/>
@@ -8828,14 +8828,14 @@
       </c>
       <c r="E45" s="10">
         <f t="shared" si="0"/>
-        <v>173665</v>
+        <v>173666</v>
       </c>
       <c r="F45" s="20">
-        <v>219405</v>
+        <v>219406</v>
       </c>
       <c r="G45" s="12">
         <f t="shared" si="1"/>
-        <v>0.92274208810850589</v>
+        <v>0.92274629376511408</v>
       </c>
       <c r="H45" s="15">
         <v>238690</v>
@@ -8845,14 +8845,14 @@
       </c>
       <c r="J45" s="10">
         <f t="shared" si="2"/>
-        <v>171219</v>
+        <v>171221</v>
       </c>
       <c r="K45" s="20">
-        <v>220013</v>
+        <v>220015</v>
       </c>
       <c r="L45" s="12">
         <f t="shared" si="3"/>
-        <v>0.92175206334576232</v>
+        <v>0.92176044241484767</v>
       </c>
       <c r="M45" s="16">
         <v>292586</v>
@@ -8862,14 +8862,14 @@
       </c>
       <c r="O45" s="10">
         <f t="shared" si="4"/>
-        <v>100443</v>
+        <v>100445</v>
       </c>
       <c r="P45" s="13">
-        <v>272781</v>
+        <v>272783</v>
       </c>
       <c r="Q45" s="12">
         <f t="shared" si="5"/>
-        <v>0.93231050016063655</v>
+        <v>0.93231733575769171</v>
       </c>
       <c r="R45" s="16">
         <v>242899</v>
@@ -8879,14 +8879,14 @@
       </c>
       <c r="T45" s="10">
         <f t="shared" si="6"/>
-        <v>58706</v>
+        <v>58708</v>
       </c>
       <c r="U45" s="20">
-        <v>223281</v>
+        <v>223283</v>
       </c>
       <c r="V45" s="12">
         <f t="shared" si="7"/>
-        <v>0.9192339202713885</v>
+        <v>0.91924215414637356</v>
       </c>
       <c r="W45" s="16">
         <v>244806</v>
@@ -8896,14 +8896,14 @@
       </c>
       <c r="Y45" s="10">
         <f t="shared" si="8"/>
-        <v>58454</v>
+        <v>58456</v>
       </c>
       <c r="Z45" s="20">
-        <v>225563</v>
+        <v>225565</v>
       </c>
       <c r="AA45" s="12">
         <f t="shared" si="9"/>
-        <v>0.92139490045178629</v>
+        <v>0.92140307018618828</v>
       </c>
       <c r="AB45" s="17">
         <v>299772</v>
@@ -8913,14 +8913,14 @@
       </c>
       <c r="AD45" s="10">
         <f t="shared" si="10"/>
-        <v>63869</v>
+        <v>63872</v>
       </c>
       <c r="AE45" s="11">
-        <v>277624</v>
+        <v>277627</v>
       </c>
       <c r="AF45" s="12">
         <f t="shared" si="11"/>
-        <v>0.92611718239195118</v>
+        <v>0.92612718999773158</v>
       </c>
       <c r="AG45" s="16">
         <v>246243</v>
@@ -8930,14 +8930,14 @@
       </c>
       <c r="AI45" s="10">
         <f t="shared" si="12"/>
-        <v>48108</v>
+        <v>48112</v>
       </c>
       <c r="AJ45" s="20">
-        <v>227302</v>
+        <v>227306</v>
       </c>
       <c r="AK45" s="12">
         <f t="shared" si="13"/>
-        <v>0.92308004694549695</v>
+        <v>0.92309629106208091</v>
       </c>
       <c r="AL45" s="18">
         <v>247584</v>
@@ -8947,14 +8947,14 @@
       </c>
       <c r="AN45" s="10">
         <f t="shared" si="14"/>
-        <v>51413</v>
-      </c>
-      <c r="AO45" s="20">
-        <v>229451</v>
+        <v>51418</v>
+      </c>
+      <c r="AO45" s="11">
+        <v>229456</v>
       </c>
       <c r="AP45" s="12">
         <f t="shared" si="15"/>
-        <v>0.92676021067597258</v>
+        <v>0.92678040584205768</v>
       </c>
       <c r="AQ45" s="11">
         <v>303759</v>
@@ -8964,14 +8964,14 @@
       </c>
       <c r="AS45" s="10">
         <f t="shared" si="16"/>
-        <v>67559</v>
+        <v>67565</v>
       </c>
       <c r="AT45" s="13">
-        <v>282310</v>
+        <v>282316</v>
       </c>
       <c r="AU45" s="12">
         <f t="shared" si="17"/>
-        <v>0.92938810043488418</v>
+        <v>0.92940785293604466</v>
       </c>
       <c r="AV45" s="18">
         <v>248547</v>
@@ -8981,14 +8981,14 @@
       </c>
       <c r="AX45" s="10">
         <f t="shared" si="18"/>
-        <v>55323</v>
+        <v>55330</v>
       </c>
       <c r="AY45" s="20">
-        <v>230976</v>
+        <v>230983</v>
       </c>
       <c r="AZ45" s="12">
         <f t="shared" si="19"/>
-        <v>0.92930512136537557</v>
+        <v>0.9293332850527265</v>
       </c>
       <c r="BA45" s="18">
         <v>248925</v>
@@ -8998,14 +8998,14 @@
       </c>
       <c r="BC45" s="10">
         <f t="shared" si="20"/>
-        <v>51914</v>
+        <v>51920</v>
       </c>
       <c r="BD45" s="20">
-        <v>233140</v>
+        <v>233146</v>
       </c>
       <c r="BE45" s="12">
         <f t="shared" si="21"/>
-        <v>0.93658732549964852</v>
+        <v>0.93661142914532491</v>
       </c>
       <c r="BF45" s="18">
         <v>305535</v>
@@ -9015,14 +9015,14 @@
       </c>
       <c r="BH45" s="10">
         <f t="shared" si="24"/>
-        <v>79692</v>
+        <v>79700</v>
       </c>
       <c r="BI45" s="11">
-        <v>287193</v>
+        <v>287201</v>
       </c>
       <c r="BJ45" s="12">
         <f t="shared" si="25"/>
-        <v>0.93996759782021699</v>
+        <v>0.93999378139983958</v>
       </c>
       <c r="BK45" s="24"/>
       <c r="BL45" s="24"/>
@@ -9163,7 +9163,7 @@
         <f t="shared" si="14"/>
         <v>747</v>
       </c>
-      <c r="AO46" s="20">
+      <c r="AO46" s="11">
         <v>2135</v>
       </c>
       <c r="AP46" s="12">
@@ -9377,7 +9377,7 @@
         <f t="shared" si="14"/>
         <v>5</v>
       </c>
-      <c r="AO47" s="20">
+      <c r="AO47" s="11">
         <v>66</v>
       </c>
       <c r="AP47" s="12">
@@ -9456,10 +9456,10 @@
       <c r="BL47" s="24"/>
     </row>
     <row r="48" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A48" s="36" t="s">
+      <c r="A48" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="B48" s="36"/>
+      <c r="B48" s="26"/>
       <c r="C48" s="6">
         <f>SUM(C10:C47)</f>
         <v>6932700</v>
@@ -9470,15 +9470,15 @@
       </c>
       <c r="E48" s="8">
         <f t="shared" si="0"/>
-        <v>5340283</v>
+        <v>5340366</v>
       </c>
       <c r="F48" s="7">
         <f>SUM(F10:F47)</f>
-        <v>6558083</v>
+        <v>6558166</v>
       </c>
       <c r="G48" s="9">
         <f t="shared" si="1"/>
-        <v>0.94596376592092546</v>
+        <v>0.94597573816839042</v>
       </c>
       <c r="H48" s="6">
         <f>SUM(H10:H47)</f>
@@ -9490,15 +9490,15 @@
       </c>
       <c r="J48" s="8">
         <f t="shared" si="2"/>
-        <v>5126126</v>
+        <v>5126201</v>
       </c>
       <c r="K48" s="7">
         <f>SUM(K10:K47)</f>
-        <v>6572567</v>
+        <v>6572642</v>
       </c>
       <c r="L48" s="9">
         <f t="shared" si="3"/>
-        <v>0.94559268382724249</v>
+        <v>0.9456034740483672</v>
       </c>
       <c r="M48" s="6">
         <f>SUM(M10:M47)</f>
@@ -9510,15 +9510,15 @@
       </c>
       <c r="O48" s="8">
         <f t="shared" si="4"/>
-        <v>3595257</v>
+        <v>3595351</v>
       </c>
       <c r="P48" s="7">
         <f>SUM(P10:P47)</f>
-        <v>10438712</v>
+        <v>10438806</v>
       </c>
       <c r="Q48" s="9">
         <f t="shared" si="5"/>
-        <v>0.96153912404215336</v>
+        <v>0.96154778264655405</v>
       </c>
       <c r="R48" s="6">
         <f>SUM(R10:R47)</f>
@@ -9530,15 +9530,15 @@
       </c>
       <c r="T48" s="8">
         <f t="shared" si="6"/>
-        <v>1738355</v>
+        <v>1738441</v>
       </c>
       <c r="U48" s="7">
         <f>SUM(U10:U47)</f>
-        <v>6647425</v>
+        <v>6647511</v>
       </c>
       <c r="V48" s="9">
         <f t="shared" si="7"/>
-        <v>0.94715735599412387</v>
+        <v>0.94716960969124953</v>
       </c>
       <c r="W48" s="6">
         <f>SUM(W10:W47)</f>
@@ -9550,15 +9550,15 @@
       </c>
       <c r="Y48" s="8">
         <f t="shared" si="8"/>
-        <v>1753718</v>
+        <v>1753805</v>
       </c>
       <c r="Z48" s="7">
         <f>SUM(Z10:Z47)</f>
-        <v>6780308</v>
+        <v>6780395</v>
       </c>
       <c r="AA48" s="9">
         <f t="shared" si="9"/>
-        <v>0.95150732683493644</v>
+        <v>0.95151953588759808</v>
       </c>
       <c r="AB48" s="6">
         <f>SUM(AB10:AB47)</f>
@@ -9570,15 +9570,15 @@
       </c>
       <c r="AD48" s="8">
         <f t="shared" si="10"/>
-        <v>2304987</v>
+        <v>2305099</v>
       </c>
       <c r="AE48" s="7">
         <f>SUM(AE10:AE47)</f>
-        <v>10747255</v>
+        <v>10747367</v>
       </c>
       <c r="AF48" s="9">
         <f t="shared" si="11"/>
-        <v>0.96119165619221869</v>
+        <v>0.96120167302586546</v>
       </c>
       <c r="AG48" s="6">
         <f>SUM(AG10:AG47)</f>
@@ -9590,15 +9590,15 @@
       </c>
       <c r="AI48" s="8">
         <f t="shared" si="12"/>
-        <v>1483334</v>
+        <v>1483432</v>
       </c>
       <c r="AJ48" s="7">
         <f>SUM(AJ10:AJ47)</f>
-        <v>6764413</v>
+        <v>6764511</v>
       </c>
       <c r="AK48" s="9">
         <f t="shared" si="13"/>
-        <v>0.94908759021674471</v>
+        <v>0.94910134020271408</v>
       </c>
       <c r="AL48" s="6">
         <f>SUM(AL10:AL47)</f>
@@ -9610,15 +9610,15 @@
       </c>
       <c r="AN48" s="8">
         <f t="shared" si="14"/>
-        <v>1501182</v>
+        <v>1501288</v>
       </c>
       <c r="AO48" s="7">
         <f>SUM(AO10:AO47)</f>
-        <v>6858546</v>
+        <v>6858652</v>
       </c>
       <c r="AP48" s="9">
         <f t="shared" si="15"/>
-        <v>0.95138277290880646</v>
+        <v>0.95139747669207597</v>
       </c>
       <c r="AQ48" s="6">
         <f>SUM(AQ10:AQ47)</f>
@@ -9630,15 +9630,15 @@
       </c>
       <c r="AS48" s="8">
         <f t="shared" si="16"/>
-        <v>2190283</v>
+        <v>2190424</v>
       </c>
       <c r="AT48" s="7">
         <f>SUM(AT10:AT47)</f>
-        <v>10966769</v>
+        <v>10966910</v>
       </c>
       <c r="AU48" s="9">
         <f t="shared" si="17"/>
-        <v>0.95954732071368309</v>
+        <v>0.95955965763554407</v>
       </c>
       <c r="AV48" s="6">
         <f>SUM(AV10:AV47)</f>
@@ -9650,15 +9650,15 @@
       </c>
       <c r="AX48" s="8">
         <f t="shared" si="18"/>
-        <v>1537006</v>
+        <v>1537128</v>
       </c>
       <c r="AY48" s="7">
         <f>SUM(AY10:AY47)</f>
-        <v>6903342</v>
+        <v>6903464</v>
       </c>
       <c r="AZ48" s="9">
         <f t="shared" si="19"/>
-        <v>0.95313613611153525</v>
+        <v>0.95315298050496178</v>
       </c>
       <c r="BA48" s="6">
         <f>SUM(BA10:BA47)</f>
@@ -9670,15 +9670,15 @@
       </c>
       <c r="BC48" s="8">
         <f t="shared" si="20"/>
-        <v>1610127</v>
+        <v>1610248</v>
       </c>
       <c r="BD48" s="7">
         <f>SUM(BD10:BD47)</f>
-        <v>7013351</v>
+        <v>7013472</v>
       </c>
       <c r="BE48" s="9">
         <f t="shared" si="21"/>
-        <v>0.95919042526129217</v>
+        <v>0.95920697398977539</v>
       </c>
       <c r="BF48" s="6">
         <f>SUM(BF10:BF47)</f>
@@ -9690,15 +9690,15 @@
       </c>
       <c r="BH48" s="8">
         <f t="shared" si="24"/>
-        <v>2687649</v>
+        <v>2687838</v>
       </c>
       <c r="BI48" s="7">
         <f>SUM(BI10:BI47)</f>
-        <v>11187518</v>
+        <v>11187707</v>
       </c>
       <c r="BJ48" s="9">
         <f t="shared" si="25"/>
-        <v>0.96185357203255006</v>
+        <v>0.96186982142094113</v>
       </c>
       <c r="BK48" s="24"/>
       <c r="BL48" s="24"/>
@@ -9802,13 +9802,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="BA8:BE8"/>
-    <mergeCell ref="AL8:AP8"/>
-    <mergeCell ref="AQ8:AU8"/>
-    <mergeCell ref="AV8:AZ8"/>
-    <mergeCell ref="AG8:AK8"/>
-    <mergeCell ref="H8:L8"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="BF8:BJ8"/>
     <mergeCell ref="M8:Q8"/>
@@ -9820,6 +9813,13 @@
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="C8:G8"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="BA8:BE8"/>
+    <mergeCell ref="AL8:AP8"/>
+    <mergeCell ref="AQ8:AU8"/>
+    <mergeCell ref="AV8:AZ8"/>
+    <mergeCell ref="AG8:AK8"/>
+    <mergeCell ref="H8:L8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/gstdatabase/GSTR-3B-2021-2022.xlsx
+++ b/gstdatabase/GSTR-3B-2021-2022.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\May-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 3B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jun-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 3B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93066253-5E0A-4C4E-B2D9-9F55659F7E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C61C158B-C3BE-403C-BB73-37F58A8FBA22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -185,10 +185,10 @@
     <t>STATE WISE RETURN PERIOD WISE GSTR-3B FILING SUMMARY</t>
   </si>
   <si>
-    <t>Data Considered upto 31st May 2026</t>
+    <t>Data Considered upto 30th Jun 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 31st May 2026</t>
+    <t>Filing %age as on 30th Jun 2026</t>
   </si>
 </sst>
 </file>
@@ -435,7 +435,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="17" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -447,6 +447,12 @@
     <xf numFmtId="17" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="17" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="17" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -454,19 +460,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -768,13 +768,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:64" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -848,10 +848,10 @@
       <c r="AK2" s="1"/>
     </row>
     <row r="3" spans="1:64" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="35"/>
+      <c r="B3" s="34"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -928,11 +928,11 @@
       <c r="AK4" s="1"/>
     </row>
     <row r="5" spans="1:64" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -1072,10 +1072,10 @@
       <c r="BJ7" s="4"/>
     </row>
     <row r="8" spans="1:64" s="24" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="36" t="s">
+      <c r="A8" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="33" t="s">
         <v>2</v>
       </c>
       <c r="C8" s="27">
@@ -1085,69 +1085,69 @@
       <c r="E8" s="28"/>
       <c r="F8" s="28"/>
       <c r="G8" s="29"/>
-      <c r="H8" s="30">
+      <c r="H8" s="32">
         <v>44317</v>
       </c>
-      <c r="I8" s="31"/>
-      <c r="J8" s="31"/>
-      <c r="K8" s="31"/>
-      <c r="L8" s="31"/>
-      <c r="M8" s="33">
+      <c r="I8" s="33"/>
+      <c r="J8" s="33"/>
+      <c r="K8" s="33"/>
+      <c r="L8" s="33"/>
+      <c r="M8" s="30">
         <v>44348</v>
       </c>
-      <c r="N8" s="34"/>
-      <c r="O8" s="34"/>
-      <c r="P8" s="34"/>
-      <c r="Q8" s="34"/>
-      <c r="R8" s="30">
+      <c r="N8" s="31"/>
+      <c r="O8" s="31"/>
+      <c r="P8" s="31"/>
+      <c r="Q8" s="31"/>
+      <c r="R8" s="32">
         <v>44378</v>
       </c>
-      <c r="S8" s="31"/>
-      <c r="T8" s="31"/>
-      <c r="U8" s="31"/>
-      <c r="V8" s="31"/>
-      <c r="W8" s="30">
+      <c r="S8" s="33"/>
+      <c r="T8" s="33"/>
+      <c r="U8" s="33"/>
+      <c r="V8" s="33"/>
+      <c r="W8" s="32">
         <v>44409</v>
       </c>
-      <c r="X8" s="31"/>
-      <c r="Y8" s="31"/>
-      <c r="Z8" s="31"/>
-      <c r="AA8" s="31"/>
-      <c r="AB8" s="33">
+      <c r="X8" s="33"/>
+      <c r="Y8" s="33"/>
+      <c r="Z8" s="33"/>
+      <c r="AA8" s="33"/>
+      <c r="AB8" s="30">
         <v>44440</v>
       </c>
-      <c r="AC8" s="34"/>
-      <c r="AD8" s="34"/>
-      <c r="AE8" s="34"/>
-      <c r="AF8" s="34"/>
-      <c r="AG8" s="30">
+      <c r="AC8" s="31"/>
+      <c r="AD8" s="31"/>
+      <c r="AE8" s="31"/>
+      <c r="AF8" s="31"/>
+      <c r="AG8" s="32">
         <v>44470</v>
       </c>
-      <c r="AH8" s="31"/>
-      <c r="AI8" s="31"/>
-      <c r="AJ8" s="31"/>
-      <c r="AK8" s="31"/>
-      <c r="AL8" s="30">
+      <c r="AH8" s="33"/>
+      <c r="AI8" s="33"/>
+      <c r="AJ8" s="33"/>
+      <c r="AK8" s="33"/>
+      <c r="AL8" s="32">
         <v>44501</v>
       </c>
-      <c r="AM8" s="31"/>
-      <c r="AN8" s="31"/>
-      <c r="AO8" s="31"/>
-      <c r="AP8" s="31"/>
-      <c r="AQ8" s="30">
+      <c r="AM8" s="33"/>
+      <c r="AN8" s="33"/>
+      <c r="AO8" s="33"/>
+      <c r="AP8" s="33"/>
+      <c r="AQ8" s="32">
         <v>44531</v>
       </c>
-      <c r="AR8" s="31"/>
-      <c r="AS8" s="31"/>
-      <c r="AT8" s="31"/>
-      <c r="AU8" s="31"/>
-      <c r="AV8" s="30">
+      <c r="AR8" s="33"/>
+      <c r="AS8" s="33"/>
+      <c r="AT8" s="33"/>
+      <c r="AU8" s="33"/>
+      <c r="AV8" s="32">
         <v>44562</v>
       </c>
-      <c r="AW8" s="31"/>
-      <c r="AX8" s="31"/>
-      <c r="AY8" s="31"/>
-      <c r="AZ8" s="31"/>
+      <c r="AW8" s="33"/>
+      <c r="AX8" s="33"/>
+      <c r="AY8" s="33"/>
+      <c r="AZ8" s="33"/>
       <c r="BA8" s="27">
         <v>44593</v>
       </c>
@@ -1164,8 +1164,8 @@
       <c r="BJ8" s="29"/>
     </row>
     <row r="9" spans="1:64" s="24" customFormat="1" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="36"/>
-      <c r="B9" s="31"/>
+      <c r="A9" s="35"/>
+      <c r="B9" s="33"/>
       <c r="C9" s="23" t="s">
         <v>3</v>
       </c>
@@ -2303,14 +2303,14 @@
       </c>
       <c r="AD14" s="10">
         <f t="shared" si="10"/>
-        <v>33622</v>
+        <v>33623</v>
       </c>
       <c r="AE14" s="11">
-        <v>139177</v>
+        <v>139178</v>
       </c>
       <c r="AF14" s="12">
         <f t="shared" si="11"/>
-        <v>0.96595688566233118</v>
+        <v>0.9659638261545509</v>
       </c>
       <c r="AG14" s="16">
         <v>79635</v>
@@ -2320,14 +2320,14 @@
       </c>
       <c r="AI14" s="10">
         <f t="shared" si="12"/>
-        <v>19172</v>
+        <v>19173</v>
       </c>
       <c r="AJ14" s="20">
-        <v>75493</v>
+        <v>75494</v>
       </c>
       <c r="AK14" s="12">
         <f t="shared" si="13"/>
-        <v>0.94798769385320525</v>
+        <v>0.94800025114585296</v>
       </c>
       <c r="AL14" s="18">
         <v>81274</v>
@@ -2337,14 +2337,14 @@
       </c>
       <c r="AN14" s="10">
         <f t="shared" si="14"/>
-        <v>19067</v>
+        <v>19068</v>
       </c>
       <c r="AO14" s="11">
-        <v>76992</v>
+        <v>76993</v>
       </c>
       <c r="AP14" s="12">
         <f t="shared" si="15"/>
-        <v>0.94731402416516963</v>
+        <v>0.94732632822304796</v>
       </c>
       <c r="AQ14" s="11">
         <v>148266</v>
@@ -2354,14 +2354,14 @@
       </c>
       <c r="AS14" s="10">
         <f t="shared" si="16"/>
-        <v>30168</v>
+        <v>30169</v>
       </c>
       <c r="AT14" s="13">
-        <v>142663</v>
+        <v>142664</v>
       </c>
       <c r="AU14" s="12">
         <f t="shared" si="17"/>
-        <v>0.96220981209447887</v>
+        <v>0.96221655672912199</v>
       </c>
       <c r="AV14" s="18">
         <v>81291</v>
@@ -2371,14 +2371,14 @@
       </c>
       <c r="AX14" s="10">
         <f t="shared" si="18"/>
-        <v>18862</v>
+        <v>18863</v>
       </c>
       <c r="AY14" s="20">
-        <v>77154</v>
+        <v>77155</v>
       </c>
       <c r="AZ14" s="12">
         <f t="shared" si="19"/>
-        <v>0.94910875742702139</v>
+        <v>0.94912105891181064</v>
       </c>
       <c r="BA14" s="18">
         <v>82359</v>
@@ -2388,14 +2388,14 @@
       </c>
       <c r="BC14" s="10">
         <f t="shared" si="20"/>
-        <v>20688</v>
+        <v>20690</v>
       </c>
       <c r="BD14" s="20">
-        <v>78377</v>
+        <v>78379</v>
       </c>
       <c r="BE14" s="12">
         <f t="shared" si="21"/>
-        <v>0.95165069998421548</v>
+        <v>0.95167498391189786</v>
       </c>
       <c r="BF14" s="18">
         <v>151377</v>
@@ -2405,14 +2405,14 @@
       </c>
       <c r="BH14" s="10">
         <f t="shared" si="22"/>
-        <v>36685</v>
+        <v>36686</v>
       </c>
       <c r="BI14" s="11">
-        <v>145235</v>
+        <v>145236</v>
       </c>
       <c r="BJ14" s="12">
         <f t="shared" si="23"/>
-        <v>0.95942580444849612</v>
+        <v>0.95943241047186822</v>
       </c>
       <c r="BK14" s="24"/>
       <c r="BL14" s="24"/>
@@ -2680,14 +2680,14 @@
       </c>
       <c r="O16" s="10">
         <f t="shared" si="4"/>
-        <v>196838</v>
+        <v>196841</v>
       </c>
       <c r="P16" s="13">
-        <v>676517</v>
+        <v>676520</v>
       </c>
       <c r="Q16" s="12">
         <f t="shared" si="5"/>
-        <v>0.94120306798056153</v>
+        <v>0.94120724172520343</v>
       </c>
       <c r="R16" s="16">
         <v>403668</v>
@@ -2697,14 +2697,14 @@
       </c>
       <c r="T16" s="10">
         <f t="shared" si="6"/>
-        <v>91177</v>
+        <v>91180</v>
       </c>
       <c r="U16" s="20">
-        <v>373774</v>
+        <v>373777</v>
       </c>
       <c r="V16" s="12">
         <f t="shared" si="7"/>
-        <v>0.92594409267021416</v>
+        <v>0.92595152452015017</v>
       </c>
       <c r="W16" s="16">
         <v>406853</v>
@@ -2714,14 +2714,14 @@
       </c>
       <c r="Y16" s="10">
         <f t="shared" si="8"/>
-        <v>87581</v>
+        <v>87584</v>
       </c>
       <c r="Z16" s="20">
-        <v>381193</v>
+        <v>381196</v>
       </c>
       <c r="AA16" s="12">
         <f t="shared" si="9"/>
-        <v>0.93693053756516487</v>
+        <v>0.93693791123575343</v>
       </c>
       <c r="AB16" s="17">
         <v>722282</v>
@@ -2731,14 +2731,14 @@
       </c>
       <c r="AD16" s="10">
         <f t="shared" si="10"/>
-        <v>123988</v>
+        <v>123992</v>
       </c>
       <c r="AE16" s="11">
-        <v>693617</v>
+        <v>693621</v>
       </c>
       <c r="AF16" s="12">
         <f t="shared" si="11"/>
-        <v>0.96031328483888567</v>
+        <v>0.96031882284204784</v>
       </c>
       <c r="AG16" s="16">
         <v>397671</v>
@@ -2748,14 +2748,14 @@
       </c>
       <c r="AI16" s="10">
         <f t="shared" si="12"/>
-        <v>76330</v>
+        <v>76333</v>
       </c>
       <c r="AJ16" s="20">
-        <v>378732</v>
+        <v>378735</v>
       </c>
       <c r="AK16" s="12">
         <f t="shared" si="13"/>
-        <v>0.95237520462895209</v>
+        <v>0.95238274855345251</v>
       </c>
       <c r="AL16" s="18">
         <v>400740</v>
@@ -2765,14 +2765,14 @@
       </c>
       <c r="AN16" s="10">
         <f t="shared" si="14"/>
-        <v>77329</v>
+        <v>77332</v>
       </c>
       <c r="AO16" s="11">
-        <v>383654</v>
+        <v>383657</v>
       </c>
       <c r="AP16" s="12">
         <f t="shared" si="15"/>
-        <v>0.9573638768278685</v>
+        <v>0.95737136297848979</v>
       </c>
       <c r="AQ16" s="11">
         <v>730568</v>
@@ -2782,14 +2782,14 @@
       </c>
       <c r="AS16" s="10">
         <f t="shared" si="16"/>
-        <v>116467</v>
+        <v>116470</v>
       </c>
       <c r="AT16" s="13">
-        <v>703043</v>
+        <v>703046</v>
       </c>
       <c r="AU16" s="12">
         <f t="shared" si="17"/>
-        <v>0.96232383570044133</v>
+        <v>0.96232794209437045</v>
       </c>
       <c r="AV16" s="18">
         <v>402711</v>
@@ -2799,14 +2799,14 @@
       </c>
       <c r="AX16" s="10">
         <f t="shared" si="18"/>
-        <v>74836</v>
+        <v>74838</v>
       </c>
       <c r="AY16" s="20">
-        <v>382479</v>
+        <v>382481</v>
       </c>
       <c r="AZ16" s="12">
         <f t="shared" si="19"/>
-        <v>0.94976049822329167</v>
+        <v>0.94976546456391808</v>
       </c>
       <c r="BA16" s="18">
         <v>402569</v>
@@ -2816,14 +2816,14 @@
       </c>
       <c r="BC16" s="10">
         <f t="shared" si="20"/>
-        <v>80936</v>
+        <v>80938</v>
       </c>
       <c r="BD16" s="20">
-        <v>387384</v>
+        <v>387386</v>
       </c>
       <c r="BE16" s="12">
         <f t="shared" si="21"/>
-        <v>0.96227975825262257</v>
+        <v>0.96228472634504891</v>
       </c>
       <c r="BF16" s="18">
         <v>736680</v>
@@ -2833,14 +2833,14 @@
       </c>
       <c r="BH16" s="10">
         <f t="shared" si="22"/>
-        <v>137187</v>
+        <v>137190</v>
       </c>
       <c r="BI16" s="11">
-        <v>709533</v>
+        <v>709536</v>
       </c>
       <c r="BJ16" s="12">
         <f t="shared" si="23"/>
-        <v>0.96314953575500895</v>
+        <v>0.9631536080794918</v>
       </c>
       <c r="BK16" s="24"/>
       <c r="BL16" s="24"/>
@@ -2877,14 +2877,14 @@
       </c>
       <c r="J17" s="10">
         <f t="shared" si="2"/>
-        <v>201003</v>
+        <v>201004</v>
       </c>
       <c r="K17" s="20">
-        <v>260764</v>
+        <v>260765</v>
       </c>
       <c r="L17" s="12">
         <f t="shared" si="3"/>
-        <v>0.98711426062202845</v>
+        <v>0.98711804609188092</v>
       </c>
       <c r="M17" s="16">
         <v>591219</v>
@@ -2894,14 +2894,14 @@
       </c>
       <c r="O17" s="10">
         <f t="shared" si="4"/>
-        <v>171689</v>
+        <v>171691</v>
       </c>
       <c r="P17" s="13">
-        <v>584077</v>
+        <v>584079</v>
       </c>
       <c r="Q17" s="12">
         <f t="shared" si="5"/>
-        <v>0.98791987402299319</v>
+        <v>0.98792325686420768</v>
       </c>
       <c r="R17" s="16">
         <v>261213</v>
@@ -2911,14 +2911,14 @@
       </c>
       <c r="T17" s="10">
         <f t="shared" si="6"/>
-        <v>69620</v>
+        <v>69621</v>
       </c>
       <c r="U17" s="20">
-        <v>257378</v>
+        <v>257379</v>
       </c>
       <c r="V17" s="12">
         <f t="shared" si="7"/>
-        <v>0.98531849486817269</v>
+        <v>0.98532232316155777</v>
       </c>
       <c r="W17" s="16">
         <v>269820</v>
@@ -2928,14 +2928,14 @@
       </c>
       <c r="Y17" s="10">
         <f t="shared" si="8"/>
-        <v>72461</v>
+        <v>72463</v>
       </c>
       <c r="Z17" s="20">
-        <v>267026</v>
+        <v>267028</v>
       </c>
       <c r="AA17" s="12">
         <f t="shared" si="9"/>
-        <v>0.98964494848417461</v>
+        <v>0.989652360833148</v>
       </c>
       <c r="AB17" s="17">
         <v>613565</v>
@@ -2945,14 +2945,14 @@
       </c>
       <c r="AD17" s="10">
         <f t="shared" si="10"/>
-        <v>123888</v>
+        <v>123890</v>
       </c>
       <c r="AE17" s="11">
-        <v>604348</v>
+        <v>604350</v>
       </c>
       <c r="AF17" s="12">
         <f t="shared" si="11"/>
-        <v>0.98497795669570465</v>
+        <v>0.98498121633404778</v>
       </c>
       <c r="AG17" s="16">
         <v>263808</v>
@@ -2962,14 +2962,14 @@
       </c>
       <c r="AI17" s="10">
         <f t="shared" si="12"/>
-        <v>62437</v>
+        <v>62439</v>
       </c>
       <c r="AJ17" s="20">
-        <v>259623</v>
+        <v>259625</v>
       </c>
       <c r="AK17" s="12">
         <f t="shared" si="13"/>
-        <v>0.9841361899563319</v>
+        <v>0.98414377122755947</v>
       </c>
       <c r="AL17" s="18">
         <v>270212</v>
@@ -2979,14 +2979,14 @@
       </c>
       <c r="AN17" s="10">
         <f t="shared" si="14"/>
-        <v>62610</v>
+        <v>62612</v>
       </c>
       <c r="AO17" s="11">
-        <v>266622</v>
+        <v>266624</v>
       </c>
       <c r="AP17" s="12">
         <f t="shared" si="15"/>
-        <v>0.98671413556762833</v>
+        <v>0.98672153716341238</v>
       </c>
       <c r="AQ17" s="11">
         <v>633137</v>
@@ -2996,14 +2996,14 @@
       </c>
       <c r="AS17" s="10">
         <f t="shared" si="16"/>
-        <v>124221</v>
+        <v>124226</v>
       </c>
       <c r="AT17" s="13">
-        <v>619710</v>
+        <v>619715</v>
       </c>
       <c r="AU17" s="12">
         <f t="shared" si="17"/>
-        <v>0.97879289948305026</v>
+        <v>0.97880079666801967</v>
       </c>
       <c r="AV17" s="18">
         <v>270996</v>
@@ -3013,14 +3013,14 @@
       </c>
       <c r="AX17" s="10">
         <f t="shared" si="18"/>
-        <v>61985</v>
+        <v>61988</v>
       </c>
       <c r="AY17" s="20">
-        <v>265735</v>
+        <v>265738</v>
       </c>
       <c r="AZ17" s="12">
         <f t="shared" si="19"/>
-        <v>0.98058642931998996</v>
+        <v>0.98059749959408993</v>
       </c>
       <c r="BA17" s="18">
         <v>277009</v>
@@ -3030,14 +3030,14 @@
       </c>
       <c r="BC17" s="10">
         <f t="shared" si="20"/>
-        <v>65556</v>
+        <v>65560</v>
       </c>
       <c r="BD17" s="20">
-        <v>274586</v>
+        <v>274590</v>
       </c>
       <c r="BE17" s="12">
         <f t="shared" si="21"/>
-        <v>0.99125299178005044</v>
+        <v>0.99126743174409493</v>
       </c>
       <c r="BF17" s="18">
         <v>651560</v>
@@ -3047,14 +3047,14 @@
       </c>
       <c r="BH17" s="10">
         <f t="shared" si="22"/>
-        <v>160478</v>
+        <v>160486</v>
       </c>
       <c r="BI17" s="11">
-        <v>635883</v>
+        <v>635891</v>
       </c>
       <c r="BJ17" s="12">
         <f t="shared" si="23"/>
-        <v>0.97593928417950759</v>
+        <v>0.97595156240407632</v>
       </c>
       <c r="BK17" s="24"/>
       <c r="BL17" s="24"/>
@@ -3074,14 +3074,14 @@
       </c>
       <c r="E18" s="10">
         <f t="shared" si="0"/>
-        <v>625829</v>
+        <v>625832</v>
       </c>
       <c r="F18" s="20">
-        <v>740854</v>
+        <v>740857</v>
       </c>
       <c r="G18" s="12">
         <f t="shared" si="1"/>
-        <v>0.96403355133546909</v>
+        <v>0.96403745507447036</v>
       </c>
       <c r="H18" s="15">
         <v>766983</v>
@@ -3091,14 +3091,14 @@
       </c>
       <c r="J18" s="10">
         <f t="shared" si="2"/>
-        <v>564996</v>
+        <v>564999</v>
       </c>
       <c r="K18" s="20">
-        <v>740258</v>
+        <v>740261</v>
       </c>
       <c r="L18" s="12">
         <f t="shared" si="3"/>
-        <v>0.96515568141666763</v>
+        <v>0.96515959284625608</v>
       </c>
       <c r="M18" s="16">
         <v>1193073</v>
@@ -3108,14 +3108,14 @@
       </c>
       <c r="O18" s="10">
         <f t="shared" si="4"/>
-        <v>410732</v>
+        <v>410735</v>
       </c>
       <c r="P18" s="13">
-        <v>1175482</v>
+        <v>1175485</v>
       </c>
       <c r="Q18" s="12">
         <f t="shared" si="5"/>
-        <v>0.98525572198851197</v>
+        <v>0.98525823650355004</v>
       </c>
       <c r="R18" s="16">
         <v>775495</v>
@@ -3125,14 +3125,14 @@
       </c>
       <c r="T18" s="10">
         <f t="shared" si="6"/>
-        <v>184172</v>
+        <v>184174</v>
       </c>
       <c r="U18" s="20">
-        <v>756201</v>
+        <v>756203</v>
       </c>
       <c r="V18" s="12">
         <f t="shared" si="7"/>
-        <v>0.97512040696587343</v>
+        <v>0.97512298596380376</v>
       </c>
       <c r="W18" s="16">
         <v>789854</v>
@@ -3142,14 +3142,14 @@
       </c>
       <c r="Y18" s="10">
         <f t="shared" si="8"/>
-        <v>178821</v>
+        <v>178823</v>
       </c>
       <c r="Z18" s="20">
-        <v>773182</v>
+        <v>773184</v>
       </c>
       <c r="AA18" s="12">
         <f t="shared" si="9"/>
-        <v>0.97889230161523522</v>
+        <v>0.97889483372876507</v>
       </c>
       <c r="AB18" s="17">
         <v>1245422</v>
@@ -3159,14 +3159,14 @@
       </c>
       <c r="AD18" s="10">
         <f t="shared" si="10"/>
-        <v>240979</v>
+        <v>240981</v>
       </c>
       <c r="AE18" s="11">
-        <v>1213769</v>
+        <v>1213771</v>
       </c>
       <c r="AF18" s="12">
         <f t="shared" si="11"/>
-        <v>0.97458451833996829</v>
+        <v>0.97458612422134827</v>
       </c>
       <c r="AG18" s="16">
         <v>794310</v>
@@ -3176,14 +3176,14 @@
       </c>
       <c r="AI18" s="10">
         <f t="shared" si="12"/>
-        <v>158878</v>
+        <v>158880</v>
       </c>
       <c r="AJ18" s="20">
-        <v>773916</v>
+        <v>773918</v>
       </c>
       <c r="AK18" s="12">
         <f t="shared" si="13"/>
-        <v>0.97432488574989617</v>
+        <v>0.97432740365852122</v>
       </c>
       <c r="AL18" s="18">
         <v>807429</v>
@@ -3193,14 +3193,14 @@
       </c>
       <c r="AN18" s="10">
         <f t="shared" si="14"/>
-        <v>156227</v>
+        <v>156230</v>
       </c>
       <c r="AO18" s="11">
-        <v>787038</v>
+        <v>787041</v>
       </c>
       <c r="AP18" s="12">
         <f t="shared" si="15"/>
-        <v>0.9747457671200811</v>
+        <v>0.97474948261704741</v>
       </c>
       <c r="AQ18" s="11">
         <v>1285494</v>
@@ -3210,14 +3210,14 @@
       </c>
       <c r="AS18" s="10">
         <f t="shared" si="16"/>
-        <v>230870</v>
+        <v>230873</v>
       </c>
       <c r="AT18" s="13">
-        <v>1245490</v>
+        <v>1245493</v>
       </c>
       <c r="AU18" s="12">
         <f t="shared" si="17"/>
-        <v>0.96888044596085243</v>
+        <v>0.96888277969403203</v>
       </c>
       <c r="AV18" s="18">
         <v>820095</v>
@@ -3227,14 +3227,14 @@
       </c>
       <c r="AX18" s="10">
         <f t="shared" si="18"/>
-        <v>161734</v>
+        <v>161737</v>
       </c>
       <c r="AY18" s="20">
-        <v>793761</v>
+        <v>793764</v>
       </c>
       <c r="AZ18" s="12">
         <f t="shared" si="19"/>
-        <v>0.96788908602052204</v>
+        <v>0.96789274413330162</v>
       </c>
       <c r="BA18" s="18">
         <v>829968</v>
@@ -3244,14 +3244,14 @@
       </c>
       <c r="BC18" s="10">
         <f t="shared" si="20"/>
-        <v>198186</v>
+        <v>198189</v>
       </c>
       <c r="BD18" s="20">
-        <v>806487</v>
+        <v>806490</v>
       </c>
       <c r="BE18" s="12">
         <f t="shared" si="21"/>
-        <v>0.97170854779943328</v>
+        <v>0.9717121623966225</v>
       </c>
       <c r="BF18" s="18">
         <v>1319511</v>
@@ -3261,14 +3261,14 @@
       </c>
       <c r="BH18" s="10">
         <f t="shared" si="22"/>
-        <v>292035</v>
+        <v>292039</v>
       </c>
       <c r="BI18" s="11">
-        <v>1272813</v>
+        <v>1272817</v>
       </c>
       <c r="BJ18" s="12">
         <f t="shared" si="23"/>
-        <v>0.96460961674438483</v>
+        <v>0.96461264817042069</v>
       </c>
       <c r="BK18" s="24"/>
       <c r="BL18" s="24"/>
@@ -3288,14 +3288,14 @@
       </c>
       <c r="E19" s="10">
         <f t="shared" si="0"/>
-        <v>181878</v>
+        <v>181880</v>
       </c>
       <c r="F19" s="20">
-        <v>215772</v>
+        <v>215774</v>
       </c>
       <c r="G19" s="12">
         <f t="shared" si="1"/>
-        <v>0.87907306460681023</v>
+        <v>0.87908121277306539</v>
       </c>
       <c r="H19" s="15">
         <v>247965</v>
@@ -3305,14 +3305,14 @@
       </c>
       <c r="J19" s="10">
         <f t="shared" si="2"/>
-        <v>170659</v>
+        <v>170660</v>
       </c>
       <c r="K19" s="20">
-        <v>216749</v>
+        <v>216750</v>
       </c>
       <c r="L19" s="12">
         <f t="shared" si="3"/>
-        <v>0.87411126570282094</v>
+        <v>0.87411529853003445</v>
       </c>
       <c r="M19" s="16">
         <v>387570</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="O19" s="10">
         <f t="shared" si="4"/>
-        <v>139738</v>
+        <v>139739</v>
       </c>
       <c r="P19" s="13">
-        <v>357136</v>
+        <v>357137</v>
       </c>
       <c r="Q19" s="12">
         <f t="shared" si="5"/>
-        <v>0.92147483035322653</v>
+        <v>0.92147741053229093</v>
       </c>
       <c r="R19" s="16">
         <v>254467</v>
@@ -3339,14 +3339,14 @@
       </c>
       <c r="T19" s="10">
         <f t="shared" si="6"/>
-        <v>69079</v>
+        <v>69080</v>
       </c>
       <c r="U19" s="20">
-        <v>229790</v>
+        <v>229791</v>
       </c>
       <c r="V19" s="12">
         <f t="shared" si="7"/>
-        <v>0.90302475370087276</v>
+        <v>0.9030286834835165</v>
       </c>
       <c r="W19" s="16">
         <v>263449</v>
@@ -3356,14 +3356,14 @@
       </c>
       <c r="Y19" s="10">
         <f t="shared" si="8"/>
-        <v>66517</v>
+        <v>66519</v>
       </c>
       <c r="Z19" s="20">
-        <v>244526</v>
+        <v>244528</v>
       </c>
       <c r="AA19" s="12">
         <f t="shared" si="9"/>
-        <v>0.9281720560715736</v>
+        <v>0.92817964767374328</v>
       </c>
       <c r="AB19" s="17">
         <v>418128</v>
@@ -3373,14 +3373,14 @@
       </c>
       <c r="AD19" s="10">
         <f t="shared" si="10"/>
-        <v>85782</v>
+        <v>85784</v>
       </c>
       <c r="AE19" s="11">
-        <v>394356</v>
+        <v>394358</v>
       </c>
       <c r="AF19" s="12">
         <f t="shared" si="11"/>
-        <v>0.94314659625760533</v>
+        <v>0.9431513794818811</v>
       </c>
       <c r="AG19" s="16">
         <v>259213</v>
@@ -3390,14 +3390,14 @@
       </c>
       <c r="AI19" s="10">
         <f t="shared" si="12"/>
-        <v>59056</v>
+        <v>59058</v>
       </c>
       <c r="AJ19" s="20">
-        <v>234180</v>
+        <v>234182</v>
       </c>
       <c r="AK19" s="12">
         <f t="shared" si="13"/>
-        <v>0.90342691145891607</v>
+        <v>0.90343462712132494</v>
       </c>
       <c r="AL19" s="18">
         <v>262802</v>
@@ -3407,14 +3407,14 @@
       </c>
       <c r="AN19" s="10">
         <f t="shared" si="14"/>
-        <v>55771</v>
+        <v>55773</v>
       </c>
       <c r="AO19" s="11">
-        <v>237106</v>
+        <v>237108</v>
       </c>
       <c r="AP19" s="12">
         <f t="shared" si="15"/>
-        <v>0.9022229663396778</v>
+        <v>0.90223057663183692</v>
       </c>
       <c r="AQ19" s="11">
         <v>437396</v>
@@ -3424,14 +3424,14 @@
       </c>
       <c r="AS19" s="10">
         <f t="shared" si="16"/>
-        <v>82223</v>
+        <v>82225</v>
       </c>
       <c r="AT19" s="13">
-        <v>401086</v>
+        <v>401088</v>
       </c>
       <c r="AU19" s="12">
         <f t="shared" si="17"/>
-        <v>0.91698598066740433</v>
+        <v>0.9169905531829281</v>
       </c>
       <c r="AV19" s="18">
         <v>265429</v>
@@ -3441,14 +3441,14 @@
       </c>
       <c r="AX19" s="10">
         <f t="shared" si="18"/>
-        <v>56295</v>
+        <v>56297</v>
       </c>
       <c r="AY19" s="20">
-        <v>237902</v>
+        <v>237904</v>
       </c>
       <c r="AZ19" s="12">
         <f t="shared" si="19"/>
-        <v>0.89629241718124242</v>
+        <v>0.89629995215292979</v>
       </c>
       <c r="BA19" s="18">
         <v>272122</v>
@@ -3458,14 +3458,14 @@
       </c>
       <c r="BC19" s="10">
         <f t="shared" si="20"/>
-        <v>65955</v>
+        <v>65958</v>
       </c>
       <c r="BD19" s="20">
-        <v>244813</v>
+        <v>244816</v>
       </c>
       <c r="BE19" s="12">
         <f t="shared" si="21"/>
-        <v>0.89964427719919737</v>
+        <v>0.89965530166616448</v>
       </c>
       <c r="BF19" s="18">
         <v>456786</v>
@@ -3475,14 +3475,14 @@
       </c>
       <c r="BH19" s="10">
         <f t="shared" si="22"/>
-        <v>115387</v>
+        <v>115391</v>
       </c>
       <c r="BI19" s="11">
-        <v>415709</v>
+        <v>415713</v>
       </c>
       <c r="BJ19" s="12">
         <f t="shared" si="23"/>
-        <v>0.91007386391001477</v>
+        <v>0.91008262074581969</v>
       </c>
       <c r="BK19" s="24"/>
       <c r="BL19" s="24"/>
@@ -3767,14 +3767,14 @@
       </c>
       <c r="T21" s="10">
         <f t="shared" si="6"/>
-        <v>3582</v>
+        <v>3583</v>
       </c>
       <c r="U21" s="20">
-        <v>7868</v>
+        <v>7869</v>
       </c>
       <c r="V21" s="12">
         <f t="shared" si="7"/>
-        <v>0.76858454625378525</v>
+        <v>0.7686822311223992</v>
       </c>
       <c r="W21" s="16">
         <v>10162</v>
@@ -3784,14 +3784,14 @@
       </c>
       <c r="Y21" s="10">
         <f t="shared" si="8"/>
-        <v>3550</v>
+        <v>3551</v>
       </c>
       <c r="Z21" s="20">
-        <v>7970</v>
+        <v>7971</v>
       </c>
       <c r="AA21" s="12">
         <f t="shared" si="9"/>
-        <v>0.78429443023026968</v>
+        <v>0.78439283605589449</v>
       </c>
       <c r="AB21" s="17">
         <v>13196</v>
@@ -3801,14 +3801,14 @@
       </c>
       <c r="AD21" s="10">
         <f t="shared" si="10"/>
-        <v>4244</v>
+        <v>4245</v>
       </c>
       <c r="AE21" s="11">
-        <v>10796</v>
+        <v>10797</v>
       </c>
       <c r="AF21" s="12">
         <f t="shared" si="11"/>
-        <v>0.81812670506214002</v>
+        <v>0.8182024856016975</v>
       </c>
       <c r="AG21" s="16">
         <v>10295</v>
@@ -3818,14 +3818,14 @@
       </c>
       <c r="AI21" s="10">
         <f t="shared" si="12"/>
-        <v>3025</v>
+        <v>3026</v>
       </c>
       <c r="AJ21" s="20">
-        <v>8031</v>
+        <v>8032</v>
       </c>
       <c r="AK21" s="12">
         <f t="shared" si="13"/>
-        <v>0.78008742107819329</v>
+        <v>0.78018455560951916</v>
       </c>
       <c r="AL21" s="18">
         <v>10459</v>
@@ -3835,14 +3835,14 @@
       </c>
       <c r="AN21" s="10">
         <f t="shared" si="14"/>
-        <v>2976</v>
+        <v>2977</v>
       </c>
       <c r="AO21" s="11">
-        <v>8139</v>
+        <v>8140</v>
       </c>
       <c r="AP21" s="12">
         <f t="shared" si="15"/>
-        <v>0.77818147050387221</v>
+        <v>0.77827708193899992</v>
       </c>
       <c r="AQ21" s="11">
         <v>13595</v>
@@ -3852,14 +3852,14 @@
       </c>
       <c r="AS21" s="10">
         <f t="shared" si="16"/>
-        <v>3827</v>
+        <v>3828</v>
       </c>
       <c r="AT21" s="13">
-        <v>11060</v>
+        <v>11061</v>
       </c>
       <c r="AU21" s="12">
         <f t="shared" si="17"/>
-        <v>0.81353438764251562</v>
+        <v>0.81360794409709447</v>
       </c>
       <c r="AV21" s="18">
         <v>10391</v>
@@ -3869,14 +3869,14 @@
       </c>
       <c r="AX21" s="10">
         <f t="shared" si="18"/>
-        <v>3012</v>
+        <v>3013</v>
       </c>
       <c r="AY21" s="20">
-        <v>8238</v>
+        <v>8239</v>
       </c>
       <c r="AZ21" s="12">
         <f t="shared" si="19"/>
-        <v>0.79280146280434993</v>
+        <v>0.79289769993263404</v>
       </c>
       <c r="BA21" s="18">
         <v>10525</v>
@@ -3886,14 +3886,14 @@
       </c>
       <c r="BC21" s="10">
         <f t="shared" si="20"/>
-        <v>3118</v>
+        <v>3119</v>
       </c>
       <c r="BD21" s="20">
-        <v>8387</v>
+        <v>8388</v>
       </c>
       <c r="BE21" s="12">
         <f t="shared" si="21"/>
-        <v>0.79686460807600945</v>
+        <v>0.79695961995249409</v>
       </c>
       <c r="BF21" s="18">
         <v>13618</v>
@@ -3903,14 +3903,14 @@
       </c>
       <c r="BH21" s="10">
         <f t="shared" si="22"/>
-        <v>5147</v>
+        <v>5148</v>
       </c>
       <c r="BI21" s="11">
-        <v>11447</v>
+        <v>11448</v>
       </c>
       <c r="BJ21" s="12">
         <f t="shared" si="23"/>
-        <v>0.84057864590982523</v>
+        <v>0.84065207813188425</v>
       </c>
       <c r="BK21" s="24"/>
       <c r="BL21" s="24"/>
@@ -3930,14 +3930,14 @@
       </c>
       <c r="E22" s="10">
         <f t="shared" si="0"/>
-        <v>3846</v>
+        <v>3847</v>
       </c>
       <c r="F22" s="20">
-        <v>5159</v>
+        <v>5160</v>
       </c>
       <c r="G22" s="12">
         <f t="shared" si="1"/>
-        <v>0.87130552271575745</v>
+        <v>0.87147441310589424</v>
       </c>
       <c r="H22" s="15">
         <v>5940</v>
@@ -3947,14 +3947,14 @@
       </c>
       <c r="J22" s="10">
         <f t="shared" si="2"/>
-        <v>4125</v>
+        <v>4126</v>
       </c>
       <c r="K22" s="20">
-        <v>5174</v>
+        <v>5175</v>
       </c>
       <c r="L22" s="12">
         <f t="shared" si="3"/>
-        <v>0.87104377104377106</v>
+        <v>0.87121212121212122</v>
       </c>
       <c r="M22" s="16">
         <v>7004</v>
@@ -3964,14 +3964,14 @@
       </c>
       <c r="O22" s="10">
         <f t="shared" si="4"/>
-        <v>3146</v>
+        <v>3147</v>
       </c>
       <c r="P22" s="13">
-        <v>6188</v>
+        <v>6189</v>
       </c>
       <c r="Q22" s="12">
         <f t="shared" si="5"/>
-        <v>0.88349514563106801</v>
+        <v>0.88363792118789264</v>
       </c>
       <c r="R22" s="16">
         <v>5966</v>
@@ -3981,14 +3981,14 @@
       </c>
       <c r="T22" s="10">
         <f t="shared" si="6"/>
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="U22" s="20">
-        <v>5136</v>
+        <v>5137</v>
       </c>
       <c r="V22" s="12">
         <f t="shared" si="7"/>
-        <v>0.86087831042574592</v>
+        <v>0.86104592691920889</v>
       </c>
       <c r="W22" s="16">
         <v>5920</v>
@@ -3998,14 +3998,14 @@
       </c>
       <c r="Y22" s="10">
         <f t="shared" si="8"/>
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="Z22" s="20">
-        <v>5200</v>
+        <v>5201</v>
       </c>
       <c r="AA22" s="12">
         <f t="shared" si="9"/>
-        <v>0.8783783783783784</v>
+        <v>0.8785472972972973</v>
       </c>
       <c r="AB22" s="17">
         <v>7073</v>
@@ -4015,14 +4015,14 @@
       </c>
       <c r="AD22" s="10">
         <f t="shared" si="10"/>
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="AE22" s="11">
-        <v>6358</v>
+        <v>6359</v>
       </c>
       <c r="AF22" s="12">
         <f t="shared" si="11"/>
-        <v>0.89891135303265945</v>
+        <v>0.89905273575569067</v>
       </c>
       <c r="AG22" s="16">
         <v>5998</v>
@@ -4032,14 +4032,14 @@
       </c>
       <c r="AI22" s="10">
         <f t="shared" si="12"/>
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="AJ22" s="20">
-        <v>5299</v>
+        <v>5300</v>
       </c>
       <c r="AK22" s="12">
         <f t="shared" si="13"/>
-        <v>0.88346115371790601</v>
+        <v>0.88362787595865289</v>
       </c>
       <c r="AL22" s="18">
         <v>5988</v>
@@ -4049,14 +4049,14 @@
       </c>
       <c r="AN22" s="10">
         <f t="shared" si="14"/>
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="AO22" s="11">
-        <v>5386</v>
+        <v>5387</v>
       </c>
       <c r="AP22" s="12">
         <f t="shared" si="15"/>
-        <v>0.89946559786239144</v>
+        <v>0.89963259853039412</v>
       </c>
       <c r="AQ22" s="11">
         <v>7036</v>
@@ -4066,14 +4066,14 @@
       </c>
       <c r="AS22" s="10">
         <f t="shared" si="16"/>
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="AT22" s="13">
-        <v>6499</v>
+        <v>6500</v>
       </c>
       <c r="AU22" s="12">
         <f t="shared" si="17"/>
-        <v>0.92367822626492324</v>
+        <v>0.92382035247299599</v>
       </c>
       <c r="AV22" s="18">
         <v>5943</v>
@@ -4083,14 +4083,14 @@
       </c>
       <c r="AX22" s="10">
         <f t="shared" si="18"/>
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="AY22" s="20">
-        <v>5411</v>
+        <v>5412</v>
       </c>
       <c r="AZ22" s="12">
         <f t="shared" si="19"/>
-        <v>0.91048292108362783</v>
+        <v>0.91065118626956087</v>
       </c>
       <c r="BA22" s="18">
         <v>5997</v>
@@ -4100,14 +4100,14 @@
       </c>
       <c r="BC22" s="10">
         <f t="shared" si="20"/>
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="BD22" s="20">
-        <v>5475</v>
+        <v>5476</v>
       </c>
       <c r="BE22" s="12">
         <f t="shared" si="21"/>
-        <v>0.91295647823911952</v>
+        <v>0.91312322828080705</v>
       </c>
       <c r="BF22" s="18">
         <v>7214</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="BH22" s="10">
         <f t="shared" si="22"/>
-        <v>2399</v>
+        <v>2400</v>
       </c>
       <c r="BI22" s="11">
-        <v>6682</v>
+        <v>6683</v>
       </c>
       <c r="BJ22" s="12">
         <f t="shared" si="23"/>
-        <v>0.92625450512891605</v>
+        <v>0.92639312448017741</v>
       </c>
       <c r="BK22" s="24"/>
       <c r="BL22" s="24"/>
@@ -4786,14 +4786,14 @@
       </c>
       <c r="E26" s="10">
         <f t="shared" si="0"/>
-        <v>9672</v>
+        <v>9673</v>
       </c>
       <c r="F26" s="20">
-        <v>13148</v>
+        <v>13149</v>
       </c>
       <c r="G26" s="12">
         <f t="shared" si="1"/>
-        <v>0.79386547518415651</v>
+        <v>0.79392585436541485</v>
       </c>
       <c r="H26" s="15">
         <v>16580</v>
@@ -4803,14 +4803,14 @@
       </c>
       <c r="J26" s="10">
         <f t="shared" si="2"/>
-        <v>9476</v>
+        <v>9477</v>
       </c>
       <c r="K26" s="20">
-        <v>13081</v>
+        <v>13082</v>
       </c>
       <c r="L26" s="12">
         <f t="shared" si="3"/>
-        <v>0.788962605548854</v>
+        <v>0.78902291917973466</v>
       </c>
       <c r="M26" s="16">
         <v>25396</v>
@@ -4820,14 +4820,14 @@
       </c>
       <c r="O26" s="10">
         <f t="shared" si="4"/>
-        <v>8461</v>
+        <v>8462</v>
       </c>
       <c r="P26" s="13">
-        <v>21704</v>
+        <v>21705</v>
       </c>
       <c r="Q26" s="12">
         <f t="shared" si="5"/>
-        <v>0.85462277524019525</v>
+        <v>0.85466215151992442</v>
       </c>
       <c r="R26" s="16">
         <v>16475</v>
@@ -4837,14 +4837,14 @@
       </c>
       <c r="T26" s="10">
         <f t="shared" si="6"/>
-        <v>4394</v>
+        <v>4395</v>
       </c>
       <c r="U26" s="20">
-        <v>12977</v>
+        <v>12978</v>
       </c>
       <c r="V26" s="12">
         <f t="shared" si="7"/>
-        <v>0.78767830045523524</v>
+        <v>0.78773899848254936</v>
       </c>
       <c r="W26" s="16">
         <v>16675</v>
@@ -4854,14 +4854,14 @@
       </c>
       <c r="Y26" s="10">
         <f t="shared" si="8"/>
-        <v>3963</v>
+        <v>3964</v>
       </c>
       <c r="Z26" s="20">
-        <v>13242</v>
+        <v>13243</v>
       </c>
       <c r="AA26" s="12">
         <f t="shared" si="9"/>
-        <v>0.79412293853073468</v>
+        <v>0.79418290854572715</v>
       </c>
       <c r="AB26" s="17">
         <v>25656</v>
@@ -4871,14 +4871,14 @@
       </c>
       <c r="AD26" s="10">
         <f t="shared" si="10"/>
-        <v>5325</v>
+        <v>5326</v>
       </c>
       <c r="AE26" s="11">
-        <v>22436</v>
+        <v>22437</v>
       </c>
       <c r="AF26" s="12">
         <f t="shared" si="11"/>
-        <v>0.87449329591518554</v>
+        <v>0.87453227315247895</v>
       </c>
       <c r="AG26" s="16">
         <v>15844</v>
@@ -4888,14 +4888,14 @@
       </c>
       <c r="AI26" s="10">
         <f t="shared" si="12"/>
-        <v>3553</v>
+        <v>3554</v>
       </c>
       <c r="AJ26" s="20">
-        <v>12770</v>
+        <v>12771</v>
       </c>
       <c r="AK26" s="12">
         <f t="shared" si="13"/>
-        <v>0.80598333754102502</v>
+        <v>0.80604645291593036</v>
       </c>
       <c r="AL26" s="18">
         <v>16081</v>
@@ -4905,14 +4905,14 @@
       </c>
       <c r="AN26" s="10">
         <f t="shared" si="14"/>
-        <v>3491</v>
+        <v>3492</v>
       </c>
       <c r="AO26" s="11">
-        <v>12977</v>
+        <v>12978</v>
       </c>
       <c r="AP26" s="12">
         <f t="shared" si="15"/>
-        <v>0.80697717803619173</v>
+        <v>0.80703936322368008</v>
       </c>
       <c r="AQ26" s="11">
         <v>26317</v>
@@ -4922,14 +4922,14 @@
       </c>
       <c r="AS26" s="10">
         <f t="shared" si="16"/>
-        <v>5519</v>
+        <v>5521</v>
       </c>
       <c r="AT26" s="13">
-        <v>22879</v>
+        <v>22881</v>
       </c>
       <c r="AU26" s="12">
         <f t="shared" si="17"/>
-        <v>0.86936200934757002</v>
+        <v>0.86943800585173081</v>
       </c>
       <c r="AV26" s="18">
         <v>15987</v>
@@ -4939,14 +4939,14 @@
       </c>
       <c r="AX26" s="10">
         <f t="shared" si="18"/>
-        <v>3713</v>
+        <v>3714</v>
       </c>
       <c r="AY26" s="20">
-        <v>12836</v>
+        <v>12837</v>
       </c>
       <c r="AZ26" s="12">
         <f t="shared" si="19"/>
-        <v>0.80290235816600986</v>
+        <v>0.80296490898855322</v>
       </c>
       <c r="BA26" s="18">
         <v>16133</v>
@@ -4956,14 +4956,14 @@
       </c>
       <c r="BC26" s="10">
         <f t="shared" si="20"/>
-        <v>3784</v>
+        <v>3785</v>
       </c>
       <c r="BD26" s="20">
-        <v>13024</v>
+        <v>13025</v>
       </c>
       <c r="BE26" s="12">
         <f t="shared" si="21"/>
-        <v>0.80728940680592576</v>
+        <v>0.80735139155767677</v>
       </c>
       <c r="BF26" s="18">
         <v>26642</v>
@@ -4973,14 +4973,14 @@
       </c>
       <c r="BH26" s="10">
         <f t="shared" si="22"/>
-        <v>6317</v>
+        <v>6319</v>
       </c>
       <c r="BI26" s="11">
-        <v>23223</v>
+        <v>23225</v>
       </c>
       <c r="BJ26" s="12">
         <f t="shared" si="23"/>
-        <v>0.87166879363411154</v>
+        <v>0.87174386307334284</v>
       </c>
       <c r="BK26" s="24"/>
       <c r="BL26" s="24"/>
@@ -5000,14 +5000,14 @@
       </c>
       <c r="E27" s="10">
         <f t="shared" si="0"/>
-        <v>84769</v>
+        <v>84773</v>
       </c>
       <c r="F27" s="20">
-        <v>102173</v>
+        <v>102177</v>
       </c>
       <c r="G27" s="12">
         <f t="shared" si="1"/>
-        <v>0.90549199287467763</v>
+        <v>0.90552744223969084</v>
       </c>
       <c r="H27" s="15">
         <v>111842</v>
@@ -5017,14 +5017,14 @@
       </c>
       <c r="J27" s="10">
         <f t="shared" si="2"/>
-        <v>84475</v>
+        <v>84479</v>
       </c>
       <c r="K27" s="20">
-        <v>102027</v>
+        <v>102031</v>
       </c>
       <c r="L27" s="12">
         <f t="shared" si="3"/>
-        <v>0.91224227034566618</v>
+        <v>0.91227803508520944</v>
       </c>
       <c r="M27" s="16">
         <v>156288</v>
@@ -5034,14 +5034,14 @@
       </c>
       <c r="O27" s="10">
         <f t="shared" si="4"/>
-        <v>74497</v>
+        <v>74501</v>
       </c>
       <c r="P27" s="13">
-        <v>145750</v>
+        <v>145754</v>
       </c>
       <c r="Q27" s="12">
         <f t="shared" si="5"/>
-        <v>0.93257319819819817</v>
+        <v>0.93259879197379192</v>
       </c>
       <c r="R27" s="16">
         <v>113087</v>
@@ -5051,14 +5051,14 @@
       </c>
       <c r="T27" s="10">
         <f t="shared" si="6"/>
-        <v>39370</v>
+        <v>39374</v>
       </c>
       <c r="U27" s="20">
-        <v>104498</v>
+        <v>104502</v>
       </c>
       <c r="V27" s="12">
         <f t="shared" si="7"/>
-        <v>0.92404962550956349</v>
+        <v>0.92408499650711395</v>
       </c>
       <c r="W27" s="16">
         <v>116164</v>
@@ -5068,14 +5068,14 @@
       </c>
       <c r="Y27" s="10">
         <f t="shared" si="8"/>
-        <v>38417</v>
+        <v>38420</v>
       </c>
       <c r="Z27" s="20">
-        <v>108027</v>
+        <v>108030</v>
       </c>
       <c r="AA27" s="12">
         <f t="shared" si="9"/>
-        <v>0.92995248097517302</v>
+        <v>0.92997830653214419</v>
       </c>
       <c r="AB27" s="17">
         <v>165468</v>
@@ -5085,14 +5085,14 @@
       </c>
       <c r="AD27" s="10">
         <f t="shared" si="10"/>
-        <v>48098</v>
+        <v>48101</v>
       </c>
       <c r="AE27" s="11">
-        <v>155637</v>
+        <v>155640</v>
       </c>
       <c r="AF27" s="12">
         <f t="shared" si="11"/>
-        <v>0.94058669954311402</v>
+        <v>0.94060482993690619</v>
       </c>
       <c r="AG27" s="16">
         <v>116084</v>
@@ -5102,14 +5102,14 @@
       </c>
       <c r="AI27" s="10">
         <f t="shared" si="12"/>
-        <v>32763</v>
+        <v>32766</v>
       </c>
       <c r="AJ27" s="20">
-        <v>107140</v>
+        <v>107143</v>
       </c>
       <c r="AK27" s="12">
         <f t="shared" si="13"/>
-        <v>0.92295234485372657</v>
+        <v>0.92297818820853861</v>
       </c>
       <c r="AL27" s="18">
         <v>117992</v>
@@ -5119,14 +5119,14 @@
       </c>
       <c r="AN27" s="10">
         <f t="shared" si="14"/>
-        <v>33347</v>
+        <v>33350</v>
       </c>
       <c r="AO27" s="11">
-        <v>109171</v>
+        <v>109174</v>
       </c>
       <c r="AP27" s="12">
         <f t="shared" si="15"/>
-        <v>0.92524069428435829</v>
+        <v>0.92526611973693129</v>
       </c>
       <c r="AQ27" s="11">
         <v>170879</v>
@@ -5136,14 +5136,14 @@
       </c>
       <c r="AS27" s="10">
         <f t="shared" si="16"/>
-        <v>45159</v>
+        <v>45162</v>
       </c>
       <c r="AT27" s="13">
-        <v>160509</v>
+        <v>160512</v>
       </c>
       <c r="AU27" s="12">
         <f t="shared" si="17"/>
-        <v>0.93931378343740313</v>
+        <v>0.93933133971991878</v>
       </c>
       <c r="AV27" s="18">
         <v>116485</v>
@@ -5153,14 +5153,14 @@
       </c>
       <c r="AX27" s="10">
         <f t="shared" si="18"/>
-        <v>34158</v>
+        <v>34162</v>
       </c>
       <c r="AY27" s="20">
-        <v>109515</v>
+        <v>109519</v>
       </c>
       <c r="AZ27" s="12">
         <f t="shared" si="19"/>
-        <v>0.94016396960982096</v>
+        <v>0.94019830879512378</v>
       </c>
       <c r="BA27" s="18">
         <v>117017</v>
@@ -5170,14 +5170,14 @@
       </c>
       <c r="BC27" s="10">
         <f t="shared" si="20"/>
-        <v>38106</v>
+        <v>38110</v>
       </c>
       <c r="BD27" s="20">
-        <v>111408</v>
+        <v>111412</v>
       </c>
       <c r="BE27" s="12">
         <f t="shared" si="21"/>
-        <v>0.95206679371373393</v>
+        <v>0.95210097678115146</v>
       </c>
       <c r="BF27" s="18">
         <v>172738</v>
@@ -5187,14 +5187,14 @@
       </c>
       <c r="BH27" s="10">
         <f t="shared" si="22"/>
-        <v>63104</v>
+        <v>63109</v>
       </c>
       <c r="BI27" s="11">
-        <v>164649</v>
+        <v>164654</v>
       </c>
       <c r="BJ27" s="12">
         <f t="shared" si="23"/>
-        <v>0.95317185564264961</v>
+        <v>0.95320080121339834</v>
       </c>
       <c r="BK27" s="24"/>
       <c r="BL27" s="24"/>
@@ -5214,14 +5214,14 @@
       </c>
       <c r="E28" s="10">
         <f t="shared" si="0"/>
-        <v>248064</v>
+        <v>248066</v>
       </c>
       <c r="F28" s="20">
-        <v>327099</v>
+        <v>327101</v>
       </c>
       <c r="G28" s="12">
         <f t="shared" si="1"/>
-        <v>0.8682284740526035</v>
+        <v>0.86823378271129126</v>
       </c>
       <c r="H28" s="15">
         <v>377506</v>
@@ -5231,14 +5231,14 @@
       </c>
       <c r="J28" s="10">
         <f t="shared" si="2"/>
-        <v>256660</v>
+        <v>256661</v>
       </c>
       <c r="K28" s="20">
-        <v>327718</v>
+        <v>327719</v>
       </c>
       <c r="L28" s="12">
         <f t="shared" si="3"/>
-        <v>0.86811335448972993</v>
+        <v>0.86811600345424977</v>
       </c>
       <c r="M28" s="16">
         <v>622937</v>
@@ -5248,14 +5248,14 @@
       </c>
       <c r="O28" s="10">
         <f t="shared" si="4"/>
-        <v>184095</v>
+        <v>184096</v>
       </c>
       <c r="P28" s="13">
-        <v>569145</v>
+        <v>569146</v>
       </c>
       <c r="Q28" s="12">
         <f t="shared" si="5"/>
-        <v>0.91364776855444452</v>
+        <v>0.91364937385321465</v>
       </c>
       <c r="R28" s="16">
         <v>379798</v>
@@ -5265,14 +5265,14 @@
       </c>
       <c r="T28" s="10">
         <f t="shared" si="6"/>
-        <v>82841</v>
+        <v>82843</v>
       </c>
       <c r="U28" s="20">
-        <v>329380</v>
+        <v>329382</v>
       </c>
       <c r="V28" s="12">
         <f t="shared" si="7"/>
-        <v>0.86725048578454866</v>
+        <v>0.86725575174171532</v>
       </c>
       <c r="W28" s="16">
         <v>378910</v>
@@ -5282,14 +5282,14 @@
       </c>
       <c r="Y28" s="10">
         <f t="shared" si="8"/>
-        <v>83067</v>
+        <v>83069</v>
       </c>
       <c r="Z28" s="20">
-        <v>334166</v>
+        <v>334168</v>
       </c>
       <c r="AA28" s="12">
         <f t="shared" si="9"/>
-        <v>0.88191391095510807</v>
+        <v>0.88191918925338475</v>
       </c>
       <c r="AB28" s="17">
         <v>628364</v>
@@ -5299,14 +5299,14 @@
       </c>
       <c r="AD28" s="10">
         <f t="shared" si="10"/>
-        <v>120946</v>
+        <v>120948</v>
       </c>
       <c r="AE28" s="11">
-        <v>580309</v>
+        <v>580311</v>
       </c>
       <c r="AF28" s="12">
         <f t="shared" si="11"/>
-        <v>0.92352362643308661</v>
+        <v>0.92352680930161501</v>
       </c>
       <c r="AG28" s="16">
         <v>375124</v>
@@ -5316,14 +5316,14 @@
       </c>
       <c r="AI28" s="10">
         <f t="shared" si="12"/>
-        <v>67357</v>
+        <v>67358</v>
       </c>
       <c r="AJ28" s="20">
-        <v>333741</v>
+        <v>333742</v>
       </c>
       <c r="AK28" s="12">
         <f t="shared" si="13"/>
-        <v>0.88968181188087136</v>
+        <v>0.88968447766605174</v>
       </c>
       <c r="AL28" s="18">
         <v>368781</v>
@@ -5333,14 +5333,14 @@
       </c>
       <c r="AN28" s="10">
         <f t="shared" si="14"/>
-        <v>68520</v>
+        <v>68521</v>
       </c>
       <c r="AO28" s="11">
-        <v>338476</v>
+        <v>338477</v>
       </c>
       <c r="AP28" s="12">
         <f t="shared" si="15"/>
-        <v>0.91782385751977458</v>
+        <v>0.91782656915622007</v>
       </c>
       <c r="AQ28" s="11">
         <v>617418</v>
@@ -5350,14 +5350,14 @@
       </c>
       <c r="AS28" s="10">
         <f t="shared" si="16"/>
-        <v>98509</v>
+        <v>98510</v>
       </c>
       <c r="AT28" s="13">
-        <v>590271</v>
+        <v>590272</v>
       </c>
       <c r="AU28" s="12">
         <f t="shared" si="17"/>
-        <v>0.95603140821939103</v>
+        <v>0.95603302786766831</v>
       </c>
       <c r="AV28" s="18">
         <v>357852</v>
@@ -5367,14 +5367,14 @@
       </c>
       <c r="AX28" s="10">
         <f t="shared" si="18"/>
-        <v>67576</v>
+        <v>67578</v>
       </c>
       <c r="AY28" s="20">
-        <v>340248</v>
+        <v>340250</v>
       </c>
       <c r="AZ28" s="12">
         <f t="shared" si="19"/>
-        <v>0.95080647865598067</v>
+        <v>0.95081206755865555</v>
       </c>
       <c r="BA28" s="18">
         <v>359943</v>
@@ -5384,14 +5384,14 @@
       </c>
       <c r="BC28" s="10">
         <f t="shared" si="20"/>
-        <v>73128</v>
+        <v>73130</v>
       </c>
       <c r="BD28" s="20">
-        <v>344956</v>
+        <v>344958</v>
       </c>
       <c r="BE28" s="12">
         <f t="shared" si="21"/>
-        <v>0.95836285189599468</v>
+        <v>0.95836840833131909</v>
       </c>
       <c r="BF28" s="18">
         <v>622234</v>
@@ -5401,14 +5401,14 @@
       </c>
       <c r="BH28" s="10">
         <f t="shared" si="22"/>
-        <v>124732</v>
+        <v>124734</v>
       </c>
       <c r="BI28" s="11">
-        <v>600524</v>
+        <v>600526</v>
       </c>
       <c r="BJ28" s="12">
         <f t="shared" si="23"/>
-        <v>0.96510958899706545</v>
+        <v>0.96511280322193904</v>
       </c>
       <c r="BK28" s="24"/>
       <c r="BL28" s="24"/>
@@ -5462,14 +5462,14 @@
       </c>
       <c r="O29" s="10">
         <f t="shared" si="4"/>
-        <v>58703</v>
+        <v>58704</v>
       </c>
       <c r="P29" s="13">
-        <v>150184</v>
+        <v>150185</v>
       </c>
       <c r="Q29" s="12">
         <f t="shared" si="5"/>
-        <v>0.96731268396679093</v>
+        <v>0.96731912481724092</v>
       </c>
       <c r="R29" s="16">
         <v>111838</v>
@@ -5513,14 +5513,14 @@
       </c>
       <c r="AD29" s="10">
         <f t="shared" si="10"/>
-        <v>33489</v>
+        <v>33490</v>
       </c>
       <c r="AE29" s="11">
-        <v>154119</v>
+        <v>154120</v>
       </c>
       <c r="AF29" s="12">
         <f t="shared" si="11"/>
-        <v>0.96229949362188349</v>
+        <v>0.96230573749508297</v>
       </c>
       <c r="AG29" s="16">
         <v>115309</v>
@@ -5564,14 +5564,14 @@
       </c>
       <c r="AS29" s="10">
         <f t="shared" si="16"/>
-        <v>29546</v>
+        <v>29547</v>
       </c>
       <c r="AT29" s="13">
-        <v>157110</v>
+        <v>157111</v>
       </c>
       <c r="AU29" s="12">
         <f t="shared" si="17"/>
-        <v>0.95572088156750146</v>
+        <v>0.95572696469958451</v>
       </c>
       <c r="AV29" s="18">
         <v>118862</v>
@@ -5615,14 +5615,14 @@
       </c>
       <c r="BH29" s="10">
         <f t="shared" si="22"/>
-        <v>41679</v>
+        <v>41680</v>
       </c>
       <c r="BI29" s="11">
-        <v>160683</v>
+        <v>160684</v>
       </c>
       <c r="BJ29" s="12">
         <f t="shared" si="23"/>
-        <v>0.96071819339563413</v>
+        <v>0.96072417236163177</v>
       </c>
       <c r="BK29" s="24"/>
       <c r="BL29" s="24"/>
@@ -5642,14 +5642,14 @@
       </c>
       <c r="E30" s="10">
         <f t="shared" si="0"/>
-        <v>116751</v>
+        <v>116753</v>
       </c>
       <c r="F30" s="20">
-        <v>143235</v>
+        <v>143237</v>
       </c>
       <c r="G30" s="12">
         <f t="shared" si="1"/>
-        <v>0.95926786635145367</v>
+        <v>0.95928126067360042</v>
       </c>
       <c r="H30" s="15">
         <v>149659</v>
@@ -5659,14 +5659,14 @@
       </c>
       <c r="J30" s="10">
         <f t="shared" si="2"/>
-        <v>116062</v>
+        <v>116063</v>
       </c>
       <c r="K30" s="20">
-        <v>143991</v>
+        <v>143992</v>
       </c>
       <c r="L30" s="12">
         <f t="shared" si="3"/>
-        <v>0.96212723591631644</v>
+        <v>0.96213391777307078</v>
       </c>
       <c r="M30" s="16">
         <v>249952</v>
@@ -5676,14 +5676,14 @@
       </c>
       <c r="O30" s="10">
         <f t="shared" si="4"/>
-        <v>99038</v>
+        <v>99040</v>
       </c>
       <c r="P30" s="13">
-        <v>241545</v>
+        <v>241547</v>
       </c>
       <c r="Q30" s="12">
         <f t="shared" si="5"/>
-        <v>0.96636554218409931</v>
+        <v>0.9663735437203943</v>
       </c>
       <c r="R30" s="16">
         <v>151431</v>
@@ -5693,14 +5693,14 @@
       </c>
       <c r="T30" s="10">
         <f t="shared" si="6"/>
-        <v>43787</v>
+        <v>43789</v>
       </c>
       <c r="U30" s="20">
-        <v>143282</v>
+        <v>143284</v>
       </c>
       <c r="V30" s="12">
         <f t="shared" si="7"/>
-        <v>0.94618671209990024</v>
+        <v>0.94619991943525439</v>
       </c>
       <c r="W30" s="16">
         <v>154416</v>
@@ -5710,14 +5710,14 @@
       </c>
       <c r="Y30" s="10">
         <f t="shared" si="8"/>
-        <v>43107</v>
+        <v>43109</v>
       </c>
       <c r="Z30" s="20">
-        <v>146807</v>
+        <v>146809</v>
       </c>
       <c r="AA30" s="12">
         <f t="shared" si="9"/>
-        <v>0.95072401823645214</v>
+        <v>0.95073697026214898</v>
       </c>
       <c r="AB30" s="17">
         <v>259264</v>
@@ -5727,14 +5727,14 @@
       </c>
       <c r="AD30" s="10">
         <f t="shared" si="10"/>
-        <v>60274</v>
+        <v>60276</v>
       </c>
       <c r="AE30" s="11">
-        <v>248441</v>
+        <v>248443</v>
       </c>
       <c r="AF30" s="12">
         <f t="shared" si="11"/>
-        <v>0.95825490619600096</v>
+        <v>0.95826262034065668</v>
       </c>
       <c r="AG30" s="16">
         <v>153178</v>
@@ -5744,14 +5744,14 @@
       </c>
       <c r="AI30" s="10">
         <f t="shared" si="12"/>
-        <v>35794</v>
+        <v>35796</v>
       </c>
       <c r="AJ30" s="20">
-        <v>144598</v>
+        <v>144600</v>
       </c>
       <c r="AK30" s="12">
         <f t="shared" si="13"/>
-        <v>0.94398673438744463</v>
+        <v>0.9439997910927157</v>
       </c>
       <c r="AL30" s="18">
         <v>156106</v>
@@ -5761,14 +5761,14 @@
       </c>
       <c r="AN30" s="10">
         <f t="shared" si="14"/>
-        <v>37174</v>
+        <v>37176</v>
       </c>
       <c r="AO30" s="11">
-        <v>147870</v>
+        <v>147872</v>
       </c>
       <c r="AP30" s="12">
         <f t="shared" si="15"/>
-        <v>0.9472409772846655</v>
+        <v>0.94725378909202718</v>
       </c>
       <c r="AQ30" s="11">
         <v>266513</v>
@@ -5778,14 +5778,14 @@
       </c>
       <c r="AS30" s="10">
         <f t="shared" si="16"/>
-        <v>56621</v>
+        <v>56623</v>
       </c>
       <c r="AT30" s="13">
-        <v>254741</v>
+        <v>254743</v>
       </c>
       <c r="AU30" s="12">
         <f t="shared" si="17"/>
-        <v>0.95582954677632981</v>
+        <v>0.95583705110069672</v>
       </c>
       <c r="AV30" s="18">
         <v>155103</v>
@@ -5795,14 +5795,14 @@
       </c>
       <c r="AX30" s="10">
         <f t="shared" si="18"/>
-        <v>39203</v>
+        <v>39204</v>
       </c>
       <c r="AY30" s="20">
-        <v>148220</v>
+        <v>148221</v>
       </c>
       <c r="AZ30" s="12">
         <f t="shared" si="19"/>
-        <v>0.95562303759437273</v>
+        <v>0.95562948492292221</v>
       </c>
       <c r="BA30" s="18">
         <v>156855</v>
@@ -5812,14 +5812,14 @@
       </c>
       <c r="BC30" s="10">
         <f t="shared" si="20"/>
-        <v>41864</v>
+        <v>41865</v>
       </c>
       <c r="BD30" s="20">
-        <v>150794</v>
+        <v>150795</v>
       </c>
       <c r="BE30" s="12">
         <f t="shared" si="21"/>
-        <v>0.96135921711134487</v>
+        <v>0.96136559242612607</v>
       </c>
       <c r="BF30" s="18">
         <v>270589</v>
@@ -5829,14 +5829,14 @@
       </c>
       <c r="BH30" s="10">
         <f t="shared" si="22"/>
-        <v>73590</v>
+        <v>73592</v>
       </c>
       <c r="BI30" s="11">
-        <v>259805</v>
+        <v>259807</v>
       </c>
       <c r="BJ30" s="12">
         <f t="shared" si="23"/>
-        <v>0.96014619958682723</v>
+        <v>0.96015359087028662</v>
       </c>
       <c r="BK30" s="24"/>
       <c r="BL30" s="24"/>
@@ -5856,14 +5856,14 @@
       </c>
       <c r="E31" s="10">
         <f t="shared" si="0"/>
-        <v>57273</v>
+        <v>57274</v>
       </c>
       <c r="F31" s="20">
-        <v>69166</v>
+        <v>69167</v>
       </c>
       <c r="G31" s="12">
         <f t="shared" si="1"/>
-        <v>0.96281860322674939</v>
+        <v>0.96283252362988436</v>
       </c>
       <c r="H31" s="15">
         <v>72505</v>
@@ -5941,14 +5941,14 @@
       </c>
       <c r="AD31" s="10">
         <f t="shared" si="10"/>
-        <v>35714</v>
+        <v>35715</v>
       </c>
       <c r="AE31" s="11">
-        <v>119899</v>
+        <v>119900</v>
       </c>
       <c r="AF31" s="12">
         <f t="shared" si="11"/>
-        <v>0.96312927246584035</v>
+        <v>0.96313730530408315</v>
       </c>
       <c r="AG31" s="16">
         <v>73552</v>
@@ -5992,14 +5992,14 @@
       </c>
       <c r="AS31" s="10">
         <f t="shared" si="16"/>
-        <v>34479</v>
+        <v>34483</v>
       </c>
       <c r="AT31" s="13">
-        <v>122368</v>
+        <v>122372</v>
       </c>
       <c r="AU31" s="12">
         <f t="shared" si="17"/>
-        <v>0.96622080444704139</v>
+        <v>0.96625238854760509</v>
       </c>
       <c r="AV31" s="18">
         <v>72827</v>
@@ -6043,14 +6043,14 @@
       </c>
       <c r="BH31" s="10">
         <f t="shared" si="22"/>
-        <v>48856</v>
+        <v>48860</v>
       </c>
       <c r="BI31" s="11">
-        <v>125617</v>
+        <v>125621</v>
       </c>
       <c r="BJ31" s="12">
         <f t="shared" si="23"/>
-        <v>0.96960364324032267</v>
+        <v>0.96963451815831114</v>
       </c>
       <c r="BK31" s="24"/>
       <c r="BL31" s="24"/>
@@ -6301,14 +6301,14 @@
       </c>
       <c r="J33" s="10">
         <f t="shared" si="2"/>
-        <v>390448</v>
+        <v>390449</v>
       </c>
       <c r="K33" s="20">
-        <v>543648</v>
+        <v>543649</v>
       </c>
       <c r="L33" s="12">
         <f t="shared" si="3"/>
-        <v>0.9732017228231099</v>
+        <v>0.97320351295518581</v>
       </c>
       <c r="M33" s="16">
         <v>943614</v>
@@ -6318,14 +6318,14 @@
       </c>
       <c r="O33" s="10">
         <f t="shared" si="4"/>
-        <v>222023</v>
+        <v>222024</v>
       </c>
       <c r="P33" s="13">
-        <v>930042</v>
+        <v>930043</v>
       </c>
       <c r="Q33" s="12">
         <f t="shared" si="5"/>
-        <v>0.98561700017168041</v>
+        <v>0.98561805992704643</v>
       </c>
       <c r="R33" s="16">
         <v>563773</v>
@@ -6335,14 +6335,14 @@
       </c>
       <c r="T33" s="10">
         <f t="shared" si="6"/>
-        <v>103843</v>
+        <v>103844</v>
       </c>
       <c r="U33" s="20">
-        <v>552423</v>
+        <v>552424</v>
       </c>
       <c r="V33" s="12">
         <f t="shared" si="7"/>
-        <v>0.97986778366470195</v>
+        <v>0.97986955742825566</v>
       </c>
       <c r="W33" s="16">
         <v>571583</v>
@@ -6352,14 +6352,14 @@
       </c>
       <c r="Y33" s="10">
         <f t="shared" si="8"/>
-        <v>110954</v>
+        <v>110955</v>
       </c>
       <c r="Z33" s="20">
-        <v>558698</v>
+        <v>558699</v>
       </c>
       <c r="AA33" s="12">
         <f t="shared" si="9"/>
-        <v>0.97745734215328306</v>
+        <v>0.9774590916804734</v>
       </c>
       <c r="AB33" s="17">
         <v>961057</v>
@@ -6369,14 +6369,14 @@
       </c>
       <c r="AD33" s="10">
         <f t="shared" si="10"/>
-        <v>149479</v>
+        <v>149480</v>
       </c>
       <c r="AE33" s="11">
-        <v>945168</v>
+        <v>945169</v>
       </c>
       <c r="AF33" s="12">
         <f t="shared" si="11"/>
-        <v>0.98346716167719506</v>
+        <v>0.98346820219820463</v>
       </c>
       <c r="AG33" s="16">
         <v>565645</v>
@@ -6386,14 +6386,14 @@
       </c>
       <c r="AI33" s="10">
         <f t="shared" si="12"/>
-        <v>97880</v>
+        <v>97881</v>
       </c>
       <c r="AJ33" s="20">
-        <v>554660</v>
+        <v>554661</v>
       </c>
       <c r="AK33" s="12">
         <f t="shared" si="13"/>
-        <v>0.98057969220977825</v>
+        <v>0.98058146010306813</v>
       </c>
       <c r="AL33" s="18">
         <v>569536</v>
@@ -6403,14 +6403,14 @@
       </c>
       <c r="AN33" s="10">
         <f t="shared" si="14"/>
-        <v>93729</v>
+        <v>93730</v>
       </c>
       <c r="AO33" s="11">
-        <v>559624</v>
+        <v>559625</v>
       </c>
       <c r="AP33" s="12">
         <f t="shared" si="15"/>
-        <v>0.98259635914147658</v>
+        <v>0.98259811495673666</v>
       </c>
       <c r="AQ33" s="11">
         <v>971221</v>
@@ -6420,14 +6420,14 @@
       </c>
       <c r="AS33" s="10">
         <f t="shared" si="16"/>
-        <v>154795</v>
+        <v>154796</v>
       </c>
       <c r="AT33" s="13">
-        <v>956295</v>
+        <v>956296</v>
       </c>
       <c r="AU33" s="12">
         <f t="shared" si="17"/>
-        <v>0.98463171615934997</v>
+        <v>0.9846327457911227</v>
       </c>
       <c r="AV33" s="18">
         <v>571074</v>
@@ -6437,14 +6437,14 @@
       </c>
       <c r="AX33" s="10">
         <f t="shared" si="18"/>
-        <v>92999</v>
+        <v>93000</v>
       </c>
       <c r="AY33" s="20">
-        <v>564192</v>
+        <v>564193</v>
       </c>
       <c r="AZ33" s="12">
         <f t="shared" si="19"/>
-        <v>0.98794902236837956</v>
+        <v>0.98795077345492877</v>
       </c>
       <c r="BA33" s="18">
         <v>575700</v>
@@ -6454,14 +6454,14 @@
       </c>
       <c r="BC33" s="10">
         <f t="shared" si="20"/>
-        <v>96947</v>
+        <v>96948</v>
       </c>
       <c r="BD33" s="20">
-        <v>573853</v>
+        <v>573854</v>
       </c>
       <c r="BE33" s="12">
         <f t="shared" si="21"/>
-        <v>0.99679173180475944</v>
+        <v>0.9967934688205663</v>
       </c>
       <c r="BF33" s="18">
         <v>986775</v>
@@ -6471,14 +6471,14 @@
       </c>
       <c r="BH33" s="10">
         <f t="shared" si="22"/>
-        <v>171034</v>
+        <v>171035</v>
       </c>
       <c r="BI33" s="11">
-        <v>975798</v>
+        <v>975799</v>
       </c>
       <c r="BJ33" s="12">
         <f t="shared" si="23"/>
-        <v>0.98887588356008205</v>
+        <v>0.98887689696232672</v>
       </c>
       <c r="BK33" s="24"/>
       <c r="BL33" s="24"/>
@@ -6902,14 +6902,14 @@
       </c>
       <c r="E36" s="10">
         <f t="shared" si="0"/>
-        <v>551050</v>
+        <v>551054</v>
       </c>
       <c r="F36" s="20">
-        <v>726057</v>
+        <v>726061</v>
       </c>
       <c r="G36" s="12">
         <f t="shared" si="1"/>
-        <v>0.97115001350942853</v>
+        <v>0.97115536377814571</v>
       </c>
       <c r="H36" s="15">
         <v>754952</v>
@@ -6919,14 +6919,14 @@
       </c>
       <c r="J36" s="10">
         <f t="shared" si="2"/>
-        <v>545534</v>
+        <v>545537</v>
       </c>
       <c r="K36" s="20">
-        <v>731884</v>
+        <v>731887</v>
       </c>
       <c r="L36" s="12">
         <f t="shared" si="3"/>
-        <v>0.96944441500916612</v>
+        <v>0.96944838877173645</v>
       </c>
       <c r="M36" s="16">
         <v>1378095</v>
@@ -6936,14 +6936,14 @@
       </c>
       <c r="O36" s="10">
         <f t="shared" si="4"/>
-        <v>493436</v>
+        <v>493441</v>
       </c>
       <c r="P36" s="13">
-        <v>1346547</v>
+        <v>1346552</v>
       </c>
       <c r="Q36" s="12">
         <f t="shared" si="5"/>
-        <v>0.97710752887137675</v>
+        <v>0.97711115706827179</v>
       </c>
       <c r="R36" s="16">
         <v>758000</v>
@@ -6953,14 +6953,14 @@
       </c>
       <c r="T36" s="10">
         <f t="shared" si="6"/>
-        <v>231296</v>
+        <v>231302</v>
       </c>
       <c r="U36" s="20">
-        <v>732468</v>
+        <v>732474</v>
       </c>
       <c r="V36" s="12">
         <f t="shared" si="7"/>
-        <v>0.96631662269129293</v>
+        <v>0.96632453825857523</v>
       </c>
       <c r="W36" s="16">
         <v>766789</v>
@@ -6970,14 +6970,14 @@
       </c>
       <c r="Y36" s="10">
         <f t="shared" si="8"/>
-        <v>245536</v>
+        <v>245542</v>
       </c>
       <c r="Z36" s="20">
-        <v>748534</v>
+        <v>748540</v>
       </c>
       <c r="AA36" s="12">
         <f t="shared" si="9"/>
-        <v>0.97619292921520784</v>
+        <v>0.9762007540535923</v>
       </c>
       <c r="AB36" s="17">
         <v>1410553</v>
@@ -6987,14 +6987,14 @@
       </c>
       <c r="AD36" s="10">
         <f t="shared" si="10"/>
-        <v>344786</v>
+        <v>344794</v>
       </c>
       <c r="AE36" s="11">
-        <v>1378463</v>
+        <v>1378471</v>
       </c>
       <c r="AF36" s="12">
         <f t="shared" si="11"/>
-        <v>0.97725005724705138</v>
+        <v>0.97725572878154876</v>
       </c>
       <c r="AG36" s="16">
         <v>767229</v>
@@ -7004,14 +7004,14 @@
       </c>
       <c r="AI36" s="10">
         <f t="shared" si="12"/>
-        <v>202696</v>
+        <v>202702</v>
       </c>
       <c r="AJ36" s="20">
-        <v>744514</v>
+        <v>744520</v>
       </c>
       <c r="AK36" s="12">
         <f t="shared" si="13"/>
-        <v>0.97039345488765416</v>
+        <v>0.97040127523855324</v>
       </c>
       <c r="AL36" s="18">
         <v>779513</v>
@@ -7021,14 +7021,14 @@
       </c>
       <c r="AN36" s="10">
         <f t="shared" si="14"/>
-        <v>205103</v>
+        <v>205109</v>
       </c>
       <c r="AO36" s="11">
-        <v>755701</v>
+        <v>755707</v>
       </c>
       <c r="AP36" s="12">
         <f t="shared" si="15"/>
-        <v>0.96945272240488611</v>
+        <v>0.96946041951834028</v>
       </c>
       <c r="AQ36" s="11">
         <v>1443943</v>
@@ -7038,14 +7038,14 @@
       </c>
       <c r="AS36" s="10">
         <f t="shared" si="16"/>
-        <v>324132</v>
+        <v>324142</v>
       </c>
       <c r="AT36" s="13">
-        <v>1402878</v>
+        <v>1402888</v>
       </c>
       <c r="AU36" s="12">
         <f t="shared" si="17"/>
-        <v>0.97156051173765168</v>
+        <v>0.97156743721878214</v>
       </c>
       <c r="AV36" s="18">
         <v>783108</v>
@@ -7055,14 +7055,14 @@
       </c>
       <c r="AX36" s="10">
         <f t="shared" si="18"/>
-        <v>207941</v>
+        <v>207948</v>
       </c>
       <c r="AY36" s="20">
-        <v>758538</v>
+        <v>758545</v>
       </c>
       <c r="AZ36" s="12">
         <f t="shared" si="19"/>
-        <v>0.96862501723900152</v>
+        <v>0.96863395598052882</v>
       </c>
       <c r="BA36" s="18">
         <v>793830</v>
@@ -7072,14 +7072,14 @@
       </c>
       <c r="BC36" s="10">
         <f t="shared" si="20"/>
-        <v>206317</v>
+        <v>206323</v>
       </c>
       <c r="BD36" s="20">
-        <v>772180</v>
+        <v>772186</v>
       </c>
       <c r="BE36" s="12">
         <f t="shared" si="21"/>
-        <v>0.97272715820767675</v>
+        <v>0.97273471650101406</v>
       </c>
       <c r="BF36" s="18">
         <v>1468416</v>
@@ -7089,14 +7089,14 @@
       </c>
       <c r="BH36" s="10">
         <f t="shared" si="24"/>
-        <v>383735</v>
+        <v>383746</v>
       </c>
       <c r="BI36" s="11">
-        <v>1426401</v>
+        <v>1426412</v>
       </c>
       <c r="BJ36" s="12">
         <f t="shared" si="25"/>
-        <v>0.97138753595711302</v>
+        <v>0.97139502702231517</v>
       </c>
       <c r="BK36" s="24"/>
       <c r="BL36" s="24"/>
@@ -7116,14 +7116,14 @@
       </c>
       <c r="E37" s="10">
         <f t="shared" si="0"/>
-        <v>478356</v>
+        <v>478357</v>
       </c>
       <c r="F37" s="20">
-        <v>566439</v>
+        <v>566440</v>
       </c>
       <c r="G37" s="12">
         <f t="shared" si="1"/>
-        <v>0.95614913143950964</v>
+        <v>0.95615081943968527</v>
       </c>
       <c r="H37" s="15">
         <v>593173</v>
@@ -7133,14 +7133,14 @@
       </c>
       <c r="J37" s="10">
         <f t="shared" si="2"/>
-        <v>459860</v>
+        <v>459862</v>
       </c>
       <c r="K37" s="20">
-        <v>566661</v>
+        <v>566663</v>
       </c>
       <c r="L37" s="12">
         <f t="shared" si="3"/>
-        <v>0.95530477617828191</v>
+        <v>0.95530814787591478</v>
       </c>
       <c r="M37" s="16">
         <v>768378</v>
@@ -7150,14 +7150,14 @@
       </c>
       <c r="O37" s="10">
         <f t="shared" si="4"/>
-        <v>267458</v>
+        <v>267461</v>
       </c>
       <c r="P37" s="13">
-        <v>738201</v>
+        <v>738204</v>
       </c>
       <c r="Q37" s="12">
         <f t="shared" si="5"/>
-        <v>0.96072636124407518</v>
+        <v>0.96073026557241359</v>
       </c>
       <c r="R37" s="16">
         <v>601605</v>
@@ -7167,14 +7167,14 @@
       </c>
       <c r="T37" s="10">
         <f t="shared" si="6"/>
-        <v>144752</v>
+        <v>144755</v>
       </c>
       <c r="U37" s="20">
-        <v>573938</v>
+        <v>573941</v>
       </c>
       <c r="V37" s="12">
         <f t="shared" si="7"/>
-        <v>0.95401135296415418</v>
+        <v>0.9540163396248369</v>
       </c>
       <c r="W37" s="16">
         <v>609453</v>
@@ -7184,14 +7184,14 @@
       </c>
       <c r="Y37" s="10">
         <f t="shared" si="8"/>
-        <v>142435</v>
+        <v>142440</v>
       </c>
       <c r="Z37" s="20">
-        <v>583171</v>
+        <v>583176</v>
       </c>
       <c r="AA37" s="12">
         <f t="shared" si="9"/>
-        <v>0.95687608396381674</v>
+        <v>0.95688428804189984</v>
       </c>
       <c r="AB37" s="17">
         <v>790568</v>
@@ -7201,14 +7201,14 @@
       </c>
       <c r="AD37" s="10">
         <f t="shared" si="10"/>
-        <v>172687</v>
+        <v>172694</v>
       </c>
       <c r="AE37" s="11">
-        <v>759619</v>
+        <v>759626</v>
       </c>
       <c r="AF37" s="12">
         <f t="shared" si="11"/>
-        <v>0.96085219740743366</v>
+        <v>0.96086105180073056</v>
       </c>
       <c r="AG37" s="16">
         <v>617773</v>
@@ -7218,14 +7218,14 @@
       </c>
       <c r="AI37" s="10">
         <f t="shared" si="12"/>
-        <v>117963</v>
+        <v>117967</v>
       </c>
       <c r="AJ37" s="20">
-        <v>589765</v>
+        <v>589769</v>
       </c>
       <c r="AK37" s="12">
         <f t="shared" si="13"/>
-        <v>0.95466295872432105</v>
+        <v>0.95466943359454037</v>
       </c>
       <c r="AL37" s="18">
         <v>624724</v>
@@ -7235,14 +7235,14 @@
       </c>
       <c r="AN37" s="10">
         <f t="shared" si="14"/>
-        <v>122518</v>
+        <v>122523</v>
       </c>
       <c r="AO37" s="11">
-        <v>596607</v>
+        <v>596612</v>
       </c>
       <c r="AP37" s="12">
         <f t="shared" si="15"/>
-        <v>0.95499292487562504</v>
+        <v>0.95500092840998585</v>
       </c>
       <c r="AQ37" s="11">
         <v>810789</v>
@@ -7252,14 +7252,14 @@
       </c>
       <c r="AS37" s="10">
         <f t="shared" si="16"/>
-        <v>156902</v>
+        <v>156909</v>
       </c>
       <c r="AT37" s="13">
-        <v>777510</v>
+        <v>777517</v>
       </c>
       <c r="AU37" s="12">
         <f t="shared" si="17"/>
-        <v>0.95895479588400923</v>
+        <v>0.95896342944958557</v>
       </c>
       <c r="AV37" s="18">
         <v>633338</v>
@@ -7269,14 +7269,14 @@
       </c>
       <c r="AX37" s="10">
         <f t="shared" si="18"/>
-        <v>130837</v>
+        <v>130842</v>
       </c>
       <c r="AY37" s="20">
-        <v>605823</v>
+        <v>605828</v>
       </c>
       <c r="AZ37" s="12">
         <f t="shared" si="19"/>
-        <v>0.95655558327464951</v>
+        <v>0.95656347795332031</v>
       </c>
       <c r="BA37" s="18">
         <v>640933</v>
@@ -7286,14 +7286,14 @@
       </c>
       <c r="BC37" s="10">
         <f t="shared" si="20"/>
-        <v>131362</v>
+        <v>131368</v>
       </c>
       <c r="BD37" s="20">
-        <v>615039</v>
+        <v>615045</v>
       </c>
       <c r="BE37" s="12">
         <f t="shared" si="21"/>
-        <v>0.95959952132282156</v>
+        <v>0.95960888267572431</v>
       </c>
       <c r="BF37" s="18">
         <v>830528</v>
@@ -7303,14 +7303,14 @@
       </c>
       <c r="BH37" s="10">
         <f t="shared" si="24"/>
-        <v>185600</v>
+        <v>185608</v>
       </c>
       <c r="BI37" s="11">
-        <v>797108</v>
+        <v>797116</v>
       </c>
       <c r="BJ37" s="12">
         <f t="shared" si="25"/>
-        <v>0.95976053787470139</v>
+        <v>0.95977017030130229</v>
       </c>
       <c r="BK37" s="24"/>
       <c r="BL37" s="24"/>
@@ -7415,14 +7415,14 @@
       </c>
       <c r="AD38" s="10">
         <f t="shared" si="10"/>
-        <v>9146</v>
+        <v>9147</v>
       </c>
       <c r="AE38" s="11">
-        <v>32051</v>
+        <v>32052</v>
       </c>
       <c r="AF38" s="12">
         <f t="shared" si="11"/>
-        <v>0.88986062524293408</v>
+        <v>0.889888389138764</v>
       </c>
       <c r="AG38" s="16">
         <v>24216</v>
@@ -7466,14 +7466,14 @@
       </c>
       <c r="AS38" s="10">
         <f t="shared" si="16"/>
-        <v>9139</v>
+        <v>9140</v>
       </c>
       <c r="AT38" s="13">
-        <v>32582</v>
+        <v>32583</v>
       </c>
       <c r="AU38" s="12">
         <f t="shared" si="17"/>
-        <v>0.89427457869023441</v>
+        <v>0.89430202558050176</v>
       </c>
       <c r="AV38" s="18">
         <v>24471</v>
@@ -7517,14 +7517,14 @@
       </c>
       <c r="BH38" s="10">
         <f t="shared" si="24"/>
-        <v>10391</v>
+        <v>10392</v>
       </c>
       <c r="BI38" s="11">
-        <v>33148</v>
+        <v>33149</v>
       </c>
       <c r="BJ38" s="12">
         <f t="shared" si="25"/>
-        <v>0.88942552791864549</v>
+        <v>0.88945235987013338</v>
       </c>
       <c r="BK38" s="24"/>
       <c r="BL38" s="24"/>
@@ -7758,14 +7758,14 @@
       </c>
       <c r="E40" s="10">
         <f t="shared" si="0"/>
-        <v>228456</v>
+        <v>228458</v>
       </c>
       <c r="F40" s="20">
-        <v>243741</v>
+        <v>243743</v>
       </c>
       <c r="G40" s="12">
         <f t="shared" si="1"/>
-        <v>0.95564843385492426</v>
+        <v>0.95565627536237563</v>
       </c>
       <c r="H40" s="15">
         <v>254802</v>
@@ -7775,14 +7775,14 @@
       </c>
       <c r="J40" s="10">
         <f t="shared" si="2"/>
-        <v>221637</v>
+        <v>221639</v>
       </c>
       <c r="K40" s="20">
-        <v>243975</v>
+        <v>243977</v>
       </c>
       <c r="L40" s="12">
         <f t="shared" si="3"/>
-        <v>0.95750818282431061</v>
+        <v>0.95751603205626334</v>
       </c>
       <c r="M40" s="16">
         <v>315837</v>
@@ -7792,14 +7792,14 @@
       </c>
       <c r="O40" s="10">
         <f t="shared" si="4"/>
-        <v>162868</v>
+        <v>162870</v>
       </c>
       <c r="P40" s="13">
-        <v>303393</v>
+        <v>303395</v>
       </c>
       <c r="Q40" s="12">
         <f t="shared" si="5"/>
-        <v>0.9605999297105785</v>
+        <v>0.96060626209088862</v>
       </c>
       <c r="R40" s="16">
         <v>257348</v>
@@ -7809,14 +7809,14 @@
       </c>
       <c r="T40" s="10">
         <f t="shared" si="6"/>
-        <v>76823</v>
+        <v>76825</v>
       </c>
       <c r="U40" s="20">
-        <v>245522</v>
+        <v>245524</v>
       </c>
       <c r="V40" s="12">
         <f t="shared" si="7"/>
-        <v>0.95404666055302545</v>
+        <v>0.9540544321308112</v>
       </c>
       <c r="W40" s="16">
         <v>259512</v>
@@ -7826,14 +7826,14 @@
       </c>
       <c r="Y40" s="10">
         <f t="shared" si="8"/>
-        <v>69281</v>
+        <v>69283</v>
       </c>
       <c r="Z40" s="20">
-        <v>247803</v>
+        <v>247805</v>
       </c>
       <c r="AA40" s="12">
         <f t="shared" si="9"/>
-        <v>0.95488069915842044</v>
+        <v>0.95488840593113233</v>
       </c>
       <c r="AB40" s="17">
         <v>322067</v>
@@ -7843,14 +7843,14 @@
       </c>
       <c r="AD40" s="10">
         <f t="shared" si="10"/>
-        <v>74965</v>
+        <v>74966</v>
       </c>
       <c r="AE40" s="11">
-        <v>309031</v>
+        <v>309032</v>
       </c>
       <c r="AF40" s="12">
         <f t="shared" si="11"/>
-        <v>0.95952394998556201</v>
+        <v>0.95952705492956436</v>
       </c>
       <c r="AG40" s="16">
         <v>262041</v>
@@ -7860,14 +7860,14 @@
       </c>
       <c r="AI40" s="10">
         <f t="shared" si="12"/>
-        <v>51915</v>
+        <v>51916</v>
       </c>
       <c r="AJ40" s="20">
-        <v>250268</v>
+        <v>250269</v>
       </c>
       <c r="AK40" s="12">
         <f t="shared" si="13"/>
-        <v>0.95507191622684995</v>
+        <v>0.95507573242355204</v>
       </c>
       <c r="AL40" s="18">
         <v>264607</v>
@@ -7877,14 +7877,14 @@
       </c>
       <c r="AN40" s="10">
         <f t="shared" si="14"/>
-        <v>57106</v>
+        <v>57107</v>
       </c>
       <c r="AO40" s="11">
-        <v>252875</v>
+        <v>252876</v>
       </c>
       <c r="AP40" s="12">
         <f t="shared" si="15"/>
-        <v>0.95566254860982514</v>
+        <v>0.95566632779934013</v>
       </c>
       <c r="AQ40" s="11">
         <v>328683</v>
@@ -7894,14 +7894,14 @@
       </c>
       <c r="AS40" s="10">
         <f t="shared" si="16"/>
-        <v>67746</v>
+        <v>67748</v>
       </c>
       <c r="AT40" s="13">
-        <v>316038</v>
+        <v>316040</v>
       </c>
       <c r="AU40" s="12">
         <f t="shared" si="17"/>
-        <v>0.96152828104891341</v>
+        <v>0.96153436593921804</v>
       </c>
       <c r="AV40" s="18">
         <v>267796</v>
@@ -7911,14 +7911,14 @@
       </c>
       <c r="AX40" s="10">
         <f t="shared" si="18"/>
-        <v>56487</v>
+        <v>56488</v>
       </c>
       <c r="AY40" s="20">
-        <v>256124</v>
+        <v>256125</v>
       </c>
       <c r="AZ40" s="12">
         <f t="shared" si="19"/>
-        <v>0.95641458423576153</v>
+        <v>0.95641831842148506</v>
       </c>
       <c r="BA40" s="18">
         <v>270158</v>
@@ -7945,14 +7945,14 @@
       </c>
       <c r="BH40" s="10">
         <f t="shared" si="24"/>
-        <v>84607</v>
+        <v>84608</v>
       </c>
       <c r="BI40" s="11">
-        <v>321795</v>
+        <v>321796</v>
       </c>
       <c r="BJ40" s="12">
         <f t="shared" si="25"/>
-        <v>0.95911049911479107</v>
+        <v>0.95911347961634985</v>
       </c>
       <c r="BK40" s="24"/>
       <c r="BL40" s="24"/>
@@ -7972,14 +7972,14 @@
       </c>
       <c r="E41" s="10">
         <f t="shared" si="0"/>
-        <v>641249</v>
+        <v>641263</v>
       </c>
       <c r="F41" s="20">
-        <v>777368</v>
+        <v>777382</v>
       </c>
       <c r="G41" s="12">
         <f t="shared" si="1"/>
-        <v>0.9679302324423128</v>
+        <v>0.96794766437063273</v>
       </c>
       <c r="H41" s="15">
         <v>805681</v>
@@ -7989,14 +7989,14 @@
       </c>
       <c r="J41" s="10">
         <f t="shared" si="2"/>
-        <v>648972</v>
+        <v>648982</v>
       </c>
       <c r="K41" s="20">
-        <v>778200</v>
+        <v>778210</v>
       </c>
       <c r="L41" s="12">
         <f t="shared" si="3"/>
-        <v>0.96589096677220887</v>
+        <v>0.9659033786324861</v>
       </c>
       <c r="M41" s="16">
         <v>924274</v>
@@ -8006,14 +8006,14 @@
       </c>
       <c r="O41" s="10">
         <f t="shared" si="4"/>
-        <v>314069</v>
+        <v>314081</v>
       </c>
       <c r="P41" s="13">
-        <v>890831</v>
+        <v>890843</v>
       </c>
       <c r="Q41" s="12">
         <f t="shared" si="5"/>
-        <v>0.96381700664521563</v>
+        <v>0.96382998980821699</v>
       </c>
       <c r="R41" s="16">
         <v>822173</v>
@@ -8023,14 +8023,14 @@
       </c>
       <c r="T41" s="10">
         <f t="shared" si="6"/>
-        <v>171599</v>
+        <v>171614</v>
       </c>
       <c r="U41" s="20">
-        <v>791158</v>
+        <v>791173</v>
       </c>
       <c r="V41" s="12">
         <f t="shared" si="7"/>
-        <v>0.96227679575952996</v>
+        <v>0.9622950400949678</v>
       </c>
       <c r="W41" s="16">
         <v>833879</v>
@@ -8040,14 +8040,14 @@
       </c>
       <c r="Y41" s="10">
         <f t="shared" si="8"/>
-        <v>179570</v>
+        <v>179585</v>
       </c>
       <c r="Z41" s="20">
-        <v>799909</v>
+        <v>799924</v>
       </c>
       <c r="AA41" s="12">
         <f t="shared" si="9"/>
-        <v>0.95926267480054062</v>
+        <v>0.95928066302185333</v>
       </c>
       <c r="AB41" s="17">
         <v>956956</v>
@@ -8057,14 +8057,14 @@
       </c>
       <c r="AD41" s="10">
         <f t="shared" si="10"/>
-        <v>182738</v>
+        <v>182756</v>
       </c>
       <c r="AE41" s="11">
-        <v>915465</v>
+        <v>915483</v>
       </c>
       <c r="AF41" s="12">
         <f t="shared" si="11"/>
-        <v>0.95664272965528196</v>
+        <v>0.95666153929752251</v>
       </c>
       <c r="AG41" s="16">
         <v>851169</v>
@@ -8074,14 +8074,14 @@
       </c>
       <c r="AI41" s="10">
         <f t="shared" si="12"/>
-        <v>150940</v>
+        <v>150958</v>
       </c>
       <c r="AJ41" s="20">
-        <v>811549</v>
+        <v>811567</v>
       </c>
       <c r="AK41" s="12">
         <f t="shared" si="13"/>
-        <v>0.95345225213794205</v>
+        <v>0.95347339952465371</v>
       </c>
       <c r="AL41" s="18">
         <v>859964</v>
@@ -8091,14 +8091,14 @@
       </c>
       <c r="AN41" s="10">
         <f t="shared" si="14"/>
-        <v>152839</v>
+        <v>152858</v>
       </c>
       <c r="AO41" s="11">
-        <v>818555</v>
+        <v>818574</v>
       </c>
       <c r="AP41" s="12">
         <f t="shared" si="15"/>
-        <v>0.9518479843342279</v>
+        <v>0.95187007828234671</v>
       </c>
       <c r="AQ41" s="11">
         <v>982238</v>
@@ -8108,14 +8108,14 @@
       </c>
       <c r="AS41" s="10">
         <f t="shared" si="16"/>
-        <v>184940</v>
+        <v>184958</v>
       </c>
       <c r="AT41" s="13">
-        <v>934365</v>
+        <v>934383</v>
       </c>
       <c r="AU41" s="12">
         <f t="shared" si="17"/>
-        <v>0.95126130326865788</v>
+        <v>0.95127962876614425</v>
       </c>
       <c r="AV41" s="18">
         <v>867973</v>
@@ -8125,14 +8125,14 @@
       </c>
       <c r="AX41" s="10">
         <f t="shared" si="18"/>
-        <v>169799</v>
+        <v>169817</v>
       </c>
       <c r="AY41" s="20">
-        <v>827363</v>
+        <v>827381</v>
       </c>
       <c r="AZ41" s="12">
         <f t="shared" si="19"/>
-        <v>0.95321283035301785</v>
+        <v>0.95323356832528205</v>
       </c>
       <c r="BA41" s="18">
         <v>869274</v>
@@ -8142,14 +8142,14 @@
       </c>
       <c r="BC41" s="10">
         <f t="shared" si="20"/>
-        <v>154198</v>
+        <v>154216</v>
       </c>
       <c r="BD41" s="20">
-        <v>833532</v>
+        <v>833550</v>
       </c>
       <c r="BE41" s="12">
         <f t="shared" si="21"/>
-        <v>0.95888292989322121</v>
+        <v>0.95890363682797364</v>
       </c>
       <c r="BF41" s="18">
         <v>986817</v>
@@ -8159,14 +8159,14 @@
       </c>
       <c r="BH41" s="10">
         <f t="shared" si="24"/>
-        <v>196709</v>
+        <v>196724</v>
       </c>
       <c r="BI41" s="11">
-        <v>950315</v>
+        <v>950330</v>
       </c>
       <c r="BJ41" s="12">
         <f t="shared" si="25"/>
-        <v>0.96301036565036879</v>
+        <v>0.96302556603706668</v>
       </c>
       <c r="BK41" s="24"/>
       <c r="BL41" s="24"/>
@@ -8519,14 +8519,14 @@
       </c>
       <c r="AN43" s="10">
         <f t="shared" si="14"/>
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="AO43" s="11">
-        <v>3069</v>
+        <v>3070</v>
       </c>
       <c r="AP43" s="12">
         <f t="shared" si="15"/>
-        <v>0.91913746630727766</v>
+        <v>0.91943695717280627</v>
       </c>
       <c r="AQ43" s="11">
         <v>4111</v>
@@ -8536,14 +8536,14 @@
       </c>
       <c r="AS43" s="10">
         <f t="shared" si="16"/>
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="AT43" s="13">
-        <v>3855</v>
+        <v>3856</v>
       </c>
       <c r="AU43" s="12">
         <f t="shared" si="17"/>
-        <v>0.93772804670396492</v>
+        <v>0.93797129652152766</v>
       </c>
       <c r="AV43" s="18">
         <v>3256</v>
@@ -8553,14 +8553,14 @@
       </c>
       <c r="AX43" s="10">
         <f t="shared" si="18"/>
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="AY43" s="20">
-        <v>3104</v>
+        <v>3105</v>
       </c>
       <c r="AZ43" s="12">
         <f t="shared" si="19"/>
-        <v>0.95331695331695332</v>
+        <v>0.95362407862407861</v>
       </c>
       <c r="BA43" s="18">
         <v>3286</v>
@@ -8570,14 +8570,14 @@
       </c>
       <c r="BC43" s="10">
         <f t="shared" si="20"/>
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="BD43" s="20">
-        <v>3125</v>
+        <v>3126</v>
       </c>
       <c r="BE43" s="12">
         <f t="shared" si="21"/>
-        <v>0.95100426049908704</v>
+        <v>0.95130858186244671</v>
       </c>
       <c r="BF43" s="18">
         <v>4091</v>
@@ -8587,14 +8587,14 @@
       </c>
       <c r="BH43" s="10">
         <f t="shared" si="24"/>
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="BI43" s="11">
-        <v>3930</v>
+        <v>3931</v>
       </c>
       <c r="BJ43" s="12">
         <f t="shared" si="25"/>
-        <v>0.96064531899291128</v>
+        <v>0.96088975800537768</v>
       </c>
       <c r="BK43" s="24"/>
       <c r="BL43" s="24"/>
@@ -8614,14 +8614,14 @@
       </c>
       <c r="E44" s="10">
         <f t="shared" si="0"/>
-        <v>211700</v>
+        <v>211701</v>
       </c>
       <c r="F44" s="20">
-        <v>276067</v>
+        <v>276068</v>
       </c>
       <c r="G44" s="12">
         <f t="shared" si="1"/>
-        <v>0.88040833378512406</v>
+        <v>0.88041152289622315</v>
       </c>
       <c r="H44" s="15">
         <v>315037</v>
@@ -8631,14 +8631,14 @@
       </c>
       <c r="J44" s="10">
         <f t="shared" si="2"/>
-        <v>208639</v>
+        <v>208640</v>
       </c>
       <c r="K44" s="20">
-        <v>276731</v>
+        <v>276732</v>
       </c>
       <c r="L44" s="12">
         <f t="shared" si="3"/>
-        <v>0.87840793303643694</v>
+        <v>0.87841110726676552</v>
       </c>
       <c r="M44" s="16">
         <v>378050</v>
@@ -8648,14 +8648,14 @@
       </c>
       <c r="O44" s="10">
         <f t="shared" si="4"/>
-        <v>137101</v>
+        <v>137102</v>
       </c>
       <c r="P44" s="13">
-        <v>338588</v>
+        <v>338589</v>
       </c>
       <c r="Q44" s="12">
         <f t="shared" si="5"/>
-        <v>0.8956169818807036</v>
+        <v>0.89561962703346121</v>
       </c>
       <c r="R44" s="16">
         <v>322476</v>
@@ -8665,14 +8665,14 @@
       </c>
       <c r="T44" s="10">
         <f t="shared" si="6"/>
-        <v>85420</v>
+        <v>85421</v>
       </c>
       <c r="U44" s="20">
-        <v>282970</v>
+        <v>282971</v>
       </c>
       <c r="V44" s="12">
         <f t="shared" si="7"/>
-        <v>0.87749165829395059</v>
+        <v>0.87749475929991694</v>
       </c>
       <c r="W44" s="16">
         <v>327345</v>
@@ -8682,14 +8682,14 @@
       </c>
       <c r="Y44" s="10">
         <f t="shared" si="8"/>
-        <v>86940</v>
+        <v>86941</v>
       </c>
       <c r="Z44" s="20">
-        <v>286832</v>
+        <v>286833</v>
       </c>
       <c r="AA44" s="12">
         <f t="shared" si="9"/>
-        <v>0.8762376086392033</v>
+        <v>0.8762406635201393</v>
       </c>
       <c r="AB44" s="17">
         <v>393681</v>
@@ -8699,14 +8699,14 @@
       </c>
       <c r="AD44" s="10">
         <f t="shared" si="10"/>
-        <v>94084</v>
+        <v>94085</v>
       </c>
       <c r="AE44" s="11">
-        <v>349808</v>
+        <v>349809</v>
       </c>
       <c r="AF44" s="12">
         <f t="shared" si="11"/>
-        <v>0.88855697887375817</v>
+        <v>0.88855951900142505</v>
       </c>
       <c r="AG44" s="16">
         <v>333199</v>
@@ -8716,14 +8716,14 @@
       </c>
       <c r="AI44" s="10">
         <f t="shared" si="12"/>
-        <v>74157</v>
+        <v>74158</v>
       </c>
       <c r="AJ44" s="20">
-        <v>290346</v>
+        <v>290347</v>
       </c>
       <c r="AK44" s="12">
         <f t="shared" si="13"/>
-        <v>0.87138916983544368</v>
+        <v>0.87139217104493105</v>
       </c>
       <c r="AL44" s="18">
         <v>336893</v>
@@ -8733,14 +8733,14 @@
       </c>
       <c r="AN44" s="10">
         <f t="shared" si="14"/>
-        <v>77993</v>
+        <v>77994</v>
       </c>
       <c r="AO44" s="11">
-        <v>294828</v>
+        <v>294829</v>
       </c>
       <c r="AP44" s="12">
         <f t="shared" si="15"/>
-        <v>0.87513839705781959</v>
+        <v>0.87514136535932774</v>
       </c>
       <c r="AQ44" s="11">
         <v>406157</v>
@@ -8750,14 +8750,14 @@
       </c>
       <c r="AS44" s="10">
         <f t="shared" si="16"/>
-        <v>90443</v>
+        <v>90444</v>
       </c>
       <c r="AT44" s="13">
-        <v>359862</v>
+        <v>359863</v>
       </c>
       <c r="AU44" s="12">
         <f t="shared" si="17"/>
-        <v>0.88601698358024117</v>
+        <v>0.88601944568233471</v>
       </c>
       <c r="AV44" s="18">
         <v>341214</v>
@@ -8767,14 +8767,14 @@
       </c>
       <c r="AX44" s="10">
         <f t="shared" si="18"/>
-        <v>79992</v>
+        <v>79993</v>
       </c>
       <c r="AY44" s="20">
-        <v>298437</v>
+        <v>298438</v>
       </c>
       <c r="AZ44" s="12">
         <f t="shared" si="19"/>
-        <v>0.87463292830892048</v>
+        <v>0.87463585902102492</v>
       </c>
       <c r="BA44" s="18">
         <v>343859</v>
@@ -8784,14 +8784,14 @@
       </c>
       <c r="BC44" s="10">
         <f t="shared" si="20"/>
-        <v>79454</v>
+        <v>79455</v>
       </c>
       <c r="BD44" s="20">
-        <v>302332</v>
+        <v>302333</v>
       </c>
       <c r="BE44" s="12">
         <f t="shared" si="21"/>
-        <v>0.87923247610212329</v>
+        <v>0.87923538427087844</v>
       </c>
       <c r="BF44" s="18">
         <v>410714</v>
@@ -8801,14 +8801,14 @@
       </c>
       <c r="BH44" s="10">
         <f t="shared" si="24"/>
-        <v>103153</v>
+        <v>103154</v>
       </c>
       <c r="BI44" s="11">
-        <v>367431</v>
+        <v>367432</v>
       </c>
       <c r="BJ44" s="12">
         <f t="shared" si="25"/>
-        <v>0.8946152310366825</v>
+        <v>0.8946176658209849</v>
       </c>
       <c r="BK44" s="24"/>
       <c r="BL44" s="24"/>
@@ -8862,14 +8862,14 @@
       </c>
       <c r="O45" s="10">
         <f t="shared" si="4"/>
-        <v>100445</v>
+        <v>100446</v>
       </c>
       <c r="P45" s="13">
-        <v>272783</v>
+        <v>272784</v>
       </c>
       <c r="Q45" s="12">
         <f t="shared" si="5"/>
-        <v>0.93231733575769171</v>
+        <v>0.93232075355621935</v>
       </c>
       <c r="R45" s="16">
         <v>242899</v>
@@ -8879,14 +8879,14 @@
       </c>
       <c r="T45" s="10">
         <f t="shared" si="6"/>
-        <v>58708</v>
+        <v>58710</v>
       </c>
       <c r="U45" s="20">
-        <v>223283</v>
+        <v>223285</v>
       </c>
       <c r="V45" s="12">
         <f t="shared" si="7"/>
-        <v>0.91924215414637356</v>
+        <v>0.91925038802135872</v>
       </c>
       <c r="W45" s="16">
         <v>244806</v>
@@ -8896,14 +8896,14 @@
       </c>
       <c r="Y45" s="10">
         <f t="shared" si="8"/>
-        <v>58456</v>
+        <v>58458</v>
       </c>
       <c r="Z45" s="20">
-        <v>225565</v>
+        <v>225567</v>
       </c>
       <c r="AA45" s="12">
         <f t="shared" si="9"/>
-        <v>0.92140307018618828</v>
+        <v>0.92141123992059015</v>
       </c>
       <c r="AB45" s="17">
         <v>299772</v>
@@ -8913,14 +8913,14 @@
       </c>
       <c r="AD45" s="10">
         <f t="shared" si="10"/>
-        <v>63872</v>
+        <v>63874</v>
       </c>
       <c r="AE45" s="11">
-        <v>277627</v>
+        <v>277629</v>
       </c>
       <c r="AF45" s="12">
         <f t="shared" si="11"/>
-        <v>0.92612718999773158</v>
+        <v>0.92613386173491852</v>
       </c>
       <c r="AG45" s="16">
         <v>246243</v>
@@ -8930,14 +8930,14 @@
       </c>
       <c r="AI45" s="10">
         <f t="shared" si="12"/>
-        <v>48112</v>
+        <v>48115</v>
       </c>
       <c r="AJ45" s="20">
-        <v>227306</v>
+        <v>227309</v>
       </c>
       <c r="AK45" s="12">
         <f t="shared" si="13"/>
-        <v>0.92309629106208091</v>
+        <v>0.92310847414951902</v>
       </c>
       <c r="AL45" s="18">
         <v>247584</v>
@@ -8947,14 +8947,14 @@
       </c>
       <c r="AN45" s="10">
         <f t="shared" si="14"/>
-        <v>51418</v>
+        <v>51421</v>
       </c>
       <c r="AO45" s="11">
-        <v>229456</v>
+        <v>229459</v>
       </c>
       <c r="AP45" s="12">
         <f t="shared" si="15"/>
-        <v>0.92678040584205768</v>
+        <v>0.92679252294170866</v>
       </c>
       <c r="AQ45" s="11">
         <v>303759</v>
@@ -8964,14 +8964,14 @@
       </c>
       <c r="AS45" s="10">
         <f t="shared" si="16"/>
-        <v>67565</v>
+        <v>67568</v>
       </c>
       <c r="AT45" s="13">
-        <v>282316</v>
+        <v>282319</v>
       </c>
       <c r="AU45" s="12">
         <f t="shared" si="17"/>
-        <v>0.92940785293604466</v>
+        <v>0.92941772918662491</v>
       </c>
       <c r="AV45" s="18">
         <v>248547</v>
@@ -8981,14 +8981,14 @@
       </c>
       <c r="AX45" s="10">
         <f t="shared" si="18"/>
-        <v>55330</v>
+        <v>55332</v>
       </c>
       <c r="AY45" s="20">
-        <v>230983</v>
+        <v>230985</v>
       </c>
       <c r="AZ45" s="12">
         <f t="shared" si="19"/>
-        <v>0.9293332850527265</v>
+        <v>0.92934133182054102</v>
       </c>
       <c r="BA45" s="18">
         <v>248925</v>
@@ -8998,14 +8998,14 @@
       </c>
       <c r="BC45" s="10">
         <f t="shared" si="20"/>
-        <v>51920</v>
+        <v>51922</v>
       </c>
       <c r="BD45" s="20">
-        <v>233146</v>
+        <v>233148</v>
       </c>
       <c r="BE45" s="12">
         <f t="shared" si="21"/>
-        <v>0.93661142914532491</v>
+        <v>0.93661946369388371</v>
       </c>
       <c r="BF45" s="18">
         <v>305535</v>
@@ -9015,14 +9015,14 @@
       </c>
       <c r="BH45" s="10">
         <f t="shared" si="24"/>
-        <v>79700</v>
+        <v>79702</v>
       </c>
       <c r="BI45" s="11">
-        <v>287201</v>
+        <v>287203</v>
       </c>
       <c r="BJ45" s="12">
         <f t="shared" si="25"/>
-        <v>0.93999378139983958</v>
+        <v>0.94000032729474525</v>
       </c>
       <c r="BK45" s="24"/>
       <c r="BL45" s="24"/>
@@ -9042,14 +9042,14 @@
       </c>
       <c r="E46" s="10">
         <f t="shared" si="0"/>
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="F46" s="20">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="G46" s="12">
         <f t="shared" si="1"/>
-        <v>0.99130434782608701</v>
+        <v>0.99178743961352656</v>
       </c>
       <c r="H46" s="15">
         <v>2134</v>
@@ -9059,14 +9059,14 @@
       </c>
       <c r="J46" s="10">
         <f t="shared" si="2"/>
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="K46" s="20">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="L46" s="12">
         <f t="shared" si="3"/>
-        <v>0.9910965323336457</v>
+        <v>0.99156513589503281</v>
       </c>
       <c r="M46" s="16">
         <v>4565</v>
@@ -9076,14 +9076,14 @@
       </c>
       <c r="O46" s="10">
         <f t="shared" si="4"/>
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="P46" s="13">
-        <v>4524</v>
+        <v>4525</v>
       </c>
       <c r="Q46" s="12">
         <f t="shared" si="5"/>
-        <v>0.99101861993428253</v>
+        <v>0.99123767798466589</v>
       </c>
       <c r="R46" s="16">
         <v>2092</v>
@@ -9093,14 +9093,14 @@
       </c>
       <c r="T46" s="10">
         <f t="shared" si="6"/>
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="U46" s="20">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="V46" s="12">
         <f t="shared" si="7"/>
-        <v>0.96175908221797324</v>
+        <v>0.96223709369024857</v>
       </c>
       <c r="W46" s="16">
         <v>2205</v>
@@ -9110,14 +9110,14 @@
       </c>
       <c r="Y46" s="10">
         <f t="shared" si="8"/>
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="Z46" s="20">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="AA46" s="12">
         <f t="shared" si="9"/>
-        <v>0.96961451247165531</v>
+        <v>0.97006802721088436</v>
       </c>
       <c r="AB46" s="17">
         <v>4967</v>
@@ -9127,14 +9127,14 @@
       </c>
       <c r="AD46" s="10">
         <f t="shared" si="10"/>
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="AE46" s="11">
-        <v>4885</v>
+        <v>4886</v>
       </c>
       <c r="AF46" s="12">
         <f t="shared" si="11"/>
-        <v>0.98349104086974026</v>
+        <v>0.98369236963962148</v>
       </c>
       <c r="AG46" s="16">
         <v>2151</v>
@@ -9144,14 +9144,14 @@
       </c>
       <c r="AI46" s="10">
         <f t="shared" si="12"/>
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AJ46" s="20">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="AK46" s="12">
         <f t="shared" si="13"/>
-        <v>0.94421199442119941</v>
+        <v>0.94467689446768943</v>
       </c>
       <c r="AL46" s="18">
         <v>2221</v>
@@ -9161,14 +9161,14 @@
       </c>
       <c r="AN46" s="10">
         <f t="shared" si="14"/>
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="AO46" s="11">
-        <v>2135</v>
+        <v>2136</v>
       </c>
       <c r="AP46" s="12">
         <f t="shared" si="15"/>
-        <v>0.96127870328680776</v>
+        <v>0.9617289509230077</v>
       </c>
       <c r="AQ46" s="11">
         <v>5242</v>
@@ -9178,14 +9178,14 @@
       </c>
       <c r="AS46" s="10">
         <f t="shared" si="16"/>
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="AT46" s="13">
-        <v>5140</v>
+        <v>5141</v>
       </c>
       <c r="AU46" s="12">
         <f t="shared" si="17"/>
-        <v>0.98054177794734831</v>
+        <v>0.98073254483021743</v>
       </c>
       <c r="AV46" s="18">
         <v>2226</v>
@@ -9195,14 +9195,14 @@
       </c>
       <c r="AX46" s="10">
         <f t="shared" si="18"/>
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AY46" s="20">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="AZ46" s="12">
         <f t="shared" si="19"/>
-        <v>0.96136567834681042</v>
+        <v>0.96181491464510327</v>
       </c>
       <c r="BA46" s="18">
         <v>2322</v>
@@ -9212,14 +9212,14 @@
       </c>
       <c r="BC46" s="10">
         <f t="shared" si="20"/>
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="BD46" s="20">
-        <v>2259</v>
+        <v>2260</v>
       </c>
       <c r="BE46" s="12">
         <f t="shared" si="21"/>
-        <v>0.97286821705426352</v>
+        <v>0.9732988802756245</v>
       </c>
       <c r="BF46" s="18">
         <v>5417</v>
@@ -9229,14 +9229,14 @@
       </c>
       <c r="BH46" s="10">
         <f t="shared" si="24"/>
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="BI46" s="11">
-        <v>5490</v>
+        <v>5491</v>
       </c>
       <c r="BJ46" s="12">
         <f t="shared" si="25"/>
-        <v>1.0134760937788443</v>
+        <v>1.0136606978032121</v>
       </c>
       <c r="BK46" s="24"/>
       <c r="BL46" s="24"/>
@@ -9456,10 +9456,10 @@
       <c r="BL47" s="24"/>
     </row>
     <row r="48" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A48" s="26" t="s">
+      <c r="A48" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="B48" s="26"/>
+      <c r="B48" s="36"/>
       <c r="C48" s="6">
         <f>SUM(C10:C47)</f>
         <v>6932700</v>
@@ -9470,15 +9470,15 @@
       </c>
       <c r="E48" s="8">
         <f t="shared" si="0"/>
-        <v>5340366</v>
+        <v>5340405</v>
       </c>
       <c r="F48" s="7">
         <f>SUM(F10:F47)</f>
-        <v>6558166</v>
+        <v>6558205</v>
       </c>
       <c r="G48" s="9">
         <f t="shared" si="1"/>
-        <v>0.94597573816839042</v>
+        <v>0.94598136368225949</v>
       </c>
       <c r="H48" s="6">
         <f>SUM(H10:H47)</f>
@@ -9490,15 +9490,15 @@
       </c>
       <c r="J48" s="8">
         <f t="shared" si="2"/>
-        <v>5126201</v>
+        <v>5126234</v>
       </c>
       <c r="K48" s="7">
         <f>SUM(K10:K47)</f>
-        <v>6572642</v>
+        <v>6572675</v>
       </c>
       <c r="L48" s="9">
         <f t="shared" si="3"/>
-        <v>0.9456034740483672</v>
+        <v>0.94560822174566217</v>
       </c>
       <c r="M48" s="6">
         <f>SUM(M10:M47)</f>
@@ -9510,15 +9510,15 @@
       </c>
       <c r="O48" s="8">
         <f t="shared" si="4"/>
-        <v>3595351</v>
+        <v>3595396</v>
       </c>
       <c r="P48" s="7">
         <f>SUM(P10:P47)</f>
-        <v>10438806</v>
+        <v>10438851</v>
       </c>
       <c r="Q48" s="9">
         <f t="shared" si="5"/>
-        <v>0.96154778264655405</v>
+        <v>0.96155192772312881</v>
       </c>
       <c r="R48" s="6">
         <f>SUM(R10:R47)</f>
@@ -9530,15 +9530,15 @@
       </c>
       <c r="T48" s="8">
         <f t="shared" si="6"/>
-        <v>1738441</v>
+        <v>1738490</v>
       </c>
       <c r="U48" s="7">
         <f>SUM(U10:U47)</f>
-        <v>6647511</v>
+        <v>6647560</v>
       </c>
       <c r="V48" s="9">
         <f t="shared" si="7"/>
-        <v>0.94716960969124953</v>
+        <v>0.9471765914489142</v>
       </c>
       <c r="W48" s="6">
         <f>SUM(W10:W47)</f>
@@ -9550,15 +9550,15 @@
       </c>
       <c r="Y48" s="8">
         <f t="shared" si="8"/>
-        <v>1753805</v>
+        <v>1753857</v>
       </c>
       <c r="Z48" s="7">
         <f>SUM(Z10:Z47)</f>
-        <v>6780395</v>
+        <v>6780447</v>
       </c>
       <c r="AA48" s="9">
         <f t="shared" si="9"/>
-        <v>0.95151953588759808</v>
+        <v>0.95152683325240739</v>
       </c>
       <c r="AB48" s="6">
         <f>SUM(AB10:AB47)</f>
@@ -9570,15 +9570,15 @@
       </c>
       <c r="AD48" s="8">
         <f t="shared" si="10"/>
-        <v>2305099</v>
+        <v>2305162</v>
       </c>
       <c r="AE48" s="7">
         <f>SUM(AE10:AE47)</f>
-        <v>10747367</v>
+        <v>10747430</v>
       </c>
       <c r="AF48" s="9">
         <f t="shared" si="11"/>
-        <v>0.96120167302586546</v>
+        <v>0.96120730749479166</v>
       </c>
       <c r="AG48" s="6">
         <f>SUM(AG10:AG47)</f>
@@ -9590,15 +9590,15 @@
       </c>
       <c r="AI48" s="8">
         <f t="shared" si="12"/>
-        <v>1483432</v>
+        <v>1483486</v>
       </c>
       <c r="AJ48" s="7">
         <f>SUM(AJ10:AJ47)</f>
-        <v>6764511</v>
+        <v>6764565</v>
       </c>
       <c r="AK48" s="9">
         <f t="shared" si="13"/>
-        <v>0.94910134020271408</v>
+        <v>0.94910891672559516</v>
       </c>
       <c r="AL48" s="6">
         <f>SUM(AL10:AL47)</f>
@@ -9610,15 +9610,15 @@
       </c>
       <c r="AN48" s="8">
         <f t="shared" si="14"/>
-        <v>1501288</v>
+        <v>1501346</v>
       </c>
       <c r="AO48" s="7">
         <f>SUM(AO10:AO47)</f>
-        <v>6858652</v>
+        <v>6858710</v>
       </c>
       <c r="AP48" s="9">
         <f t="shared" si="15"/>
-        <v>0.95139747669207597</v>
+        <v>0.95140552215839336</v>
       </c>
       <c r="AQ48" s="6">
         <f>SUM(AQ10:AQ47)</f>
@@ -9630,15 +9630,15 @@
       </c>
       <c r="AS48" s="8">
         <f t="shared" si="16"/>
-        <v>2190424</v>
+        <v>2190498</v>
       </c>
       <c r="AT48" s="7">
         <f>SUM(AT10:AT47)</f>
-        <v>10966910</v>
+        <v>10966984</v>
       </c>
       <c r="AU48" s="9">
         <f t="shared" si="17"/>
-        <v>0.95955965763554407</v>
+        <v>0.95956613233212362</v>
       </c>
       <c r="AV48" s="6">
         <f>SUM(AV10:AV47)</f>
@@ -9650,15 +9650,15 @@
       </c>
       <c r="AX48" s="8">
         <f t="shared" si="18"/>
-        <v>1537128</v>
+        <v>1537186</v>
       </c>
       <c r="AY48" s="7">
         <f>SUM(AY10:AY47)</f>
-        <v>6903464</v>
+        <v>6903522</v>
       </c>
       <c r="AZ48" s="9">
         <f t="shared" si="19"/>
-        <v>0.95315298050496178</v>
+        <v>0.9531609884952793</v>
       </c>
       <c r="BA48" s="6">
         <f>SUM(BA10:BA47)</f>
@@ -9670,15 +9670,15 @@
       </c>
       <c r="BC48" s="8">
         <f t="shared" si="20"/>
-        <v>1610248</v>
+        <v>1610308</v>
       </c>
       <c r="BD48" s="7">
         <f>SUM(BD10:BD47)</f>
-        <v>7013472</v>
+        <v>7013532</v>
       </c>
       <c r="BE48" s="9">
         <f t="shared" si="21"/>
-        <v>0.95920697398977539</v>
+        <v>0.95921517997084138</v>
       </c>
       <c r="BF48" s="6">
         <f>SUM(BF10:BF47)</f>
@@ -9690,15 +9690,15 @@
       </c>
       <c r="BH48" s="8">
         <f t="shared" si="24"/>
-        <v>2687838</v>
+        <v>2687918</v>
       </c>
       <c r="BI48" s="7">
         <f>SUM(BI10:BI47)</f>
-        <v>11187707</v>
+        <v>11187787</v>
       </c>
       <c r="BJ48" s="9">
         <f t="shared" si="25"/>
-        <v>0.96186982142094113</v>
+        <v>0.96187669946893728</v>
       </c>
       <c r="BK48" s="24"/>
       <c r="BL48" s="24"/>
@@ -9802,6 +9802,13 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="BA8:BE8"/>
+    <mergeCell ref="AL8:AP8"/>
+    <mergeCell ref="AQ8:AU8"/>
+    <mergeCell ref="AV8:AZ8"/>
+    <mergeCell ref="AG8:AK8"/>
+    <mergeCell ref="H8:L8"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="BF8:BJ8"/>
     <mergeCell ref="M8:Q8"/>
@@ -9813,13 +9820,6 @@
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="C8:G8"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="BA8:BE8"/>
-    <mergeCell ref="AL8:AP8"/>
-    <mergeCell ref="AQ8:AU8"/>
-    <mergeCell ref="AV8:AZ8"/>
-    <mergeCell ref="AG8:AK8"/>
-    <mergeCell ref="H8:L8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/gstdatabase/GSTR-3B-2021-2022.xlsx
+++ b/gstdatabase/GSTR-3B-2021-2022.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jun-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 3B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jul-26\GST Statistics Downloads 31st Jul 26\Downloads\GSTR 3B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C61C158B-C3BE-403C-BB73-37F58A8FBA22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D91B4865-C668-4261-9515-E0B3783D669D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -185,10 +185,10 @@
     <t>STATE WISE RETURN PERIOD WISE GSTR-3B FILING SUMMARY</t>
   </si>
   <si>
-    <t>Data Considered upto 30th Jun 2026</t>
+    <t>Data Considered upto 31st Jul 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 30th Jun 2026</t>
+    <t>Filing %age as on 31st Jul 2026</t>
   </si>
 </sst>
 </file>
@@ -435,7 +435,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="17" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -447,12 +447,6 @@
     <xf numFmtId="17" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="17" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -460,13 +454,19 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -759,7 +759,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:BL57"/>
+  <dimension ref="A1:BL55"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.21875" customWidth="1"/>
@@ -768,13 +768,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:64" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -848,10 +848,10 @@
       <c r="AK2" s="1"/>
     </row>
     <row r="3" spans="1:64" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="34"/>
+      <c r="B3" s="35"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -928,11 +928,11 @@
       <c r="AK4" s="1"/>
     </row>
     <row r="5" spans="1:64" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -1072,10 +1072,10 @@
       <c r="BJ7" s="4"/>
     </row>
     <row r="8" spans="1:64" s="24" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="35" t="s">
+      <c r="A8" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="33" t="s">
+      <c r="B8" s="31" t="s">
         <v>2</v>
       </c>
       <c r="C8" s="27">
@@ -1085,69 +1085,69 @@
       <c r="E8" s="28"/>
       <c r="F8" s="28"/>
       <c r="G8" s="29"/>
-      <c r="H8" s="32">
+      <c r="H8" s="30">
         <v>44317</v>
       </c>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
-      <c r="K8" s="33"/>
-      <c r="L8" s="33"/>
-      <c r="M8" s="30">
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="31"/>
+      <c r="M8" s="33">
         <v>44348</v>
       </c>
-      <c r="N8" s="31"/>
-      <c r="O8" s="31"/>
-      <c r="P8" s="31"/>
-      <c r="Q8" s="31"/>
-      <c r="R8" s="32">
+      <c r="N8" s="34"/>
+      <c r="O8" s="34"/>
+      <c r="P8" s="34"/>
+      <c r="Q8" s="34"/>
+      <c r="R8" s="30">
         <v>44378</v>
       </c>
-      <c r="S8" s="33"/>
-      <c r="T8" s="33"/>
-      <c r="U8" s="33"/>
-      <c r="V8" s="33"/>
-      <c r="W8" s="32">
+      <c r="S8" s="31"/>
+      <c r="T8" s="31"/>
+      <c r="U8" s="31"/>
+      <c r="V8" s="31"/>
+      <c r="W8" s="30">
         <v>44409</v>
       </c>
-      <c r="X8" s="33"/>
-      <c r="Y8" s="33"/>
-      <c r="Z8" s="33"/>
-      <c r="AA8" s="33"/>
-      <c r="AB8" s="30">
+      <c r="X8" s="31"/>
+      <c r="Y8" s="31"/>
+      <c r="Z8" s="31"/>
+      <c r="AA8" s="31"/>
+      <c r="AB8" s="33">
         <v>44440</v>
       </c>
-      <c r="AC8" s="31"/>
-      <c r="AD8" s="31"/>
-      <c r="AE8" s="31"/>
-      <c r="AF8" s="31"/>
-      <c r="AG8" s="32">
+      <c r="AC8" s="34"/>
+      <c r="AD8" s="34"/>
+      <c r="AE8" s="34"/>
+      <c r="AF8" s="34"/>
+      <c r="AG8" s="30">
         <v>44470</v>
       </c>
-      <c r="AH8" s="33"/>
-      <c r="AI8" s="33"/>
-      <c r="AJ8" s="33"/>
-      <c r="AK8" s="33"/>
-      <c r="AL8" s="32">
+      <c r="AH8" s="31"/>
+      <c r="AI8" s="31"/>
+      <c r="AJ8" s="31"/>
+      <c r="AK8" s="31"/>
+      <c r="AL8" s="30">
         <v>44501</v>
       </c>
-      <c r="AM8" s="33"/>
-      <c r="AN8" s="33"/>
-      <c r="AO8" s="33"/>
-      <c r="AP8" s="33"/>
-      <c r="AQ8" s="32">
+      <c r="AM8" s="31"/>
+      <c r="AN8" s="31"/>
+      <c r="AO8" s="31"/>
+      <c r="AP8" s="31"/>
+      <c r="AQ8" s="30">
         <v>44531</v>
       </c>
-      <c r="AR8" s="33"/>
-      <c r="AS8" s="33"/>
-      <c r="AT8" s="33"/>
-      <c r="AU8" s="33"/>
-      <c r="AV8" s="32">
+      <c r="AR8" s="31"/>
+      <c r="AS8" s="31"/>
+      <c r="AT8" s="31"/>
+      <c r="AU8" s="31"/>
+      <c r="AV8" s="30">
         <v>44562</v>
       </c>
-      <c r="AW8" s="33"/>
-      <c r="AX8" s="33"/>
-      <c r="AY8" s="33"/>
-      <c r="AZ8" s="33"/>
+      <c r="AW8" s="31"/>
+      <c r="AX8" s="31"/>
+      <c r="AY8" s="31"/>
+      <c r="AZ8" s="31"/>
       <c r="BA8" s="27">
         <v>44593</v>
       </c>
@@ -1164,8 +1164,8 @@
       <c r="BJ8" s="29"/>
     </row>
     <row r="9" spans="1:64" s="24" customFormat="1" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="35"/>
-      <c r="B9" s="33"/>
+      <c r="A9" s="36"/>
+      <c r="B9" s="31"/>
       <c r="C9" s="23" t="s">
         <v>3</v>
       </c>
@@ -1532,14 +1532,14 @@
       </c>
       <c r="BC10" s="10">
         <f>BD10-BB10</f>
-        <v>14036</v>
+        <v>80220</v>
       </c>
       <c r="BD10" s="20">
-        <v>66184</v>
+        <v>132368</v>
       </c>
       <c r="BE10" s="12">
         <f>BD10/BA10</f>
-        <v>1.0161362135937235</v>
+        <v>2.0322724271874471</v>
       </c>
       <c r="BF10" s="18">
         <v>104274</v>
@@ -1746,14 +1746,14 @@
       </c>
       <c r="BC11" s="10">
         <f t="shared" ref="BC11:BC48" si="20">BD11-BB11</f>
-        <v>9293</v>
+        <v>52420</v>
       </c>
       <c r="BD11" s="20">
-        <v>43127</v>
+        <v>86254</v>
       </c>
       <c r="BE11" s="12">
         <f t="shared" ref="BE11:BE48" si="21">BD11/BA11</f>
-        <v>0.97651933701657456</v>
+        <v>1.9530386740331491</v>
       </c>
       <c r="BF11" s="18">
         <v>97423</v>
@@ -1790,14 +1790,14 @@
       </c>
       <c r="E12" s="10">
         <f t="shared" si="0"/>
-        <v>115333</v>
+        <v>115334</v>
       </c>
       <c r="F12" s="20">
-        <v>150924</v>
+        <v>150925</v>
       </c>
       <c r="G12" s="12">
         <f t="shared" si="1"/>
-        <v>0.94056499710209962</v>
+        <v>0.94057122914602298</v>
       </c>
       <c r="H12" s="15">
         <v>161190</v>
@@ -1960,14 +1960,14 @@
       </c>
       <c r="BC12" s="10">
         <f t="shared" si="20"/>
-        <v>27498</v>
+        <v>182017</v>
       </c>
       <c r="BD12" s="20">
-        <v>154519</v>
+        <v>309038</v>
       </c>
       <c r="BE12" s="12">
         <f t="shared" si="21"/>
-        <v>0.94640166595210384</v>
+        <v>1.8928033319042077</v>
       </c>
       <c r="BF12" s="18">
         <v>336608</v>
@@ -2004,14 +2004,14 @@
       </c>
       <c r="E13" s="10">
         <f t="shared" si="0"/>
-        <v>11235</v>
+        <v>11236</v>
       </c>
       <c r="F13" s="20">
-        <v>15242</v>
+        <v>15243</v>
       </c>
       <c r="G13" s="12">
         <f t="shared" si="1"/>
-        <v>0.99341719350844038</v>
+        <v>0.993482369810337</v>
       </c>
       <c r="H13" s="15">
         <v>15350</v>
@@ -2174,14 +2174,14 @@
       </c>
       <c r="BC13" s="10">
         <f t="shared" si="20"/>
-        <v>2773</v>
+        <v>18450</v>
       </c>
       <c r="BD13" s="20">
-        <v>15677</v>
+        <v>31354</v>
       </c>
       <c r="BE13" s="12">
         <f t="shared" si="21"/>
-        <v>0.99027225064746383</v>
+        <v>1.9805445012949277</v>
       </c>
       <c r="BF13" s="18">
         <v>27469</v>
@@ -2218,14 +2218,14 @@
       </c>
       <c r="E14" s="10">
         <f t="shared" si="0"/>
-        <v>62140</v>
+        <v>62141</v>
       </c>
       <c r="F14" s="20">
-        <v>75021</v>
+        <v>75022</v>
       </c>
       <c r="G14" s="12">
         <f t="shared" si="1"/>
-        <v>0.95063167631815704</v>
+        <v>0.9506443478591432</v>
       </c>
       <c r="H14" s="15">
         <v>78856</v>
@@ -2235,14 +2235,14 @@
       </c>
       <c r="J14" s="10">
         <f t="shared" si="2"/>
-        <v>57277</v>
+        <v>57278</v>
       </c>
       <c r="K14" s="20">
-        <v>74804</v>
+        <v>74805</v>
       </c>
       <c r="L14" s="12">
         <f t="shared" si="3"/>
-        <v>0.9486151973217003</v>
+        <v>0.94862787866490816</v>
       </c>
       <c r="M14" s="16">
         <v>139510</v>
@@ -2252,14 +2252,14 @@
       </c>
       <c r="O14" s="10">
         <f t="shared" si="4"/>
-        <v>47171</v>
+        <v>47172</v>
       </c>
       <c r="P14" s="13">
-        <v>134823</v>
+        <v>134824</v>
       </c>
       <c r="Q14" s="12">
         <f t="shared" si="5"/>
-        <v>0.96640384201849328</v>
+        <v>0.96641100996344353</v>
       </c>
       <c r="R14" s="16">
         <v>78838</v>
@@ -2269,14 +2269,14 @@
       </c>
       <c r="T14" s="10">
         <f t="shared" si="6"/>
-        <v>22055</v>
+        <v>22056</v>
       </c>
       <c r="U14" s="20">
-        <v>74604</v>
+        <v>74605</v>
       </c>
       <c r="V14" s="12">
         <f t="shared" si="7"/>
-        <v>0.9462949339151171</v>
+        <v>0.94630761815368225</v>
       </c>
       <c r="W14" s="16">
         <v>80553</v>
@@ -2286,14 +2286,14 @@
       </c>
       <c r="Y14" s="10">
         <f t="shared" si="8"/>
-        <v>22358</v>
+        <v>22359</v>
       </c>
       <c r="Z14" s="20">
-        <v>76599</v>
+        <v>76600</v>
       </c>
       <c r="AA14" s="12">
         <f t="shared" si="9"/>
-        <v>0.95091430486760264</v>
+        <v>0.95092671905453552</v>
       </c>
       <c r="AB14" s="17">
         <v>144082</v>
@@ -2303,14 +2303,14 @@
       </c>
       <c r="AD14" s="10">
         <f t="shared" si="10"/>
-        <v>33623</v>
+        <v>33624</v>
       </c>
       <c r="AE14" s="11">
-        <v>139178</v>
+        <v>139179</v>
       </c>
       <c r="AF14" s="12">
         <f t="shared" si="11"/>
-        <v>0.9659638261545509</v>
+        <v>0.96597076664677062</v>
       </c>
       <c r="AG14" s="16">
         <v>79635</v>
@@ -2320,14 +2320,14 @@
       </c>
       <c r="AI14" s="10">
         <f t="shared" si="12"/>
-        <v>19173</v>
+        <v>19174</v>
       </c>
       <c r="AJ14" s="20">
-        <v>75494</v>
+        <v>75495</v>
       </c>
       <c r="AK14" s="12">
         <f t="shared" si="13"/>
-        <v>0.94800025114585296</v>
+        <v>0.94801280843850066</v>
       </c>
       <c r="AL14" s="18">
         <v>81274</v>
@@ -2388,14 +2388,14 @@
       </c>
       <c r="BC14" s="10">
         <f t="shared" si="20"/>
-        <v>20690</v>
+        <v>99069</v>
       </c>
       <c r="BD14" s="20">
-        <v>78379</v>
+        <v>156758</v>
       </c>
       <c r="BE14" s="12">
         <f t="shared" si="21"/>
-        <v>0.95167498391189786</v>
+        <v>1.9033499678237957</v>
       </c>
       <c r="BF14" s="18">
         <v>151377</v>
@@ -2405,14 +2405,14 @@
       </c>
       <c r="BH14" s="10">
         <f t="shared" si="22"/>
-        <v>36686</v>
+        <v>36688</v>
       </c>
       <c r="BI14" s="11">
-        <v>145236</v>
+        <v>145238</v>
       </c>
       <c r="BJ14" s="12">
         <f t="shared" si="23"/>
-        <v>0.95943241047186822</v>
+        <v>0.95944562251861243</v>
       </c>
       <c r="BK14" s="24"/>
       <c r="BL14" s="24"/>
@@ -2602,14 +2602,14 @@
       </c>
       <c r="BC15" s="10">
         <f t="shared" si="20"/>
-        <v>56297</v>
+        <v>311422</v>
       </c>
       <c r="BD15" s="20">
-        <v>255125</v>
+        <v>510250</v>
       </c>
       <c r="BE15" s="12">
         <f t="shared" si="21"/>
-        <v>0.95295457941132522</v>
+        <v>1.9059091588226504</v>
       </c>
       <c r="BF15" s="18">
         <v>469904</v>
@@ -2697,14 +2697,14 @@
       </c>
       <c r="T16" s="10">
         <f t="shared" si="6"/>
-        <v>91180</v>
+        <v>91181</v>
       </c>
       <c r="U16" s="20">
-        <v>373777</v>
+        <v>373778</v>
       </c>
       <c r="V16" s="12">
         <f t="shared" si="7"/>
-        <v>0.92595152452015017</v>
+        <v>0.92595400180346221</v>
       </c>
       <c r="W16" s="16">
         <v>406853</v>
@@ -2799,14 +2799,14 @@
       </c>
       <c r="AX16" s="10">
         <f t="shared" si="18"/>
-        <v>74838</v>
+        <v>74839</v>
       </c>
       <c r="AY16" s="20">
-        <v>382481</v>
+        <v>382482</v>
       </c>
       <c r="AZ16" s="12">
         <f t="shared" si="19"/>
-        <v>0.94976546456391808</v>
+        <v>0.94976794773423123</v>
       </c>
       <c r="BA16" s="18">
         <v>402569</v>
@@ -2816,14 +2816,14 @@
       </c>
       <c r="BC16" s="10">
         <f t="shared" si="20"/>
-        <v>80938</v>
+        <v>468325</v>
       </c>
       <c r="BD16" s="20">
-        <v>387386</v>
+        <v>774773</v>
       </c>
       <c r="BE16" s="12">
         <f t="shared" si="21"/>
-        <v>0.96228472634504891</v>
+        <v>1.924571936736311</v>
       </c>
       <c r="BF16" s="18">
         <v>736680</v>
@@ -2833,14 +2833,14 @@
       </c>
       <c r="BH16" s="10">
         <f t="shared" si="22"/>
-        <v>137190</v>
+        <v>137191</v>
       </c>
       <c r="BI16" s="11">
-        <v>709536</v>
+        <v>709537</v>
       </c>
       <c r="BJ16" s="12">
         <f t="shared" si="23"/>
-        <v>0.9631536080794918</v>
+        <v>0.96315496552098601</v>
       </c>
       <c r="BK16" s="24"/>
       <c r="BL16" s="24"/>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="E17" s="10">
         <f t="shared" si="0"/>
-        <v>221392</v>
+        <v>221393</v>
       </c>
       <c r="F17" s="20">
-        <v>259930</v>
+        <v>259931</v>
       </c>
       <c r="G17" s="12">
         <f t="shared" si="1"/>
-        <v>0.98487058725461596</v>
+        <v>0.98487437623852414</v>
       </c>
       <c r="H17" s="15">
         <v>264168</v>
@@ -2877,14 +2877,14 @@
       </c>
       <c r="J17" s="10">
         <f t="shared" si="2"/>
-        <v>201004</v>
+        <v>201005</v>
       </c>
       <c r="K17" s="20">
-        <v>260765</v>
+        <v>260766</v>
       </c>
       <c r="L17" s="12">
         <f t="shared" si="3"/>
-        <v>0.98711804609188092</v>
+        <v>0.98712183156173339</v>
       </c>
       <c r="M17" s="16">
         <v>591219</v>
@@ -2894,14 +2894,14 @@
       </c>
       <c r="O17" s="10">
         <f t="shared" si="4"/>
-        <v>171691</v>
+        <v>171693</v>
       </c>
       <c r="P17" s="13">
-        <v>584079</v>
+        <v>584081</v>
       </c>
       <c r="Q17" s="12">
         <f t="shared" si="5"/>
-        <v>0.98792325686420768</v>
+        <v>0.98792663970542216</v>
       </c>
       <c r="R17" s="16">
         <v>261213</v>
@@ -2911,14 +2911,14 @@
       </c>
       <c r="T17" s="10">
         <f t="shared" si="6"/>
-        <v>69621</v>
+        <v>69622</v>
       </c>
       <c r="U17" s="20">
-        <v>257379</v>
+        <v>257380</v>
       </c>
       <c r="V17" s="12">
         <f t="shared" si="7"/>
-        <v>0.98532232316155777</v>
+        <v>0.98532615145494296</v>
       </c>
       <c r="W17" s="16">
         <v>269820</v>
@@ -2928,14 +2928,14 @@
       </c>
       <c r="Y17" s="10">
         <f t="shared" si="8"/>
-        <v>72463</v>
+        <v>72465</v>
       </c>
       <c r="Z17" s="20">
-        <v>267028</v>
+        <v>267030</v>
       </c>
       <c r="AA17" s="12">
         <f t="shared" si="9"/>
-        <v>0.989652360833148</v>
+        <v>0.98965977318212139</v>
       </c>
       <c r="AB17" s="17">
         <v>613565</v>
@@ -2945,14 +2945,14 @@
       </c>
       <c r="AD17" s="10">
         <f t="shared" si="10"/>
-        <v>123890</v>
+        <v>123891</v>
       </c>
       <c r="AE17" s="11">
-        <v>604350</v>
+        <v>604351</v>
       </c>
       <c r="AF17" s="12">
         <f t="shared" si="11"/>
-        <v>0.98498121633404778</v>
+        <v>0.98498284615321929</v>
       </c>
       <c r="AG17" s="16">
         <v>263808</v>
@@ -2962,14 +2962,14 @@
       </c>
       <c r="AI17" s="10">
         <f t="shared" si="12"/>
-        <v>62439</v>
+        <v>62440</v>
       </c>
       <c r="AJ17" s="20">
-        <v>259625</v>
+        <v>259626</v>
       </c>
       <c r="AK17" s="12">
         <f t="shared" si="13"/>
-        <v>0.98414377122755947</v>
+        <v>0.9841475618631732</v>
       </c>
       <c r="AL17" s="18">
         <v>270212</v>
@@ -2979,14 +2979,14 @@
       </c>
       <c r="AN17" s="10">
         <f t="shared" si="14"/>
-        <v>62612</v>
+        <v>62613</v>
       </c>
       <c r="AO17" s="11">
-        <v>266624</v>
+        <v>266625</v>
       </c>
       <c r="AP17" s="12">
         <f t="shared" si="15"/>
-        <v>0.98672153716341238</v>
+        <v>0.9867252379613044</v>
       </c>
       <c r="AQ17" s="11">
         <v>633137</v>
@@ -2996,14 +2996,14 @@
       </c>
       <c r="AS17" s="10">
         <f t="shared" si="16"/>
-        <v>124226</v>
+        <v>124229</v>
       </c>
       <c r="AT17" s="13">
-        <v>619715</v>
+        <v>619718</v>
       </c>
       <c r="AU17" s="12">
         <f t="shared" si="17"/>
-        <v>0.97880079666801967</v>
+        <v>0.97880553497900136</v>
       </c>
       <c r="AV17" s="18">
         <v>270996</v>
@@ -3013,14 +3013,14 @@
       </c>
       <c r="AX17" s="10">
         <f t="shared" si="18"/>
-        <v>61988</v>
+        <v>61989</v>
       </c>
       <c r="AY17" s="20">
-        <v>265738</v>
+        <v>265739</v>
       </c>
       <c r="AZ17" s="12">
         <f t="shared" si="19"/>
-        <v>0.98059749959408993</v>
+        <v>0.98060118968545662</v>
       </c>
       <c r="BA17" s="18">
         <v>277009</v>
@@ -3030,14 +3030,14 @@
       </c>
       <c r="BC17" s="10">
         <f t="shared" si="20"/>
-        <v>65560</v>
+        <v>340151</v>
       </c>
       <c r="BD17" s="20">
-        <v>274590</v>
+        <v>549181</v>
       </c>
       <c r="BE17" s="12">
         <f t="shared" si="21"/>
-        <v>0.99126743174409493</v>
+        <v>1.9825384734792011</v>
       </c>
       <c r="BF17" s="18">
         <v>651560</v>
@@ -3047,14 +3047,14 @@
       </c>
       <c r="BH17" s="10">
         <f t="shared" si="22"/>
-        <v>160486</v>
+        <v>160492</v>
       </c>
       <c r="BI17" s="11">
-        <v>635891</v>
+        <v>635897</v>
       </c>
       <c r="BJ17" s="12">
         <f t="shared" si="23"/>
-        <v>0.97595156240407632</v>
+        <v>0.9759607710725029</v>
       </c>
       <c r="BK17" s="24"/>
       <c r="BL17" s="24"/>
@@ -3074,14 +3074,14 @@
       </c>
       <c r="E18" s="10">
         <f t="shared" si="0"/>
-        <v>625832</v>
+        <v>625833</v>
       </c>
       <c r="F18" s="20">
-        <v>740857</v>
+        <v>740858</v>
       </c>
       <c r="G18" s="12">
         <f t="shared" si="1"/>
-        <v>0.96403745507447036</v>
+        <v>0.96403875632080405</v>
       </c>
       <c r="H18" s="15">
         <v>766983</v>
@@ -3091,14 +3091,14 @@
       </c>
       <c r="J18" s="10">
         <f t="shared" si="2"/>
-        <v>564999</v>
+        <v>565000</v>
       </c>
       <c r="K18" s="20">
-        <v>740261</v>
+        <v>740262</v>
       </c>
       <c r="L18" s="12">
         <f t="shared" si="3"/>
-        <v>0.96515959284625608</v>
+        <v>0.96516089665611882</v>
       </c>
       <c r="M18" s="16">
         <v>1193073</v>
@@ -3108,14 +3108,14 @@
       </c>
       <c r="O18" s="10">
         <f t="shared" si="4"/>
-        <v>410735</v>
+        <v>410737</v>
       </c>
       <c r="P18" s="13">
-        <v>1175485</v>
+        <v>1175487</v>
       </c>
       <c r="Q18" s="12">
         <f t="shared" si="5"/>
-        <v>0.98525823650355004</v>
+        <v>0.98525991284690884</v>
       </c>
       <c r="R18" s="16">
         <v>775495</v>
@@ -3125,14 +3125,14 @@
       </c>
       <c r="T18" s="10">
         <f t="shared" si="6"/>
-        <v>184174</v>
+        <v>184176</v>
       </c>
       <c r="U18" s="20">
-        <v>756203</v>
+        <v>756205</v>
       </c>
       <c r="V18" s="12">
         <f t="shared" si="7"/>
-        <v>0.97512298596380376</v>
+        <v>0.97512556496173408</v>
       </c>
       <c r="W18" s="16">
         <v>789854</v>
@@ -3142,14 +3142,14 @@
       </c>
       <c r="Y18" s="10">
         <f t="shared" si="8"/>
-        <v>178823</v>
+        <v>178826</v>
       </c>
       <c r="Z18" s="20">
-        <v>773184</v>
+        <v>773187</v>
       </c>
       <c r="AA18" s="12">
         <f t="shared" si="9"/>
-        <v>0.97889483372876507</v>
+        <v>0.97889863189905979</v>
       </c>
       <c r="AB18" s="17">
         <v>1245422</v>
@@ -3159,14 +3159,14 @@
       </c>
       <c r="AD18" s="10">
         <f t="shared" si="10"/>
-        <v>240981</v>
+        <v>240983</v>
       </c>
       <c r="AE18" s="11">
-        <v>1213771</v>
+        <v>1213773</v>
       </c>
       <c r="AF18" s="12">
         <f t="shared" si="11"/>
-        <v>0.97458612422134827</v>
+        <v>0.97458773010272826</v>
       </c>
       <c r="AG18" s="16">
         <v>794310</v>
@@ -3176,14 +3176,14 @@
       </c>
       <c r="AI18" s="10">
         <f t="shared" si="12"/>
-        <v>158880</v>
+        <v>158883</v>
       </c>
       <c r="AJ18" s="20">
-        <v>773918</v>
+        <v>773921</v>
       </c>
       <c r="AK18" s="12">
         <f t="shared" si="13"/>
-        <v>0.97432740365852122</v>
+        <v>0.97433118052145884</v>
       </c>
       <c r="AL18" s="18">
         <v>807429</v>
@@ -3193,14 +3193,14 @@
       </c>
       <c r="AN18" s="10">
         <f t="shared" si="14"/>
-        <v>156230</v>
+        <v>156233</v>
       </c>
       <c r="AO18" s="11">
-        <v>787041</v>
+        <v>787044</v>
       </c>
       <c r="AP18" s="12">
         <f t="shared" si="15"/>
-        <v>0.97474948261704741</v>
+        <v>0.97475319811401373</v>
       </c>
       <c r="AQ18" s="11">
         <v>1285494</v>
@@ -3210,14 +3210,14 @@
       </c>
       <c r="AS18" s="10">
         <f t="shared" si="16"/>
-        <v>230873</v>
+        <v>230876</v>
       </c>
       <c r="AT18" s="13">
-        <v>1245493</v>
+        <v>1245496</v>
       </c>
       <c r="AU18" s="12">
         <f t="shared" si="17"/>
-        <v>0.96888277969403203</v>
+        <v>0.96888511342721162</v>
       </c>
       <c r="AV18" s="18">
         <v>820095</v>
@@ -3227,14 +3227,14 @@
       </c>
       <c r="AX18" s="10">
         <f t="shared" si="18"/>
-        <v>161737</v>
+        <v>161741</v>
       </c>
       <c r="AY18" s="20">
-        <v>793764</v>
+        <v>793768</v>
       </c>
       <c r="AZ18" s="12">
         <f t="shared" si="19"/>
-        <v>0.96789274413330162</v>
+        <v>0.96789762161700776</v>
       </c>
       <c r="BA18" s="18">
         <v>829968</v>
@@ -3244,14 +3244,14 @@
       </c>
       <c r="BC18" s="10">
         <f t="shared" si="20"/>
-        <v>198189</v>
+        <v>1004683</v>
       </c>
       <c r="BD18" s="20">
-        <v>806490</v>
+        <v>1612984</v>
       </c>
       <c r="BE18" s="12">
         <f t="shared" si="21"/>
-        <v>0.9717121623966225</v>
+        <v>1.9434291442561642</v>
       </c>
       <c r="BF18" s="18">
         <v>1319511</v>
@@ -3261,14 +3261,14 @@
       </c>
       <c r="BH18" s="10">
         <f t="shared" si="22"/>
-        <v>292039</v>
+        <v>292043</v>
       </c>
       <c r="BI18" s="11">
-        <v>1272817</v>
+        <v>1272821</v>
       </c>
       <c r="BJ18" s="12">
         <f t="shared" si="23"/>
-        <v>0.96461264817042069</v>
+        <v>0.96461567959645655</v>
       </c>
       <c r="BK18" s="24"/>
       <c r="BL18" s="24"/>
@@ -3407,14 +3407,14 @@
       </c>
       <c r="AN19" s="10">
         <f t="shared" si="14"/>
-        <v>55773</v>
+        <v>55774</v>
       </c>
       <c r="AO19" s="11">
-        <v>237108</v>
+        <v>237109</v>
       </c>
       <c r="AP19" s="12">
         <f t="shared" si="15"/>
-        <v>0.90223057663183692</v>
+        <v>0.90223438177791648</v>
       </c>
       <c r="AQ19" s="11">
         <v>437396</v>
@@ -3424,14 +3424,14 @@
       </c>
       <c r="AS19" s="10">
         <f t="shared" si="16"/>
-        <v>82225</v>
+        <v>82226</v>
       </c>
       <c r="AT19" s="13">
-        <v>401088</v>
+        <v>401089</v>
       </c>
       <c r="AU19" s="12">
         <f t="shared" si="17"/>
-        <v>0.9169905531829281</v>
+        <v>0.91699283944068988</v>
       </c>
       <c r="AV19" s="18">
         <v>265429</v>
@@ -3441,14 +3441,14 @@
       </c>
       <c r="AX19" s="10">
         <f t="shared" si="18"/>
-        <v>56297</v>
+        <v>56299</v>
       </c>
       <c r="AY19" s="20">
-        <v>237904</v>
+        <v>237906</v>
       </c>
       <c r="AZ19" s="12">
         <f t="shared" si="19"/>
-        <v>0.89629995215292979</v>
+        <v>0.89630748712461716</v>
       </c>
       <c r="BA19" s="18">
         <v>272122</v>
@@ -3458,14 +3458,14 @@
       </c>
       <c r="BC19" s="10">
         <f t="shared" si="20"/>
-        <v>65958</v>
+        <v>310776</v>
       </c>
       <c r="BD19" s="20">
-        <v>244816</v>
+        <v>489634</v>
       </c>
       <c r="BE19" s="12">
         <f t="shared" si="21"/>
-        <v>0.89965530166616448</v>
+        <v>1.7993179529769736</v>
       </c>
       <c r="BF19" s="18">
         <v>456786</v>
@@ -3655,14 +3655,14 @@
       </c>
       <c r="AX20" s="10">
         <f t="shared" si="18"/>
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="AY20" s="20">
-        <v>4957</v>
+        <v>4958</v>
       </c>
       <c r="AZ20" s="12">
         <f t="shared" si="19"/>
-        <v>0.84923762206612985</v>
+        <v>0.84940894295014557</v>
       </c>
       <c r="BA20" s="18">
         <v>5912</v>
@@ -3672,14 +3672,14 @@
       </c>
       <c r="BC20" s="10">
         <f t="shared" si="20"/>
-        <v>1554</v>
+        <v>6617</v>
       </c>
       <c r="BD20" s="20">
-        <v>5062</v>
+        <v>10125</v>
       </c>
       <c r="BE20" s="12">
         <f t="shared" si="21"/>
-        <v>0.85622462787550746</v>
+        <v>1.7126184032476319</v>
       </c>
       <c r="BF20" s="18">
         <v>8941</v>
@@ -3689,14 +3689,14 @@
       </c>
       <c r="BH20" s="10">
         <f t="shared" si="22"/>
-        <v>2249</v>
+        <v>2250</v>
       </c>
       <c r="BI20" s="11">
-        <v>8005</v>
+        <v>8006</v>
       </c>
       <c r="BJ20" s="12">
         <f t="shared" si="23"/>
-        <v>0.89531372329717029</v>
+        <v>0.89542556760988701</v>
       </c>
       <c r="BK20" s="24"/>
       <c r="BL20" s="24"/>
@@ -3716,14 +3716,14 @@
       </c>
       <c r="E21" s="10">
         <f t="shared" si="0"/>
-        <v>6393</v>
+        <v>6395</v>
       </c>
       <c r="F21" s="20">
-        <v>7778</v>
+        <v>7780</v>
       </c>
       <c r="G21" s="12">
         <f t="shared" si="1"/>
-        <v>0.76941339400534181</v>
+        <v>0.7696112375111287</v>
       </c>
       <c r="H21" s="15">
         <v>10163</v>
@@ -3733,14 +3733,14 @@
       </c>
       <c r="J21" s="10">
         <f t="shared" si="2"/>
-        <v>6391</v>
+        <v>6393</v>
       </c>
       <c r="K21" s="20">
-        <v>7812</v>
+        <v>7814</v>
       </c>
       <c r="L21" s="12">
         <f t="shared" si="3"/>
-        <v>0.76867066810981011</v>
+        <v>0.76886746039555254</v>
       </c>
       <c r="M21" s="16">
         <v>12994</v>
@@ -3750,14 +3750,14 @@
       </c>
       <c r="O21" s="10">
         <f t="shared" si="4"/>
-        <v>5671</v>
+        <v>5673</v>
       </c>
       <c r="P21" s="13">
-        <v>10522</v>
+        <v>10524</v>
       </c>
       <c r="Q21" s="12">
         <f t="shared" si="5"/>
-        <v>0.80975835000769592</v>
+        <v>0.80991226720024623</v>
       </c>
       <c r="R21" s="16">
         <v>10237</v>
@@ -3767,14 +3767,14 @@
       </c>
       <c r="T21" s="10">
         <f t="shared" si="6"/>
-        <v>3583</v>
+        <v>3584</v>
       </c>
       <c r="U21" s="20">
-        <v>7869</v>
+        <v>7870</v>
       </c>
       <c r="V21" s="12">
         <f t="shared" si="7"/>
-        <v>0.7686822311223992</v>
+        <v>0.76877991599101303</v>
       </c>
       <c r="W21" s="16">
         <v>10162</v>
@@ -3784,14 +3784,14 @@
       </c>
       <c r="Y21" s="10">
         <f t="shared" si="8"/>
-        <v>3551</v>
+        <v>3552</v>
       </c>
       <c r="Z21" s="20">
-        <v>7971</v>
+        <v>7972</v>
       </c>
       <c r="AA21" s="12">
         <f t="shared" si="9"/>
-        <v>0.78439283605589449</v>
+        <v>0.78449124188151942</v>
       </c>
       <c r="AB21" s="17">
         <v>13196</v>
@@ -3801,14 +3801,14 @@
       </c>
       <c r="AD21" s="10">
         <f t="shared" si="10"/>
-        <v>4245</v>
+        <v>4246</v>
       </c>
       <c r="AE21" s="11">
-        <v>10797</v>
+        <v>10798</v>
       </c>
       <c r="AF21" s="12">
         <f t="shared" si="11"/>
-        <v>0.8182024856016975</v>
+        <v>0.81827826614125487</v>
       </c>
       <c r="AG21" s="16">
         <v>10295</v>
@@ -3818,14 +3818,14 @@
       </c>
       <c r="AI21" s="10">
         <f t="shared" si="12"/>
-        <v>3026</v>
+        <v>3027</v>
       </c>
       <c r="AJ21" s="20">
-        <v>8032</v>
+        <v>8033</v>
       </c>
       <c r="AK21" s="12">
         <f t="shared" si="13"/>
-        <v>0.78018455560951916</v>
+        <v>0.78028169014084503</v>
       </c>
       <c r="AL21" s="18">
         <v>10459</v>
@@ -3835,14 +3835,14 @@
       </c>
       <c r="AN21" s="10">
         <f t="shared" si="14"/>
-        <v>2977</v>
+        <v>2978</v>
       </c>
       <c r="AO21" s="11">
-        <v>8140</v>
+        <v>8141</v>
       </c>
       <c r="AP21" s="12">
         <f t="shared" si="15"/>
-        <v>0.77827708193899992</v>
+        <v>0.77837269337412751</v>
       </c>
       <c r="AQ21" s="11">
         <v>13595</v>
@@ -3852,14 +3852,14 @@
       </c>
       <c r="AS21" s="10">
         <f t="shared" si="16"/>
-        <v>3828</v>
+        <v>3829</v>
       </c>
       <c r="AT21" s="13">
-        <v>11061</v>
+        <v>11062</v>
       </c>
       <c r="AU21" s="12">
         <f t="shared" si="17"/>
-        <v>0.81360794409709447</v>
+        <v>0.81368150055167343</v>
       </c>
       <c r="AV21" s="18">
         <v>10391</v>
@@ -3869,14 +3869,14 @@
       </c>
       <c r="AX21" s="10">
         <f t="shared" si="18"/>
-        <v>3013</v>
+        <v>3014</v>
       </c>
       <c r="AY21" s="20">
-        <v>8239</v>
+        <v>8240</v>
       </c>
       <c r="AZ21" s="12">
         <f t="shared" si="19"/>
-        <v>0.79289769993263404</v>
+        <v>0.79299393706091814</v>
       </c>
       <c r="BA21" s="18">
         <v>10525</v>
@@ -3886,14 +3886,14 @@
       </c>
       <c r="BC21" s="10">
         <f t="shared" si="20"/>
-        <v>3119</v>
+        <v>11508</v>
       </c>
       <c r="BD21" s="20">
-        <v>8388</v>
+        <v>16777</v>
       </c>
       <c r="BE21" s="12">
         <f t="shared" si="21"/>
-        <v>0.79695961995249409</v>
+        <v>1.5940142517814726</v>
       </c>
       <c r="BF21" s="18">
         <v>13618</v>
@@ -3903,14 +3903,14 @@
       </c>
       <c r="BH21" s="10">
         <f t="shared" si="22"/>
-        <v>5148</v>
+        <v>5149</v>
       </c>
       <c r="BI21" s="11">
-        <v>11448</v>
+        <v>11449</v>
       </c>
       <c r="BJ21" s="12">
         <f t="shared" si="23"/>
-        <v>0.84065207813188425</v>
+        <v>0.84072551035394327</v>
       </c>
       <c r="BK21" s="24"/>
       <c r="BL21" s="24"/>
@@ -4015,14 +4015,14 @@
       </c>
       <c r="AD22" s="10">
         <f t="shared" si="10"/>
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="AE22" s="11">
-        <v>6359</v>
+        <v>6360</v>
       </c>
       <c r="AF22" s="12">
         <f t="shared" si="11"/>
-        <v>0.89905273575569067</v>
+        <v>0.89919411847872188</v>
       </c>
       <c r="AG22" s="16">
         <v>5998</v>
@@ -4066,14 +4066,14 @@
       </c>
       <c r="AS22" s="10">
         <f t="shared" si="16"/>
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="AT22" s="13">
-        <v>6500</v>
+        <v>6501</v>
       </c>
       <c r="AU22" s="12">
         <f t="shared" si="17"/>
-        <v>0.92382035247299599</v>
+        <v>0.92396247868106884</v>
       </c>
       <c r="AV22" s="18">
         <v>5943</v>
@@ -4100,14 +4100,14 @@
       </c>
       <c r="BC22" s="10">
         <f t="shared" si="20"/>
-        <v>1610</v>
+        <v>7086</v>
       </c>
       <c r="BD22" s="20">
-        <v>5476</v>
+        <v>10952</v>
       </c>
       <c r="BE22" s="12">
         <f t="shared" si="21"/>
-        <v>0.91312322828080705</v>
+        <v>1.8262464565616141</v>
       </c>
       <c r="BF22" s="18">
         <v>7214</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="BH22" s="10">
         <f t="shared" si="22"/>
-        <v>2400</v>
+        <v>2402</v>
       </c>
       <c r="BI22" s="11">
-        <v>6683</v>
+        <v>6685</v>
       </c>
       <c r="BJ22" s="12">
         <f t="shared" si="23"/>
-        <v>0.92639312448017741</v>
+        <v>0.92667036318270035</v>
       </c>
       <c r="BK22" s="24"/>
       <c r="BL22" s="24"/>
@@ -4144,14 +4144,14 @@
       </c>
       <c r="E23" s="10">
         <f t="shared" si="0"/>
-        <v>6139</v>
+        <v>6140</v>
       </c>
       <c r="F23" s="20">
-        <v>7286</v>
+        <v>7287</v>
       </c>
       <c r="G23" s="12">
         <f t="shared" si="1"/>
-        <v>0.76856540084388181</v>
+        <v>0.76867088607594936</v>
       </c>
       <c r="H23" s="15">
         <v>9486</v>
@@ -4161,14 +4161,14 @@
       </c>
       <c r="J23" s="10">
         <f t="shared" si="2"/>
-        <v>5884</v>
+        <v>5885</v>
       </c>
       <c r="K23" s="20">
-        <v>7257</v>
+        <v>7258</v>
       </c>
       <c r="L23" s="12">
         <f t="shared" si="3"/>
-        <v>0.76502213788741302</v>
+        <v>0.76512755639890362</v>
       </c>
       <c r="M23" s="16">
         <v>11077</v>
@@ -4178,14 +4178,14 @@
       </c>
       <c r="O23" s="10">
         <f t="shared" si="4"/>
-        <v>5404</v>
+        <v>5405</v>
       </c>
       <c r="P23" s="13">
-        <v>8721</v>
+        <v>8722</v>
       </c>
       <c r="Q23" s="12">
         <f t="shared" si="5"/>
-        <v>0.78730703259005141</v>
+        <v>0.78739730974090461</v>
       </c>
       <c r="R23" s="16">
         <v>9575</v>
@@ -4195,14 +4195,14 @@
       </c>
       <c r="T23" s="10">
         <f t="shared" si="6"/>
-        <v>3281</v>
+        <v>3282</v>
       </c>
       <c r="U23" s="20">
-        <v>7312</v>
+        <v>7313</v>
       </c>
       <c r="V23" s="12">
         <f t="shared" si="7"/>
-        <v>0.76365535248041772</v>
+        <v>0.76375979112271541</v>
       </c>
       <c r="W23" s="16">
         <v>9750</v>
@@ -4212,14 +4212,14 @@
       </c>
       <c r="Y23" s="10">
         <f t="shared" si="8"/>
-        <v>3172</v>
+        <v>3173</v>
       </c>
       <c r="Z23" s="20">
-        <v>7383</v>
+        <v>7384</v>
       </c>
       <c r="AA23" s="12">
         <f t="shared" si="9"/>
-        <v>0.75723076923076926</v>
+        <v>0.7573333333333333</v>
       </c>
       <c r="AB23" s="17">
         <v>11436</v>
@@ -4229,14 +4229,14 @@
       </c>
       <c r="AD23" s="10">
         <f t="shared" si="10"/>
-        <v>3624</v>
+        <v>3625</v>
       </c>
       <c r="AE23" s="11">
-        <v>8997</v>
+        <v>8998</v>
       </c>
       <c r="AF23" s="12">
         <f t="shared" si="11"/>
-        <v>0.78672612801678909</v>
+        <v>0.78681357117873385</v>
       </c>
       <c r="AG23" s="16">
         <v>9837</v>
@@ -4246,14 +4246,14 @@
       </c>
       <c r="AI23" s="10">
         <f t="shared" si="12"/>
-        <v>2843</v>
+        <v>2844</v>
       </c>
       <c r="AJ23" s="20">
-        <v>7451</v>
+        <v>7452</v>
       </c>
       <c r="AK23" s="12">
         <f t="shared" si="13"/>
-        <v>0.75744637592762021</v>
+        <v>0.75754803293687101</v>
       </c>
       <c r="AL23" s="18">
         <v>9887</v>
@@ -4263,14 +4263,14 @@
       </c>
       <c r="AN23" s="10">
         <f t="shared" si="14"/>
-        <v>2895</v>
+        <v>2896</v>
       </c>
       <c r="AO23" s="11">
-        <v>7537</v>
+        <v>7538</v>
       </c>
       <c r="AP23" s="12">
         <f t="shared" si="15"/>
-        <v>0.76231414989379997</v>
+        <v>0.76241529280873876</v>
       </c>
       <c r="AQ23" s="11">
         <v>10570</v>
@@ -4280,14 +4280,14 @@
       </c>
       <c r="AS23" s="10">
         <f t="shared" si="16"/>
-        <v>3377</v>
+        <v>3378</v>
       </c>
       <c r="AT23" s="13">
-        <v>9207</v>
+        <v>9208</v>
       </c>
       <c r="AU23" s="12">
         <f t="shared" si="17"/>
-        <v>0.87105014191106911</v>
+        <v>0.87114474929044461</v>
       </c>
       <c r="AV23" s="18">
         <v>8848</v>
@@ -4297,14 +4297,14 @@
       </c>
       <c r="AX23" s="10">
         <f t="shared" si="18"/>
-        <v>3200</v>
+        <v>3201</v>
       </c>
       <c r="AY23" s="20">
-        <v>7517</v>
+        <v>7518</v>
       </c>
       <c r="AZ23" s="12">
         <f t="shared" si="19"/>
-        <v>0.84957052441229652</v>
+        <v>0.84968354430379744</v>
       </c>
       <c r="BA23" s="18">
         <v>8869</v>
@@ -4314,14 +4314,14 @@
       </c>
       <c r="BC23" s="10">
         <f t="shared" si="20"/>
-        <v>3262</v>
+        <v>10873</v>
       </c>
       <c r="BD23" s="20">
-        <v>7610</v>
+        <v>15221</v>
       </c>
       <c r="BE23" s="12">
         <f t="shared" si="21"/>
-        <v>0.85804487540872698</v>
+        <v>1.7162025031006878</v>
       </c>
       <c r="BF23" s="18">
         <v>10711</v>
@@ -4331,14 +4331,14 @@
       </c>
       <c r="BH23" s="10">
         <f t="shared" si="22"/>
-        <v>4034</v>
+        <v>4035</v>
       </c>
       <c r="BI23" s="11">
-        <v>9396</v>
+        <v>9397</v>
       </c>
       <c r="BJ23" s="12">
         <f t="shared" si="23"/>
-        <v>0.87722901689851551</v>
+        <v>0.87732237886285125</v>
       </c>
       <c r="BK23" s="24"/>
       <c r="BL23" s="24"/>
@@ -4358,14 +4358,14 @@
       </c>
       <c r="E24" s="10">
         <f t="shared" si="0"/>
-        <v>3079</v>
+        <v>3080</v>
       </c>
       <c r="F24" s="20">
-        <v>4720</v>
+        <v>4721</v>
       </c>
       <c r="G24" s="12">
         <f t="shared" si="1"/>
-        <v>0.8001356162061366</v>
+        <v>0.80030513646380741</v>
       </c>
       <c r="H24" s="15">
         <v>5806</v>
@@ -4375,14 +4375,14 @@
       </c>
       <c r="J24" s="10">
         <f t="shared" si="2"/>
-        <v>3124</v>
+        <v>3125</v>
       </c>
       <c r="K24" s="20">
-        <v>4710</v>
+        <v>4711</v>
       </c>
       <c r="L24" s="12">
         <f t="shared" si="3"/>
-        <v>0.81122976231484667</v>
+        <v>0.81140199793317258</v>
       </c>
       <c r="M24" s="16">
         <v>6586</v>
@@ -4392,14 +4392,14 @@
       </c>
       <c r="O24" s="10">
         <f t="shared" si="4"/>
-        <v>2387</v>
+        <v>2388</v>
       </c>
       <c r="P24" s="13">
-        <v>5443</v>
+        <v>5444</v>
       </c>
       <c r="Q24" s="12">
         <f t="shared" si="5"/>
-        <v>0.82645004555116919</v>
+        <v>0.82660188278165803</v>
       </c>
       <c r="R24" s="16">
         <v>5878</v>
@@ -4409,14 +4409,14 @@
       </c>
       <c r="T24" s="10">
         <f t="shared" si="6"/>
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="U24" s="20">
-        <v>4692</v>
+        <v>4693</v>
       </c>
       <c r="V24" s="12">
         <f t="shared" si="7"/>
-        <v>0.79823069071112618</v>
+        <v>0.79840081660428719</v>
       </c>
       <c r="W24" s="16">
         <v>5897</v>
@@ -4426,14 +4426,14 @@
       </c>
       <c r="Y24" s="10">
         <f t="shared" si="8"/>
-        <v>1368</v>
+        <v>1370</v>
       </c>
       <c r="Z24" s="20">
-        <v>4716</v>
+        <v>4718</v>
       </c>
       <c r="AA24" s="12">
         <f t="shared" si="9"/>
-        <v>0.79972867559776162</v>
+        <v>0.80006783110055957</v>
       </c>
       <c r="AB24" s="17">
         <v>6699</v>
@@ -4443,14 +4443,14 @@
       </c>
       <c r="AD24" s="10">
         <f t="shared" si="10"/>
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="AE24" s="11">
-        <v>5515</v>
+        <v>5517</v>
       </c>
       <c r="AF24" s="12">
         <f t="shared" si="11"/>
-        <v>0.82325720256754742</v>
+        <v>0.82355575459023733</v>
       </c>
       <c r="AG24" s="16">
         <v>5948</v>
@@ -4460,14 +4460,14 @@
       </c>
       <c r="AI24" s="10">
         <f t="shared" si="12"/>
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="AJ24" s="20">
-        <v>4778</v>
+        <v>4780</v>
       </c>
       <c r="AK24" s="12">
         <f t="shared" si="13"/>
-        <v>0.80329522528581032</v>
+        <v>0.8036314727639543</v>
       </c>
       <c r="AL24" s="18">
         <v>5965</v>
@@ -4477,14 +4477,14 @@
       </c>
       <c r="AN24" s="10">
         <f t="shared" si="14"/>
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="AO24" s="11">
-        <v>4882</v>
+        <v>4884</v>
       </c>
       <c r="AP24" s="12">
         <f t="shared" si="15"/>
-        <v>0.81844090528080471</v>
+        <v>0.81877619446772842</v>
       </c>
       <c r="AQ24" s="11">
         <v>6810</v>
@@ -4494,14 +4494,14 @@
       </c>
       <c r="AS24" s="10">
         <f t="shared" si="16"/>
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="AT24" s="13">
-        <v>5731</v>
+        <v>5733</v>
       </c>
       <c r="AU24" s="12">
         <f t="shared" si="17"/>
-        <v>0.84155653450807633</v>
+        <v>0.84185022026431722</v>
       </c>
       <c r="AV24" s="18">
         <v>6017</v>
@@ -4511,14 +4511,14 @@
       </c>
       <c r="AX24" s="10">
         <f t="shared" si="18"/>
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="AY24" s="20">
-        <v>4959</v>
+        <v>4961</v>
       </c>
       <c r="AZ24" s="12">
         <f t="shared" si="19"/>
-        <v>0.82416486621239815</v>
+        <v>0.82449725776965266</v>
       </c>
       <c r="BA24" s="18">
         <v>6141</v>
@@ -4528,14 +4528,14 @@
       </c>
       <c r="BC24" s="10">
         <f t="shared" si="20"/>
-        <v>1302</v>
+        <v>6338</v>
       </c>
       <c r="BD24" s="20">
-        <v>5034</v>
+        <v>10070</v>
       </c>
       <c r="BE24" s="12">
         <f t="shared" si="21"/>
-        <v>0.81973619931607233</v>
+        <v>1.6397980784888455</v>
       </c>
       <c r="BF24" s="18">
         <v>7097</v>
@@ -4545,14 +4545,14 @@
       </c>
       <c r="BH24" s="10">
         <f t="shared" si="22"/>
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="BI24" s="11">
-        <v>5921</v>
+        <v>5923</v>
       </c>
       <c r="BJ24" s="12">
         <f t="shared" si="23"/>
-        <v>0.83429618148513451</v>
+        <v>0.83457799070029592</v>
       </c>
       <c r="BK24" s="24"/>
       <c r="BL24" s="24"/>
@@ -4742,14 +4742,14 @@
       </c>
       <c r="BC25" s="10">
         <f t="shared" si="20"/>
-        <v>3558</v>
+        <v>20871</v>
       </c>
       <c r="BD25" s="20">
-        <v>17313</v>
+        <v>34626</v>
       </c>
       <c r="BE25" s="12">
         <f t="shared" si="21"/>
-        <v>0.93045627989466329</v>
+        <v>1.8609125597893266</v>
       </c>
       <c r="BF25" s="18">
         <v>26131</v>
@@ -4956,14 +4956,14 @@
       </c>
       <c r="BC26" s="10">
         <f t="shared" si="20"/>
-        <v>3785</v>
+        <v>16810</v>
       </c>
       <c r="BD26" s="20">
-        <v>13025</v>
+        <v>26050</v>
       </c>
       <c r="BE26" s="12">
         <f t="shared" si="21"/>
-        <v>0.80735139155767677</v>
+        <v>1.6147027831153535</v>
       </c>
       <c r="BF26" s="18">
         <v>26642</v>
@@ -5000,14 +5000,14 @@
       </c>
       <c r="E27" s="10">
         <f t="shared" si="0"/>
-        <v>84773</v>
+        <v>84777</v>
       </c>
       <c r="F27" s="20">
-        <v>102177</v>
+        <v>102181</v>
       </c>
       <c r="G27" s="12">
         <f t="shared" si="1"/>
-        <v>0.90552744223969084</v>
+        <v>0.90556289160470416</v>
       </c>
       <c r="H27" s="15">
         <v>111842</v>
@@ -5017,14 +5017,14 @@
       </c>
       <c r="J27" s="10">
         <f t="shared" si="2"/>
-        <v>84479</v>
+        <v>84483</v>
       </c>
       <c r="K27" s="20">
-        <v>102031</v>
+        <v>102035</v>
       </c>
       <c r="L27" s="12">
         <f t="shared" si="3"/>
-        <v>0.91227803508520944</v>
+        <v>0.9123137998247528</v>
       </c>
       <c r="M27" s="16">
         <v>156288</v>
@@ -5034,14 +5034,14 @@
       </c>
       <c r="O27" s="10">
         <f t="shared" si="4"/>
-        <v>74501</v>
+        <v>74506</v>
       </c>
       <c r="P27" s="13">
-        <v>145754</v>
+        <v>145759</v>
       </c>
       <c r="Q27" s="12">
         <f t="shared" si="5"/>
-        <v>0.93259879197379192</v>
+        <v>0.93263078419328416</v>
       </c>
       <c r="R27" s="16">
         <v>113087</v>
@@ -5051,14 +5051,14 @@
       </c>
       <c r="T27" s="10">
         <f t="shared" si="6"/>
-        <v>39374</v>
+        <v>39379</v>
       </c>
       <c r="U27" s="20">
-        <v>104502</v>
+        <v>104507</v>
       </c>
       <c r="V27" s="12">
         <f t="shared" si="7"/>
-        <v>0.92408499650711395</v>
+        <v>0.92412921025405215</v>
       </c>
       <c r="W27" s="16">
         <v>116164</v>
@@ -5068,14 +5068,14 @@
       </c>
       <c r="Y27" s="10">
         <f t="shared" si="8"/>
-        <v>38420</v>
+        <v>38424</v>
       </c>
       <c r="Z27" s="20">
-        <v>108030</v>
+        <v>108034</v>
       </c>
       <c r="AA27" s="12">
         <f t="shared" si="9"/>
-        <v>0.92997830653214419</v>
+        <v>0.93001274060810579</v>
       </c>
       <c r="AB27" s="17">
         <v>165468</v>
@@ -5085,14 +5085,14 @@
       </c>
       <c r="AD27" s="10">
         <f t="shared" si="10"/>
-        <v>48101</v>
+        <v>48105</v>
       </c>
       <c r="AE27" s="11">
-        <v>155640</v>
+        <v>155644</v>
       </c>
       <c r="AF27" s="12">
         <f t="shared" si="11"/>
-        <v>0.94060482993690619</v>
+        <v>0.94062900379529579</v>
       </c>
       <c r="AG27" s="16">
         <v>116084</v>
@@ -5102,14 +5102,14 @@
       </c>
       <c r="AI27" s="10">
         <f t="shared" si="12"/>
-        <v>32766</v>
+        <v>32769</v>
       </c>
       <c r="AJ27" s="20">
-        <v>107143</v>
+        <v>107146</v>
       </c>
       <c r="AK27" s="12">
         <f t="shared" si="13"/>
-        <v>0.92297818820853861</v>
+        <v>0.92300403156335065</v>
       </c>
       <c r="AL27" s="18">
         <v>117992</v>
@@ -5119,14 +5119,14 @@
       </c>
       <c r="AN27" s="10">
         <f t="shared" si="14"/>
-        <v>33350</v>
+        <v>33353</v>
       </c>
       <c r="AO27" s="11">
-        <v>109174</v>
+        <v>109177</v>
       </c>
       <c r="AP27" s="12">
         <f t="shared" si="15"/>
-        <v>0.92526611973693129</v>
+        <v>0.92529154518950441</v>
       </c>
       <c r="AQ27" s="11">
         <v>170879</v>
@@ -5136,14 +5136,14 @@
       </c>
       <c r="AS27" s="10">
         <f t="shared" si="16"/>
-        <v>45162</v>
+        <v>45165</v>
       </c>
       <c r="AT27" s="13">
-        <v>160512</v>
+        <v>160515</v>
       </c>
       <c r="AU27" s="12">
         <f t="shared" si="17"/>
-        <v>0.93933133971991878</v>
+        <v>0.93934889600243443</v>
       </c>
       <c r="AV27" s="18">
         <v>116485</v>
@@ -5153,14 +5153,14 @@
       </c>
       <c r="AX27" s="10">
         <f t="shared" si="18"/>
-        <v>34162</v>
+        <v>34165</v>
       </c>
       <c r="AY27" s="20">
-        <v>109519</v>
+        <v>109522</v>
       </c>
       <c r="AZ27" s="12">
         <f t="shared" si="19"/>
-        <v>0.94019830879512378</v>
+        <v>0.94022406318410101</v>
       </c>
       <c r="BA27" s="18">
         <v>117017</v>
@@ -5170,14 +5170,14 @@
       </c>
       <c r="BC27" s="10">
         <f t="shared" si="20"/>
-        <v>38110</v>
+        <v>149525</v>
       </c>
       <c r="BD27" s="20">
-        <v>111412</v>
+        <v>222827</v>
       </c>
       <c r="BE27" s="12">
         <f t="shared" si="21"/>
-        <v>0.95210097678115146</v>
+        <v>1.9042275908628661</v>
       </c>
       <c r="BF27" s="18">
         <v>172738</v>
@@ -5187,14 +5187,14 @@
       </c>
       <c r="BH27" s="10">
         <f t="shared" si="22"/>
-        <v>63109</v>
+        <v>63112</v>
       </c>
       <c r="BI27" s="11">
-        <v>164654</v>
+        <v>164657</v>
       </c>
       <c r="BJ27" s="12">
         <f t="shared" si="23"/>
-        <v>0.95320080121339834</v>
+        <v>0.95321816855584762</v>
       </c>
       <c r="BK27" s="24"/>
       <c r="BL27" s="24"/>
@@ -5214,14 +5214,14 @@
       </c>
       <c r="E28" s="10">
         <f t="shared" si="0"/>
-        <v>248066</v>
+        <v>248067</v>
       </c>
       <c r="F28" s="20">
-        <v>327101</v>
+        <v>327102</v>
       </c>
       <c r="G28" s="12">
         <f t="shared" si="1"/>
-        <v>0.86823378271129126</v>
+        <v>0.86823643704063513</v>
       </c>
       <c r="H28" s="15">
         <v>377506</v>
@@ -5231,14 +5231,14 @@
       </c>
       <c r="J28" s="10">
         <f t="shared" si="2"/>
-        <v>256661</v>
+        <v>256662</v>
       </c>
       <c r="K28" s="20">
-        <v>327719</v>
+        <v>327720</v>
       </c>
       <c r="L28" s="12">
         <f t="shared" si="3"/>
-        <v>0.86811600345424977</v>
+        <v>0.86811865241876951</v>
       </c>
       <c r="M28" s="16">
         <v>622937</v>
@@ -5248,14 +5248,14 @@
       </c>
       <c r="O28" s="10">
         <f t="shared" si="4"/>
-        <v>184096</v>
+        <v>184097</v>
       </c>
       <c r="P28" s="13">
-        <v>569146</v>
+        <v>569147</v>
       </c>
       <c r="Q28" s="12">
         <f t="shared" si="5"/>
-        <v>0.91364937385321465</v>
+        <v>0.9136509791519849</v>
       </c>
       <c r="R28" s="16">
         <v>379798</v>
@@ -5265,14 +5265,14 @@
       </c>
       <c r="T28" s="10">
         <f t="shared" si="6"/>
-        <v>82843</v>
+        <v>82844</v>
       </c>
       <c r="U28" s="20">
-        <v>329382</v>
+        <v>329383</v>
       </c>
       <c r="V28" s="12">
         <f t="shared" si="7"/>
-        <v>0.86725575174171532</v>
+        <v>0.8672583847202987</v>
       </c>
       <c r="W28" s="16">
         <v>378910</v>
@@ -5282,14 +5282,14 @@
       </c>
       <c r="Y28" s="10">
         <f t="shared" si="8"/>
-        <v>83069</v>
+        <v>83070</v>
       </c>
       <c r="Z28" s="20">
-        <v>334168</v>
+        <v>334169</v>
       </c>
       <c r="AA28" s="12">
         <f t="shared" si="9"/>
-        <v>0.88191918925338475</v>
+        <v>0.88192182840252298</v>
       </c>
       <c r="AB28" s="17">
         <v>628364</v>
@@ -5299,14 +5299,14 @@
       </c>
       <c r="AD28" s="10">
         <f t="shared" si="10"/>
-        <v>120948</v>
+        <v>120949</v>
       </c>
       <c r="AE28" s="11">
-        <v>580311</v>
+        <v>580312</v>
       </c>
       <c r="AF28" s="12">
         <f t="shared" si="11"/>
-        <v>0.92352680930161501</v>
+        <v>0.92352840073587916</v>
       </c>
       <c r="AG28" s="16">
         <v>375124</v>
@@ -5316,14 +5316,14 @@
       </c>
       <c r="AI28" s="10">
         <f t="shared" si="12"/>
-        <v>67358</v>
+        <v>67359</v>
       </c>
       <c r="AJ28" s="20">
-        <v>333742</v>
+        <v>333743</v>
       </c>
       <c r="AK28" s="12">
         <f t="shared" si="13"/>
-        <v>0.88968447766605174</v>
+        <v>0.88968714345123212</v>
       </c>
       <c r="AL28" s="18">
         <v>368781</v>
@@ -5333,14 +5333,14 @@
       </c>
       <c r="AN28" s="10">
         <f t="shared" si="14"/>
-        <v>68521</v>
+        <v>68522</v>
       </c>
       <c r="AO28" s="11">
-        <v>338477</v>
+        <v>338478</v>
       </c>
       <c r="AP28" s="12">
         <f t="shared" si="15"/>
-        <v>0.91782656915622007</v>
+        <v>0.91782928079266557</v>
       </c>
       <c r="AQ28" s="11">
         <v>617418</v>
@@ -5350,14 +5350,14 @@
       </c>
       <c r="AS28" s="10">
         <f t="shared" si="16"/>
-        <v>98510</v>
+        <v>98511</v>
       </c>
       <c r="AT28" s="13">
-        <v>590272</v>
+        <v>590273</v>
       </c>
       <c r="AU28" s="12">
         <f t="shared" si="17"/>
-        <v>0.95603302786766831</v>
+        <v>0.95603464751594547</v>
       </c>
       <c r="AV28" s="18">
         <v>357852</v>
@@ -5367,14 +5367,14 @@
       </c>
       <c r="AX28" s="10">
         <f t="shared" si="18"/>
-        <v>67578</v>
+        <v>67579</v>
       </c>
       <c r="AY28" s="20">
-        <v>340250</v>
+        <v>340251</v>
       </c>
       <c r="AZ28" s="12">
         <f t="shared" si="19"/>
-        <v>0.95081206755865555</v>
+        <v>0.95081486200999299</v>
       </c>
       <c r="BA28" s="18">
         <v>359943</v>
@@ -5384,14 +5384,14 @@
       </c>
       <c r="BC28" s="10">
         <f t="shared" si="20"/>
-        <v>73130</v>
+        <v>418089</v>
       </c>
       <c r="BD28" s="20">
-        <v>344958</v>
+        <v>689917</v>
       </c>
       <c r="BE28" s="12">
         <f t="shared" si="21"/>
-        <v>0.95836840833131909</v>
+        <v>1.9167395948803005</v>
       </c>
       <c r="BF28" s="18">
         <v>622234</v>
@@ -5401,14 +5401,14 @@
       </c>
       <c r="BH28" s="10">
         <f t="shared" si="22"/>
-        <v>124734</v>
+        <v>124735</v>
       </c>
       <c r="BI28" s="11">
-        <v>600526</v>
+        <v>600527</v>
       </c>
       <c r="BJ28" s="12">
         <f t="shared" si="23"/>
-        <v>0.96511280322193904</v>
+        <v>0.96511441033437584</v>
       </c>
       <c r="BK28" s="24"/>
       <c r="BL28" s="24"/>
@@ -5428,14 +5428,14 @@
       </c>
       <c r="E29" s="10">
         <f t="shared" si="0"/>
-        <v>85754</v>
+        <v>85755</v>
       </c>
       <c r="F29" s="20">
-        <v>104765</v>
+        <v>104766</v>
       </c>
       <c r="G29" s="12">
         <f t="shared" si="1"/>
-        <v>0.96635981256687453</v>
+        <v>0.96636903663801055</v>
       </c>
       <c r="H29" s="15">
         <v>108534</v>
@@ -5445,14 +5445,14 @@
       </c>
       <c r="J29" s="10">
         <f t="shared" si="2"/>
-        <v>81762</v>
+        <v>81763</v>
       </c>
       <c r="K29" s="20">
-        <v>104730</v>
+        <v>104731</v>
       </c>
       <c r="L29" s="12">
         <f t="shared" si="3"/>
-        <v>0.96495107523909562</v>
+        <v>0.96496028894171415</v>
       </c>
       <c r="M29" s="16">
         <v>155259</v>
@@ -5462,14 +5462,14 @@
       </c>
       <c r="O29" s="10">
         <f t="shared" si="4"/>
-        <v>58704</v>
+        <v>58705</v>
       </c>
       <c r="P29" s="13">
-        <v>150185</v>
+        <v>150186</v>
       </c>
       <c r="Q29" s="12">
         <f t="shared" si="5"/>
-        <v>0.96731912481724092</v>
+        <v>0.96732556566769079</v>
       </c>
       <c r="R29" s="16">
         <v>111838</v>
@@ -5479,14 +5479,14 @@
       </c>
       <c r="T29" s="10">
         <f t="shared" si="6"/>
-        <v>29092</v>
+        <v>29093</v>
       </c>
       <c r="U29" s="20">
-        <v>106914</v>
+        <v>106915</v>
       </c>
       <c r="V29" s="12">
         <f t="shared" si="7"/>
-        <v>0.95597203097337224</v>
+        <v>0.95598097247804859</v>
       </c>
       <c r="W29" s="16">
         <v>113722</v>
@@ -5496,14 +5496,14 @@
       </c>
       <c r="Y29" s="10">
         <f t="shared" si="8"/>
-        <v>27481</v>
+        <v>27482</v>
       </c>
       <c r="Z29" s="20">
-        <v>108539</v>
+        <v>108540</v>
       </c>
       <c r="AA29" s="12">
         <f t="shared" si="9"/>
-        <v>0.95442394611420833</v>
+        <v>0.95443273948752216</v>
       </c>
       <c r="AB29" s="17">
         <v>160157</v>
@@ -5513,14 +5513,14 @@
       </c>
       <c r="AD29" s="10">
         <f t="shared" si="10"/>
-        <v>33490</v>
+        <v>33491</v>
       </c>
       <c r="AE29" s="11">
-        <v>154120</v>
+        <v>154121</v>
       </c>
       <c r="AF29" s="12">
         <f t="shared" si="11"/>
-        <v>0.96230573749508297</v>
+        <v>0.96231198136828233</v>
       </c>
       <c r="AG29" s="16">
         <v>115309</v>
@@ -5530,14 +5530,14 @@
       </c>
       <c r="AI29" s="10">
         <f t="shared" si="12"/>
-        <v>25252</v>
+        <v>25253</v>
       </c>
       <c r="AJ29" s="20">
-        <v>109813</v>
+        <v>109814</v>
       </c>
       <c r="AK29" s="12">
         <f t="shared" si="13"/>
-        <v>0.95233676469312889</v>
+        <v>0.95234543704307562</v>
       </c>
       <c r="AL29" s="18">
         <v>116530</v>
@@ -5547,14 +5547,14 @@
       </c>
       <c r="AN29" s="10">
         <f t="shared" si="14"/>
-        <v>23998</v>
+        <v>23999</v>
       </c>
       <c r="AO29" s="11">
-        <v>110929</v>
+        <v>110930</v>
       </c>
       <c r="AP29" s="12">
         <f t="shared" si="15"/>
-        <v>0.95193512400240277</v>
+        <v>0.95194370548356644</v>
       </c>
       <c r="AQ29" s="11">
         <v>164389</v>
@@ -5564,14 +5564,14 @@
       </c>
       <c r="AS29" s="10">
         <f t="shared" si="16"/>
-        <v>29547</v>
+        <v>29548</v>
       </c>
       <c r="AT29" s="13">
-        <v>157111</v>
+        <v>157112</v>
       </c>
       <c r="AU29" s="12">
         <f t="shared" si="17"/>
-        <v>0.95572696469958451</v>
+        <v>0.95573304783166757</v>
       </c>
       <c r="AV29" s="18">
         <v>118862</v>
@@ -5581,14 +5581,14 @@
       </c>
       <c r="AX29" s="10">
         <f t="shared" si="18"/>
-        <v>23779</v>
+        <v>23780</v>
       </c>
       <c r="AY29" s="20">
-        <v>112719</v>
+        <v>112720</v>
       </c>
       <c r="AZ29" s="12">
         <f t="shared" si="19"/>
-        <v>0.94831821776513936</v>
+        <v>0.94832663088287261</v>
       </c>
       <c r="BA29" s="18">
         <v>119046</v>
@@ -5598,14 +5598,14 @@
       </c>
       <c r="BC29" s="10">
         <f t="shared" si="20"/>
-        <v>29754</v>
+        <v>143890</v>
       </c>
       <c r="BD29" s="20">
-        <v>114135</v>
+        <v>228271</v>
       </c>
       <c r="BE29" s="12">
         <f t="shared" si="21"/>
-        <v>0.9587470389597299</v>
+        <v>1.9175024780337013</v>
       </c>
       <c r="BF29" s="18">
         <v>167253</v>
@@ -5615,14 +5615,14 @@
       </c>
       <c r="BH29" s="10">
         <f t="shared" si="22"/>
-        <v>41680</v>
+        <v>41681</v>
       </c>
       <c r="BI29" s="11">
-        <v>160684</v>
+        <v>160685</v>
       </c>
       <c r="BJ29" s="12">
         <f t="shared" si="23"/>
-        <v>0.96072417236163177</v>
+        <v>0.9607301513276294</v>
       </c>
       <c r="BK29" s="24"/>
       <c r="BL29" s="24"/>
@@ -5676,14 +5676,14 @@
       </c>
       <c r="O30" s="10">
         <f t="shared" si="4"/>
-        <v>99040</v>
+        <v>99041</v>
       </c>
       <c r="P30" s="13">
-        <v>241547</v>
+        <v>241548</v>
       </c>
       <c r="Q30" s="12">
         <f t="shared" si="5"/>
-        <v>0.9663735437203943</v>
+        <v>0.96637754448854185</v>
       </c>
       <c r="R30" s="16">
         <v>151431</v>
@@ -5693,14 +5693,14 @@
       </c>
       <c r="T30" s="10">
         <f t="shared" si="6"/>
-        <v>43789</v>
+        <v>43790</v>
       </c>
       <c r="U30" s="20">
-        <v>143284</v>
+        <v>143285</v>
       </c>
       <c r="V30" s="12">
         <f t="shared" si="7"/>
-        <v>0.94619991943525439</v>
+        <v>0.94620652310293141</v>
       </c>
       <c r="W30" s="16">
         <v>154416</v>
@@ -5710,14 +5710,14 @@
       </c>
       <c r="Y30" s="10">
         <f t="shared" si="8"/>
-        <v>43109</v>
+        <v>43110</v>
       </c>
       <c r="Z30" s="20">
-        <v>146809</v>
+        <v>146810</v>
       </c>
       <c r="AA30" s="12">
         <f t="shared" si="9"/>
-        <v>0.95073697026214898</v>
+        <v>0.95074344627499741</v>
       </c>
       <c r="AB30" s="17">
         <v>259264</v>
@@ -5727,14 +5727,14 @@
       </c>
       <c r="AD30" s="10">
         <f t="shared" si="10"/>
-        <v>60276</v>
+        <v>60277</v>
       </c>
       <c r="AE30" s="11">
-        <v>248443</v>
+        <v>248444</v>
       </c>
       <c r="AF30" s="12">
         <f t="shared" si="11"/>
-        <v>0.95826262034065668</v>
+        <v>0.95826647741298443</v>
       </c>
       <c r="AG30" s="16">
         <v>153178</v>
@@ -5744,14 +5744,14 @@
       </c>
       <c r="AI30" s="10">
         <f t="shared" si="12"/>
-        <v>35796</v>
+        <v>35797</v>
       </c>
       <c r="AJ30" s="20">
-        <v>144600</v>
+        <v>144601</v>
       </c>
       <c r="AK30" s="12">
         <f t="shared" si="13"/>
-        <v>0.9439997910927157</v>
+        <v>0.94400631944535118</v>
       </c>
       <c r="AL30" s="18">
         <v>156106</v>
@@ -5761,14 +5761,14 @@
       </c>
       <c r="AN30" s="10">
         <f t="shared" si="14"/>
-        <v>37176</v>
+        <v>37177</v>
       </c>
       <c r="AO30" s="11">
-        <v>147872</v>
+        <v>147873</v>
       </c>
       <c r="AP30" s="12">
         <f t="shared" si="15"/>
-        <v>0.94725378909202718</v>
+        <v>0.94726019499570802</v>
       </c>
       <c r="AQ30" s="11">
         <v>266513</v>
@@ -5778,14 +5778,14 @@
       </c>
       <c r="AS30" s="10">
         <f t="shared" si="16"/>
-        <v>56623</v>
+        <v>56624</v>
       </c>
       <c r="AT30" s="13">
-        <v>254743</v>
+        <v>254744</v>
       </c>
       <c r="AU30" s="12">
         <f t="shared" si="17"/>
-        <v>0.95583705110069672</v>
+        <v>0.95584080326288023</v>
       </c>
       <c r="AV30" s="18">
         <v>155103</v>
@@ -5795,14 +5795,14 @@
       </c>
       <c r="AX30" s="10">
         <f t="shared" si="18"/>
-        <v>39204</v>
+        <v>39205</v>
       </c>
       <c r="AY30" s="20">
-        <v>148221</v>
+        <v>148222</v>
       </c>
       <c r="AZ30" s="12">
         <f t="shared" si="19"/>
-        <v>0.95562948492292221</v>
+        <v>0.95563593225147159</v>
       </c>
       <c r="BA30" s="18">
         <v>156855</v>
@@ -5812,14 +5812,14 @@
       </c>
       <c r="BC30" s="10">
         <f t="shared" si="20"/>
-        <v>41865</v>
+        <v>192661</v>
       </c>
       <c r="BD30" s="20">
-        <v>150795</v>
+        <v>301591</v>
       </c>
       <c r="BE30" s="12">
         <f t="shared" si="21"/>
-        <v>0.96136559242612607</v>
+        <v>1.9227375601670333</v>
       </c>
       <c r="BF30" s="18">
         <v>270589</v>
@@ -5829,14 +5829,14 @@
       </c>
       <c r="BH30" s="10">
         <f t="shared" si="22"/>
-        <v>73592</v>
+        <v>73593</v>
       </c>
       <c r="BI30" s="11">
-        <v>259807</v>
+        <v>259808</v>
       </c>
       <c r="BJ30" s="12">
         <f t="shared" si="23"/>
-        <v>0.96015359087028662</v>
+        <v>0.96015728651201637</v>
       </c>
       <c r="BK30" s="24"/>
       <c r="BL30" s="24"/>
@@ -6026,14 +6026,14 @@
       </c>
       <c r="BC31" s="10">
         <f t="shared" si="20"/>
-        <v>25490</v>
+        <v>97273</v>
       </c>
       <c r="BD31" s="20">
-        <v>71783</v>
+        <v>143566</v>
       </c>
       <c r="BE31" s="12">
         <f t="shared" si="21"/>
-        <v>0.97032901673470495</v>
+        <v>1.9406580334694099</v>
       </c>
       <c r="BF31" s="18">
         <v>129555</v>
@@ -6043,14 +6043,14 @@
       </c>
       <c r="BH31" s="10">
         <f t="shared" si="22"/>
-        <v>48860</v>
+        <v>48862</v>
       </c>
       <c r="BI31" s="11">
-        <v>125621</v>
+        <v>125623</v>
       </c>
       <c r="BJ31" s="12">
         <f t="shared" si="23"/>
-        <v>0.96963451815831114</v>
+        <v>0.96964995561730538</v>
       </c>
       <c r="BK31" s="24"/>
       <c r="BL31" s="24"/>
@@ -6223,14 +6223,14 @@
       </c>
       <c r="AX32" s="10">
         <f t="shared" si="18"/>
-        <v>44447</v>
+        <v>44448</v>
       </c>
       <c r="AY32" s="20">
-        <v>183819</v>
+        <v>183820</v>
       </c>
       <c r="AZ32" s="12">
         <f t="shared" si="19"/>
-        <v>0.98256895445798587</v>
+        <v>0.98257429976480648</v>
       </c>
       <c r="BA32" s="18">
         <v>189893</v>
@@ -6240,14 +6240,14 @@
       </c>
       <c r="BC32" s="10">
         <f t="shared" si="20"/>
-        <v>49711</v>
+        <v>238146</v>
       </c>
       <c r="BD32" s="20">
-        <v>188435</v>
+        <v>376870</v>
       </c>
       <c r="BE32" s="12">
         <f t="shared" si="21"/>
-        <v>0.99232199185857295</v>
+        <v>1.9846439837171459</v>
       </c>
       <c r="BF32" s="18">
         <v>410654</v>
@@ -6284,14 +6284,14 @@
       </c>
       <c r="E33" s="10">
         <f t="shared" si="0"/>
-        <v>412435</v>
+        <v>412438</v>
       </c>
       <c r="F33" s="20">
-        <v>538750</v>
+        <v>538753</v>
       </c>
       <c r="G33" s="12">
         <f t="shared" si="1"/>
-        <v>0.97156098968477245</v>
+        <v>0.9715663997691697</v>
       </c>
       <c r="H33" s="15">
         <v>558618</v>
@@ -6301,14 +6301,14 @@
       </c>
       <c r="J33" s="10">
         <f t="shared" si="2"/>
-        <v>390449</v>
+        <v>390451</v>
       </c>
       <c r="K33" s="20">
-        <v>543649</v>
+        <v>543651</v>
       </c>
       <c r="L33" s="12">
         <f t="shared" si="3"/>
-        <v>0.97320351295518581</v>
+        <v>0.97320709321933774</v>
       </c>
       <c r="M33" s="16">
         <v>943614</v>
@@ -6318,14 +6318,14 @@
       </c>
       <c r="O33" s="10">
         <f t="shared" si="4"/>
-        <v>222024</v>
+        <v>222027</v>
       </c>
       <c r="P33" s="13">
-        <v>930043</v>
+        <v>930046</v>
       </c>
       <c r="Q33" s="12">
         <f t="shared" si="5"/>
-        <v>0.98561805992704643</v>
+        <v>0.9856212391931447</v>
       </c>
       <c r="R33" s="16">
         <v>563773</v>
@@ -6335,14 +6335,14 @@
       </c>
       <c r="T33" s="10">
         <f t="shared" si="6"/>
-        <v>103844</v>
+        <v>103847</v>
       </c>
       <c r="U33" s="20">
-        <v>552424</v>
+        <v>552427</v>
       </c>
       <c r="V33" s="12">
         <f t="shared" si="7"/>
-        <v>0.97986955742825566</v>
+        <v>0.97987487871891699</v>
       </c>
       <c r="W33" s="16">
         <v>571583</v>
@@ -6352,14 +6352,14 @@
       </c>
       <c r="Y33" s="10">
         <f t="shared" si="8"/>
-        <v>110955</v>
+        <v>110957</v>
       </c>
       <c r="Z33" s="20">
-        <v>558699</v>
+        <v>558701</v>
       </c>
       <c r="AA33" s="12">
         <f t="shared" si="9"/>
-        <v>0.9774590916804734</v>
+        <v>0.97746259073485386</v>
       </c>
       <c r="AB33" s="17">
         <v>961057</v>
@@ -6369,14 +6369,14 @@
       </c>
       <c r="AD33" s="10">
         <f t="shared" si="10"/>
-        <v>149480</v>
+        <v>149482</v>
       </c>
       <c r="AE33" s="11">
-        <v>945169</v>
+        <v>945171</v>
       </c>
       <c r="AF33" s="12">
         <f t="shared" si="11"/>
-        <v>0.98346820219820463</v>
+        <v>0.98347028324022401</v>
       </c>
       <c r="AG33" s="16">
         <v>565645</v>
@@ -6386,14 +6386,14 @@
       </c>
       <c r="AI33" s="10">
         <f t="shared" si="12"/>
-        <v>97881</v>
+        <v>97883</v>
       </c>
       <c r="AJ33" s="20">
-        <v>554661</v>
+        <v>554663</v>
       </c>
       <c r="AK33" s="12">
         <f t="shared" si="13"/>
-        <v>0.98058146010306813</v>
+        <v>0.98058499588964809</v>
       </c>
       <c r="AL33" s="18">
         <v>569536</v>
@@ -6403,14 +6403,14 @@
       </c>
       <c r="AN33" s="10">
         <f t="shared" si="14"/>
-        <v>93730</v>
+        <v>93732</v>
       </c>
       <c r="AO33" s="11">
-        <v>559625</v>
+        <v>559627</v>
       </c>
       <c r="AP33" s="12">
         <f t="shared" si="15"/>
-        <v>0.98259811495673666</v>
+        <v>0.98260162658725703</v>
       </c>
       <c r="AQ33" s="11">
         <v>971221</v>
@@ -6420,14 +6420,14 @@
       </c>
       <c r="AS33" s="10">
         <f t="shared" si="16"/>
-        <v>154796</v>
+        <v>154798</v>
       </c>
       <c r="AT33" s="13">
-        <v>956296</v>
+        <v>956298</v>
       </c>
       <c r="AU33" s="12">
         <f t="shared" si="17"/>
-        <v>0.9846327457911227</v>
+        <v>0.98463480505466827</v>
       </c>
       <c r="AV33" s="18">
         <v>571074</v>
@@ -6437,14 +6437,14 @@
       </c>
       <c r="AX33" s="10">
         <f t="shared" si="18"/>
-        <v>93000</v>
+        <v>93001</v>
       </c>
       <c r="AY33" s="20">
-        <v>564193</v>
+        <v>564194</v>
       </c>
       <c r="AZ33" s="12">
         <f t="shared" si="19"/>
-        <v>0.98795077345492877</v>
+        <v>0.98795252454147797</v>
       </c>
       <c r="BA33" s="18">
         <v>575700</v>
@@ -6454,14 +6454,14 @@
       </c>
       <c r="BC33" s="10">
         <f t="shared" si="20"/>
-        <v>96948</v>
+        <v>670804</v>
       </c>
       <c r="BD33" s="20">
-        <v>573854</v>
+        <v>1147710</v>
       </c>
       <c r="BE33" s="12">
         <f t="shared" si="21"/>
-        <v>0.9967934688205663</v>
+        <v>1.9935904116727463</v>
       </c>
       <c r="BF33" s="18">
         <v>986775</v>
@@ -6471,14 +6471,14 @@
       </c>
       <c r="BH33" s="10">
         <f t="shared" si="22"/>
-        <v>171035</v>
+        <v>171038</v>
       </c>
       <c r="BI33" s="11">
-        <v>975799</v>
+        <v>975802</v>
       </c>
       <c r="BJ33" s="12">
         <f t="shared" si="23"/>
-        <v>0.98887689696232672</v>
+        <v>0.98887993716906086</v>
       </c>
       <c r="BK33" s="24"/>
       <c r="BL33" s="24"/>
@@ -6858,14 +6858,14 @@
       </c>
       <c r="BC35" s="10">
         <f t="shared" si="20"/>
-        <v>2551</v>
+        <v>13651</v>
       </c>
       <c r="BD35" s="20">
-        <v>11100</v>
+        <v>22200</v>
       </c>
       <c r="BE35" s="12">
         <f t="shared" si="21"/>
-        <v>0.96429502215272345</v>
+        <v>1.9285900443054469</v>
       </c>
       <c r="BF35" s="18">
         <v>14581</v>
@@ -6902,14 +6902,14 @@
       </c>
       <c r="E36" s="10">
         <f t="shared" si="0"/>
-        <v>551054</v>
+        <v>551058</v>
       </c>
       <c r="F36" s="20">
-        <v>726061</v>
+        <v>726065</v>
       </c>
       <c r="G36" s="12">
         <f t="shared" si="1"/>
-        <v>0.97115536377814571</v>
+        <v>0.97116071404686299</v>
       </c>
       <c r="H36" s="15">
         <v>754952</v>
@@ -6919,14 +6919,14 @@
       </c>
       <c r="J36" s="10">
         <f t="shared" si="2"/>
-        <v>545537</v>
+        <v>545540</v>
       </c>
       <c r="K36" s="20">
-        <v>731887</v>
+        <v>731890</v>
       </c>
       <c r="L36" s="12">
         <f t="shared" si="3"/>
-        <v>0.96944838877173645</v>
+        <v>0.96945236253430678</v>
       </c>
       <c r="M36" s="16">
         <v>1378095</v>
@@ -6936,14 +6936,14 @@
       </c>
       <c r="O36" s="10">
         <f t="shared" si="4"/>
-        <v>493441</v>
+        <v>493444</v>
       </c>
       <c r="P36" s="13">
-        <v>1346552</v>
+        <v>1346555</v>
       </c>
       <c r="Q36" s="12">
         <f t="shared" si="5"/>
-        <v>0.97711115706827179</v>
+        <v>0.97711333398640876</v>
       </c>
       <c r="R36" s="16">
         <v>758000</v>
@@ -6953,14 +6953,14 @@
       </c>
       <c r="T36" s="10">
         <f t="shared" si="6"/>
-        <v>231302</v>
+        <v>231304</v>
       </c>
       <c r="U36" s="20">
-        <v>732474</v>
+        <v>732476</v>
       </c>
       <c r="V36" s="12">
         <f t="shared" si="7"/>
-        <v>0.96632453825857523</v>
+        <v>0.96632717678100266</v>
       </c>
       <c r="W36" s="16">
         <v>766789</v>
@@ -6970,14 +6970,14 @@
       </c>
       <c r="Y36" s="10">
         <f t="shared" si="8"/>
-        <v>245542</v>
+        <v>245544</v>
       </c>
       <c r="Z36" s="20">
-        <v>748540</v>
+        <v>748542</v>
       </c>
       <c r="AA36" s="12">
         <f t="shared" si="9"/>
-        <v>0.9762007540535923</v>
+        <v>0.97620336233305383</v>
       </c>
       <c r="AB36" s="17">
         <v>1410553</v>
@@ -6987,14 +6987,14 @@
       </c>
       <c r="AD36" s="10">
         <f t="shared" si="10"/>
-        <v>344794</v>
+        <v>344797</v>
       </c>
       <c r="AE36" s="11">
-        <v>1378471</v>
+        <v>1378474</v>
       </c>
       <c r="AF36" s="12">
         <f t="shared" si="11"/>
-        <v>0.97725572878154876</v>
+        <v>0.9772578556069853</v>
       </c>
       <c r="AG36" s="16">
         <v>767229</v>
@@ -7004,14 +7004,14 @@
       </c>
       <c r="AI36" s="10">
         <f t="shared" si="12"/>
-        <v>202702</v>
+        <v>202706</v>
       </c>
       <c r="AJ36" s="20">
-        <v>744520</v>
+        <v>744524</v>
       </c>
       <c r="AK36" s="12">
         <f t="shared" si="13"/>
-        <v>0.97040127523855324</v>
+        <v>0.97040648880581937</v>
       </c>
       <c r="AL36" s="18">
         <v>779513</v>
@@ -7021,14 +7021,14 @@
       </c>
       <c r="AN36" s="10">
         <f t="shared" si="14"/>
-        <v>205109</v>
+        <v>205112</v>
       </c>
       <c r="AO36" s="11">
-        <v>755707</v>
+        <v>755710</v>
       </c>
       <c r="AP36" s="12">
         <f t="shared" si="15"/>
-        <v>0.96946041951834028</v>
+        <v>0.96946426807506736</v>
       </c>
       <c r="AQ36" s="11">
         <v>1443943</v>
@@ -7038,14 +7038,14 @@
       </c>
       <c r="AS36" s="10">
         <f t="shared" si="16"/>
-        <v>324142</v>
+        <v>324145</v>
       </c>
       <c r="AT36" s="13">
-        <v>1402888</v>
+        <v>1402891</v>
       </c>
       <c r="AU36" s="12">
         <f t="shared" si="17"/>
-        <v>0.97156743721878214</v>
+        <v>0.97156951486312138</v>
       </c>
       <c r="AV36" s="18">
         <v>783108</v>
@@ -7055,14 +7055,14 @@
       </c>
       <c r="AX36" s="10">
         <f t="shared" si="18"/>
-        <v>207948</v>
+        <v>207951</v>
       </c>
       <c r="AY36" s="20">
-        <v>758545</v>
+        <v>758548</v>
       </c>
       <c r="AZ36" s="12">
         <f t="shared" si="19"/>
-        <v>0.96863395598052882</v>
+        <v>0.96863778686975488</v>
       </c>
       <c r="BA36" s="18">
         <v>793830</v>
@@ -7072,14 +7072,14 @@
       </c>
       <c r="BC36" s="10">
         <f t="shared" si="20"/>
-        <v>206323</v>
+        <v>978512</v>
       </c>
       <c r="BD36" s="20">
-        <v>772186</v>
+        <v>1544375</v>
       </c>
       <c r="BE36" s="12">
         <f t="shared" si="21"/>
-        <v>0.97273471650101406</v>
+        <v>1.9454732121486968</v>
       </c>
       <c r="BF36" s="18">
         <v>1468416</v>
@@ -7089,14 +7089,14 @@
       </c>
       <c r="BH36" s="10">
         <f t="shared" si="24"/>
-        <v>383746</v>
+        <v>383749</v>
       </c>
       <c r="BI36" s="11">
-        <v>1426412</v>
+        <v>1426415</v>
       </c>
       <c r="BJ36" s="12">
         <f t="shared" si="25"/>
-        <v>0.97139502702231517</v>
+        <v>0.97139707004009768</v>
       </c>
       <c r="BK36" s="24"/>
       <c r="BL36" s="24"/>
@@ -7116,14 +7116,14 @@
       </c>
       <c r="E37" s="10">
         <f t="shared" si="0"/>
-        <v>478357</v>
+        <v>478360</v>
       </c>
       <c r="F37" s="20">
-        <v>566440</v>
+        <v>566443</v>
       </c>
       <c r="G37" s="12">
         <f t="shared" si="1"/>
-        <v>0.95615081943968527</v>
+        <v>0.95615588344021185</v>
       </c>
       <c r="H37" s="15">
         <v>593173</v>
@@ -7133,14 +7133,14 @@
       </c>
       <c r="J37" s="10">
         <f t="shared" si="2"/>
-        <v>459862</v>
+        <v>459865</v>
       </c>
       <c r="K37" s="20">
-        <v>566663</v>
+        <v>566666</v>
       </c>
       <c r="L37" s="12">
         <f t="shared" si="3"/>
-        <v>0.95530814787591478</v>
+        <v>0.95531320542236409</v>
       </c>
       <c r="M37" s="16">
         <v>768378</v>
@@ -7150,14 +7150,14 @@
       </c>
       <c r="O37" s="10">
         <f t="shared" si="4"/>
-        <v>267461</v>
+        <v>267464</v>
       </c>
       <c r="P37" s="13">
-        <v>738204</v>
+        <v>738207</v>
       </c>
       <c r="Q37" s="12">
         <f t="shared" si="5"/>
-        <v>0.96073026557241359</v>
+        <v>0.960734169900752</v>
       </c>
       <c r="R37" s="16">
         <v>601605</v>
@@ -7167,14 +7167,14 @@
       </c>
       <c r="T37" s="10">
         <f t="shared" si="6"/>
-        <v>144755</v>
+        <v>144760</v>
       </c>
       <c r="U37" s="20">
-        <v>573941</v>
+        <v>573946</v>
       </c>
       <c r="V37" s="12">
         <f t="shared" si="7"/>
-        <v>0.9540163396248369</v>
+        <v>0.95402465072597464</v>
       </c>
       <c r="W37" s="16">
         <v>609453</v>
@@ -7184,14 +7184,14 @@
       </c>
       <c r="Y37" s="10">
         <f t="shared" si="8"/>
-        <v>142440</v>
+        <v>142443</v>
       </c>
       <c r="Z37" s="20">
-        <v>583176</v>
+        <v>583179</v>
       </c>
       <c r="AA37" s="12">
         <f t="shared" si="9"/>
-        <v>0.95688428804189984</v>
+        <v>0.95688921048874975</v>
       </c>
       <c r="AB37" s="17">
         <v>790568</v>
@@ -7201,14 +7201,14 @@
       </c>
       <c r="AD37" s="10">
         <f t="shared" si="10"/>
-        <v>172694</v>
+        <v>172697</v>
       </c>
       <c r="AE37" s="11">
-        <v>759626</v>
+        <v>759629</v>
       </c>
       <c r="AF37" s="12">
         <f t="shared" si="11"/>
-        <v>0.96086105180073056</v>
+        <v>0.96086484654071502</v>
       </c>
       <c r="AG37" s="16">
         <v>617773</v>
@@ -7218,14 +7218,14 @@
       </c>
       <c r="AI37" s="10">
         <f t="shared" si="12"/>
-        <v>117967</v>
+        <v>117973</v>
       </c>
       <c r="AJ37" s="20">
-        <v>589769</v>
+        <v>589775</v>
       </c>
       <c r="AK37" s="12">
         <f t="shared" si="13"/>
-        <v>0.95466943359454037</v>
+        <v>0.95467914589986935</v>
       </c>
       <c r="AL37" s="18">
         <v>624724</v>
@@ -7235,14 +7235,14 @@
       </c>
       <c r="AN37" s="10">
         <f t="shared" si="14"/>
-        <v>122523</v>
+        <v>122527</v>
       </c>
       <c r="AO37" s="11">
-        <v>596612</v>
+        <v>596616</v>
       </c>
       <c r="AP37" s="12">
         <f t="shared" si="15"/>
-        <v>0.95500092840998585</v>
+        <v>0.9550073312374745</v>
       </c>
       <c r="AQ37" s="11">
         <v>810789</v>
@@ -7252,14 +7252,14 @@
       </c>
       <c r="AS37" s="10">
         <f t="shared" si="16"/>
-        <v>156909</v>
+        <v>156914</v>
       </c>
       <c r="AT37" s="13">
-        <v>777517</v>
+        <v>777522</v>
       </c>
       <c r="AU37" s="12">
         <f t="shared" si="17"/>
-        <v>0.95896342944958557</v>
+        <v>0.95896959628213996</v>
       </c>
       <c r="AV37" s="18">
         <v>633338</v>
@@ -7269,14 +7269,14 @@
       </c>
       <c r="AX37" s="10">
         <f t="shared" si="18"/>
-        <v>130842</v>
+        <v>130846</v>
       </c>
       <c r="AY37" s="20">
-        <v>605828</v>
+        <v>605832</v>
       </c>
       <c r="AZ37" s="12">
         <f t="shared" si="19"/>
-        <v>0.95656347795332031</v>
+        <v>0.95656979369625694</v>
       </c>
       <c r="BA37" s="18">
         <v>640933</v>
@@ -7286,14 +7286,14 @@
       </c>
       <c r="BC37" s="10">
         <f t="shared" si="20"/>
-        <v>131368</v>
+        <v>746417</v>
       </c>
       <c r="BD37" s="20">
-        <v>615045</v>
+        <v>1230094</v>
       </c>
       <c r="BE37" s="12">
         <f t="shared" si="21"/>
-        <v>0.95960888267572431</v>
+        <v>1.9192240062533836</v>
       </c>
       <c r="BF37" s="18">
         <v>830528</v>
@@ -7303,14 +7303,14 @@
       </c>
       <c r="BH37" s="10">
         <f t="shared" si="24"/>
-        <v>185608</v>
+        <v>185612</v>
       </c>
       <c r="BI37" s="11">
-        <v>797116</v>
+        <v>797120</v>
       </c>
       <c r="BJ37" s="12">
         <f t="shared" si="25"/>
-        <v>0.95977017030130229</v>
+        <v>0.9597749865146028</v>
       </c>
       <c r="BK37" s="24"/>
       <c r="BL37" s="24"/>
@@ -7500,14 +7500,14 @@
       </c>
       <c r="BC38" s="10">
         <f t="shared" si="20"/>
-        <v>6725</v>
+        <v>27729</v>
       </c>
       <c r="BD38" s="20">
-        <v>21004</v>
+        <v>42008</v>
       </c>
       <c r="BE38" s="12">
         <f t="shared" si="21"/>
-        <v>0.84799547821874122</v>
+        <v>1.6959909564374824</v>
       </c>
       <c r="BF38" s="18">
         <v>37269</v>
@@ -7714,14 +7714,14 @@
       </c>
       <c r="BC39" s="10">
         <f t="shared" si="20"/>
-        <v>46</v>
+        <v>219</v>
       </c>
       <c r="BD39" s="20">
-        <v>173</v>
+        <v>346</v>
       </c>
       <c r="BE39" s="12">
         <f t="shared" si="21"/>
-        <v>1.0058139534883721</v>
+        <v>2.0116279069767442</v>
       </c>
       <c r="BF39" s="18">
         <v>228</v>
@@ -7758,14 +7758,14 @@
       </c>
       <c r="E40" s="10">
         <f t="shared" si="0"/>
-        <v>228458</v>
+        <v>228460</v>
       </c>
       <c r="F40" s="20">
-        <v>243743</v>
+        <v>243745</v>
       </c>
       <c r="G40" s="12">
         <f t="shared" si="1"/>
-        <v>0.95565627536237563</v>
+        <v>0.95566411686982711</v>
       </c>
       <c r="H40" s="15">
         <v>254802</v>
@@ -7775,14 +7775,14 @@
       </c>
       <c r="J40" s="10">
         <f t="shared" si="2"/>
-        <v>221639</v>
+        <v>221640</v>
       </c>
       <c r="K40" s="20">
-        <v>243977</v>
+        <v>243978</v>
       </c>
       <c r="L40" s="12">
         <f t="shared" si="3"/>
-        <v>0.95751603205626334</v>
+        <v>0.95751995667223966</v>
       </c>
       <c r="M40" s="16">
         <v>315837</v>
@@ -7792,14 +7792,14 @@
       </c>
       <c r="O40" s="10">
         <f t="shared" si="4"/>
-        <v>162870</v>
+        <v>162873</v>
       </c>
       <c r="P40" s="13">
-        <v>303395</v>
+        <v>303398</v>
       </c>
       <c r="Q40" s="12">
         <f t="shared" si="5"/>
-        <v>0.96060626209088862</v>
+        <v>0.96061576066135379</v>
       </c>
       <c r="R40" s="16">
         <v>257348</v>
@@ -7809,14 +7809,14 @@
       </c>
       <c r="T40" s="10">
         <f t="shared" si="6"/>
-        <v>76825</v>
+        <v>76828</v>
       </c>
       <c r="U40" s="20">
-        <v>245524</v>
+        <v>245527</v>
       </c>
       <c r="V40" s="12">
         <f t="shared" si="7"/>
-        <v>0.9540544321308112</v>
+        <v>0.95406608949748983</v>
       </c>
       <c r="W40" s="16">
         <v>259512</v>
@@ -7826,14 +7826,14 @@
       </c>
       <c r="Y40" s="10">
         <f t="shared" si="8"/>
-        <v>69283</v>
+        <v>69285</v>
       </c>
       <c r="Z40" s="20">
-        <v>247805</v>
+        <v>247807</v>
       </c>
       <c r="AA40" s="12">
         <f t="shared" si="9"/>
-        <v>0.95488840593113233</v>
+        <v>0.95489611270384411</v>
       </c>
       <c r="AB40" s="17">
         <v>322067</v>
@@ -7843,14 +7843,14 @@
       </c>
       <c r="AD40" s="10">
         <f t="shared" si="10"/>
-        <v>74966</v>
+        <v>74967</v>
       </c>
       <c r="AE40" s="11">
-        <v>309032</v>
+        <v>309033</v>
       </c>
       <c r="AF40" s="12">
         <f t="shared" si="11"/>
-        <v>0.95952705492956436</v>
+        <v>0.95953015987356671</v>
       </c>
       <c r="AG40" s="16">
         <v>262041</v>
@@ -7860,14 +7860,14 @@
       </c>
       <c r="AI40" s="10">
         <f t="shared" si="12"/>
-        <v>51916</v>
+        <v>51917</v>
       </c>
       <c r="AJ40" s="20">
-        <v>250269</v>
+        <v>250270</v>
       </c>
       <c r="AK40" s="12">
         <f t="shared" si="13"/>
-        <v>0.95507573242355204</v>
+        <v>0.95507954862025413</v>
       </c>
       <c r="AL40" s="18">
         <v>264607</v>
@@ -7877,14 +7877,14 @@
       </c>
       <c r="AN40" s="10">
         <f t="shared" si="14"/>
-        <v>57107</v>
+        <v>57108</v>
       </c>
       <c r="AO40" s="11">
-        <v>252876</v>
+        <v>252877</v>
       </c>
       <c r="AP40" s="12">
         <f t="shared" si="15"/>
-        <v>0.95566632779934013</v>
+        <v>0.95567010698885513</v>
       </c>
       <c r="AQ40" s="11">
         <v>328683</v>
@@ -7894,14 +7894,14 @@
       </c>
       <c r="AS40" s="10">
         <f t="shared" si="16"/>
-        <v>67748</v>
+        <v>67752</v>
       </c>
       <c r="AT40" s="13">
-        <v>316040</v>
+        <v>316044</v>
       </c>
       <c r="AU40" s="12">
         <f t="shared" si="17"/>
-        <v>0.96153436593921804</v>
+        <v>0.96154653571982729</v>
       </c>
       <c r="AV40" s="18">
         <v>267796</v>
@@ -7911,14 +7911,14 @@
       </c>
       <c r="AX40" s="10">
         <f t="shared" si="18"/>
-        <v>56488</v>
+        <v>56490</v>
       </c>
       <c r="AY40" s="20">
-        <v>256125</v>
+        <v>256127</v>
       </c>
       <c r="AZ40" s="12">
         <f t="shared" si="19"/>
-        <v>0.95641831842148506</v>
+        <v>0.95642578679293189</v>
       </c>
       <c r="BA40" s="18">
         <v>270158</v>
@@ -7928,14 +7928,14 @@
       </c>
       <c r="BC40" s="10">
         <f t="shared" si="20"/>
-        <v>57698</v>
+        <v>316582</v>
       </c>
       <c r="BD40" s="20">
-        <v>258881</v>
+        <v>517765</v>
       </c>
       <c r="BE40" s="12">
         <f t="shared" si="21"/>
-        <v>0.95825776027361764</v>
+        <v>1.9165266251600914</v>
       </c>
       <c r="BF40" s="18">
         <v>335514</v>
@@ -7945,14 +7945,14 @@
       </c>
       <c r="BH40" s="10">
         <f t="shared" si="24"/>
-        <v>84608</v>
+        <v>84612</v>
       </c>
       <c r="BI40" s="11">
-        <v>321796</v>
+        <v>321800</v>
       </c>
       <c r="BJ40" s="12">
         <f t="shared" si="25"/>
-        <v>0.95911347961634985</v>
+        <v>0.95912540162258508</v>
       </c>
       <c r="BK40" s="24"/>
       <c r="BL40" s="24"/>
@@ -7972,14 +7972,14 @@
       </c>
       <c r="E41" s="10">
         <f t="shared" si="0"/>
-        <v>641263</v>
+        <v>641269</v>
       </c>
       <c r="F41" s="20">
-        <v>777382</v>
+        <v>777388</v>
       </c>
       <c r="G41" s="12">
         <f t="shared" si="1"/>
-        <v>0.96794766437063273</v>
+        <v>0.96795513519705545</v>
       </c>
       <c r="H41" s="15">
         <v>805681</v>
@@ -7989,14 +7989,14 @@
       </c>
       <c r="J41" s="10">
         <f t="shared" si="2"/>
-        <v>648982</v>
+        <v>648989</v>
       </c>
       <c r="K41" s="20">
-        <v>778210</v>
+        <v>778217</v>
       </c>
       <c r="L41" s="12">
         <f t="shared" si="3"/>
-        <v>0.9659033786324861</v>
+        <v>0.96591206693468012</v>
       </c>
       <c r="M41" s="16">
         <v>924274</v>
@@ -8006,14 +8006,14 @@
       </c>
       <c r="O41" s="10">
         <f t="shared" si="4"/>
-        <v>314081</v>
+        <v>314090</v>
       </c>
       <c r="P41" s="13">
-        <v>890843</v>
+        <v>890852</v>
       </c>
       <c r="Q41" s="12">
         <f t="shared" si="5"/>
-        <v>0.96382998980821699</v>
+        <v>0.96383972718046818</v>
       </c>
       <c r="R41" s="16">
         <v>822173</v>
@@ -8023,14 +8023,14 @@
       </c>
       <c r="T41" s="10">
         <f t="shared" si="6"/>
-        <v>171614</v>
+        <v>171622</v>
       </c>
       <c r="U41" s="20">
-        <v>791173</v>
+        <v>791181</v>
       </c>
       <c r="V41" s="12">
         <f t="shared" si="7"/>
-        <v>0.9622950400949678</v>
+        <v>0.96230477040720142</v>
       </c>
       <c r="W41" s="16">
         <v>833879</v>
@@ -8040,14 +8040,14 @@
       </c>
       <c r="Y41" s="10">
         <f t="shared" si="8"/>
-        <v>179585</v>
+        <v>179595</v>
       </c>
       <c r="Z41" s="20">
-        <v>799924</v>
+        <v>799934</v>
       </c>
       <c r="AA41" s="12">
         <f t="shared" si="9"/>
-        <v>0.95928066302185333</v>
+        <v>0.9592926551693951</v>
       </c>
       <c r="AB41" s="17">
         <v>956956</v>
@@ -8057,14 +8057,14 @@
       </c>
       <c r="AD41" s="10">
         <f t="shared" si="10"/>
-        <v>182756</v>
+        <v>182771</v>
       </c>
       <c r="AE41" s="11">
-        <v>915483</v>
+        <v>915498</v>
       </c>
       <c r="AF41" s="12">
         <f t="shared" si="11"/>
-        <v>0.95666153929752251</v>
+        <v>0.95667721399938976</v>
       </c>
       <c r="AG41" s="16">
         <v>851169</v>
@@ -8074,14 +8074,14 @@
       </c>
       <c r="AI41" s="10">
         <f t="shared" si="12"/>
-        <v>150958</v>
+        <v>150969</v>
       </c>
       <c r="AJ41" s="20">
-        <v>811567</v>
+        <v>811578</v>
       </c>
       <c r="AK41" s="12">
         <f t="shared" si="13"/>
-        <v>0.95347339952465371</v>
+        <v>0.95348632292764424</v>
       </c>
       <c r="AL41" s="18">
         <v>859964</v>
@@ -8091,14 +8091,14 @@
       </c>
       <c r="AN41" s="10">
         <f t="shared" si="14"/>
-        <v>152858</v>
+        <v>152871</v>
       </c>
       <c r="AO41" s="11">
-        <v>818574</v>
+        <v>818587</v>
       </c>
       <c r="AP41" s="12">
         <f t="shared" si="15"/>
-        <v>0.95187007828234671</v>
+        <v>0.95188519519421744</v>
       </c>
       <c r="AQ41" s="11">
         <v>982238</v>
@@ -8108,14 +8108,14 @@
       </c>
       <c r="AS41" s="10">
         <f t="shared" si="16"/>
-        <v>184958</v>
+        <v>184975</v>
       </c>
       <c r="AT41" s="13">
-        <v>934383</v>
+        <v>934400</v>
       </c>
       <c r="AU41" s="12">
         <f t="shared" si="17"/>
-        <v>0.95127962876614425</v>
+        <v>0.95129693618043687</v>
       </c>
       <c r="AV41" s="18">
         <v>867973</v>
@@ -8125,14 +8125,14 @@
       </c>
       <c r="AX41" s="10">
         <f t="shared" si="18"/>
-        <v>169817</v>
+        <v>169830</v>
       </c>
       <c r="AY41" s="20">
-        <v>827381</v>
+        <v>827394</v>
       </c>
       <c r="AZ41" s="12">
         <f t="shared" si="19"/>
-        <v>0.95323356832528205</v>
+        <v>0.95324854574969498</v>
       </c>
       <c r="BA41" s="18">
         <v>869274</v>
@@ -8142,14 +8142,14 @@
       </c>
       <c r="BC41" s="10">
         <f t="shared" si="20"/>
-        <v>154216</v>
+        <v>987782</v>
       </c>
       <c r="BD41" s="20">
-        <v>833550</v>
+        <v>1667116</v>
       </c>
       <c r="BE41" s="12">
         <f t="shared" si="21"/>
-        <v>0.95890363682797364</v>
+        <v>1.9178256798201718</v>
       </c>
       <c r="BF41" s="18">
         <v>986817</v>
@@ -8159,14 +8159,14 @@
       </c>
       <c r="BH41" s="10">
         <f t="shared" si="24"/>
-        <v>196724</v>
+        <v>196739</v>
       </c>
       <c r="BI41" s="11">
-        <v>950330</v>
+        <v>950345</v>
       </c>
       <c r="BJ41" s="12">
         <f t="shared" si="25"/>
-        <v>0.96302556603706668</v>
+        <v>0.96304076642376446</v>
       </c>
       <c r="BK41" s="24"/>
       <c r="BL41" s="24"/>
@@ -8356,14 +8356,14 @@
       </c>
       <c r="BC42" s="10">
         <f t="shared" si="20"/>
-        <v>3739</v>
+        <v>20826</v>
       </c>
       <c r="BD42" s="20">
-        <v>17087</v>
+        <v>34174</v>
       </c>
       <c r="BE42" s="12">
         <f t="shared" si="21"/>
-        <v>0.95677249566045131</v>
+        <v>1.9135449913209026</v>
       </c>
       <c r="BF42" s="18">
         <v>20264</v>
@@ -8570,14 +8570,14 @@
       </c>
       <c r="BC43" s="10">
         <f t="shared" si="20"/>
-        <v>1093</v>
+        <v>4219</v>
       </c>
       <c r="BD43" s="20">
-        <v>3126</v>
+        <v>6252</v>
       </c>
       <c r="BE43" s="12">
         <f t="shared" si="21"/>
-        <v>0.95130858186244671</v>
+        <v>1.9026171637248934</v>
       </c>
       <c r="BF43" s="18">
         <v>4091</v>
@@ -8614,14 +8614,14 @@
       </c>
       <c r="E44" s="10">
         <f t="shared" si="0"/>
-        <v>211701</v>
+        <v>211703</v>
       </c>
       <c r="F44" s="20">
-        <v>276068</v>
+        <v>276070</v>
       </c>
       <c r="G44" s="12">
         <f t="shared" si="1"/>
-        <v>0.88041152289622315</v>
+        <v>0.88041790111842122</v>
       </c>
       <c r="H44" s="15">
         <v>315037</v>
@@ -8631,14 +8631,14 @@
       </c>
       <c r="J44" s="10">
         <f t="shared" si="2"/>
-        <v>208640</v>
+        <v>208642</v>
       </c>
       <c r="K44" s="20">
-        <v>276732</v>
+        <v>276734</v>
       </c>
       <c r="L44" s="12">
         <f t="shared" si="3"/>
-        <v>0.87841110726676552</v>
+        <v>0.87841745572742247</v>
       </c>
       <c r="M44" s="16">
         <v>378050</v>
@@ -8648,14 +8648,14 @@
       </c>
       <c r="O44" s="10">
         <f t="shared" si="4"/>
-        <v>137102</v>
+        <v>137104</v>
       </c>
       <c r="P44" s="13">
-        <v>338589</v>
+        <v>338591</v>
       </c>
       <c r="Q44" s="12">
         <f t="shared" si="5"/>
-        <v>0.89561962703346121</v>
+        <v>0.89562491733897631</v>
       </c>
       <c r="R44" s="16">
         <v>322476</v>
@@ -8665,14 +8665,14 @@
       </c>
       <c r="T44" s="10">
         <f t="shared" si="6"/>
-        <v>85421</v>
+        <v>85423</v>
       </c>
       <c r="U44" s="20">
-        <v>282971</v>
+        <v>282973</v>
       </c>
       <c r="V44" s="12">
         <f t="shared" si="7"/>
-        <v>0.87749475929991694</v>
+        <v>0.87750096131184951</v>
       </c>
       <c r="W44" s="16">
         <v>327345</v>
@@ -8682,14 +8682,14 @@
       </c>
       <c r="Y44" s="10">
         <f t="shared" si="8"/>
-        <v>86941</v>
+        <v>86943</v>
       </c>
       <c r="Z44" s="20">
-        <v>286833</v>
+        <v>286835</v>
       </c>
       <c r="AA44" s="12">
         <f t="shared" si="9"/>
-        <v>0.8762406635201393</v>
+        <v>0.87624677328201128</v>
       </c>
       <c r="AB44" s="17">
         <v>393681</v>
@@ -8699,14 +8699,14 @@
       </c>
       <c r="AD44" s="10">
         <f t="shared" si="10"/>
-        <v>94085</v>
+        <v>94088</v>
       </c>
       <c r="AE44" s="11">
-        <v>349809</v>
+        <v>349812</v>
       </c>
       <c r="AF44" s="12">
         <f t="shared" si="11"/>
-        <v>0.88855951900142505</v>
+        <v>0.88856713938442544</v>
       </c>
       <c r="AG44" s="16">
         <v>333199</v>
@@ -8716,14 +8716,14 @@
       </c>
       <c r="AI44" s="10">
         <f t="shared" si="12"/>
-        <v>74158</v>
+        <v>74161</v>
       </c>
       <c r="AJ44" s="20">
-        <v>290347</v>
+        <v>290350</v>
       </c>
       <c r="AK44" s="12">
         <f t="shared" si="13"/>
-        <v>0.87139217104493105</v>
+        <v>0.8714011746733934</v>
       </c>
       <c r="AL44" s="18">
         <v>336893</v>
@@ -8733,14 +8733,14 @@
       </c>
       <c r="AN44" s="10">
         <f t="shared" si="14"/>
-        <v>77994</v>
+        <v>77997</v>
       </c>
       <c r="AO44" s="11">
-        <v>294829</v>
+        <v>294832</v>
       </c>
       <c r="AP44" s="12">
         <f t="shared" si="15"/>
-        <v>0.87514136535932774</v>
+        <v>0.87515027026385228</v>
       </c>
       <c r="AQ44" s="11">
         <v>406157</v>
@@ -8750,14 +8750,14 @@
       </c>
       <c r="AS44" s="10">
         <f t="shared" si="16"/>
-        <v>90444</v>
+        <v>90447</v>
       </c>
       <c r="AT44" s="13">
-        <v>359863</v>
+        <v>359866</v>
       </c>
       <c r="AU44" s="12">
         <f t="shared" si="17"/>
-        <v>0.88601944568233471</v>
+        <v>0.8860268319886152</v>
       </c>
       <c r="AV44" s="18">
         <v>341214</v>
@@ -8767,14 +8767,14 @@
       </c>
       <c r="AX44" s="10">
         <f t="shared" si="18"/>
-        <v>79993</v>
+        <v>79996</v>
       </c>
       <c r="AY44" s="20">
-        <v>298438</v>
+        <v>298441</v>
       </c>
       <c r="AZ44" s="12">
         <f t="shared" si="19"/>
-        <v>0.87463585902102492</v>
+        <v>0.87464465115733825</v>
       </c>
       <c r="BA44" s="18">
         <v>343859</v>
@@ -8784,14 +8784,14 @@
       </c>
       <c r="BC44" s="10">
         <f t="shared" si="20"/>
-        <v>79455</v>
+        <v>381791</v>
       </c>
       <c r="BD44" s="20">
-        <v>302333</v>
+        <v>604669</v>
       </c>
       <c r="BE44" s="12">
         <f t="shared" si="21"/>
-        <v>0.87923538427087844</v>
+        <v>1.7584794930480225</v>
       </c>
       <c r="BF44" s="18">
         <v>410714</v>
@@ -8801,14 +8801,14 @@
       </c>
       <c r="BH44" s="10">
         <f t="shared" si="24"/>
-        <v>103154</v>
+        <v>103157</v>
       </c>
       <c r="BI44" s="11">
-        <v>367432</v>
+        <v>367435</v>
       </c>
       <c r="BJ44" s="12">
         <f t="shared" si="25"/>
-        <v>0.8946176658209849</v>
+        <v>0.89462497017389231</v>
       </c>
       <c r="BK44" s="24"/>
       <c r="BL44" s="24"/>
@@ -8828,14 +8828,14 @@
       </c>
       <c r="E45" s="10">
         <f t="shared" si="0"/>
-        <v>173666</v>
+        <v>173667</v>
       </c>
       <c r="F45" s="20">
-        <v>219406</v>
+        <v>219407</v>
       </c>
       <c r="G45" s="12">
         <f t="shared" si="1"/>
-        <v>0.92274629376511408</v>
+        <v>0.92275049942172227</v>
       </c>
       <c r="H45" s="15">
         <v>238690</v>
@@ -8845,14 +8845,14 @@
       </c>
       <c r="J45" s="10">
         <f t="shared" si="2"/>
-        <v>171221</v>
+        <v>171222</v>
       </c>
       <c r="K45" s="20">
-        <v>220015</v>
+        <v>220016</v>
       </c>
       <c r="L45" s="12">
         <f t="shared" si="3"/>
-        <v>0.92176044241484767</v>
+        <v>0.9217646319493904</v>
       </c>
       <c r="M45" s="16">
         <v>292586</v>
@@ -8862,14 +8862,14 @@
       </c>
       <c r="O45" s="10">
         <f t="shared" si="4"/>
-        <v>100446</v>
+        <v>100447</v>
       </c>
       <c r="P45" s="13">
-        <v>272784</v>
+        <v>272785</v>
       </c>
       <c r="Q45" s="12">
         <f t="shared" si="5"/>
-        <v>0.93232075355621935</v>
+        <v>0.93232417135474699</v>
       </c>
       <c r="R45" s="16">
         <v>242899</v>
@@ -8879,14 +8879,14 @@
       </c>
       <c r="T45" s="10">
         <f t="shared" si="6"/>
-        <v>58710</v>
+        <v>58711</v>
       </c>
       <c r="U45" s="20">
-        <v>223285</v>
+        <v>223286</v>
       </c>
       <c r="V45" s="12">
         <f t="shared" si="7"/>
-        <v>0.91925038802135872</v>
+        <v>0.91925450495885119</v>
       </c>
       <c r="W45" s="16">
         <v>244806</v>
@@ -8896,14 +8896,14 @@
       </c>
       <c r="Y45" s="10">
         <f t="shared" si="8"/>
-        <v>58458</v>
+        <v>58460</v>
       </c>
       <c r="Z45" s="20">
-        <v>225567</v>
+        <v>225569</v>
       </c>
       <c r="AA45" s="12">
         <f t="shared" si="9"/>
-        <v>0.92141123992059015</v>
+        <v>0.92141940965499214</v>
       </c>
       <c r="AB45" s="17">
         <v>299772</v>
@@ -8913,14 +8913,14 @@
       </c>
       <c r="AD45" s="10">
         <f t="shared" si="10"/>
-        <v>63874</v>
+        <v>63876</v>
       </c>
       <c r="AE45" s="11">
-        <v>277629</v>
+        <v>277631</v>
       </c>
       <c r="AF45" s="12">
         <f t="shared" si="11"/>
-        <v>0.92613386173491852</v>
+        <v>0.92614053347210545</v>
       </c>
       <c r="AG45" s="16">
         <v>246243</v>
@@ -8930,14 +8930,14 @@
       </c>
       <c r="AI45" s="10">
         <f t="shared" si="12"/>
-        <v>48115</v>
+        <v>48117</v>
       </c>
       <c r="AJ45" s="20">
-        <v>227309</v>
+        <v>227311</v>
       </c>
       <c r="AK45" s="12">
         <f t="shared" si="13"/>
-        <v>0.92310847414951902</v>
+        <v>0.92311659620781095</v>
       </c>
       <c r="AL45" s="18">
         <v>247584</v>
@@ -8947,14 +8947,14 @@
       </c>
       <c r="AN45" s="10">
         <f t="shared" si="14"/>
-        <v>51421</v>
+        <v>51423</v>
       </c>
       <c r="AO45" s="11">
-        <v>229459</v>
+        <v>229461</v>
       </c>
       <c r="AP45" s="12">
         <f t="shared" si="15"/>
-        <v>0.92679252294170866</v>
+        <v>0.92680060100814265</v>
       </c>
       <c r="AQ45" s="11">
         <v>303759</v>
@@ -8964,14 +8964,14 @@
       </c>
       <c r="AS45" s="10">
         <f t="shared" si="16"/>
-        <v>67568</v>
+        <v>67570</v>
       </c>
       <c r="AT45" s="13">
-        <v>282319</v>
+        <v>282321</v>
       </c>
       <c r="AU45" s="12">
         <f t="shared" si="17"/>
-        <v>0.92941772918662491</v>
+        <v>0.92942431335367837</v>
       </c>
       <c r="AV45" s="18">
         <v>248547</v>
@@ -8981,14 +8981,14 @@
       </c>
       <c r="AX45" s="10">
         <f t="shared" si="18"/>
-        <v>55332</v>
+        <v>55334</v>
       </c>
       <c r="AY45" s="20">
-        <v>230985</v>
+        <v>230987</v>
       </c>
       <c r="AZ45" s="12">
         <f t="shared" si="19"/>
-        <v>0.92934133182054102</v>
+        <v>0.92934937858835553</v>
       </c>
       <c r="BA45" s="18">
         <v>248925</v>
@@ -8998,14 +8998,14 @@
       </c>
       <c r="BC45" s="10">
         <f t="shared" si="20"/>
-        <v>51922</v>
+        <v>285072</v>
       </c>
       <c r="BD45" s="20">
-        <v>233148</v>
+        <v>466298</v>
       </c>
       <c r="BE45" s="12">
         <f t="shared" si="21"/>
-        <v>0.93661946369388371</v>
+        <v>1.8732469619363261</v>
       </c>
       <c r="BF45" s="18">
         <v>305535</v>
@@ -9015,14 +9015,14 @@
       </c>
       <c r="BH45" s="10">
         <f t="shared" si="24"/>
-        <v>79702</v>
+        <v>79704</v>
       </c>
       <c r="BI45" s="11">
-        <v>287203</v>
+        <v>287205</v>
       </c>
       <c r="BJ45" s="12">
         <f t="shared" si="25"/>
-        <v>0.94000032729474525</v>
+        <v>0.94000687318965093</v>
       </c>
       <c r="BK45" s="24"/>
       <c r="BL45" s="24"/>
@@ -9212,14 +9212,14 @@
       </c>
       <c r="BC46" s="10">
         <f t="shared" si="20"/>
-        <v>735</v>
+        <v>2995</v>
       </c>
       <c r="BD46" s="20">
-        <v>2260</v>
+        <v>4520</v>
       </c>
       <c r="BE46" s="12">
         <f t="shared" si="21"/>
-        <v>0.9732988802756245</v>
+        <v>1.946597760551249</v>
       </c>
       <c r="BF46" s="18">
         <v>5417</v>
@@ -9426,14 +9426,14 @@
       </c>
       <c r="BC47" s="10">
         <f t="shared" si="20"/>
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="BD47" s="20">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="BE47" s="12">
         <f t="shared" si="21"/>
-        <v>0.81481481481481477</v>
+        <v>1.6296296296296295</v>
       </c>
       <c r="BF47" s="18">
         <v>89</v>
@@ -9456,10 +9456,10 @@
       <c r="BL47" s="24"/>
     </row>
     <row r="48" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A48" s="36" t="s">
+      <c r="A48" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="B48" s="36"/>
+      <c r="B48" s="26"/>
       <c r="C48" s="6">
         <f>SUM(C10:C47)</f>
         <v>6932700</v>
@@ -9470,15 +9470,15 @@
       </c>
       <c r="E48" s="8">
         <f t="shared" si="0"/>
-        <v>5340405</v>
+        <v>5340441</v>
       </c>
       <c r="F48" s="7">
         <f>SUM(F10:F47)</f>
-        <v>6558205</v>
+        <v>6558241</v>
       </c>
       <c r="G48" s="9">
         <f t="shared" si="1"/>
-        <v>0.94598136368225949</v>
+        <v>0.94598655646429242</v>
       </c>
       <c r="H48" s="6">
         <f>SUM(H10:H47)</f>
@@ -9490,15 +9490,15 @@
       </c>
       <c r="J48" s="8">
         <f t="shared" si="2"/>
-        <v>5126234</v>
+        <v>5126266</v>
       </c>
       <c r="K48" s="7">
         <f>SUM(K10:K47)</f>
-        <v>6572675</v>
+        <v>6572707</v>
       </c>
       <c r="L48" s="9">
         <f t="shared" si="3"/>
-        <v>0.94560822174566217</v>
+        <v>0.94561282557334203</v>
       </c>
       <c r="M48" s="6">
         <f>SUM(M10:M47)</f>
@@ -9510,15 +9510,15 @@
       </c>
       <c r="O48" s="8">
         <f t="shared" si="4"/>
-        <v>3595396</v>
+        <v>3595437</v>
       </c>
       <c r="P48" s="7">
         <f>SUM(P10:P47)</f>
-        <v>10438851</v>
+        <v>10438892</v>
       </c>
       <c r="Q48" s="9">
         <f t="shared" si="5"/>
-        <v>0.96155192772312881</v>
+        <v>0.9615557043484525</v>
       </c>
       <c r="R48" s="6">
         <f>SUM(R10:R47)</f>
@@ -9530,15 +9530,15 @@
       </c>
       <c r="T48" s="8">
         <f t="shared" si="6"/>
-        <v>1738490</v>
+        <v>1738530</v>
       </c>
       <c r="U48" s="7">
         <f>SUM(U10:U47)</f>
-        <v>6647560</v>
+        <v>6647600</v>
       </c>
       <c r="V48" s="9">
         <f t="shared" si="7"/>
-        <v>0.9471765914489142</v>
+        <v>0.94718229084292616</v>
       </c>
       <c r="W48" s="6">
         <f>SUM(W10:W47)</f>
@@ -9550,15 +9550,15 @@
       </c>
       <c r="Y48" s="8">
         <f t="shared" si="8"/>
-        <v>1753857</v>
+        <v>1753897</v>
       </c>
       <c r="Z48" s="7">
         <f>SUM(Z10:Z47)</f>
-        <v>6780447</v>
+        <v>6780487</v>
       </c>
       <c r="AA48" s="9">
         <f t="shared" si="9"/>
-        <v>0.95152683325240739</v>
+        <v>0.95153244660995306</v>
       </c>
       <c r="AB48" s="6">
         <f>SUM(AB10:AB47)</f>
@@ -9570,15 +9570,15 @@
       </c>
       <c r="AD48" s="8">
         <f t="shared" si="10"/>
-        <v>2305162</v>
+        <v>2305207</v>
       </c>
       <c r="AE48" s="7">
         <f>SUM(AE10:AE47)</f>
-        <v>10747430</v>
+        <v>10747475</v>
       </c>
       <c r="AF48" s="9">
         <f t="shared" si="11"/>
-        <v>0.96120730749479166</v>
+        <v>0.96121133211545329</v>
       </c>
       <c r="AG48" s="6">
         <f>SUM(AG10:AG47)</f>
@@ -9590,15 +9590,15 @@
       </c>
       <c r="AI48" s="8">
         <f t="shared" si="12"/>
-        <v>1483486</v>
+        <v>1483530</v>
       </c>
       <c r="AJ48" s="7">
         <f>SUM(AJ10:AJ47)</f>
-        <v>6764565</v>
+        <v>6764609</v>
       </c>
       <c r="AK48" s="9">
         <f t="shared" si="13"/>
-        <v>0.94910891672559516</v>
+        <v>0.94911509018868345</v>
       </c>
       <c r="AL48" s="6">
         <f>SUM(AL10:AL47)</f>
@@ -9610,15 +9610,15 @@
       </c>
       <c r="AN48" s="8">
         <f t="shared" si="14"/>
-        <v>1501346</v>
+        <v>1501389</v>
       </c>
       <c r="AO48" s="7">
         <f>SUM(AO10:AO47)</f>
-        <v>6858710</v>
+        <v>6858753</v>
       </c>
       <c r="AP48" s="9">
         <f t="shared" si="15"/>
-        <v>0.95140552215839336</v>
+        <v>0.95141148690066302</v>
       </c>
       <c r="AQ48" s="6">
         <f>SUM(AQ10:AQ47)</f>
@@ -9630,15 +9630,15 @@
       </c>
       <c r="AS48" s="8">
         <f t="shared" si="16"/>
-        <v>2190498</v>
+        <v>2190552</v>
       </c>
       <c r="AT48" s="7">
         <f>SUM(AT10:AT47)</f>
-        <v>10966984</v>
+        <v>10967038</v>
       </c>
       <c r="AU48" s="9">
         <f t="shared" si="17"/>
-        <v>0.95956613233212362</v>
+        <v>0.95957085711070866</v>
       </c>
       <c r="AV48" s="6">
         <f>SUM(AV10:AV47)</f>
@@ -9650,15 +9650,15 @@
       </c>
       <c r="AX48" s="8">
         <f t="shared" si="18"/>
-        <v>1537186</v>
+        <v>1537234</v>
       </c>
       <c r="AY48" s="7">
         <f>SUM(AY10:AY47)</f>
-        <v>6903522</v>
+        <v>6903570</v>
       </c>
       <c r="AZ48" s="9">
         <f t="shared" si="19"/>
-        <v>0.9531609884952793</v>
+        <v>0.953167615797611</v>
       </c>
       <c r="BA48" s="6">
         <f>SUM(BA10:BA47)</f>
@@ -9670,15 +9670,15 @@
       </c>
       <c r="BC48" s="8">
         <f t="shared" si="20"/>
-        <v>1610308</v>
+        <v>8623892</v>
       </c>
       <c r="BD48" s="7">
         <f>SUM(BD10:BD47)</f>
-        <v>7013532</v>
+        <v>14027116</v>
       </c>
       <c r="BE48" s="9">
         <f t="shared" si="21"/>
-        <v>0.95921517997084138</v>
+        <v>1.9184374717919401</v>
       </c>
       <c r="BF48" s="6">
         <f>SUM(BF10:BF47)</f>
@@ -9690,15 +9690,15 @@
       </c>
       <c r="BH48" s="8">
         <f t="shared" si="24"/>
-        <v>2687918</v>
+        <v>2687980</v>
       </c>
       <c r="BI48" s="7">
         <f>SUM(BI10:BI47)</f>
-        <v>11187787</v>
+        <v>11187849</v>
       </c>
       <c r="BJ48" s="9">
         <f t="shared" si="25"/>
-        <v>0.96187669946893728</v>
+        <v>0.96188202995613437</v>
       </c>
       <c r="BK48" s="24"/>
       <c r="BL48" s="24"/>
@@ -9720,95 +9720,82 @@
     </row>
     <row r="54" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
+      <c r="K54" s="1"/>
+      <c r="L54" s="1"/>
+      <c r="M54" s="1"/>
+      <c r="N54" s="1"/>
+      <c r="O54" s="1"/>
+      <c r="P54" s="1"/>
+      <c r="Q54" s="1"/>
+      <c r="R54" s="1"/>
+      <c r="S54" s="1"/>
+      <c r="T54" s="1"/>
+      <c r="U54" s="1"/>
+      <c r="V54" s="1"/>
+      <c r="W54" s="1"/>
+      <c r="X54" s="1"/>
+      <c r="Y54" s="1"/>
+      <c r="Z54" s="1"/>
+      <c r="AA54" s="1"/>
+      <c r="AB54" s="1"/>
+      <c r="AC54" s="1"/>
+      <c r="AD54" s="1"/>
+      <c r="AE54" s="1"/>
+      <c r="AF54" s="1"/>
+      <c r="AG54" s="1"/>
+      <c r="AH54" s="1"/>
+      <c r="AI54" s="1"/>
+      <c r="AJ54" s="1"/>
+      <c r="AK54" s="1"/>
     </row>
     <row r="55" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A55" s="1"/>
-    </row>
-    <row r="56" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A56" s="1"/>
-      <c r="B56" s="1"/>
-      <c r="C56" s="1"/>
-      <c r="D56" s="1"/>
-      <c r="G56" s="1"/>
-      <c r="H56" s="1"/>
-      <c r="I56" s="1"/>
-      <c r="J56" s="1"/>
-      <c r="K56" s="1"/>
-      <c r="L56" s="1"/>
-      <c r="M56" s="1"/>
-      <c r="N56" s="1"/>
-      <c r="O56" s="1"/>
-      <c r="P56" s="1"/>
-      <c r="Q56" s="1"/>
-      <c r="R56" s="1"/>
-      <c r="S56" s="1"/>
-      <c r="T56" s="1"/>
-      <c r="U56" s="1"/>
-      <c r="V56" s="1"/>
-      <c r="W56" s="1"/>
-      <c r="X56" s="1"/>
-      <c r="Y56" s="1"/>
-      <c r="Z56" s="1"/>
-      <c r="AA56" s="1"/>
-      <c r="AB56" s="1"/>
-      <c r="AC56" s="1"/>
-      <c r="AD56" s="1"/>
-      <c r="AE56" s="1"/>
-      <c r="AF56" s="1"/>
-      <c r="AG56" s="1"/>
-      <c r="AH56" s="1"/>
-      <c r="AI56" s="1"/>
-      <c r="AJ56" s="1"/>
-      <c r="AK56" s="1"/>
-    </row>
-    <row r="57" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A57" s="25" t="s">
+      <c r="A55" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="B57" s="25"/>
-      <c r="C57" s="25"/>
-      <c r="D57" s="25"/>
-      <c r="G57" s="1"/>
-      <c r="H57" s="1"/>
-      <c r="I57" s="1"/>
-      <c r="J57" s="1"/>
-      <c r="K57" s="1"/>
-      <c r="L57" s="1"/>
-      <c r="M57" s="1"/>
-      <c r="N57" s="1"/>
-      <c r="O57" s="1"/>
-      <c r="P57" s="1"/>
-      <c r="Q57" s="1"/>
-      <c r="R57" s="1"/>
-      <c r="S57" s="1"/>
-      <c r="T57" s="1"/>
-      <c r="U57" s="1"/>
-      <c r="V57" s="1"/>
-      <c r="W57" s="1"/>
-      <c r="X57" s="1"/>
-      <c r="Y57" s="1"/>
-      <c r="Z57" s="1"/>
-      <c r="AA57" s="1"/>
-      <c r="AB57" s="1"/>
-      <c r="AC57" s="1"/>
-      <c r="AD57" s="1"/>
-      <c r="AE57" s="1"/>
-      <c r="AF57" s="1"/>
-      <c r="AG57" s="1"/>
-      <c r="AH57" s="1"/>
-      <c r="AI57" s="1"/>
-      <c r="AJ57" s="1"/>
-      <c r="AK57" s="1"/>
+      <c r="B55" s="25"/>
+      <c r="C55" s="25"/>
+      <c r="D55" s="25"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
+      <c r="K55" s="1"/>
+      <c r="L55" s="1"/>
+      <c r="M55" s="1"/>
+      <c r="N55" s="1"/>
+      <c r="O55" s="1"/>
+      <c r="P55" s="1"/>
+      <c r="Q55" s="1"/>
+      <c r="R55" s="1"/>
+      <c r="S55" s="1"/>
+      <c r="T55" s="1"/>
+      <c r="U55" s="1"/>
+      <c r="V55" s="1"/>
+      <c r="W55" s="1"/>
+      <c r="X55" s="1"/>
+      <c r="Y55" s="1"/>
+      <c r="Z55" s="1"/>
+      <c r="AA55" s="1"/>
+      <c r="AB55" s="1"/>
+      <c r="AC55" s="1"/>
+      <c r="AD55" s="1"/>
+      <c r="AE55" s="1"/>
+      <c r="AF55" s="1"/>
+      <c r="AG55" s="1"/>
+      <c r="AH55" s="1"/>
+      <c r="AI55" s="1"/>
+      <c r="AJ55" s="1"/>
+      <c r="AK55" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="BA8:BE8"/>
-    <mergeCell ref="AL8:AP8"/>
-    <mergeCell ref="AQ8:AU8"/>
-    <mergeCell ref="AV8:AZ8"/>
-    <mergeCell ref="AG8:AK8"/>
-    <mergeCell ref="H8:L8"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="BF8:BJ8"/>
     <mergeCell ref="M8:Q8"/>
@@ -9820,6 +9807,13 @@
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="C8:G8"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="BA8:BE8"/>
+    <mergeCell ref="AL8:AP8"/>
+    <mergeCell ref="AQ8:AU8"/>
+    <mergeCell ref="AV8:AZ8"/>
+    <mergeCell ref="AG8:AK8"/>
+    <mergeCell ref="H8:L8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
